--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>6126</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>9.69999980926514</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>9.47999954223633</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>9.47999954223633</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>9.69999980926514</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>8926</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>9.69999980926514</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>9.38000011444092</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>9.69999980926514</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>9.39999961853027</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>2588</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>9.4399995803833</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>9.35999965667725</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>9.38000011444092</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>9.35999965667725</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>3492</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>9.68000030517578</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>9.39999961853027</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>9.42000007629395</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>9.65999984741211</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -62796,19 +62796,19 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>5639</v>
+        <v>10891</v>
       </c>
       <c r="C2715" t="n">
-        <v>9.60000038146973</v>
+        <v>9.64000034332275</v>
       </c>
       <c r="D2715" t="n">
-        <v>9.46000003814697</v>
+        <v>9.31999969482422</v>
       </c>
       <c r="E2715" t="n">
-        <v>9.5</v>
+        <v>9.31999969482422</v>
       </c>
       <c r="F2715" t="n">
         <v>9.60000038146973</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>8690</v>
+        <v>5639</v>
       </c>
       <c r="C2716" t="n">
-        <v>9.68000030517578</v>
+        <v>9.60000038146973</v>
       </c>
       <c r="D2716" t="n">
-        <v>9.30000019073486</v>
+        <v>9.46000003814697</v>
       </c>
       <c r="E2716" t="n">
-        <v>9.61999988555908</v>
+        <v>9.5</v>
       </c>
       <c r="F2716" t="n">
-        <v>9.47999954223633</v>
+        <v>9.60000038146973</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>2255</v>
+        <v>8690</v>
       </c>
       <c r="C2717" t="n">
-        <v>9.5600004196167</v>
+        <v>9.68000030517578</v>
       </c>
       <c r="D2717" t="n">
-        <v>9.39999961853027</v>
+        <v>9.30000019073486</v>
       </c>
       <c r="E2717" t="n">
-        <v>9.39999961853027</v>
+        <v>9.61999988555908</v>
       </c>
       <c r="F2717" t="n">
-        <v>9.4399995803833</v>
+        <v>9.47999954223633</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>3637</v>
+        <v>2255</v>
       </c>
       <c r="C2718" t="n">
-        <v>9.5</v>
+        <v>9.5600004196167</v>
       </c>
       <c r="D2718" t="n">
-        <v>9.38000011444092</v>
+        <v>9.39999961853027</v>
       </c>
       <c r="E2718" t="n">
-        <v>9.38000011444092</v>
+        <v>9.39999961853027</v>
       </c>
       <c r="F2718" t="n">
-        <v>9.42000007629395</v>
+        <v>9.4399995803833</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>6126</v>
+        <v>3637</v>
       </c>
       <c r="C2719" t="n">
-        <v>9.69999980926514</v>
+        <v>9.5</v>
       </c>
       <c r="D2719" t="n">
-        <v>9.47999954223633</v>
+        <v>9.38000011444092</v>
       </c>
       <c r="E2719" t="n">
-        <v>9.47999954223633</v>
+        <v>9.38000011444092</v>
       </c>
       <c r="F2719" t="n">
-        <v>9.69999980926514</v>
+        <v>9.42000007629395</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>8926</v>
+        <v>6126</v>
       </c>
       <c r="C2720" t="n">
         <v>9.69999980926514</v>
       </c>
       <c r="D2720" t="n">
-        <v>9.38000011444092</v>
+        <v>9.47999954223633</v>
       </c>
       <c r="E2720" t="n">
+        <v>9.47999954223633</v>
+      </c>
+      <c r="F2720" t="n">
         <v>9.69999980926514</v>
-      </c>
-      <c r="F2720" t="n">
-        <v>9.39999961853027</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>2588</v>
+        <v>8926</v>
       </c>
       <c r="C2721" t="n">
-        <v>9.4399995803833</v>
+        <v>9.69999980926514</v>
       </c>
       <c r="D2721" t="n">
-        <v>9.35999965667725</v>
+        <v>9.38000011444092</v>
       </c>
       <c r="E2721" t="n">
-        <v>9.38000011444092</v>
+        <v>9.69999980926514</v>
       </c>
       <c r="F2721" t="n">
-        <v>9.35999965667725</v>
+        <v>9.39999961853027</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>3492</v>
+        <v>2588</v>
       </c>
       <c r="C2722" t="n">
+        <v>9.4399995803833</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>9.35999965667725</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>9.38000011444092</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>9.35999965667725</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>5587</v>
+      </c>
+      <c r="C2723" t="n">
         <v>9.68000030517578</v>
       </c>
-      <c r="D2722" t="n">
+      <c r="D2723" t="n">
         <v>9.39999961853027</v>
       </c>
-      <c r="E2722" t="n">
-        <v>9.42000007629395</v>
-      </c>
-      <c r="F2722" t="n">
-        <v>9.65999984741211</v>
-      </c>
-      <c r="G2722" t="s">
+      <c r="E2723" t="n">
+        <v>9.68000030517578</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>9.46000003814697</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>9.38000011444092</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>9.18000030517578</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>1721</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>9.26000022888184</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>9.14000034332275</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>9.26000022888184</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>9.26000022888184</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>9.26000022888184</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>731</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>9.26000022888184</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>9.26000022888184</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -63311,13 +63311,36 @@
         <v>9.26000022888184</v>
       </c>
       <c r="D2737" t="n">
-        <v>9.19999980926514</v>
+        <v>9.14000034332275</v>
       </c>
       <c r="E2737" t="n">
         <v>9.26000022888184</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>9.14000034332275</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>3106</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>9.30000019073486</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>9.14000034332275</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>9.22000026702881</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>9.22000026702881</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>9.19999980926514</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>646</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>9.26000022888184</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>9.14000034332275</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>9.26000022888184</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>2230</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>9.26000022888184</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>9.15999984741211</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>9.22000026702881</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>9.26000022888184</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -421,7 +421,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G2" t="n">
-        <v>4.91287708282471</v>
+        <v>4.91287660598755</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>4.91287708282471</v>
+        <v>4.91287660598755</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>4.91287708282471</v>
+        <v>4.91287660598755</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>6.13500022888184</v>
       </c>
       <c r="G7" t="n">
-        <v>4.90089416503906</v>
+        <v>4.90089464187622</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G8" t="n">
-        <v>4.95281839370728</v>
+        <v>4.95281887054443</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>6.25</v>
       </c>
       <c r="G9" t="n">
-        <v>4.99276113510132</v>
+        <v>4.99276065826416</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>4.92485952377319</v>
+        <v>4.92485904693604</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G12" t="n">
-        <v>5.00474405288696</v>
+        <v>5.0047435760498</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G13" t="n">
-        <v>5.04868030548096</v>
+        <v>5.04868078231812</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G15" t="n">
-        <v>5.11258745193481</v>
+        <v>5.11258697509766</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G18" t="n">
-        <v>5.18448305130005</v>
+        <v>5.18448257446289</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>6.44500017166138</v>
       </c>
       <c r="G19" t="n">
-        <v>5.14853525161743</v>
+        <v>5.14853477478027</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G20" t="n">
-        <v>5.11258745193481</v>
+        <v>5.11258697509766</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G22" t="n">
-        <v>5.15252876281738</v>
+        <v>5.15252923965454</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G23" t="n">
-        <v>5.16850566864014</v>
+        <v>5.16850614547729</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G24" t="n">
-        <v>5.20844888687134</v>
+        <v>5.20844793319702</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G26" t="n">
-        <v>5.14054727554321</v>
+        <v>5.14054679870605</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>6.5</v>
       </c>
       <c r="G27" t="n">
-        <v>5.19247198104858</v>
+        <v>5.19247150421143</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G28" t="n">
-        <v>5.15252876281738</v>
+        <v>5.15252923965454</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>6.5</v>
       </c>
       <c r="G29" t="n">
-        <v>5.19247198104858</v>
+        <v>5.19247150421143</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>5.15252876281738</v>
+        <v>5.15252923965454</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G31" t="n">
-        <v>5.27235507965088</v>
+        <v>5.27235555648804</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>5.27634954452515</v>
+        <v>5.27634906768799</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G33" t="n">
-        <v>5.49603128433228</v>
+        <v>5.49603176116943</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G34" t="n">
-        <v>5.71171808242798</v>
+        <v>5.71171903610229</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G37" t="n">
-        <v>5.63982343673706</v>
+        <v>5.6398229598999</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G38" t="n">
-        <v>5.75166082382202</v>
+        <v>5.75166034698486</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G39" t="n">
-        <v>5.7436728477478</v>
+        <v>5.74367237091064</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G40" t="n">
-        <v>5.67976474761963</v>
+        <v>5.67976522445679</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G41" t="n">
-        <v>5.71171808242798</v>
+        <v>5.71171903610229</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>5.72769546508789</v>
+        <v>5.72769594192505</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G45" t="n">
-        <v>5.72769546508789</v>
+        <v>5.72769594192505</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G46" t="n">
-        <v>5.72370052337646</v>
+        <v>5.72370147705078</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>5.65579986572266</v>
+        <v>5.6557993888855</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G52" t="n">
-        <v>5.82355690002441</v>
+        <v>5.82355642318726</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G53" t="n">
-        <v>5.90344047546387</v>
+        <v>5.90343999862671</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G55" t="n">
-        <v>6.23096561431885</v>
+        <v>6.23096609115601</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>7.66499996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>6.12312173843384</v>
+        <v>6.123122215271</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>7.89499998092651</v>
       </c>
       <c r="G57" t="n">
-        <v>6.30685567855835</v>
+        <v>6.30685615539551</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G58" t="n">
-        <v>6.32682609558105</v>
+        <v>6.32682752609253</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>7.90500020980835</v>
       </c>
       <c r="G59" t="n">
-        <v>6.31484365463257</v>
+        <v>6.31484413146973</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G62" t="n">
-        <v>6.34679794311523</v>
+        <v>6.34679746627808</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>7.93499994277954</v>
       </c>
       <c r="G63" t="n">
-        <v>6.33880949020386</v>
+        <v>6.3388090133667</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G65" t="n">
-        <v>6.3667688369751</v>
+        <v>6.36676836013794</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G67" t="n">
-        <v>6.55050182342529</v>
+        <v>6.55050230026245</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G68" t="n">
-        <v>6.70228242874146</v>
+        <v>6.70228290557861</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G69" t="n">
-        <v>6.75021314620972</v>
+        <v>6.7502121925354</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G70" t="n">
-        <v>6.76619005203247</v>
+        <v>6.76618909835815</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G72" t="n">
-        <v>6.86205148696899</v>
+        <v>6.86205053329468</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G73" t="n">
-        <v>7.02980756759644</v>
+        <v>7.02980804443359</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9</v>
       </c>
       <c r="G74" t="n">
-        <v>7.18957614898682</v>
+        <v>7.1895751953125</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G75" t="n">
-        <v>7.69284677505493</v>
+        <v>7.69284629821777</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G76" t="n">
-        <v>8.34789657592773</v>
+        <v>8.34789752960205</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.79500007629395</v>
       </c>
       <c r="G77" t="n">
-        <v>7.82465553283691</v>
+        <v>7.82465505599976</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>9.24499988555908</v>
       </c>
       <c r="G78" t="n">
-        <v>7.38529300689697</v>
+        <v>7.3852915763855</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G79" t="n">
-        <v>7.10969114303589</v>
+        <v>7.10969066619873</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G80" t="n">
-        <v>7.14963293075562</v>
+        <v>7.14963340759277</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>8.875</v>
       </c>
       <c r="G81" t="n">
-        <v>7.08972072601318</v>
+        <v>7.08971977233887</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G82" t="n">
-        <v>7.02980756759644</v>
+        <v>7.02980804443359</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G83" t="n">
-        <v>6.8940052986145</v>
+        <v>6.89400482177734</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G84" t="n">
-        <v>6.94592905044556</v>
+        <v>6.94592809677124</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>8.78499984741211</v>
       </c>
       <c r="G85" t="n">
-        <v>7.15776968002319</v>
+        <v>7.15777015686035</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G86" t="n">
-        <v>6.95000219345093</v>
+        <v>6.95000267028809</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G87" t="n">
-        <v>6.9377818107605</v>
+        <v>6.93778085708618</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>8.14500045776367</v>
       </c>
       <c r="G88" t="n">
-        <v>6.63631629943848</v>
+        <v>6.63631677627563</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G89" t="n">
-        <v>6.47743463516235</v>
+        <v>6.47743511199951</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>8.25</v>
       </c>
       <c r="G91" t="n">
-        <v>6.72186708450317</v>
+        <v>6.72186613082886</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>8.00500011444092</v>
       </c>
       <c r="G93" t="n">
-        <v>6.52224826812744</v>
+        <v>6.52224779129028</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>8.24499988555908</v>
       </c>
       <c r="G94" t="n">
-        <v>6.71779298782349</v>
+        <v>6.71779346466064</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G95" t="n">
-        <v>6.73001480102539</v>
+        <v>6.73001432418823</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G96" t="n">
-        <v>7.2107310295105</v>
+        <v>7.21072959899902</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G97" t="n">
-        <v>7.09666204452515</v>
+        <v>7.0966625213623</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G98" t="n">
-        <v>7.00703716278076</v>
+        <v>7.00703763961792</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G100" t="n">
-        <v>7.02333211898804</v>
+        <v>7.02333164215088</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G102" t="n">
-        <v>7.00703716278076</v>
+        <v>7.00703763961792</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G103" t="n">
-        <v>7.02333211898804</v>
+        <v>7.02333164215088</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G104" t="n">
-        <v>7.03148031234741</v>
+        <v>7.03148078918457</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G105" t="n">
-        <v>7.00703716278076</v>
+        <v>7.00703763961792</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G106" t="n">
-        <v>7.08851385116577</v>
+        <v>7.08851480484009</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G107" t="n">
-        <v>6.92963409423828</v>
+        <v>6.92963361740112</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G109" t="n">
-        <v>6.96629858016968</v>
+        <v>6.96629810333252</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>6.89296913146973</v>
+        <v>6.89296865463257</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G112" t="n">
-        <v>6.89296913146973</v>
+        <v>6.89296865463257</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G114" t="n">
-        <v>6.61594676971436</v>
+        <v>6.6159462928772</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G115" t="n">
-        <v>6.43669652938843</v>
+        <v>6.43669605255127</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>6.20856046676636</v>
+        <v>6.20856094360352</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G117" t="n">
-        <v>6.42040157318115</v>
+        <v>6.42040205001831</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>8.24499988555908</v>
       </c>
       <c r="G119" t="n">
-        <v>6.71779298782349</v>
+        <v>6.71779346466064</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>6.88482141494751</v>
+        <v>6.88482093811035</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G121" t="n">
-        <v>6.81963968276978</v>
+        <v>6.81963920593262</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G122" t="n">
-        <v>6.70557069778442</v>
+        <v>6.70557117462158</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G124" t="n">
-        <v>6.47336196899414</v>
+        <v>6.47336149215698</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>8</v>
       </c>
       <c r="G125" t="n">
-        <v>6.5181736946106</v>
+        <v>6.51817417144775</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G126" t="n">
-        <v>6.59150314331055</v>
+        <v>6.59150362014771</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G137" t="n">
-        <v>6.84000968933105</v>
+        <v>6.84000873565674</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G139" t="n">
-        <v>6.82778644561768</v>
+        <v>6.82778787612915</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>8.375</v>
       </c>
       <c r="G141" t="n">
-        <v>6.8237133026123</v>
+        <v>6.82371282577515</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G142" t="n">
-        <v>6.79519701004028</v>
+        <v>6.79519605636597</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>8.32499980926514</v>
       </c>
       <c r="G143" t="n">
-        <v>6.78297424316406</v>
+        <v>6.78297519683838</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G144" t="n">
-        <v>6.79519701004028</v>
+        <v>6.79519605636597</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>8.3149995803833</v>
       </c>
       <c r="G146" t="n">
-        <v>6.77482652664185</v>
+        <v>6.77482604980469</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>8.30500030517578</v>
       </c>
       <c r="G147" t="n">
-        <v>6.76667976379395</v>
+        <v>6.76667928695679</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G150" t="n">
-        <v>6.82778644561768</v>
+        <v>6.82778787612915</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>8.3149995803833</v>
       </c>
       <c r="G152" t="n">
-        <v>6.77482652664185</v>
+        <v>6.77482604980469</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>8.375</v>
       </c>
       <c r="G155" t="n">
-        <v>6.8237133026123</v>
+        <v>6.82371282577515</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G156" t="n">
-        <v>6.84000968933105</v>
+        <v>6.84000873565674</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G157" t="n">
-        <v>6.79519701004028</v>
+        <v>6.79519605636597</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G159" t="n">
-        <v>6.77075386047363</v>
+        <v>6.77075338363647</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G160" t="n">
-        <v>6.77075386047363</v>
+        <v>6.77075338363647</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G161" t="n">
-        <v>6.85223007202148</v>
+        <v>6.85223054885864</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G162" t="n">
-        <v>6.85223007202148</v>
+        <v>6.85223054885864</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>6.81963968276978</v>
+        <v>6.81963920593262</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G165" t="n">
-        <v>6.85223007202148</v>
+        <v>6.85223054885864</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G168" t="n">
-        <v>6.83593463897705</v>
+        <v>6.83593559265137</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G169" t="n">
-        <v>6.79519701004028</v>
+        <v>6.79519605636597</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G170" t="n">
-        <v>7.11295747756958</v>
+        <v>7.11295652389526</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>8.54500007629395</v>
       </c>
       <c r="G172" t="n">
-        <v>6.96222448348999</v>
+        <v>6.96222496032715</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G174" t="n">
-        <v>6.94185543060303</v>
+        <v>6.94185590744019</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G175" t="n">
-        <v>6.97444725036621</v>
+        <v>6.97444534301758</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>8.75</v>
       </c>
       <c r="G176" t="n">
-        <v>7.12925291061401</v>
+        <v>7.12925243377686</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G177" t="n">
-        <v>7.15369606018066</v>
+        <v>7.15369558334351</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G178" t="n">
-        <v>7.2188777923584</v>
+        <v>7.21887731552124</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G179" t="n">
-        <v>7.14554786682129</v>
+        <v>7.14554834365845</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G180" t="n">
-        <v>7.10480928421021</v>
+        <v>7.10481023788452</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>8.60499954223633</v>
       </c>
       <c r="G181" t="n">
-        <v>7.01111078262329</v>
+        <v>7.01111030578613</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>8.79500007629395</v>
       </c>
       <c r="G182" t="n">
-        <v>7.16591787338257</v>
+        <v>7.16591691970825</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G183" t="n">
-        <v>7.1211051940918</v>
+        <v>7.12110471725464</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G184" t="n">
-        <v>7.19443416595459</v>
+        <v>7.19443464279175</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G185" t="n">
-        <v>7.35738849639893</v>
+        <v>7.35738897323608</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>9.25</v>
       </c>
       <c r="G186" t="n">
-        <v>7.5366382598877</v>
+        <v>7.53663921356201</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>9.04500007629395</v>
       </c>
       <c r="G187" t="n">
-        <v>7.36961078643799</v>
+        <v>7.36961030960083</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G188" t="n">
-        <v>7.49182605743408</v>
+        <v>7.49182558059692</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G189" t="n">
-        <v>7.30035495758057</v>
+        <v>7.30035448074341</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G190" t="n">
-        <v>7.16999197006226</v>
+        <v>7.1699914932251</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G191" t="n">
-        <v>7.25146865844727</v>
+        <v>7.25146818161011</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9</v>
       </c>
       <c r="G192" t="n">
-        <v>7.33294534683228</v>
+        <v>7.33294582366943</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>7.36553621292114</v>
+        <v>7.36553716659546</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9</v>
       </c>
       <c r="G195" t="n">
-        <v>7.33294534683228</v>
+        <v>7.33294582366943</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9</v>
       </c>
       <c r="G196" t="n">
-        <v>7.33294534683228</v>
+        <v>7.33294582366943</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.09500026702881</v>
       </c>
       <c r="G197" t="n">
-        <v>7.41035032272339</v>
+        <v>7.41034936904907</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G198" t="n">
-        <v>7.45516109466553</v>
+        <v>7.45516061782837</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>9.29500007629395</v>
       </c>
       <c r="G199" t="n">
-        <v>7.57330465316772</v>
+        <v>7.57330322265625</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G200" t="n">
-        <v>7.63441038131714</v>
+        <v>7.63441133499146</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G201" t="n">
-        <v>7.62626361846924</v>
+        <v>7.62626314163208</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>9.24499988555908</v>
       </c>
       <c r="G202" t="n">
-        <v>7.53256511688232</v>
+        <v>7.53256416320801</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G203" t="n">
-        <v>7.63441038131714</v>
+        <v>7.63441133499146</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G204" t="n">
-        <v>7.59367179870605</v>
+        <v>7.59367275238037</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G205" t="n">
-        <v>7.61811637878418</v>
+        <v>7.61811685562134</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>9.39500045776367</v>
       </c>
       <c r="G206" t="n">
-        <v>7.65478086471558</v>
+        <v>7.65478181838989</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G207" t="n">
-        <v>7.65070581436157</v>
+        <v>7.65070676803589</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>9.39500045776367</v>
       </c>
       <c r="G209" t="n">
-        <v>7.65478086471558</v>
+        <v>7.65478181838989</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G210" t="n">
-        <v>7.4144229888916</v>
+        <v>7.41442203521729</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G211" t="n">
-        <v>7.4144229888916</v>
+        <v>7.41442203521729</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G212" t="n">
-        <v>7.35738849639893</v>
+        <v>7.35738897323608</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>8.99499988555908</v>
       </c>
       <c r="G213" t="n">
-        <v>7.32887172698975</v>
+        <v>7.32887125015259</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G214" t="n">
-        <v>7.19443416595459</v>
+        <v>7.19443464279175</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>8.67500019073486</v>
       </c>
       <c r="G216" t="n">
-        <v>7.06814575195312</v>
+        <v>7.06814527511597</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G217" t="n">
-        <v>7.09666204452515</v>
+        <v>7.0966625213623</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G220" t="n">
-        <v>6.84000968933105</v>
+        <v>6.84000873565674</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G221" t="n">
-        <v>6.83593463897705</v>
+        <v>6.83593559265137</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G224" t="n">
-        <v>7.17813968658447</v>
+        <v>7.17813920974731</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G226" t="n">
-        <v>7.44701337814331</v>
+        <v>7.44701385498047</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G228" t="n">
-        <v>7.10480928421021</v>
+        <v>7.10481023788452</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>8.63500022888184</v>
       </c>
       <c r="G229" t="n">
-        <v>7.03555393218994</v>
+        <v>7.03555345535278</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>8.74499988555908</v>
       </c>
       <c r="G230" t="n">
-        <v>7.12517881393433</v>
+        <v>7.12517929077148</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G231" t="n">
-        <v>7.10480928421021</v>
+        <v>7.10481023788452</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G232" t="n">
-        <v>7.07221937179565</v>
+        <v>7.07221841812134</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G234" t="n">
-        <v>6.99888896942139</v>
+        <v>6.9988899230957</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>8.52499961853027</v>
       </c>
       <c r="G235" t="n">
-        <v>6.94592905044556</v>
+        <v>6.94592809677124</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G236" t="n">
-        <v>7.00703716278076</v>
+        <v>7.00703763961792</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>8.67500019073486</v>
       </c>
       <c r="G237" t="n">
-        <v>7.06814575195312</v>
+        <v>7.06814527511597</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G238" t="n">
-        <v>7.07221937179565</v>
+        <v>7.07221841812134</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>7.09666204452515</v>
+        <v>7.0966625213623</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>9.24499988555908</v>
       </c>
       <c r="G241" t="n">
-        <v>7.53256511688232</v>
+        <v>7.53256416320801</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G242" t="n">
-        <v>7.65885496139526</v>
+        <v>7.65885400772095</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G243" t="n">
-        <v>7.71181535720825</v>
+        <v>7.71181440353394</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G244" t="n">
-        <v>7.724036693573</v>
+        <v>7.72403621673584</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G246" t="n">
-        <v>7.90328550338745</v>
+        <v>7.90328598022461</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>9.98499965667725</v>
       </c>
       <c r="G249" t="n">
-        <v>8.13549423217773</v>
+        <v>8.13549518585205</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>9.76500034332275</v>
       </c>
       <c r="G251" t="n">
-        <v>7.95624589920044</v>
+        <v>7.95624542236328</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G252" t="n">
-        <v>7.90328550338745</v>
+        <v>7.90328598022461</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>9.72500038146973</v>
       </c>
       <c r="G253" t="n">
-        <v>7.92365550994873</v>
+        <v>7.92365598678589</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>9.8149995803833</v>
       </c>
       <c r="G254" t="n">
-        <v>7.99698400497437</v>
+        <v>7.99698543548584</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>9.83500003814697</v>
       </c>
       <c r="G255" t="n">
-        <v>8.01327991485596</v>
+        <v>8.01328086853027</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G256" t="n">
-        <v>8.06623935699463</v>
+        <v>8.06624031066895</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G257" t="n">
-        <v>8.06623935699463</v>
+        <v>8.06624031066895</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G258" t="n">
-        <v>8.38400173187256</v>
+        <v>8.38400077819824</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G261" t="n">
-        <v>8.67731857299805</v>
+        <v>8.67731761932373</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G262" t="n">
-        <v>8.66102409362793</v>
+        <v>8.66102504730225</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G264" t="n">
-        <v>8.68546581268311</v>
+        <v>8.68546772003174</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G265" t="n">
-        <v>8.84842014312744</v>
+        <v>8.84842109680176</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G266" t="n">
-        <v>8.83212566375732</v>
+        <v>8.83212471008301</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G269" t="n">
-        <v>9.61430644989014</v>
+        <v>9.61430740356445</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G271" t="n">
-        <v>9.35357856750488</v>
+        <v>9.35358047485352</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G272" t="n">
-        <v>9.75281810760498</v>
+        <v>9.75281715393066</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G273" t="n">
-        <v>9.53282833099365</v>
+        <v>9.53282928466797</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>10.1031694412231</v>
+        <v>10.1031684875488</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>12.75</v>
       </c>
       <c r="G275" t="n">
-        <v>10.3883409500122</v>
+        <v>10.3883399963379</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G277" t="n">
-        <v>10.5512933731079</v>
+        <v>10.5512924194336</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G278" t="n">
-        <v>10.6409187316895</v>
+        <v>10.6409196853638</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>15</v>
       </c>
       <c r="G285" t="n">
-        <v>12.2215757369995</v>
+        <v>12.2215766906738</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>15.7700004577637</v>
       </c>
       <c r="G287" t="n">
-        <v>12.8489513397217</v>
+        <v>12.8489503860474</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G288" t="n">
-        <v>13.7289047241211</v>
+        <v>13.7289028167725</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G289" t="n">
-        <v>15.4154825210571</v>
+        <v>15.4154815673828</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G291" t="n">
-        <v>12.0423250198364</v>
+        <v>12.0423259735107</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G294" t="n">
-        <v>13.5659484863281</v>
+        <v>13.5659503936768</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G295" t="n">
-        <v>13.9733362197876</v>
+        <v>13.973334312439</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G300" t="n">
-        <v>12.9141311645508</v>
+        <v>12.9141330718994</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G301" t="n">
-        <v>12.9711666107178</v>
+        <v>12.9711647033691</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G302" t="n">
-        <v>12.9304285049438</v>
+        <v>12.9304265975952</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>16</v>
       </c>
       <c r="G303" t="n">
-        <v>13.0363473892212</v>
+        <v>13.0363483428955</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G304" t="n">
-        <v>13.0037565231323</v>
+        <v>13.0037574768066</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G308" t="n">
-        <v>13.2481889724731</v>
+        <v>13.2481880187988</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G311" t="n">
-        <v>13.769642829895</v>
+        <v>13.7696418762207</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>17.25</v>
       </c>
       <c r="G313" t="n">
-        <v>14.0548133850098</v>
+        <v>14.0548124313354</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G315" t="n">
-        <v>14.0140743255615</v>
+        <v>14.0140752792358</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G316" t="n">
-        <v>13.9651870727539</v>
+        <v>13.9651880264282</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G319" t="n">
-        <v>13.875563621521</v>
+        <v>13.8755617141724</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G325" t="n">
-        <v>13.4600296020508</v>
+        <v>13.4600286483765</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G327" t="n">
-        <v>13.2237453460693</v>
+        <v>13.223744392395</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>16</v>
       </c>
       <c r="G329" t="n">
-        <v>13.0363473892212</v>
+        <v>13.0363483428955</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G331" t="n">
-        <v>12.6371097564697</v>
+        <v>12.6371088027954</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>12.303053855896</v>
+        <v>12.3030529022217</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G334" t="n">
-        <v>12.2623157501221</v>
+        <v>12.2623138427734</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>15</v>
       </c>
       <c r="G335" t="n">
-        <v>12.2215757369995</v>
+        <v>12.2215766906738</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>15.3900003433228</v>
       </c>
       <c r="G336" t="n">
-        <v>12.5393381118774</v>
+        <v>12.5393371582031</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G339" t="n">
-        <v>13.0444965362549</v>
+        <v>13.0444955825806</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G340" t="n">
-        <v>12.9385747909546</v>
+        <v>12.9385766983032</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G341" t="n">
-        <v>13.0355958938599</v>
+        <v>13.0355949401855</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G342" t="n">
-        <v>12.7121934890747</v>
+        <v>12.7121925354004</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G343" t="n">
-        <v>12.5463457107544</v>
+        <v>12.5463466644287</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G345" t="n">
-        <v>12.4551296234131</v>
+        <v>12.4551305770874</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G348" t="n">
-        <v>12.5297613143921</v>
+        <v>12.5297603607178</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G354" t="n">
-        <v>12.728777885437</v>
+        <v>12.7287788391113</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G355" t="n">
-        <v>12.728777885437</v>
+        <v>12.7287788391113</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>12.728777885437</v>
+        <v>12.7287788391113</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G363" t="n">
-        <v>12.8282852172852</v>
+        <v>12.8282871246338</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G368" t="n">
-        <v>12.5712232589722</v>
+        <v>12.5712242126465</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G369" t="n">
-        <v>12.4468383789062</v>
+        <v>12.4468374252319</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G374" t="n">
-        <v>11.5844326019287</v>
+        <v>11.5844316482544</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G375" t="n">
-        <v>11.451753616333</v>
+        <v>11.4517545700073</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G378" t="n">
-        <v>11.8912487030029</v>
+        <v>11.8912496566772</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>11.8580799102783</v>
+        <v>11.858078956604</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G384" t="n">
-        <v>11.5346784591675</v>
+        <v>11.5346775054932</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G385" t="n">
-        <v>11.451753616333</v>
+        <v>11.4517545700073</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G386" t="n">
-        <v>11.3937063217163</v>
+        <v>11.3937082290649</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G387" t="n">
-        <v>11.3439540863037</v>
+        <v>11.3439531326294</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G388" t="n">
-        <v>11.2776155471802</v>
+        <v>11.2776145935059</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G389" t="n">
-        <v>11.3688297271729</v>
+        <v>11.3688306808472</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>11.3190765380859</v>
+        <v>11.3190755844116</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>11.2941989898682</v>
+        <v>11.2941999435425</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>13.5</v>
       </c>
       <c r="G397" t="n">
-        <v>11.1946907043457</v>
+        <v>11.1946897506714</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G398" t="n">
-        <v>11.5678472518921</v>
+        <v>11.5678482055664</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>14</v>
       </c>
       <c r="G399" t="n">
-        <v>11.6093091964722</v>
+        <v>11.6093082427979</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G400" t="n">
-        <v>11.6258935928345</v>
+        <v>11.6258945465088</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G402" t="n">
-        <v>11.6839399337769</v>
+        <v>11.6839389801025</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G403" t="n">
-        <v>11.6258935928345</v>
+        <v>11.6258945465088</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>11.5678472518921</v>
+        <v>11.5678482055664</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G405" t="n">
-        <v>11.6839399337769</v>
+        <v>11.6839389801025</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G406" t="n">
-        <v>11.5927248001099</v>
+        <v>11.5927238464355</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G414" t="n">
-        <v>12.0322198867798</v>
+        <v>12.0322189331055</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G416" t="n">
-        <v>12.2809915542603</v>
+        <v>12.2809906005859</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G417" t="n">
-        <v>12.2395296096802</v>
+        <v>12.2395286560059</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G418" t="n">
-        <v>11.9575891494751</v>
+        <v>11.9575881958008</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G421" t="n">
-        <v>11.8995409011841</v>
+        <v>11.8995418548584</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G422" t="n">
-        <v>11.8995409011841</v>
+        <v>11.8995418548584</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G424" t="n">
-        <v>12.15660572052</v>
+        <v>12.1566047668457</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G437" t="n">
-        <v>12.15660572052</v>
+        <v>12.1566047668457</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G442" t="n">
-        <v>12.15660572052</v>
+        <v>12.1566047668457</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G443" t="n">
-        <v>12.2726974487305</v>
+        <v>12.2726984024048</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G444" t="n">
-        <v>12.1151437759399</v>
+        <v>12.1151418685913</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>14.75</v>
       </c>
       <c r="G445" t="n">
-        <v>12.2312364578247</v>
+        <v>12.2312355041504</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G447" t="n">
-        <v>12.2726974487305</v>
+        <v>12.2726984024048</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>14.7700004577637</v>
       </c>
       <c r="G451" t="n">
-        <v>12.247820854187</v>
+        <v>12.2478218078613</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G452" t="n">
-        <v>12.3141593933105</v>
+        <v>12.3141603469849</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G456" t="n">
-        <v>12.5048847198486</v>
+        <v>12.5048837661743</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G457" t="n">
-        <v>12.5297613143921</v>
+        <v>12.5297603607178</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G459" t="n">
-        <v>12.5463457107544</v>
+        <v>12.5463466644287</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G463" t="n">
-        <v>12.4717149734497</v>
+        <v>12.4717140197754</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G465" t="n">
-        <v>12.5048847198486</v>
+        <v>12.5048837661743</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>15.25</v>
       </c>
       <c r="G475" t="n">
-        <v>12.6458549499512</v>
+        <v>12.6458539962769</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G478" t="n">
-        <v>12.4468383789062</v>
+        <v>12.4468374252319</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G480" t="n">
-        <v>12.7039003372192</v>
+        <v>12.7039012908936</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G483" t="n">
-        <v>12.9858417510986</v>
+        <v>12.9858407974243</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G484" t="n">
-        <v>13.1433954238892</v>
+        <v>13.1433973312378</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>15.9899997711182</v>
       </c>
       <c r="G485" t="n">
-        <v>13.2594900131226</v>
+        <v>13.2594890594482</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>16</v>
       </c>
       <c r="G486" t="n">
-        <v>13.2677812576294</v>
+        <v>13.2677822113037</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>16</v>
       </c>
       <c r="G487" t="n">
-        <v>13.2677812576294</v>
+        <v>13.2677822113037</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G490" t="n">
-        <v>13.9477548599243</v>
+        <v>13.9477558135986</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>13.9726324081421</v>
+        <v>13.9726333618164</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>16.5</v>
       </c>
       <c r="G492" t="n">
-        <v>13.6823987960815</v>
+        <v>13.6824007034302</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G493" t="n">
-        <v>13.1848573684692</v>
+        <v>13.1848583221436</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G494" t="n">
-        <v>13.3755807876587</v>
+        <v>13.375581741333</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>16.0900001525879</v>
       </c>
       <c r="G495" t="n">
-        <v>13.3424139022827</v>
+        <v>13.3424129486084</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G496" t="n">
-        <v>13.3755807876587</v>
+        <v>13.375581741333</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>15.9300003051758</v>
       </c>
       <c r="G497" t="n">
-        <v>13.2097358703613</v>
+        <v>13.2097339630127</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>15.9300003051758</v>
       </c>
       <c r="G498" t="n">
-        <v>13.2097358703613</v>
+        <v>13.2097339630127</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G499" t="n">
-        <v>13.6243534088135</v>
+        <v>13.6243524551392</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>15.9899997711182</v>
       </c>
       <c r="G503" t="n">
-        <v>13.2594900131226</v>
+        <v>13.2594890594482</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G509" t="n">
-        <v>13.0438871383667</v>
+        <v>13.0438861846924</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G510" t="n">
-        <v>13.1516885757446</v>
+        <v>13.1516876220703</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G511" t="n">
-        <v>13.300952911377</v>
+        <v>13.3009510040283</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>16</v>
       </c>
       <c r="G512" t="n">
-        <v>13.2677812576294</v>
+        <v>13.2677822113037</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>16</v>
       </c>
       <c r="G513" t="n">
-        <v>13.2677812576294</v>
+        <v>13.2677822113037</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>13.3507051467896</v>
+        <v>13.3507061004639</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G518" t="n">
-        <v>13.2843675613403</v>
+        <v>13.284366607666</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G519" t="n">
-        <v>13.2180280685425</v>
+        <v>13.2180261611938</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G520" t="n">
-        <v>13.2014436721802</v>
+        <v>13.2014427185059</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G522" t="n">
-        <v>13.2843675613403</v>
+        <v>13.284366607666</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G523" t="n">
-        <v>13.300952911377</v>
+        <v>13.3009510040283</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G526" t="n">
-        <v>13.300952911377</v>
+        <v>13.3009510040283</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G528" t="n">
-        <v>13.300952911377</v>
+        <v>13.3009510040283</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G529" t="n">
-        <v>13.2180280685425</v>
+        <v>13.2180261611938</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G530" t="n">
-        <v>13.3507051467896</v>
+        <v>13.3507061004639</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G531" t="n">
-        <v>13.1848573684692</v>
+        <v>13.1848583221436</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G532" t="n">
-        <v>12.9526720046997</v>
+        <v>12.9526710510254</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G533" t="n">
-        <v>13.1019344329834</v>
+        <v>13.1019353866577</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>15.5</v>
       </c>
       <c r="G534" t="n">
-        <v>12.8531627655029</v>
+        <v>12.8531637191772</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G538" t="n">
-        <v>12.9526720046997</v>
+        <v>12.9526710510254</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G540" t="n">
-        <v>12.9858417510986</v>
+        <v>12.9858407974243</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>15.5</v>
       </c>
       <c r="G541" t="n">
-        <v>12.8531627655029</v>
+        <v>12.8531637191772</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G542" t="n">
-        <v>12.819993019104</v>
+        <v>12.8199949264526</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G547" t="n">
-        <v>13.11851978302</v>
+        <v>13.1185188293457</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G548" t="n">
-        <v>13.0355958938599</v>
+        <v>13.0355949401855</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G549" t="n">
-        <v>12.8697471618652</v>
+        <v>12.8697481155396</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G551" t="n">
-        <v>12.9526720046997</v>
+        <v>12.9526710510254</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G552" t="n">
-        <v>12.819993019104</v>
+        <v>12.8199949264526</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G553" t="n">
-        <v>12.7868242263794</v>
+        <v>12.7868251800537</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G560" t="n">
-        <v>12.8697471618652</v>
+        <v>12.8697481155396</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G562" t="n">
-        <v>13.1516885757446</v>
+        <v>13.1516876220703</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G563" t="n">
-        <v>12.9526720046997</v>
+        <v>12.9526710510254</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G564" t="n">
-        <v>13.1019344329834</v>
+        <v>13.1019353866577</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G565" t="n">
-        <v>12.8365783691406</v>
+        <v>12.8365793228149</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G566" t="n">
-        <v>13.0687656402588</v>
+        <v>13.0687646865845</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G567" t="n">
-        <v>12.9526720046997</v>
+        <v>12.9526710510254</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G568" t="n">
-        <v>12.9858417510986</v>
+        <v>12.9858407974243</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G570" t="n">
-        <v>13.0355958938599</v>
+        <v>13.0355949401855</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G571" t="n">
-        <v>12.9858417510986</v>
+        <v>12.9858407974243</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G573" t="n">
-        <v>12.8697471618652</v>
+        <v>12.8697481155396</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G575" t="n">
-        <v>13.0355958938599</v>
+        <v>13.0355949401855</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>15.5</v>
       </c>
       <c r="G577" t="n">
-        <v>12.8531627655029</v>
+        <v>12.8531637191772</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G578" t="n">
-        <v>13.1019344329834</v>
+        <v>13.1019353866577</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G583" t="n">
-        <v>13.0355958938599</v>
+        <v>13.0355949401855</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G586" t="n">
-        <v>13.2014436721802</v>
+        <v>13.2014427185059</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G587" t="n">
-        <v>13.0687656402588</v>
+        <v>13.0687646865845</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G588" t="n">
-        <v>13.1019344329834</v>
+        <v>13.1019353866577</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G589" t="n">
-        <v>13.1019344329834</v>
+        <v>13.1019353866577</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G590" t="n">
-        <v>13.2014436721802</v>
+        <v>13.2014427185059</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G591" t="n">
-        <v>13.1516885757446</v>
+        <v>13.1516876220703</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>16</v>
       </c>
       <c r="G592" t="n">
-        <v>13.2677812576294</v>
+        <v>13.2677822113037</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G593" t="n">
-        <v>13.2843675613403</v>
+        <v>13.284366607666</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G596" t="n">
-        <v>13.2843675613403</v>
+        <v>13.284366607666</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>13.3507051467896</v>
+        <v>13.3507061004639</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G598" t="n">
-        <v>13.4968938827515</v>
+        <v>13.4968929290771</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G600" t="n">
-        <v>13.4288988113403</v>
+        <v>13.4288997650146</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G602" t="n">
-        <v>13.2589139938354</v>
+        <v>13.2589130401611</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G604" t="n">
-        <v>13.4118995666504</v>
+        <v>13.4119005203247</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G606" t="n">
-        <v>13.4288988113403</v>
+        <v>13.4288997650146</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G607" t="n">
-        <v>13.1059255599976</v>
+        <v>13.1059246063232</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G610" t="n">
-        <v>12.5959663391113</v>
+        <v>12.5959672927856</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G614" t="n">
-        <v>12.5789680480957</v>
+        <v>12.5789699554443</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G620" t="n">
-        <v>13.4798946380615</v>
+        <v>13.4798936843872</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G621" t="n">
-        <v>13.4118995666504</v>
+        <v>13.4119005203247</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G624" t="n">
-        <v>13.4288988113403</v>
+        <v>13.4288997650146</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G626" t="n">
-        <v>13.5478897094727</v>
+        <v>13.5478887557983</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G627" t="n">
-        <v>13.4118995666504</v>
+        <v>13.4119005203247</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G632" t="n">
-        <v>13.3269071578979</v>
+        <v>13.3269090652466</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G634" t="n">
-        <v>13.292911529541</v>
+        <v>13.2929105758667</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G635" t="n">
-        <v>13.0889263153076</v>
+        <v>13.0889253616333</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G636" t="n">
-        <v>12.8849439620972</v>
+        <v>12.8849430084229</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G638" t="n">
-        <v>13.2079172134399</v>
+        <v>13.2079181671143</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G639" t="n">
-        <v>13.1399221420288</v>
+        <v>13.1399230957031</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G640" t="n">
-        <v>12.9699373245239</v>
+        <v>12.9699363708496</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>15.5</v>
       </c>
       <c r="G641" t="n">
-        <v>13.1739196777344</v>
+        <v>13.1739206314087</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G642" t="n">
-        <v>13.0719289779663</v>
+        <v>13.071928024292</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G643" t="n">
-        <v>13.1229238510132</v>
+        <v>13.1229228973389</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>15.5</v>
       </c>
       <c r="G644" t="n">
-        <v>13.1739196777344</v>
+        <v>13.1739206314087</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G646" t="n">
-        <v>12.9869356155396</v>
+        <v>12.9869346618652</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G647" t="n">
-        <v>13.0719289779663</v>
+        <v>13.071928024292</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G648" t="n">
-        <v>13.1569213867188</v>
+        <v>13.1569223403931</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G655" t="n">
-        <v>12.9699373245239</v>
+        <v>12.9699363708496</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G657" t="n">
-        <v>13.1059255599976</v>
+        <v>13.1059246063232</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G658" t="n">
-        <v>12.9869356155396</v>
+        <v>12.9869346618652</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G659" t="n">
-        <v>12.9699373245239</v>
+        <v>12.9699363708496</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G660" t="n">
-        <v>13.0889263153076</v>
+        <v>13.0889253616333</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G661" t="n">
-        <v>12.8509454727173</v>
+        <v>12.8509464263916</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G664" t="n">
-        <v>12.7319564819336</v>
+        <v>12.7319555282593</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G667" t="n">
-        <v>12.7319564819336</v>
+        <v>12.7319555282593</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G669" t="n">
-        <v>12.7659530639648</v>
+        <v>12.7659549713135</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G674" t="n">
-        <v>12.5959663391113</v>
+        <v>12.5959672927856</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G676" t="n">
-        <v>12.5959663391113</v>
+        <v>12.5959672927856</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G677" t="n">
-        <v>12.9869356155396</v>
+        <v>12.9869346618652</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G679" t="n">
-        <v>12.8169498443604</v>
+        <v>12.816948890686</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G680" t="n">
-        <v>12.5109739303589</v>
+        <v>12.5109748840332</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G681" t="n">
-        <v>12.5789680480957</v>
+        <v>12.5789699554443</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G689" t="n">
-        <v>12.6639614105225</v>
+        <v>12.6639623641968</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G690" t="n">
-        <v>12.714958190918</v>
+        <v>12.7149572372437</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G691" t="n">
-        <v>12.4429807662964</v>
+        <v>12.4429798126221</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G694" t="n">
-        <v>12.6469631195068</v>
+        <v>12.6469640731812</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G697" t="n">
-        <v>12.4429807662964</v>
+        <v>12.4429798126221</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G698" t="n">
-        <v>12.5789680480957</v>
+        <v>12.5789699554443</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G699" t="n">
-        <v>12.5789680480957</v>
+        <v>12.5789699554443</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G706" t="n">
-        <v>11.7800340652466</v>
+        <v>11.7800331115723</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G709" t="n">
-        <v>10.9131050109863</v>
+        <v>10.9131059646606</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G711" t="n">
-        <v>11.0320959091187</v>
+        <v>11.0320949554443</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G712" t="n">
-        <v>10.7601175308228</v>
+        <v>10.7601184844971</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G713" t="n">
-        <v>10.9980983734131</v>
+        <v>10.9980974197388</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G715" t="n">
-        <v>10.5901308059692</v>
+        <v>10.5901317596436</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G716" t="n">
-        <v>10.7941160202026</v>
+        <v>10.7941150665283</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G717" t="n">
-        <v>10.930103302002</v>
+        <v>10.9301042556763</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G718" t="n">
-        <v>10.675124168396</v>
+        <v>10.6751251220703</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G719" t="n">
-        <v>10.4711418151855</v>
+        <v>10.4711408615112</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G720" t="n">
-        <v>10.5221376419067</v>
+        <v>10.5221366882324</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G721" t="n">
-        <v>10.6581258773804</v>
+        <v>10.6581268310547</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G722" t="n">
-        <v>10.5221376419067</v>
+        <v>10.5221366882324</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G723" t="n">
-        <v>10.7601175308228</v>
+        <v>10.7601184844971</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G728" t="n">
-        <v>10.930103302002</v>
+        <v>10.9301042556763</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G732" t="n">
-        <v>11.3210716247559</v>
+        <v>11.3210725784302</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G742" t="n">
-        <v>9.9951810836792</v>
+        <v>9.99518203735352</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>12</v>
       </c>
       <c r="G744" t="n">
-        <v>10.199164390564</v>
+        <v>10.1991634368896</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>12</v>
       </c>
       <c r="G745" t="n">
-        <v>10.199164390564</v>
+        <v>10.1991634368896</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G749" t="n">
-        <v>10.8791084289551</v>
+        <v>10.8791074752808</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G751" t="n">
-        <v>10.7601175308228</v>
+        <v>10.7601184844971</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G753" t="n">
-        <v>10.4711418151855</v>
+        <v>10.4711408615112</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>12</v>
       </c>
       <c r="G756" t="n">
-        <v>10.199164390564</v>
+        <v>10.1991634368896</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>11.5</v>
       </c>
       <c r="G757" t="n">
-        <v>9.77419757843018</v>
+        <v>9.77419853210449</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G758" t="n">
-        <v>9.06025791168213</v>
+        <v>9.06025695800781</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G762" t="n">
-        <v>9.17924785614014</v>
+        <v>9.17924690246582</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G764" t="n">
-        <v>10.318154335022</v>
+        <v>10.3181533813477</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G766" t="n">
-        <v>10.9131050109863</v>
+        <v>10.9131059646606</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G767" t="n">
-        <v>10.7771158218384</v>
+        <v>10.7771167755127</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G768" t="n">
-        <v>10.6581258773804</v>
+        <v>10.6581268310547</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G770" t="n">
-        <v>10.9131050109863</v>
+        <v>10.9131059646606</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G772" t="n">
-        <v>10.3521509170532</v>
+        <v>10.3521518707275</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G777" t="n">
-        <v>9.89319038391113</v>
+        <v>9.89318943023682</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>9.85919094085693</v>
+        <v>9.85919189453125</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G779" t="n">
-        <v>10.0971717834473</v>
+        <v>10.0971727371216</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G781" t="n">
-        <v>10.182165145874</v>
+        <v>10.1821660995483</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G785" t="n">
-        <v>10.3351526260376</v>
+        <v>10.3351516723633</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G786" t="n">
-        <v>10.42014503479</v>
+        <v>10.4201459884644</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G787" t="n">
-        <v>10.318154335022</v>
+        <v>10.3181533813477</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G789" t="n">
-        <v>10.2161636352539</v>
+        <v>10.2161626815796</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G793" t="n">
-        <v>9.9951810836792</v>
+        <v>9.99518203735352</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G795" t="n">
-        <v>10.182165145874</v>
+        <v>10.1821660995483</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G800" t="n">
-        <v>9.89319038391113</v>
+        <v>9.89318943023682</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G802" t="n">
-        <v>9.89319038391113</v>
+        <v>9.89318943023682</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G804" t="n">
-        <v>9.9951810836792</v>
+        <v>9.99518203735352</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G806" t="n">
-        <v>10.0291776657104</v>
+        <v>10.0291786193848</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G807" t="n">
-        <v>10.0291776657104</v>
+        <v>10.0291786193848</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G808" t="n">
-        <v>10.0121784210205</v>
+        <v>10.0121793746948</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G811" t="n">
-        <v>10.0461759567261</v>
+        <v>10.0461769104004</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G813" t="n">
-        <v>10.0291776657104</v>
+        <v>10.0291786193848</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G814" t="n">
-        <v>9.9951810836792</v>
+        <v>9.99518203735352</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G815" t="n">
-        <v>10.0971717834473</v>
+        <v>10.0971727371216</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G817" t="n">
-        <v>10.7941160202026</v>
+        <v>10.7941150665283</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G819" t="n">
-        <v>10.675124168396</v>
+        <v>10.6751251220703</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G820" t="n">
-        <v>10.7771158218384</v>
+        <v>10.7771167755127</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G821" t="n">
-        <v>10.5901308059692</v>
+        <v>10.5901317596436</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G822" t="n">
-        <v>10.4881401062012</v>
+        <v>10.4881391525269</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G823" t="n">
-        <v>10.42014503479</v>
+        <v>10.4201459884644</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G825" t="n">
-        <v>10.5901308059692</v>
+        <v>10.5901317596436</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G826" t="n">
-        <v>10.5051383972168</v>
+        <v>10.5051374435425</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G827" t="n">
-        <v>10.6581258773804</v>
+        <v>10.6581268310547</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G832" t="n">
-        <v>10.675124168396</v>
+        <v>10.6751251220703</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G833" t="n">
-        <v>10.675124168396</v>
+        <v>10.6751251220703</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G835" t="n">
-        <v>10.5731325149536</v>
+        <v>10.5731334686279</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G841" t="n">
-        <v>10.6581258773804</v>
+        <v>10.6581268310547</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G842" t="n">
-        <v>10.6581258773804</v>
+        <v>10.6581268310547</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G843" t="n">
-        <v>10.5731325149536</v>
+        <v>10.5731334686279</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G845" t="n">
-        <v>10.9131050109863</v>
+        <v>10.9131059646606</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G847" t="n">
-        <v>10.8791084289551</v>
+        <v>10.8791074752808</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G848" t="n">
-        <v>11.3450660705566</v>
+        <v>11.345067024231</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G853" t="n">
-        <v>10.5523204803467</v>
+        <v>10.552321434021</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G857" t="n">
-        <v>9.91812515258789</v>
+        <v>9.91812419891357</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G858" t="n">
-        <v>9.91812515258789</v>
+        <v>9.91812419891357</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G861" t="n">
-        <v>9.47771072387695</v>
+        <v>9.47770977020264</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G868" t="n">
-        <v>9.56579303741455</v>
+        <v>9.56579399108887</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G869" t="n">
-        <v>9.49532699584961</v>
+        <v>9.49532604217529</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G870" t="n">
-        <v>9.44247722625732</v>
+        <v>9.44247817993164</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G877" t="n">
-        <v>9.77719306945801</v>
+        <v>9.77719211578369</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G879" t="n">
-        <v>9.83004093170166</v>
+        <v>9.83004188537598</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G883" t="n">
-        <v>9.86527442932129</v>
+        <v>9.86527538299561</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G889" t="n">
-        <v>9.83004093170166</v>
+        <v>9.83004188537598</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G890" t="n">
-        <v>9.79480934143066</v>
+        <v>9.79480838775635</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G895" t="n">
-        <v>9.88289165496826</v>
+        <v>9.88289070129395</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G896" t="n">
-        <v>10.0238246917725</v>
+        <v>10.0238237380981</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G897" t="n">
-        <v>10.0590562820435</v>
+        <v>10.0590572357178</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G900" t="n">
-        <v>10.2528390884399</v>
+        <v>10.2528400421143</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G903" t="n">
-        <v>10.2528390884399</v>
+        <v>10.2528400421143</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G908" t="n">
-        <v>10.2880725860596</v>
+        <v>10.2880716323853</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G912" t="n">
-        <v>10.2880725860596</v>
+        <v>10.2880716323853</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G922" t="n">
-        <v>10.2528390884399</v>
+        <v>10.2528400421143</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G923" t="n">
-        <v>10.2880725860596</v>
+        <v>10.2880716323853</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G924" t="n">
-        <v>10.2880725860596</v>
+        <v>10.2880716323853</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G928" t="n">
-        <v>10.2528390884399</v>
+        <v>10.2528400421143</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G929" t="n">
-        <v>10.2880725860596</v>
+        <v>10.2880716323853</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G934" t="n">
-        <v>10.5523204803467</v>
+        <v>10.552321434021</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>12</v>
       </c>
       <c r="G935" t="n">
-        <v>10.5699377059937</v>
+        <v>10.5699367523193</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G940" t="n">
-        <v>10.8694190979004</v>
+        <v>10.8694181442261</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G941" t="n">
-        <v>10.7989521026611</v>
+        <v>10.7989530563354</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G943" t="n">
-        <v>10.887035369873</v>
+        <v>10.8870344161987</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G945" t="n">
-        <v>10.7813367843628</v>
+        <v>10.7813358306885</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G946" t="n">
-        <v>10.8694190979004</v>
+        <v>10.8694181442261</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G957" t="n">
-        <v>10.3585386276245</v>
+        <v>10.3585395812988</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G959" t="n">
-        <v>10.3585386276245</v>
+        <v>10.3585395812988</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G960" t="n">
-        <v>10.3585386276245</v>
+        <v>10.3585395812988</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G962" t="n">
-        <v>10.3585386276245</v>
+        <v>10.3585395812988</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G963" t="n">
-        <v>10.3585386276245</v>
+        <v>10.3585395812988</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G964" t="n">
-        <v>10.3585386276245</v>
+        <v>10.3585395812988</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G966" t="n">
-        <v>10.2880725860596</v>
+        <v>10.2880716323853</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G968" t="n">
-        <v>10.2880725860596</v>
+        <v>10.2880716323853</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G972" t="n">
-        <v>10.2528390884399</v>
+        <v>10.2528400421143</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G975" t="n">
-        <v>10.2528390884399</v>
+        <v>10.2528400421143</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>12</v>
       </c>
       <c r="G983" t="n">
-        <v>10.5699377059937</v>
+        <v>10.5699367523193</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>12</v>
       </c>
       <c r="G992" t="n">
-        <v>10.5699377059937</v>
+        <v>10.5699367523193</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>12</v>
       </c>
       <c r="G998" t="n">
-        <v>10.5699377059937</v>
+        <v>10.5699367523193</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>12</v>
       </c>
       <c r="G999" t="n">
-        <v>10.5699377059937</v>
+        <v>10.5699367523193</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>12</v>
       </c>
       <c r="G1001" t="n">
-        <v>10.5699377059937</v>
+        <v>10.5699367523193</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>12</v>
       </c>
       <c r="G1002" t="n">
-        <v>10.5699377059937</v>
+        <v>10.5699367523193</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>12</v>
       </c>
       <c r="G1004" t="n">
-        <v>10.5699377059937</v>
+        <v>10.5699367523193</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>12</v>
       </c>
       <c r="G1005" t="n">
-        <v>10.5699377059937</v>
+        <v>10.5699367523193</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>12</v>
       </c>
       <c r="G1006" t="n">
-        <v>10.5699377059937</v>
+        <v>10.5699367523193</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>12</v>
       </c>
       <c r="G1008" t="n">
-        <v>10.5699377059937</v>
+        <v>10.5699367523193</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1010" t="n">
-        <v>10.5523204803467</v>
+        <v>10.552321434021</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>12</v>
       </c>
       <c r="G1011" t="n">
-        <v>10.5699377059937</v>
+        <v>10.5699367523193</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G1014" t="n">
-        <v>10.6756372451782</v>
+        <v>10.6756362915039</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G1015" t="n">
-        <v>10.6756372451782</v>
+        <v>10.6756362915039</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1029" t="n">
-        <v>10.5523204803467</v>
+        <v>10.552321434021</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1036" t="n">
-        <v>10.2880725860596</v>
+        <v>10.2880716323853</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1045" t="n">
-        <v>10.2880725860596</v>
+        <v>10.2880716323853</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G1051" t="n">
-        <v>10.0238246917725</v>
+        <v>10.0238237380981</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G1052" t="n">
-        <v>9.91812515258789</v>
+        <v>9.91812419891357</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G1054" t="n">
-        <v>9.44247722625732</v>
+        <v>9.44247817993164</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>9</v>
       </c>
       <c r="G1058" t="n">
-        <v>7.9274525642395</v>
+        <v>7.92745304107666</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>9</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.9274525642395</v>
+        <v>7.92745304107666</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1062" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1063" t="n">
-        <v>6.43885374069214</v>
+        <v>6.43885326385498</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1065" t="n">
-        <v>6.44766235351562</v>
+        <v>6.44766187667847</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>7.25</v>
       </c>
       <c r="G1067" t="n">
-        <v>6.38600397109985</v>
+        <v>6.3860034942627</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G1068" t="n">
-        <v>6.1569881439209</v>
+        <v>6.15698862075806</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1069" t="n">
-        <v>6.13056421279907</v>
+        <v>6.13056373596191</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G1070" t="n">
-        <v>6.1569881439209</v>
+        <v>6.15698862075806</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>8</v>
       </c>
       <c r="G1074" t="n">
-        <v>7.04662466049194</v>
+        <v>7.0466251373291</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1079" t="n">
-        <v>6.83522605895996</v>
+        <v>6.83522653579712</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1086" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1087" t="n">
-        <v>7.36372232437134</v>
+        <v>7.3637228012085</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1088" t="n">
-        <v>7.13470840454102</v>
+        <v>7.13470792770386</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1090" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1092" t="n">
-        <v>7.18755722045898</v>
+        <v>7.18755674362183</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1098" t="n">
-        <v>7.08185815811157</v>
+        <v>7.08185768127441</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>8</v>
       </c>
       <c r="G1100" t="n">
-        <v>7.04662466049194</v>
+        <v>7.0466251373291</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1110" t="n">
-        <v>7.08185815811157</v>
+        <v>7.08185768127441</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1111" t="n">
-        <v>7.13470840454102</v>
+        <v>7.13470792770386</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1112" t="n">
-        <v>6.92330932617188</v>
+        <v>6.92330884933472</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>8</v>
       </c>
       <c r="G1115" t="n">
-        <v>7.04662466049194</v>
+        <v>7.0466251373291</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1117" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1121" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>9.5</v>
       </c>
       <c r="G1123" t="n">
-        <v>8.36786651611328</v>
+        <v>8.3678674697876</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G1127" t="n">
-        <v>8.29740142822266</v>
+        <v>8.29740047454834</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1128" t="n">
-        <v>7.69843769073486</v>
+        <v>7.69843721389771</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1130" t="n">
-        <v>7.87460327148438</v>
+        <v>7.87460279464722</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1131" t="n">
-        <v>8.01553726196289</v>
+        <v>8.01553630828857</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1132" t="n">
-        <v>8.01553726196289</v>
+        <v>8.01553630828857</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1134" t="n">
-        <v>7.87460327148438</v>
+        <v>7.87460279464722</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>9</v>
       </c>
       <c r="G1136" t="n">
-        <v>7.9274525642395</v>
+        <v>7.92745304107666</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1138" t="n">
-        <v>7.7689037322998</v>
+        <v>7.76890325546265</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>9</v>
       </c>
       <c r="G1139" t="n">
-        <v>7.9274525642395</v>
+        <v>7.92745304107666</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1143" t="n">
-        <v>7.57512187957764</v>
+        <v>7.57512140274048</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1152" t="n">
-        <v>7.36372232437134</v>
+        <v>7.3637228012085</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1153" t="n">
-        <v>7.57512187957764</v>
+        <v>7.57512140274048</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1154" t="n">
-        <v>7.52227163314819</v>
+        <v>7.52227210998535</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1155" t="n">
-        <v>7.69843769073486</v>
+        <v>7.69843721389771</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1160" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1161" t="n">
-        <v>7.39895582199097</v>
+        <v>7.39895534515381</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1162" t="n">
-        <v>7.32848978042603</v>
+        <v>7.32848930358887</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1163" t="n">
-        <v>7.39895582199097</v>
+        <v>7.39895534515381</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1165" t="n">
-        <v>7.32848978042603</v>
+        <v>7.32848930358887</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1166" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1167" t="n">
-        <v>7.32848978042603</v>
+        <v>7.32848930358887</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1171" t="n">
-        <v>7.36372232437134</v>
+        <v>7.3637228012085</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1172" t="n">
-        <v>7.39895582199097</v>
+        <v>7.39895534515381</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1173" t="n">
-        <v>7.32848978042603</v>
+        <v>7.32848930358887</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1174" t="n">
-        <v>7.32848978042603</v>
+        <v>7.32848930358887</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1176" t="n">
-        <v>7.18755722045898</v>
+        <v>7.18755674362183</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1179" t="n">
-        <v>6.83522605895996</v>
+        <v>6.83522653579712</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1180" t="n">
-        <v>6.83522605895996</v>
+        <v>6.83522653579712</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1181" t="n">
-        <v>6.83522605895996</v>
+        <v>6.83522653579712</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1182" t="n">
-        <v>6.92330932617188</v>
+        <v>6.92330884933472</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1185" t="n">
-        <v>6.90569257736206</v>
+        <v>6.90569305419922</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1191" t="n">
-        <v>6.41242837905884</v>
+        <v>6.412428855896</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1193" t="n">
-        <v>6.39481258392334</v>
+        <v>6.39481210708618</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1194" t="n">
-        <v>6.35957860946655</v>
+        <v>6.35957908630371</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1195" t="n">
-        <v>6.21864604949951</v>
+        <v>6.21864652633667</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1196" t="n">
-        <v>6.21864604949951</v>
+        <v>6.21864652633667</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1197" t="n">
-        <v>6.07771444320679</v>
+        <v>6.07771396636963</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>6.5</v>
       </c>
       <c r="G1204" t="n">
-        <v>5.72538232803345</v>
+        <v>5.72538280487061</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G1216" t="n">
-        <v>5.83108186721802</v>
+        <v>5.83108139038086</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>6.5</v>
       </c>
       <c r="G1218" t="n">
-        <v>5.72538232803345</v>
+        <v>5.72538280487061</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>6.5</v>
       </c>
       <c r="G1219" t="n">
-        <v>5.72538232803345</v>
+        <v>5.72538280487061</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1223" t="n">
-        <v>5.44351768493652</v>
+        <v>5.44351720809937</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1229" t="n">
-        <v>4.91502046585083</v>
+        <v>4.91502094268799</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1232" t="n">
-        <v>5.40828418731689</v>
+        <v>5.40828466415405</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1233" t="n">
-        <v>5.47875070571899</v>
+        <v>5.47875118255615</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1235" t="n">
-        <v>6.07771444320679</v>
+        <v>6.07771396636963</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1240" t="n">
-        <v>6.35957860946655</v>
+        <v>6.35957908630371</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1246" t="n">
-        <v>7.69843769073486</v>
+        <v>7.69843721389771</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1252" t="n">
-        <v>7.32848978042603</v>
+        <v>7.32848930358887</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1253" t="n">
-        <v>7.36372232437134</v>
+        <v>7.3637228012085</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G1255" t="n">
-        <v>7.64558839797974</v>
+        <v>7.64558887481689</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1256" t="n">
-        <v>7.68082141876221</v>
+        <v>7.68082189559937</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1258" t="n">
-        <v>7.57512187957764</v>
+        <v>7.57512140274048</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1259" t="n">
-        <v>7.7689037322998</v>
+        <v>7.76890325546265</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1261" t="n">
-        <v>7.68082141876221</v>
+        <v>7.68082189559937</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1262" t="n">
-        <v>7.68082141876221</v>
+        <v>7.68082189559937</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1265" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1266" t="n">
-        <v>7.39895582199097</v>
+        <v>7.39895534515381</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1271" t="n">
-        <v>7.36372232437134</v>
+        <v>7.3637228012085</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1282" t="n">
-        <v>7.13470840454102</v>
+        <v>7.13470792770386</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1283" t="n">
-        <v>7.13470840454102</v>
+        <v>7.13470792770386</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1287" t="n">
-        <v>6.83522605895996</v>
+        <v>6.83522653579712</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1297" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1299" t="n">
-        <v>7.13470840454102</v>
+        <v>7.13470792770386</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1302" t="n">
-        <v>7.13470840454102</v>
+        <v>7.13470792770386</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1303" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>8</v>
       </c>
       <c r="G1305" t="n">
-        <v>7.04662466049194</v>
+        <v>7.0466251373291</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>8</v>
       </c>
       <c r="G1306" t="n">
-        <v>7.04662466049194</v>
+        <v>7.0466251373291</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>8</v>
       </c>
       <c r="G1307" t="n">
-        <v>7.04662466049194</v>
+        <v>7.0466251373291</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1309" t="n">
-        <v>7.32848978042603</v>
+        <v>7.32848930358887</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1310" t="n">
-        <v>7.15232372283936</v>
+        <v>7.15232419967651</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1312" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1313" t="n">
-        <v>7.32848978042603</v>
+        <v>7.32848930358887</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1316" t="n">
-        <v>7.36372232437134</v>
+        <v>7.3637228012085</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1317" t="n">
-        <v>7.32848978042603</v>
+        <v>7.32848930358887</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1319" t="n">
-        <v>7.32848978042603</v>
+        <v>7.32848930358887</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1322" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G1328" t="n">
-        <v>8.06838512420654</v>
+        <v>8.06838607788086</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G1330" t="n">
-        <v>8.06838512420654</v>
+        <v>8.06838607788086</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>9.5</v>
       </c>
       <c r="G1332" t="n">
-        <v>8.36786651611328</v>
+        <v>8.3678674697876</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1338" t="n">
-        <v>8.77304744720459</v>
+        <v>8.77304840087891</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G1339" t="n">
-        <v>8.40310096740723</v>
+        <v>8.40310001373291</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1340" t="n">
-        <v>8.54403305053711</v>
+        <v>8.54403209686279</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1343" t="n">
-        <v>8.52641677856445</v>
+        <v>8.52641582489014</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1352" t="n">
-        <v>8.52641677856445</v>
+        <v>8.52641582489014</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1358" t="n">
-        <v>8.77304744720459</v>
+        <v>8.77304840087891</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1359" t="n">
-        <v>8.79066467285156</v>
+        <v>8.79066371917725</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1362" t="n">
-        <v>8.77304744720459</v>
+        <v>8.77304840087891</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1364" t="n">
-        <v>8.77304744720459</v>
+        <v>8.77304840087891</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1373" t="n">
-        <v>8.79066467285156</v>
+        <v>8.79066371917725</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1380" t="n">
-        <v>9.2046537399292</v>
+        <v>9.20465278625488</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G1386" t="n">
-        <v>9.99739837646484</v>
+        <v>9.99739933013916</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1387" t="n">
-        <v>9.77719306945801</v>
+        <v>9.77719211578369</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1395" t="n">
-        <v>9.2046537399292</v>
+        <v>9.20465278625488</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1421" t="n">
-        <v>8.77304744720459</v>
+        <v>8.77304840087891</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1423" t="n">
-        <v>8.79066467285156</v>
+        <v>8.79066371917725</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1438" t="n">
-        <v>8.79066467285156</v>
+        <v>8.79066371917725</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1440" t="n">
-        <v>8.79066467285156</v>
+        <v>8.79066371917725</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1441" t="n">
-        <v>8.77304744720459</v>
+        <v>8.77304840087891</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1460" t="n">
-        <v>8.77304744720459</v>
+        <v>8.77304840087891</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1461" t="n">
-        <v>8.77304744720459</v>
+        <v>8.77304840087891</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1473" t="n">
-        <v>8.77304744720459</v>
+        <v>8.77304840087891</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1478" t="n">
-        <v>8.79066467285156</v>
+        <v>8.79066371917725</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1483" t="n">
-        <v>8.52641677856445</v>
+        <v>8.52641582489014</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1485" t="n">
-        <v>8.56164836883545</v>
+        <v>8.56164932250977</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1486" t="n">
-        <v>8.56164836883545</v>
+        <v>8.56164932250977</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1489" t="n">
-        <v>8.56164836883545</v>
+        <v>8.56164932250977</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1491" t="n">
-        <v>8.56164836883545</v>
+        <v>8.56164932250977</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1492" t="n">
-        <v>8.54403305053711</v>
+        <v>8.54403209686279</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1493" t="n">
-        <v>8.4559497833252</v>
+        <v>8.45595073699951</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1494" t="n">
-        <v>8.52641677856445</v>
+        <v>8.52641582489014</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1495" t="n">
-        <v>8.52641677856445</v>
+        <v>8.52641582489014</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G1496" t="n">
-        <v>8.40310096740723</v>
+        <v>8.40310001373291</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G1501" t="n">
-        <v>7.98030281066895</v>
+        <v>7.98030233383179</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1502" t="n">
-        <v>8.12123584747314</v>
+        <v>8.12123489379883</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1509" t="n">
-        <v>7.7689037322998</v>
+        <v>7.76890325546265</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G1510" t="n">
-        <v>7.96268558502197</v>
+        <v>7.96268606185913</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1512" t="n">
-        <v>8.01553726196289</v>
+        <v>8.01553630828857</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G1513" t="n">
-        <v>8.06838512420654</v>
+        <v>8.06838607788086</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G1514" t="n">
-        <v>7.96268558502197</v>
+        <v>7.96268606185913</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1515" t="n">
-        <v>7.94506931304932</v>
+        <v>7.94507026672363</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1519" t="n">
-        <v>7.82175397872925</v>
+        <v>7.82175445556641</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1523" t="n">
-        <v>7.7689037322998</v>
+        <v>7.76890325546265</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G1531" t="n">
-        <v>8.29740142822266</v>
+        <v>8.29740047454834</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1540" t="n">
-        <v>8.01553726196289</v>
+        <v>8.01553630828857</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1541" t="n">
-        <v>8.01553726196289</v>
+        <v>8.01553630828857</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1542" t="n">
-        <v>8.05076885223389</v>
+        <v>8.0507698059082</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1544" t="n">
-        <v>8.12123584747314</v>
+        <v>8.12123489379883</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>9</v>
       </c>
       <c r="G1545" t="n">
-        <v>7.9274525642395</v>
+        <v>7.92745304107666</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1546" t="n">
-        <v>7.94506931304932</v>
+        <v>7.94507026672363</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1547" t="n">
-        <v>8.05076885223389</v>
+        <v>8.0507698059082</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1548" t="n">
-        <v>8.05076885223389</v>
+        <v>8.0507698059082</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G1552" t="n">
-        <v>7.96268558502197</v>
+        <v>7.96268606185913</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G1553" t="n">
-        <v>7.96268558502197</v>
+        <v>7.96268606185913</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1557" t="n">
-        <v>7.94506931304932</v>
+        <v>7.94507026672363</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1559" t="n">
-        <v>8.12123584747314</v>
+        <v>8.12123489379883</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1561" t="n">
-        <v>8.01553726196289</v>
+        <v>8.01553630828857</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G1563" t="n">
-        <v>8.06838512420654</v>
+        <v>8.06838607788086</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G1564" t="n">
-        <v>7.96268558502197</v>
+        <v>7.96268606185913</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>9</v>
       </c>
       <c r="G1566" t="n">
-        <v>7.9274525642395</v>
+        <v>7.92745304107666</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1568" t="n">
-        <v>7.68082141876221</v>
+        <v>7.68082189559937</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1571" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1574" t="n">
-        <v>7.39895582199097</v>
+        <v>7.39895534515381</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1580" t="n">
-        <v>7.68082141876221</v>
+        <v>7.68082189559937</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1581" t="n">
-        <v>7.57512187957764</v>
+        <v>7.57512140274048</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1583" t="n">
-        <v>7.57512187957764</v>
+        <v>7.57512140274048</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1584" t="n">
-        <v>7.52227163314819</v>
+        <v>7.52227210998535</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1585" t="n">
-        <v>7.57512187957764</v>
+        <v>7.57512140274048</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1592" t="n">
-        <v>7.69843769073486</v>
+        <v>7.69843721389771</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1594" t="n">
-        <v>7.7689037322998</v>
+        <v>7.76890325546265</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G1595" t="n">
-        <v>7.71605443954468</v>
+        <v>7.71605396270752</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1596" t="n">
-        <v>7.82175397872925</v>
+        <v>7.82175445556641</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1597" t="n">
-        <v>7.69843769073486</v>
+        <v>7.69843721389771</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1598" t="n">
-        <v>7.68082141876221</v>
+        <v>7.68082189559937</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1599" t="n">
-        <v>7.87460327148438</v>
+        <v>7.87460279464722</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G1601" t="n">
-        <v>7.64558839797974</v>
+        <v>7.64558887481689</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1610" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1611" t="n">
-        <v>7.36372232437134</v>
+        <v>7.3637228012085</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1613" t="n">
-        <v>7.32848978042603</v>
+        <v>7.32848930358887</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1617" t="n">
-        <v>7.69843769073486</v>
+        <v>7.69843721389771</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G1619" t="n">
-        <v>7.71605443954468</v>
+        <v>7.71605396270752</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G1621" t="n">
-        <v>7.71605443954468</v>
+        <v>7.71605396270752</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1623" t="n">
-        <v>7.68082141876221</v>
+        <v>7.68082189559937</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G1625" t="n">
-        <v>7.71605443954468</v>
+        <v>7.71605396270752</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1627" t="n">
-        <v>7.52227163314819</v>
+        <v>7.52227210998535</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1633" t="n">
-        <v>7.94506931304932</v>
+        <v>7.94507026672363</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1636" t="n">
-        <v>8.05076885223389</v>
+        <v>8.0507698059082</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G1637" t="n">
-        <v>8.06838512420654</v>
+        <v>8.06838607788086</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>9</v>
       </c>
       <c r="G1639" t="n">
-        <v>7.9274525642395</v>
+        <v>7.92745304107666</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1640" t="n">
-        <v>7.57512187957764</v>
+        <v>7.57512140274048</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1641" t="n">
-        <v>7.52227163314819</v>
+        <v>7.52227210998535</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1647" t="n">
-        <v>7.57512187957764</v>
+        <v>7.57512140274048</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1653" t="n">
-        <v>7.39895582199097</v>
+        <v>7.39895534515381</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1654" t="n">
-        <v>7.32848978042603</v>
+        <v>7.32848930358887</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1658" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1662" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1663" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1664" t="n">
-        <v>7.36372232437134</v>
+        <v>7.3637228012085</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1667" t="n">
-        <v>7.13470840454102</v>
+        <v>7.13470792770386</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1671" t="n">
-        <v>7.39895582199097</v>
+        <v>7.39895534515381</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1672" t="n">
-        <v>7.15232372283936</v>
+        <v>7.15232419967651</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1673" t="n">
-        <v>7.39895582199097</v>
+        <v>7.39895534515381</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1678" t="n">
-        <v>7.36372232437134</v>
+        <v>7.3637228012085</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1679" t="n">
-        <v>7.32848978042603</v>
+        <v>7.32848930358887</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1680" t="n">
-        <v>7.39895582199097</v>
+        <v>7.39895534515381</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1681" t="n">
-        <v>7.39895582199097</v>
+        <v>7.39895534515381</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1682" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1687" t="n">
-        <v>7.32848978042603</v>
+        <v>7.32848930358887</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1690" t="n">
-        <v>7.15232372283936</v>
+        <v>7.15232419967651</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1693" t="n">
-        <v>6.87045955657959</v>
+        <v>6.87045907974243</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1694" t="n">
-        <v>6.87045955657959</v>
+        <v>6.87045907974243</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1697" t="n">
-        <v>6.87045955657959</v>
+        <v>6.87045907974243</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1699" t="n">
-        <v>6.87045955657959</v>
+        <v>6.87045907974243</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1700" t="n">
-        <v>6.87045955657959</v>
+        <v>6.87045907974243</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1704" t="n">
-        <v>6.87045955657959</v>
+        <v>6.87045907974243</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1706" t="n">
-        <v>6.83522605895996</v>
+        <v>6.83522653579712</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1713" t="n">
-        <v>6.1834135055542</v>
+        <v>6.18341302871704</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1715" t="n">
-        <v>6.39481258392334</v>
+        <v>6.39481210708618</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1717" t="n">
-        <v>6.32434606552124</v>
+        <v>6.32434558868408</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1720" t="n">
-        <v>6.41242837905884</v>
+        <v>6.412428855896</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G1721" t="n">
-        <v>6.37719535827637</v>
+        <v>6.37719488143921</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1723" t="n">
-        <v>6.41242837905884</v>
+        <v>6.412428855896</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1724" t="n">
-        <v>6.44766235351562</v>
+        <v>6.44766187667847</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1725" t="n">
-        <v>6.46527814865112</v>
+        <v>6.46527862548828</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1732" t="n">
-        <v>6.46527814865112</v>
+        <v>6.46527862548828</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1735" t="n">
-        <v>6.41242837905884</v>
+        <v>6.412428855896</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1736" t="n">
-        <v>6.39481258392334</v>
+        <v>6.39481210708618</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1737" t="n">
-        <v>6.39481258392334</v>
+        <v>6.39481210708618</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1742" t="n">
-        <v>6.35957860946655</v>
+        <v>6.35957908630371</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1743" t="n">
-        <v>6.39481258392334</v>
+        <v>6.39481210708618</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1745" t="n">
-        <v>6.32434606552124</v>
+        <v>6.32434558868408</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1752" t="n">
-        <v>6.41242837905884</v>
+        <v>6.412428855896</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1754" t="n">
-        <v>6.44766235351562</v>
+        <v>6.44766187667847</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1758" t="n">
-        <v>6.90569257736206</v>
+        <v>6.90569305419922</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1759" t="n">
-        <v>6.87045955657959</v>
+        <v>6.87045907974243</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1762" t="n">
-        <v>6.90569257736206</v>
+        <v>6.90569305419922</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1770" t="n">
-        <v>6.90569257736206</v>
+        <v>6.90569305419922</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1777" t="n">
-        <v>6.90569257736206</v>
+        <v>6.90569305419922</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1778" t="n">
-        <v>6.90569257736206</v>
+        <v>6.90569305419922</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1779" t="n">
-        <v>6.90569257736206</v>
+        <v>6.90569305419922</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1780" t="n">
-        <v>6.90569257736206</v>
+        <v>6.90569305419922</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1781" t="n">
-        <v>6.87045955657959</v>
+        <v>6.87045907974243</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1782" t="n">
-        <v>6.87045955657959</v>
+        <v>6.87045907974243</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1787" t="n">
-        <v>6.87045955657959</v>
+        <v>6.87045907974243</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1794" t="n">
-        <v>6.92330932617188</v>
+        <v>6.92330884933472</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1799" t="n">
-        <v>7.13470840454102</v>
+        <v>7.13470792770386</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1803" t="n">
-        <v>7.13470840454102</v>
+        <v>7.13470792770386</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1806" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1815" t="n">
-        <v>7.13470840454102</v>
+        <v>7.13470792770386</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1821" t="n">
-        <v>7.15232372283936</v>
+        <v>7.15232419967651</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>8</v>
       </c>
       <c r="G1823" t="n">
-        <v>7.04662466049194</v>
+        <v>7.0466251373291</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1824" t="n">
-        <v>7.13470840454102</v>
+        <v>7.13470792770386</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1825" t="n">
-        <v>7.08185815811157</v>
+        <v>7.08185768127441</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>8</v>
       </c>
       <c r="G1827" t="n">
-        <v>7.04662466049194</v>
+        <v>7.0466251373291</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1831" t="n">
-        <v>6.90569257736206</v>
+        <v>6.90569305419922</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1834" t="n">
-        <v>7.13470840454102</v>
+        <v>7.13470792770386</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1836" t="n">
-        <v>6.90569257736206</v>
+        <v>6.90569305419922</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1838" t="n">
-        <v>6.87045955657959</v>
+        <v>6.87045907974243</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>8</v>
       </c>
       <c r="G1839" t="n">
-        <v>7.04662466049194</v>
+        <v>7.0466251373291</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1844" t="n">
-        <v>6.87045955657959</v>
+        <v>6.87045907974243</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>8</v>
       </c>
       <c r="G1849" t="n">
-        <v>7.04662466049194</v>
+        <v>7.0466251373291</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1850" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1851" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>8</v>
       </c>
       <c r="G1852" t="n">
-        <v>7.04662466049194</v>
+        <v>7.0466251373291</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1854" t="n">
-        <v>7.08185815811157</v>
+        <v>7.08185768127441</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1855" t="n">
-        <v>7.13470840454102</v>
+        <v>7.13470792770386</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1856" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1857" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1858" t="n">
-        <v>7.13470840454102</v>
+        <v>7.13470792770386</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1859" t="n">
-        <v>7.13470840454102</v>
+        <v>7.13470792770386</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1860" t="n">
-        <v>7.13470840454102</v>
+        <v>7.13470792770386</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1861" t="n">
-        <v>7.18755722045898</v>
+        <v>7.18755674362183</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1863" t="n">
-        <v>7.18755722045898</v>
+        <v>7.18755674362183</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1865" t="n">
-        <v>7.18755722045898</v>
+        <v>7.18755674362183</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1869" t="n">
-        <v>7.32848978042603</v>
+        <v>7.32848930358887</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1870" t="n">
-        <v>7.32848978042603</v>
+        <v>7.32848930358887</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1872" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1876" t="n">
-        <v>7.52227163314819</v>
+        <v>7.52227210998535</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1877" t="n">
-        <v>7.39895582199097</v>
+        <v>7.39895534515381</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1878" t="n">
-        <v>7.57512187957764</v>
+        <v>7.57512140274048</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1888" t="n">
-        <v>7.39895582199097</v>
+        <v>7.39895534515381</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1889" t="n">
-        <v>7.52227163314819</v>
+        <v>7.52227210998535</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49509,7 +49509,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1890" t="n">
-        <v>7.39895582199097</v>
+        <v>7.39895534515381</v>
       </c>
       <c r="H1890" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1891" t="n">
-        <v>7.32848978042603</v>
+        <v>7.32848930358887</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49561,7 +49561,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1892" t="n">
-        <v>7.32848978042603</v>
+        <v>7.32848930358887</v>
       </c>
       <c r="H1892" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1893" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1894" t="n">
-        <v>7.39895582199097</v>
+        <v>7.39895534515381</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1895" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1896" t="n">
-        <v>7.39895582199097</v>
+        <v>7.39895534515381</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1898" t="n">
-        <v>7.39895582199097</v>
+        <v>7.39895534515381</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1899" t="n">
-        <v>7.39895582199097</v>
+        <v>7.39895534515381</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1903" t="n">
-        <v>7.32848978042603</v>
+        <v>7.32848930358887</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49873,7 +49873,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1904" t="n">
-        <v>7.39895582199097</v>
+        <v>7.39895534515381</v>
       </c>
       <c r="H1904" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1905" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1906" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1909" t="n">
-        <v>7.36372232437134</v>
+        <v>7.3637228012085</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1910" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1911" t="n">
-        <v>7.32848978042603</v>
+        <v>7.32848930358887</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50107,7 +50107,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1913" t="n">
-        <v>7.13470840454102</v>
+        <v>7.13470792770386</v>
       </c>
       <c r="H1913" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1919" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1921" t="n">
-        <v>7.18755722045898</v>
+        <v>7.18755674362183</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50341,7 +50341,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1922" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1922" t="s">
         <v>8</v>
@@ -50393,7 +50393,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1924" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1924" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1925" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1926" t="n">
-        <v>7.39895582199097</v>
+        <v>7.39895534515381</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50497,7 +50497,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1928" t="n">
-        <v>7.39895582199097</v>
+        <v>7.39895534515381</v>
       </c>
       <c r="H1928" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1930" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50601,7 +50601,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1932" t="n">
-        <v>7.32848978042603</v>
+        <v>7.32848930358887</v>
       </c>
       <c r="H1932" t="s">
         <v>8</v>
@@ -50731,7 +50731,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1937" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1937" t="s">
         <v>8</v>
@@ -50757,7 +50757,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1938" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1938" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1940" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -50861,7 +50861,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1942" t="n">
-        <v>7.32848978042603</v>
+        <v>7.32848930358887</v>
       </c>
       <c r="H1942" t="s">
         <v>8</v>
@@ -50913,7 +50913,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1944" t="n">
-        <v>7.18755722045898</v>
+        <v>7.18755674362183</v>
       </c>
       <c r="H1944" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1945" t="n">
-        <v>7.18755722045898</v>
+        <v>7.18755674362183</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -51069,7 +51069,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1950" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1950" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1951" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51173,7 +51173,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1954" t="n">
-        <v>7.36372232437134</v>
+        <v>7.3637228012085</v>
       </c>
       <c r="H1954" t="s">
         <v>8</v>
@@ -51199,7 +51199,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1955" t="n">
-        <v>7.39895582199097</v>
+        <v>7.39895534515381</v>
       </c>
       <c r="H1955" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1956" t="n">
-        <v>7.36372232437134</v>
+        <v>7.3637228012085</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51329,7 +51329,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1960" t="n">
-        <v>7.39895582199097</v>
+        <v>7.39895534515381</v>
       </c>
       <c r="H1960" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1961" t="n">
-        <v>7.36372232437134</v>
+        <v>7.3637228012085</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1970" t="n">
-        <v>7.32848978042603</v>
+        <v>7.32848930358887</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51693,7 +51693,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1974" t="n">
-        <v>7.18755722045898</v>
+        <v>7.18755674362183</v>
       </c>
       <c r="H1974" t="s">
         <v>8</v>
@@ -51797,7 +51797,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1978" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1978" t="s">
         <v>8</v>
@@ -51875,7 +51875,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1981" t="n">
-        <v>7.32848978042603</v>
+        <v>7.32848930358887</v>
       </c>
       <c r="H1981" t="s">
         <v>8</v>
@@ -51901,7 +51901,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1982" t="n">
-        <v>7.39895582199097</v>
+        <v>7.39895534515381</v>
       </c>
       <c r="H1982" t="s">
         <v>8</v>
@@ -51953,7 +51953,7 @@
         <v>8</v>
       </c>
       <c r="G1984" t="n">
-        <v>7.04662466049194</v>
+        <v>7.0466251373291</v>
       </c>
       <c r="H1984" t="s">
         <v>8</v>
@@ -51979,7 +51979,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1985" t="n">
-        <v>7.15232372283936</v>
+        <v>7.15232419967651</v>
       </c>
       <c r="H1985" t="s">
         <v>8</v>
@@ -52005,7 +52005,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1986" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H1986" t="s">
         <v>8</v>
@@ -52057,7 +52057,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1988" t="n">
-        <v>7.18755722045898</v>
+        <v>7.18755674362183</v>
       </c>
       <c r="H1988" t="s">
         <v>8</v>
@@ -52083,7 +52083,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1989" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H1989" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1990" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52135,7 +52135,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1991" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H1991" t="s">
         <v>8</v>
@@ -52187,7 +52187,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1993" t="n">
-        <v>7.13470840454102</v>
+        <v>7.13470792770386</v>
       </c>
       <c r="H1993" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1994" t="n">
-        <v>7.15232372283936</v>
+        <v>7.15232419967651</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1995" t="n">
-        <v>7.13470840454102</v>
+        <v>7.13470792770386</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -52291,7 +52291,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1997" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H1997" t="s">
         <v>8</v>
@@ -52317,7 +52317,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1998" t="n">
-        <v>7.13470840454102</v>
+        <v>7.13470792770386</v>
       </c>
       <c r="H1998" t="s">
         <v>8</v>
@@ -52473,7 +52473,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G2004" t="n">
-        <v>7.13470840454102</v>
+        <v>7.13470792770386</v>
       </c>
       <c r="H2004" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2005" t="n">
-        <v>7.15232372283936</v>
+        <v>7.15232419967651</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2006" t="n">
-        <v>7.15232372283936</v>
+        <v>7.15232419967651</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52551,7 +52551,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2007" t="n">
-        <v>7.15232372283936</v>
+        <v>7.15232419967651</v>
       </c>
       <c r="H2007" t="s">
         <v>8</v>
@@ -52577,7 +52577,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2008" t="n">
-        <v>7.15232372283936</v>
+        <v>7.15232419967651</v>
       </c>
       <c r="H2008" t="s">
         <v>8</v>
@@ -52603,7 +52603,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G2009" t="n">
-        <v>7.13470840454102</v>
+        <v>7.13470792770386</v>
       </c>
       <c r="H2009" t="s">
         <v>8</v>
@@ -52811,7 +52811,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2017" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H2017" t="s">
         <v>8</v>
@@ -52941,7 +52941,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2022" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H2022" t="s">
         <v>8</v>
@@ -52993,7 +52993,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2024" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H2024" t="s">
         <v>8</v>
@@ -53149,7 +53149,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G2030" t="n">
-        <v>7.18755722045898</v>
+        <v>7.18755674362183</v>
       </c>
       <c r="H2030" t="s">
         <v>8</v>
@@ -53487,7 +53487,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G2043" t="n">
-        <v>7.32848978042603</v>
+        <v>7.32848930358887</v>
       </c>
       <c r="H2043" t="s">
         <v>8</v>
@@ -53669,7 +53669,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G2050" t="n">
-        <v>7.36372232437134</v>
+        <v>7.3637228012085</v>
       </c>
       <c r="H2050" t="s">
         <v>8</v>
@@ -53747,7 +53747,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G2053" t="n">
-        <v>7.32848978042603</v>
+        <v>7.32848930358887</v>
       </c>
       <c r="H2053" t="s">
         <v>8</v>
@@ -53773,7 +53773,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2054" t="n">
-        <v>7.31087350845337</v>
+        <v>7.31087398529053</v>
       </c>
       <c r="H2054" t="s">
         <v>8</v>
@@ -53877,7 +53877,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G2058" t="n">
-        <v>7.18755722045898</v>
+        <v>7.18755674362183</v>
       </c>
       <c r="H2058" t="s">
         <v>8</v>
@@ -54137,7 +54137,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G2068" t="n">
-        <v>7.08185815811157</v>
+        <v>7.08185768127441</v>
       </c>
       <c r="H2068" t="s">
         <v>8</v>
@@ -54215,7 +54215,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G2071" t="n">
-        <v>7.13470840454102</v>
+        <v>7.13470792770386</v>
       </c>
       <c r="H2071" t="s">
         <v>8</v>
@@ -54241,7 +54241,7 @@
         <v>8</v>
       </c>
       <c r="G2072" t="n">
-        <v>7.04662466049194</v>
+        <v>7.0466251373291</v>
       </c>
       <c r="H2072" t="s">
         <v>8</v>
@@ -54345,7 +54345,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2076" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H2076" t="s">
         <v>8</v>
@@ -54371,7 +54371,7 @@
         <v>8</v>
       </c>
       <c r="G2077" t="n">
-        <v>7.04662466049194</v>
+        <v>7.0466251373291</v>
       </c>
       <c r="H2077" t="s">
         <v>8</v>
@@ -54553,7 +54553,7 @@
         <v>8</v>
       </c>
       <c r="G2084" t="n">
-        <v>7.04662466049194</v>
+        <v>7.0466251373291</v>
       </c>
       <c r="H2084" t="s">
         <v>8</v>
@@ -54735,7 +54735,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G2091" t="n">
-        <v>6.92330932617188</v>
+        <v>6.92330884933472</v>
       </c>
       <c r="H2091" t="s">
         <v>8</v>
@@ -54787,7 +54787,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2093" t="n">
-        <v>6.90569257736206</v>
+        <v>6.90569305419922</v>
       </c>
       <c r="H2093" t="s">
         <v>8</v>
@@ -54917,7 +54917,7 @@
         <v>8</v>
       </c>
       <c r="G2098" t="n">
-        <v>7.04662466049194</v>
+        <v>7.0466251373291</v>
       </c>
       <c r="H2098" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>8</v>
       </c>
       <c r="G2105" t="n">
-        <v>7.04662466049194</v>
+        <v>7.0466251373291</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55125,7 +55125,7 @@
         <v>8</v>
       </c>
       <c r="G2106" t="n">
-        <v>7.04662466049194</v>
+        <v>7.0466251373291</v>
       </c>
       <c r="H2106" t="s">
         <v>8</v>
@@ -55151,7 +55151,7 @@
         <v>8</v>
       </c>
       <c r="G2107" t="n">
-        <v>7.04662466049194</v>
+        <v>7.0466251373291</v>
       </c>
       <c r="H2107" t="s">
         <v>8</v>
@@ -55203,7 +55203,7 @@
         <v>8</v>
       </c>
       <c r="G2109" t="n">
-        <v>7.04662466049194</v>
+        <v>7.0466251373291</v>
       </c>
       <c r="H2109" t="s">
         <v>8</v>
@@ -55411,7 +55411,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2117" t="n">
-        <v>6.90569257736206</v>
+        <v>6.90569305419922</v>
       </c>
       <c r="H2117" t="s">
         <v>8</v>
@@ -55437,7 +55437,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G2118" t="n">
-        <v>6.92330932617188</v>
+        <v>6.92330884933472</v>
       </c>
       <c r="H2118" t="s">
         <v>8</v>
@@ -55489,7 +55489,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G2120" t="n">
-        <v>7.13470840454102</v>
+        <v>7.13470792770386</v>
       </c>
       <c r="H2120" t="s">
         <v>8</v>
@@ -55541,7 +55541,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2122" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H2122" t="s">
         <v>8</v>
@@ -55567,7 +55567,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2123" t="n">
-        <v>7.33988809585571</v>
+        <v>7.33988857269287</v>
       </c>
       <c r="H2123" t="s">
         <v>8</v>
@@ -55619,7 +55619,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G2125" t="n">
-        <v>7.23060941696167</v>
+        <v>7.23060894012451</v>
       </c>
       <c r="H2125" t="s">
         <v>8</v>
@@ -55671,7 +55671,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2127" t="n">
-        <v>7.2488226890564</v>
+        <v>7.24882221221924</v>
       </c>
       <c r="H2127" t="s">
         <v>8</v>
@@ -55775,7 +55775,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2131" t="n">
-        <v>7.33988809585571</v>
+        <v>7.33988857269287</v>
       </c>
       <c r="H2131" t="s">
         <v>8</v>
@@ -55853,7 +55853,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2134" t="n">
-        <v>7.2488226890564</v>
+        <v>7.24882221221924</v>
       </c>
       <c r="H2134" t="s">
         <v>8</v>
@@ -55983,7 +55983,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2139" t="n">
-        <v>7.33988809585571</v>
+        <v>7.33988857269287</v>
       </c>
       <c r="H2139" t="s">
         <v>8</v>
@@ -56035,7 +56035,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2141" t="n">
-        <v>7.2488226890564</v>
+        <v>7.24882221221924</v>
       </c>
       <c r="H2141" t="s">
         <v>8</v>
@@ -56113,7 +56113,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G2144" t="n">
-        <v>7.23060941696167</v>
+        <v>7.23060894012451</v>
       </c>
       <c r="H2144" t="s">
         <v>8</v>
@@ -56243,7 +56243,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G2149" t="n">
-        <v>7.32167434692383</v>
+        <v>7.32167482376099</v>
       </c>
       <c r="H2149" t="s">
         <v>8</v>
@@ -56295,7 +56295,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2151" t="n">
-        <v>7.33988809585571</v>
+        <v>7.33988857269287</v>
       </c>
       <c r="H2151" t="s">
         <v>8</v>
@@ -56399,7 +56399,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2155" t="n">
-        <v>7.33988809585571</v>
+        <v>7.33988857269287</v>
       </c>
       <c r="H2155" t="s">
         <v>8</v>
@@ -56425,7 +56425,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G2156" t="n">
-        <v>7.23060941696167</v>
+        <v>7.23060894012451</v>
       </c>
       <c r="H2156" t="s">
         <v>8</v>
@@ -56477,7 +56477,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G2158" t="n">
-        <v>7.23060941696167</v>
+        <v>7.23060894012451</v>
       </c>
       <c r="H2158" t="s">
         <v>8</v>
@@ -56503,7 +56503,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G2159" t="n">
-        <v>7.23060941696167</v>
+        <v>7.23060894012451</v>
       </c>
       <c r="H2159" t="s">
         <v>8</v>
@@ -56659,7 +56659,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2165" t="n">
-        <v>7.13954401016235</v>
+        <v>7.1395435333252</v>
       </c>
       <c r="H2165" t="s">
         <v>8</v>
@@ -56711,7 +56711,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2167" t="n">
-        <v>7.2488226890564</v>
+        <v>7.24882221221924</v>
       </c>
       <c r="H2167" t="s">
         <v>8</v>
@@ -56737,7 +56737,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2168" t="n">
-        <v>7.2488226890564</v>
+        <v>7.24882221221924</v>
       </c>
       <c r="H2168" t="s">
         <v>8</v>
@@ -56763,7 +56763,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G2169" t="n">
-        <v>7.23060941696167</v>
+        <v>7.23060894012451</v>
       </c>
       <c r="H2169" t="s">
         <v>8</v>
@@ -56815,7 +56815,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2171" t="n">
-        <v>7.13954401016235</v>
+        <v>7.1395435333252</v>
       </c>
       <c r="H2171" t="s">
         <v>8</v>
@@ -56867,7 +56867,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2173" t="n">
-        <v>7.2488226890564</v>
+        <v>7.24882221221924</v>
       </c>
       <c r="H2173" t="s">
         <v>8</v>
@@ -56893,7 +56893,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G2174" t="n">
-        <v>7.23060941696167</v>
+        <v>7.23060894012451</v>
       </c>
       <c r="H2174" t="s">
         <v>8</v>
@@ -56919,7 +56919,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2175" t="n">
-        <v>7.13954401016235</v>
+        <v>7.1395435333252</v>
       </c>
       <c r="H2175" t="s">
         <v>8</v>
@@ -56945,7 +56945,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G2176" t="n">
-        <v>7.23060941696167</v>
+        <v>7.23060894012451</v>
       </c>
       <c r="H2176" t="s">
         <v>8</v>
@@ -57023,7 +57023,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2179" t="n">
-        <v>7.2488226890564</v>
+        <v>7.24882221221924</v>
       </c>
       <c r="H2179" t="s">
         <v>8</v>
@@ -57049,7 +57049,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2180" t="n">
-        <v>7.2488226890564</v>
+        <v>7.24882221221924</v>
       </c>
       <c r="H2180" t="s">
         <v>8</v>
@@ -57075,7 +57075,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G2181" t="n">
-        <v>7.23060941696167</v>
+        <v>7.23060894012451</v>
       </c>
       <c r="H2181" t="s">
         <v>8</v>
@@ -57127,7 +57127,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2183" t="n">
-        <v>7.2488226890564</v>
+        <v>7.24882221221924</v>
       </c>
       <c r="H2183" t="s">
         <v>8</v>
@@ -57153,7 +57153,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G2184" t="n">
-        <v>7.17597007751465</v>
+        <v>7.17596960067749</v>
       </c>
       <c r="H2184" t="s">
         <v>8</v>
@@ -57179,7 +57179,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2185" t="n">
-        <v>7.2488226890564</v>
+        <v>7.24882221221924</v>
       </c>
       <c r="H2185" t="s">
         <v>8</v>
@@ -57257,7 +57257,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G2188" t="n">
-        <v>7.17597007751465</v>
+        <v>7.17596960067749</v>
       </c>
       <c r="H2188" t="s">
         <v>8</v>
@@ -57335,7 +57335,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G2191" t="n">
-        <v>7.17597007751465</v>
+        <v>7.17596960067749</v>
       </c>
       <c r="H2191" t="s">
         <v>8</v>
@@ -57517,7 +57517,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2198" t="n">
-        <v>7.13954401016235</v>
+        <v>7.1395435333252</v>
       </c>
       <c r="H2198" t="s">
         <v>8</v>
@@ -57647,7 +57647,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2203" t="n">
-        <v>7.13954401016235</v>
+        <v>7.1395435333252</v>
       </c>
       <c r="H2203" t="s">
         <v>8</v>
@@ -57751,7 +57751,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2207" t="n">
-        <v>7.13954401016235</v>
+        <v>7.1395435333252</v>
       </c>
       <c r="H2207" t="s">
         <v>8</v>
@@ -57829,7 +57829,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2210" t="n">
-        <v>7.04847764968872</v>
+        <v>7.04847812652588</v>
       </c>
       <c r="H2210" t="s">
         <v>8</v>
@@ -57881,7 +57881,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2212" t="n">
-        <v>7.04847764968872</v>
+        <v>7.04847812652588</v>
       </c>
       <c r="H2212" t="s">
         <v>8</v>
@@ -57907,7 +57907,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2213" t="n">
-        <v>7.13954401016235</v>
+        <v>7.1395435333252</v>
       </c>
       <c r="H2213" t="s">
         <v>8</v>
@@ -58167,7 +58167,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G2223" t="n">
-        <v>6.97562503814697</v>
+        <v>6.97562551498413</v>
       </c>
       <c r="H2223" t="s">
         <v>8</v>
@@ -58479,7 +58479,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2235" t="n">
-        <v>7.04847764968872</v>
+        <v>7.04847812652588</v>
       </c>
       <c r="H2235" t="s">
         <v>8</v>
@@ -58557,7 +58557,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2238" t="n">
-        <v>7.04847764968872</v>
+        <v>7.04847812652588</v>
       </c>
       <c r="H2238" t="s">
         <v>8</v>
@@ -58583,7 +58583,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2239" t="n">
-        <v>7.13954401016235</v>
+        <v>7.1395435333252</v>
       </c>
       <c r="H2239" t="s">
         <v>8</v>
@@ -58687,7 +58687,7 @@
         <v>7.5</v>
       </c>
       <c r="G2243" t="n">
-        <v>6.82992029190063</v>
+        <v>6.82992076873779</v>
       </c>
       <c r="H2243" t="s">
         <v>8</v>
@@ -58713,7 +58713,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2244" t="n">
-        <v>6.62957620620728</v>
+        <v>6.62957668304443</v>
       </c>
       <c r="H2244" t="s">
         <v>8</v>
@@ -58739,7 +58739,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2245" t="n">
-        <v>6.7934947013855</v>
+        <v>6.79349422454834</v>
       </c>
       <c r="H2245" t="s">
         <v>8</v>
@@ -58817,7 +58817,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2248" t="n">
-        <v>6.73885536193848</v>
+        <v>6.73885488510132</v>
       </c>
       <c r="H2248" t="s">
         <v>8</v>
@@ -58869,7 +58869,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G2250" t="n">
-        <v>6.75706815719604</v>
+        <v>6.75706768035889</v>
       </c>
       <c r="H2250" t="s">
         <v>8</v>
@@ -58947,7 +58947,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G2253" t="n">
-        <v>6.75706815719604</v>
+        <v>6.75706768035889</v>
       </c>
       <c r="H2253" t="s">
         <v>8</v>
@@ -59025,7 +59025,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G2256" t="n">
-        <v>6.75706815719604</v>
+        <v>6.75706768035889</v>
       </c>
       <c r="H2256" t="s">
         <v>8</v>
@@ -59051,7 +59051,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2257" t="n">
-        <v>6.73885536193848</v>
+        <v>6.73885488510132</v>
       </c>
       <c r="H2257" t="s">
         <v>8</v>
@@ -59129,7 +59129,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2260" t="n">
-        <v>6.7934947013855</v>
+        <v>6.79349422454834</v>
       </c>
       <c r="H2260" t="s">
         <v>8</v>
@@ -59181,7 +59181,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2262" t="n">
-        <v>6.73885536193848</v>
+        <v>6.73885488510132</v>
       </c>
       <c r="H2262" t="s">
         <v>8</v>
@@ -59233,7 +59233,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2264" t="n">
-        <v>6.7934947013855</v>
+        <v>6.79349422454834</v>
       </c>
       <c r="H2264" t="s">
         <v>8</v>
@@ -59311,7 +59311,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G2267" t="n">
-        <v>6.75706815719604</v>
+        <v>6.75706768035889</v>
       </c>
       <c r="H2267" t="s">
         <v>8</v>
@@ -59337,7 +59337,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2268" t="n">
-        <v>6.92098569869995</v>
+        <v>6.92098617553711</v>
       </c>
       <c r="H2268" t="s">
         <v>8</v>
@@ -59363,7 +59363,7 @@
         <v>7.5</v>
       </c>
       <c r="G2269" t="n">
-        <v>6.82992029190063</v>
+        <v>6.82992076873779</v>
       </c>
       <c r="H2269" t="s">
         <v>8</v>
@@ -59389,7 +59389,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2270" t="n">
-        <v>6.86634635925293</v>
+        <v>6.86634683609009</v>
       </c>
       <c r="H2270" t="s">
         <v>8</v>
@@ -59415,7 +59415,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2271" t="n">
-        <v>6.86634635925293</v>
+        <v>6.86634683609009</v>
       </c>
       <c r="H2271" t="s">
         <v>8</v>
@@ -59519,7 +59519,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2275" t="n">
-        <v>6.92098569869995</v>
+        <v>6.92098617553711</v>
       </c>
       <c r="H2275" t="s">
         <v>8</v>
@@ -59805,7 +59805,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2286" t="n">
-        <v>6.73885536193848</v>
+        <v>6.73885488510132</v>
       </c>
       <c r="H2286" t="s">
         <v>8</v>
@@ -59909,7 +59909,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2290" t="n">
-        <v>6.86634635925293</v>
+        <v>6.86634683609009</v>
       </c>
       <c r="H2290" t="s">
         <v>8</v>
@@ -59935,7 +59935,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2291" t="n">
-        <v>6.86634635925293</v>
+        <v>6.86634683609009</v>
       </c>
       <c r="H2291" t="s">
         <v>8</v>
@@ -60013,7 +60013,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2294" t="n">
-        <v>7.04847764968872</v>
+        <v>7.04847812652588</v>
       </c>
       <c r="H2294" t="s">
         <v>8</v>
@@ -60143,7 +60143,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2299" t="n">
-        <v>7.04847764968872</v>
+        <v>7.04847812652588</v>
       </c>
       <c r="H2299" t="s">
         <v>8</v>
@@ -60169,7 +60169,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2300" t="n">
-        <v>7.04847764968872</v>
+        <v>7.04847812652588</v>
       </c>
       <c r="H2300" t="s">
         <v>8</v>
@@ -60221,7 +60221,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2302" t="n">
-        <v>7.04847764968872</v>
+        <v>7.04847812652588</v>
       </c>
       <c r="H2302" t="s">
         <v>8</v>
@@ -60247,7 +60247,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2303" t="n">
-        <v>6.86634635925293</v>
+        <v>6.86634683609009</v>
       </c>
       <c r="H2303" t="s">
         <v>8</v>
@@ -60273,7 +60273,7 @@
         <v>7.5</v>
       </c>
       <c r="G2304" t="n">
-        <v>6.82992029190063</v>
+        <v>6.82992076873779</v>
       </c>
       <c r="H2304" t="s">
         <v>8</v>
@@ -60585,7 +60585,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2316" t="n">
-        <v>7.04847764968872</v>
+        <v>7.04847812652588</v>
       </c>
       <c r="H2316" t="s">
         <v>8</v>
@@ -60819,7 +60819,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G2325" t="n">
-        <v>6.97562503814697</v>
+        <v>6.97562551498413</v>
       </c>
       <c r="H2325" t="s">
         <v>8</v>
@@ -61079,7 +61079,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2335" t="n">
-        <v>7.04847764968872</v>
+        <v>7.04847812652588</v>
       </c>
       <c r="H2335" t="s">
         <v>8</v>
@@ -61131,7 +61131,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2337" t="n">
-        <v>7.04847764968872</v>
+        <v>7.04847812652588</v>
       </c>
       <c r="H2337" t="s">
         <v>8</v>
@@ -61157,7 +61157,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2338" t="n">
-        <v>7.04847764968872</v>
+        <v>7.04847812652588</v>
       </c>
       <c r="H2338" t="s">
         <v>8</v>
@@ -61261,7 +61261,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G2342" t="n">
-        <v>7.32167434692383</v>
+        <v>7.32167482376099</v>
       </c>
       <c r="H2342" t="s">
         <v>8</v>
@@ -61287,7 +61287,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G2343" t="n">
-        <v>7.23060941696167</v>
+        <v>7.23060894012451</v>
       </c>
       <c r="H2343" t="s">
         <v>8</v>
@@ -61365,7 +61365,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2346" t="n">
-        <v>7.33988809585571</v>
+        <v>7.33988857269287</v>
       </c>
       <c r="H2346" t="s">
         <v>8</v>
@@ -61391,7 +61391,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G2347" t="n">
-        <v>7.43095302581787</v>
+        <v>7.43095350265503</v>
       </c>
       <c r="H2347" t="s">
         <v>8</v>
@@ -61417,7 +61417,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G2348" t="n">
-        <v>7.43095302581787</v>
+        <v>7.43095350265503</v>
       </c>
       <c r="H2348" t="s">
         <v>8</v>
@@ -61521,7 +61521,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2352" t="n">
-        <v>7.39452695846558</v>
+        <v>7.39452743530273</v>
       </c>
       <c r="H2352" t="s">
         <v>8</v>
@@ -61547,7 +61547,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2353" t="n">
-        <v>7.39452695846558</v>
+        <v>7.39452743530273</v>
       </c>
       <c r="H2353" t="s">
         <v>8</v>
@@ -61625,7 +61625,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2356" t="n">
-        <v>7.13954401016235</v>
+        <v>7.1395435333252</v>
       </c>
       <c r="H2356" t="s">
         <v>8</v>
@@ -61703,7 +61703,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G2359" t="n">
-        <v>7.32167434692383</v>
+        <v>7.32167482376099</v>
       </c>
       <c r="H2359" t="s">
         <v>8</v>
@@ -61755,7 +61755,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G2361" t="n">
-        <v>7.32167434692383</v>
+        <v>7.32167482376099</v>
       </c>
       <c r="H2361" t="s">
         <v>8</v>
@@ -61833,7 +61833,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2364" t="n">
-        <v>7.39452695846558</v>
+        <v>7.39452743530273</v>
       </c>
       <c r="H2364" t="s">
         <v>8</v>
@@ -62015,7 +62015,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G2371" t="n">
-        <v>7.48559284210205</v>
+        <v>7.48559331893921</v>
       </c>
       <c r="H2371" t="s">
         <v>8</v>
@@ -62119,7 +62119,7 @@
         <v>8.5</v>
       </c>
       <c r="G2375" t="n">
-        <v>7.74057722091675</v>
+        <v>7.74057626724243</v>
       </c>
       <c r="H2375" t="s">
         <v>8</v>
@@ -62145,7 +62145,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G2376" t="n">
-        <v>7.81342887878418</v>
+        <v>7.81342935562134</v>
       </c>
       <c r="H2376" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>9.03999996185303</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>12648</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>9.14000034332275</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>8.42000007629395</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>9.14000034332275</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>8.88000011444092</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>8.88000011444092</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -681,7 +681,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G12" t="n">
-        <v>5.0047435760498</v>
+        <v>5.00474309921265</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G13" t="n">
-        <v>5.04868078231812</v>
+        <v>5.04868030548096</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G14" t="n">
-        <v>5.10459852218628</v>
+        <v>5.10459899902344</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G18" t="n">
-        <v>5.18448257446289</v>
+        <v>5.18448305130005</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>6.44500017166138</v>
       </c>
       <c r="G19" t="n">
-        <v>5.14853477478027</v>
+        <v>5.14853525161743</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G22" t="n">
-        <v>5.15252923965454</v>
+        <v>5.15252876281738</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G23" t="n">
-        <v>5.16850614547729</v>
+        <v>5.16850662231445</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>6.5</v>
       </c>
       <c r="G27" t="n">
-        <v>5.19247150421143</v>
+        <v>5.19247198104858</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G28" t="n">
-        <v>5.15252923965454</v>
+        <v>5.15252876281738</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>6.5</v>
       </c>
       <c r="G29" t="n">
-        <v>5.19247150421143</v>
+        <v>5.19247198104858</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>5.15252923965454</v>
+        <v>5.15252876281738</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G31" t="n">
-        <v>5.27235555648804</v>
+        <v>5.27235507965088</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>5.27634906768799</v>
+        <v>5.2763500213623</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G33" t="n">
-        <v>5.49603176116943</v>
+        <v>5.49603223800659</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G34" t="n">
-        <v>5.71171903610229</v>
+        <v>5.71171855926514</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G35" t="n">
-        <v>5.67177629470825</v>
+        <v>5.67177677154541</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>6.88500022888184</v>
       </c>
       <c r="G36" t="n">
-        <v>5.50002574920654</v>
+        <v>5.50002527236938</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G37" t="n">
-        <v>5.6398229598999</v>
+        <v>5.63982343673706</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G39" t="n">
-        <v>5.74367237091064</v>
+        <v>5.74367189407349</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G41" t="n">
-        <v>5.71171903610229</v>
+        <v>5.71171855926514</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>7.18499994277954</v>
       </c>
       <c r="G42" t="n">
-        <v>5.73967838287354</v>
+        <v>5.73967790603638</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G44" t="n">
-        <v>5.67177629470825</v>
+        <v>5.67177677154541</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G46" t="n">
-        <v>5.72370147705078</v>
+        <v>5.72370100021362</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G52" t="n">
-        <v>5.82355642318726</v>
+        <v>5.82355690002441</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G53" t="n">
-        <v>5.90343999862671</v>
+        <v>5.90344047546387</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G54" t="n">
-        <v>5.95935964584351</v>
+        <v>5.95935916900635</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G55" t="n">
-        <v>6.23096609115601</v>
+        <v>6.23096561431885</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>7.89499998092651</v>
       </c>
       <c r="G57" t="n">
-        <v>6.30685615539551</v>
+        <v>6.30685567855835</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G58" t="n">
-        <v>6.32682752609253</v>
+        <v>6.32682657241821</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G61" t="n">
-        <v>6.29487276077271</v>
+        <v>6.29487323760986</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G62" t="n">
-        <v>6.34679746627808</v>
+        <v>6.34679794311523</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G65" t="n">
-        <v>6.36676836013794</v>
+        <v>6.36676931381226</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G67" t="n">
-        <v>6.55050230026245</v>
+        <v>6.55050182342529</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G69" t="n">
-        <v>6.7502121925354</v>
+        <v>6.75021266937256</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G70" t="n">
-        <v>6.76618909835815</v>
+        <v>6.76618957519531</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>8.5</v>
       </c>
       <c r="G71" t="n">
-        <v>6.79015493392944</v>
+        <v>6.79015445709229</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9</v>
       </c>
       <c r="G74" t="n">
-        <v>7.1895751953125</v>
+        <v>7.18957614898682</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G75" t="n">
-        <v>7.69284629821777</v>
+        <v>7.69284677505493</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.79500007629395</v>
       </c>
       <c r="G77" t="n">
-        <v>7.82465505599976</v>
+        <v>7.82465410232544</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>9.24499988555908</v>
       </c>
       <c r="G78" t="n">
-        <v>7.3852915763855</v>
+        <v>7.38529300689697</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G83" t="n">
-        <v>6.89400482177734</v>
+        <v>6.89400434494019</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>8.78499984741211</v>
       </c>
       <c r="G85" t="n">
-        <v>7.15777015686035</v>
+        <v>7.15776968002319</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G87" t="n">
-        <v>6.93778085708618</v>
+        <v>6.93778133392334</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>8.14500045776367</v>
       </c>
       <c r="G88" t="n">
-        <v>6.63631677627563</v>
+        <v>6.63631629943848</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>8.00500011444092</v>
       </c>
       <c r="G93" t="n">
-        <v>6.52224779129028</v>
+        <v>6.52224826812744</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G96" t="n">
-        <v>7.21072959899902</v>
+        <v>7.21073007583618</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G100" t="n">
-        <v>7.02333164215088</v>
+        <v>7.02333211898804</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G103" t="n">
-        <v>7.02333164215088</v>
+        <v>7.02333211898804</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G104" t="n">
-        <v>7.03148078918457</v>
+        <v>7.03148031234741</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G106" t="n">
-        <v>7.08851480484009</v>
+        <v>7.08851432800293</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G107" t="n">
-        <v>6.92963361740112</v>
+        <v>6.92963314056396</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>6.89296865463257</v>
+        <v>6.89296913146973</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G112" t="n">
-        <v>6.89296865463257</v>
+        <v>6.89296913146973</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G113" t="n">
-        <v>6.76260566711426</v>
+        <v>6.76260614395142</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G114" t="n">
-        <v>6.6159462928772</v>
+        <v>6.61594676971436</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G115" t="n">
-        <v>6.43669605255127</v>
+        <v>6.43669652938843</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>6.20856094360352</v>
+        <v>6.20856046676636</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>7.75</v>
       </c>
       <c r="G118" t="n">
-        <v>6.31448078155518</v>
+        <v>6.31448125839233</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>6.88482093811035</v>
+        <v>6.88482046127319</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G126" t="n">
-        <v>6.59150362014771</v>
+        <v>6.59150314331055</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G127" t="n">
-        <v>6.6281681060791</v>
+        <v>6.62816905975342</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G132" t="n">
-        <v>6.78704833984375</v>
+        <v>6.78704786300659</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>8.4350004196167</v>
       </c>
       <c r="G135" t="n">
-        <v>6.87260007858276</v>
+        <v>6.87260055541992</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>8.4350004196167</v>
       </c>
       <c r="G136" t="n">
-        <v>6.87260007858276</v>
+        <v>6.87260055541992</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G139" t="n">
-        <v>6.82778787612915</v>
+        <v>6.82778739929199</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G140" t="n">
-        <v>6.76260566711426</v>
+        <v>6.76260614395142</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>8.375</v>
       </c>
       <c r="G141" t="n">
-        <v>6.82371282577515</v>
+        <v>6.8237133026123</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G142" t="n">
-        <v>6.79519605636597</v>
+        <v>6.79519653320312</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>8.32499980926514</v>
       </c>
       <c r="G143" t="n">
-        <v>6.78297519683838</v>
+        <v>6.78297472000122</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G144" t="n">
-        <v>6.79519605636597</v>
+        <v>6.79519653320312</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>8.23499965667725</v>
       </c>
       <c r="G145" t="n">
-        <v>6.70964479446411</v>
+        <v>6.70964527130127</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>8.30500030517578</v>
       </c>
       <c r="G147" t="n">
-        <v>6.76667928695679</v>
+        <v>6.76667881011963</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G150" t="n">
-        <v>6.82778787612915</v>
+        <v>6.82778739929199</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G153" t="n">
-        <v>6.83186101913452</v>
+        <v>6.83186149597168</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>8.375</v>
       </c>
       <c r="G155" t="n">
-        <v>6.82371282577515</v>
+        <v>6.8237133026123</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G157" t="n">
-        <v>6.79519605636597</v>
+        <v>6.79519653320312</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G164" t="n">
-        <v>6.74630975723267</v>
+        <v>6.74631023406982</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G168" t="n">
-        <v>6.83593559265137</v>
+        <v>6.83593606948853</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G169" t="n">
-        <v>6.79519605636597</v>
+        <v>6.79519653320312</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G170" t="n">
-        <v>7.11295652389526</v>
+        <v>7.11295700073242</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G171" t="n">
-        <v>6.93370819091797</v>
+        <v>6.93370771408081</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G174" t="n">
-        <v>6.94185590744019</v>
+        <v>6.94185543060303</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G175" t="n">
-        <v>6.97444534301758</v>
+        <v>6.97444581985474</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G179" t="n">
-        <v>7.14554834365845</v>
+        <v>7.14554882049561</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G180" t="n">
-        <v>7.10481023788452</v>
+        <v>7.10480976104736</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>8.79500007629395</v>
       </c>
       <c r="G182" t="n">
-        <v>7.16591691970825</v>
+        <v>7.16591739654541</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G183" t="n">
-        <v>7.12110471725464</v>
+        <v>7.1211051940918</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G184" t="n">
-        <v>7.19443464279175</v>
+        <v>7.19443511962891</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>9.25</v>
       </c>
       <c r="G186" t="n">
-        <v>7.53663921356201</v>
+        <v>7.53663873672485</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G188" t="n">
-        <v>7.49182558059692</v>
+        <v>7.49182653427124</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G189" t="n">
-        <v>7.30035448074341</v>
+        <v>7.30035543441772</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G190" t="n">
-        <v>7.1699914932251</v>
+        <v>7.16999053955078</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>7.36553716659546</v>
+        <v>7.36553621292114</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.09500026702881</v>
       </c>
       <c r="G197" t="n">
-        <v>7.41034936904907</v>
+        <v>7.41034889221191</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G198" t="n">
-        <v>7.45516061782837</v>
+        <v>7.45516014099121</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>9.29500007629395</v>
       </c>
       <c r="G199" t="n">
-        <v>7.57330322265625</v>
+        <v>7.57330369949341</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G200" t="n">
-        <v>7.63441133499146</v>
+        <v>7.6344108581543</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G201" t="n">
-        <v>7.62626314163208</v>
+        <v>7.6262640953064</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G203" t="n">
-        <v>7.63441133499146</v>
+        <v>7.6344108581543</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G204" t="n">
-        <v>7.59367275238037</v>
+        <v>7.59367227554321</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G205" t="n">
-        <v>7.61811685562134</v>
+        <v>7.61811637878418</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>9.39500045776367</v>
       </c>
       <c r="G206" t="n">
-        <v>7.65478181838989</v>
+        <v>7.65478038787842</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>9.39500045776367</v>
       </c>
       <c r="G209" t="n">
-        <v>7.65478181838989</v>
+        <v>7.65478038787842</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G210" t="n">
-        <v>7.41442203521729</v>
+        <v>7.41442251205444</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G211" t="n">
-        <v>7.41442203521729</v>
+        <v>7.41442251205444</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G214" t="n">
-        <v>7.19443464279175</v>
+        <v>7.19443511962891</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>8.67500019073486</v>
       </c>
       <c r="G216" t="n">
-        <v>7.06814527511597</v>
+        <v>7.06814479827881</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G221" t="n">
-        <v>6.83593559265137</v>
+        <v>6.83593606948853</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G226" t="n">
-        <v>7.44701385498047</v>
+        <v>7.44701480865479</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G228" t="n">
-        <v>7.10481023788452</v>
+        <v>7.10480976104736</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>8.74499988555908</v>
       </c>
       <c r="G230" t="n">
-        <v>7.12517929077148</v>
+        <v>7.12517833709717</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G231" t="n">
-        <v>7.10481023788452</v>
+        <v>7.10480976104736</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G234" t="n">
-        <v>6.9988899230957</v>
+        <v>6.99889039993286</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>8.67500019073486</v>
       </c>
       <c r="G237" t="n">
-        <v>7.06814527511597</v>
+        <v>7.06814479827881</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G240" t="n">
-        <v>7.22702503204346</v>
+        <v>7.22702550888062</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G242" t="n">
-        <v>7.65885400772095</v>
+        <v>7.65885448455811</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G243" t="n">
-        <v>7.71181440353394</v>
+        <v>7.71181392669678</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G244" t="n">
-        <v>7.72403621673584</v>
+        <v>7.72403526306152</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G246" t="n">
-        <v>7.90328598022461</v>
+        <v>7.90328502655029</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>9.76500034332275</v>
       </c>
       <c r="G251" t="n">
-        <v>7.95624542236328</v>
+        <v>7.9562463760376</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G252" t="n">
-        <v>7.90328598022461</v>
+        <v>7.90328502655029</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>9.8149995803833</v>
       </c>
       <c r="G254" t="n">
-        <v>7.99698543548584</v>
+        <v>7.99698448181152</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G259" t="n">
-        <v>8.54695510864258</v>
+        <v>8.54695606231689</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G260" t="n">
-        <v>8.77509117126465</v>
+        <v>8.77509212493896</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G261" t="n">
-        <v>8.67731761932373</v>
+        <v>8.67731857299805</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G262" t="n">
-        <v>8.66102504730225</v>
+        <v>8.66102409362793</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G264" t="n">
-        <v>8.68546772003174</v>
+        <v>8.68546676635742</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G265" t="n">
-        <v>8.84842109680176</v>
+        <v>8.84842014312744</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G266" t="n">
-        <v>8.83212471008301</v>
+        <v>8.83212661743164</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G267" t="n">
-        <v>8.94619369506836</v>
+        <v>8.94619274139404</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G270" t="n">
-        <v>10.0624313354492</v>
+        <v>10.0624303817749</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G272" t="n">
-        <v>9.75281715393066</v>
+        <v>9.75281810760498</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G276" t="n">
-        <v>10.5349988937378</v>
+        <v>10.5349979400635</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G277" t="n">
-        <v>10.5512924194336</v>
+        <v>10.5512943267822</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G278" t="n">
-        <v>10.6409196853638</v>
+        <v>10.6409187316895</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G282" t="n">
-        <v>11.3253259658813</v>
+        <v>11.3253269195557</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>14.5</v>
       </c>
       <c r="G284" t="n">
-        <v>11.8141899108887</v>
+        <v>11.8141889572144</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>15</v>
       </c>
       <c r="G285" t="n">
-        <v>12.2215766906738</v>
+        <v>12.2215757369995</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G290" t="n">
-        <v>13.5252113342285</v>
+        <v>13.5252122879028</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G293" t="n">
-        <v>14.0955495834351</v>
+        <v>14.0955505371094</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G294" t="n">
-        <v>13.5659503936768</v>
+        <v>13.5659494400024</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>15.5</v>
       </c>
       <c r="G298" t="n">
-        <v>12.6289615631104</v>
+        <v>12.6289625167847</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>12.3437919616699</v>
+        <v>12.3437910079956</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G300" t="n">
-        <v>12.9141330718994</v>
+        <v>12.9141321182251</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G301" t="n">
-        <v>12.9711647033691</v>
+        <v>12.9711656570435</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G302" t="n">
-        <v>12.9304265975952</v>
+        <v>12.9304275512695</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G304" t="n">
-        <v>13.0037574768066</v>
+        <v>13.0037565231323</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G306" t="n">
-        <v>12.9874610900879</v>
+        <v>12.9874601364136</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G310" t="n">
-        <v>13.5252113342285</v>
+        <v>13.5252122879028</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G311" t="n">
-        <v>13.7696418762207</v>
+        <v>13.7696409225464</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>17.25</v>
       </c>
       <c r="G313" t="n">
-        <v>14.0548124313354</v>
+        <v>14.0548133850098</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G316" t="n">
-        <v>13.9651880264282</v>
+        <v>13.9651870727539</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G318" t="n">
-        <v>13.8674163818359</v>
+        <v>13.8674154281616</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G319" t="n">
-        <v>13.8755617141724</v>
+        <v>13.8755626678467</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G320" t="n">
-        <v>13.7940864562988</v>
+        <v>13.7940855026245</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G321" t="n">
-        <v>13.7940864562988</v>
+        <v>13.7940855026245</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G327" t="n">
-        <v>13.223744392395</v>
+        <v>13.2237453460693</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G331" t="n">
-        <v>12.6371088027954</v>
+        <v>12.6371097564697</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>12.3030529022217</v>
+        <v>12.303053855896</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G334" t="n">
-        <v>12.2623138427734</v>
+        <v>12.2623147964478</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>15</v>
       </c>
       <c r="G335" t="n">
-        <v>12.2215766906738</v>
+        <v>12.2215757369995</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>15.5</v>
       </c>
       <c r="G337" t="n">
-        <v>12.6289615631104</v>
+        <v>12.6289625167847</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G338" t="n">
-        <v>13.0200510025024</v>
+        <v>13.0200529098511</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G339" t="n">
-        <v>13.0444955825806</v>
+        <v>13.0444965362549</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G340" t="n">
-        <v>12.9385766983032</v>
+        <v>12.9385757446289</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G342" t="n">
-        <v>12.7121925354004</v>
+        <v>12.7121915817261</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G346" t="n">
-        <v>12.9360876083374</v>
+        <v>12.9360885620117</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G351" t="n">
-        <v>12.6375617980957</v>
+        <v>12.6375608444214</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G356" t="n">
-        <v>12.6873159408569</v>
+        <v>12.6873168945312</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G357" t="n">
-        <v>12.6292695999146</v>
+        <v>12.6292686462402</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>15</v>
       </c>
       <c r="G359" t="n">
-        <v>12.4385452270508</v>
+        <v>12.4385442733765</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G365" t="n">
-        <v>12.7536554336548</v>
+        <v>12.7536563873291</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G368" t="n">
-        <v>12.5712242126465</v>
+        <v>12.5712223052979</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G369" t="n">
-        <v>12.4468374252319</v>
+        <v>12.4468383789062</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G370" t="n">
-        <v>12.3390369415283</v>
+        <v>12.3390378952026</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G371" t="n">
-        <v>12.0156345367432</v>
+        <v>12.0156335830688</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G372" t="n">
-        <v>11.7751560211182</v>
+        <v>11.7751550674438</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G373" t="n">
-        <v>11.8746643066406</v>
+        <v>11.8746633529663</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G374" t="n">
-        <v>11.5844316482544</v>
+        <v>11.5844326019287</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G375" t="n">
-        <v>11.4517545700073</v>
+        <v>11.451753616333</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G378" t="n">
-        <v>11.8912496566772</v>
+        <v>11.8912506103516</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>11.7751560211182</v>
+        <v>11.7751550674438</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>11.858078956604</v>
+        <v>11.8580799102783</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G385" t="n">
-        <v>11.4517545700073</v>
+        <v>11.451753616333</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G386" t="n">
-        <v>11.3937082290649</v>
+        <v>11.3937072753906</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G390" t="n">
-        <v>11.3854150772095</v>
+        <v>11.3854141235352</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>11.3190755844116</v>
+        <v>11.3190765380859</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G393" t="n">
-        <v>11.3356609344482</v>
+        <v>11.3356618881226</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>11.2941999435425</v>
+        <v>11.2941989898682</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>13.5</v>
       </c>
       <c r="G397" t="n">
-        <v>11.1946897506714</v>
+        <v>11.1946907043457</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G398" t="n">
-        <v>11.5678482055664</v>
+        <v>11.5678472518921</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G401" t="n">
-        <v>11.7751560211182</v>
+        <v>11.7751550674438</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G402" t="n">
-        <v>11.6839389801025</v>
+        <v>11.6839408874512</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>11.5678482055664</v>
+        <v>11.5678472518921</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G405" t="n">
-        <v>11.6839389801025</v>
+        <v>11.6839408874512</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>15</v>
       </c>
       <c r="G412" t="n">
-        <v>12.4385452270508</v>
+        <v>12.4385442733765</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G413" t="n">
-        <v>12.2229442596436</v>
+        <v>12.2229433059692</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G414" t="n">
-        <v>12.0322189331055</v>
+        <v>12.0322198867798</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G416" t="n">
-        <v>12.2809906005859</v>
+        <v>12.2809896469116</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G417" t="n">
-        <v>12.2395286560059</v>
+        <v>12.2395296096802</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>14.5</v>
       </c>
       <c r="G419" t="n">
-        <v>12.0239267349243</v>
+        <v>12.02392578125</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G421" t="n">
-        <v>11.8995418548584</v>
+        <v>11.8995428085327</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G422" t="n">
-        <v>11.8995418548584</v>
+        <v>11.8995428085327</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G428" t="n">
-        <v>12.3058671951294</v>
+        <v>12.3058681488037</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G430" t="n">
-        <v>12.6375617980957</v>
+        <v>12.6375608444214</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G431" t="n">
-        <v>12.3556213378906</v>
+        <v>12.3556203842163</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G441" t="n">
-        <v>12.1897745132446</v>
+        <v>12.1897735595703</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G444" t="n">
-        <v>12.1151418685913</v>
+        <v>12.1151428222656</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G448" t="n">
-        <v>12.2229442596436</v>
+        <v>12.2229433059692</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G449" t="n">
-        <v>12.1400213241577</v>
+        <v>12.1400203704834</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G450" t="n">
-        <v>12.2229442596436</v>
+        <v>12.2229433059692</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G455" t="n">
-        <v>12.3887910842896</v>
+        <v>12.3887901306152</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>15</v>
       </c>
       <c r="G460" t="n">
-        <v>12.4385452270508</v>
+        <v>12.4385442733765</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>15</v>
       </c>
       <c r="G461" t="n">
-        <v>12.4385452270508</v>
+        <v>12.4385442733765</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G462" t="n">
-        <v>12.3887910842896</v>
+        <v>12.3887901306152</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G463" t="n">
-        <v>12.4717140197754</v>
+        <v>12.4717149734497</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G464" t="n">
-        <v>12.3556213378906</v>
+        <v>12.3556203842163</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G469" t="n">
-        <v>12.5878076553345</v>
+        <v>12.5878086090088</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G471" t="n">
-        <v>12.6292695999146</v>
+        <v>12.6292686462402</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G472" t="n">
-        <v>12.6375617980957</v>
+        <v>12.6375608444214</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>15.25</v>
       </c>
       <c r="G475" t="n">
-        <v>12.6458539962769</v>
+        <v>12.6458549499512</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G477" t="n">
-        <v>12.6375617980957</v>
+        <v>12.6375608444214</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G478" t="n">
-        <v>12.4468374252319</v>
+        <v>12.4468383789062</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G480" t="n">
-        <v>12.7039012908936</v>
+        <v>12.7038993835449</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G482" t="n">
-        <v>12.7702388763428</v>
+        <v>12.7702398300171</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G484" t="n">
-        <v>13.1433973312378</v>
+        <v>13.1433963775635</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G489" t="n">
-        <v>13.5994749069214</v>
+        <v>13.5994758605957</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>16.5</v>
       </c>
       <c r="G492" t="n">
-        <v>13.6824007034302</v>
+        <v>13.6823997497559</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>15.9300003051758</v>
       </c>
       <c r="G497" t="n">
-        <v>13.2097339630127</v>
+        <v>13.2097358703613</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>15.9300003051758</v>
       </c>
       <c r="G498" t="n">
-        <v>13.2097339630127</v>
+        <v>13.2097358703613</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G499" t="n">
-        <v>13.6243524551392</v>
+        <v>13.6243543624878</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G502" t="n">
-        <v>13.4170436859131</v>
+        <v>13.4170455932617</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G504" t="n">
-        <v>13.3258285522461</v>
+        <v>13.3258275985718</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G505" t="n">
-        <v>13.5828905105591</v>
+        <v>13.5828914642334</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G508" t="n">
-        <v>13.1102275848389</v>
+        <v>13.1102266311646</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G509" t="n">
-        <v>13.0438861846924</v>
+        <v>13.0438871383667</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G510" t="n">
-        <v>13.1516876220703</v>
+        <v>13.1516885757446</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G511" t="n">
-        <v>13.3009510040283</v>
+        <v>13.3009519577026</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G519" t="n">
-        <v>13.2180261611938</v>
+        <v>13.2180271148682</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G523" t="n">
-        <v>13.3009510040283</v>
+        <v>13.3009519577026</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G526" t="n">
-        <v>13.3009510040283</v>
+        <v>13.3009519577026</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G528" t="n">
-        <v>13.3009510040283</v>
+        <v>13.3009519577026</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G529" t="n">
-        <v>13.2180261611938</v>
+        <v>13.2180271148682</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G535" t="n">
-        <v>12.7702388763428</v>
+        <v>12.7702398300171</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>12.9360876083374</v>
+        <v>12.9360885620117</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G537" t="n">
-        <v>12.9360876083374</v>
+        <v>12.9360885620117</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G542" t="n">
-        <v>12.8199949264526</v>
+        <v>12.8199939727783</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G546" t="n">
-        <v>13.2511968612671</v>
+        <v>13.2511959075928</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G547" t="n">
-        <v>13.1185188293457</v>
+        <v>13.1185178756714</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G549" t="n">
-        <v>12.8697481155396</v>
+        <v>12.8697490692139</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G552" t="n">
-        <v>12.8199949264526</v>
+        <v>12.8199939727783</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G553" t="n">
-        <v>12.7868251800537</v>
+        <v>12.7868242263794</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G555" t="n">
-        <v>12.6375617980957</v>
+        <v>12.6375608444214</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G556" t="n">
-        <v>12.6375617980957</v>
+        <v>12.6375608444214</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G560" t="n">
-        <v>12.8697481155396</v>
+        <v>12.8697490692139</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G561" t="n">
-        <v>13.0521802902222</v>
+        <v>13.0521793365479</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G562" t="n">
-        <v>13.1516876220703</v>
+        <v>13.1516885757446</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G565" t="n">
-        <v>12.8365793228149</v>
+        <v>12.8365783691406</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G566" t="n">
-        <v>13.0687646865845</v>
+        <v>13.0687656402588</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G569" t="n">
-        <v>13.0521802902222</v>
+        <v>13.0521793365479</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G573" t="n">
-        <v>12.8697481155396</v>
+        <v>12.8697490692139</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G574" t="n">
-        <v>13.0190114974976</v>
+        <v>13.0190105438232</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G576" t="n">
-        <v>12.9360876083374</v>
+        <v>12.9360885620117</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G579" t="n">
-        <v>13.0521802902222</v>
+        <v>13.0521793365479</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G581" t="n">
-        <v>13.0024261474609</v>
+        <v>13.0024271011353</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G582" t="n">
-        <v>13.0521802902222</v>
+        <v>13.0521793365479</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>12.9360876083374</v>
+        <v>12.9360885620117</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G585" t="n">
-        <v>13.0024261474609</v>
+        <v>13.0024271011353</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G587" t="n">
-        <v>13.0687646865845</v>
+        <v>13.0687656402588</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G591" t="n">
-        <v>13.1516876220703</v>
+        <v>13.1516885757446</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G598" t="n">
-        <v>13.4968929290771</v>
+        <v>13.4968938827515</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G599" t="n">
-        <v>13.3439064025879</v>
+        <v>13.3439054489136</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G601" t="n">
-        <v>13.4458980560303</v>
+        <v>13.445897102356</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G602" t="n">
-        <v>13.2589130401611</v>
+        <v>13.2589139938354</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G603" t="n">
-        <v>13.5818862915039</v>
+        <v>13.5818853378296</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G607" t="n">
-        <v>13.1059246063232</v>
+        <v>13.1059255599976</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G608" t="n">
-        <v>13.0209321975708</v>
+        <v>13.0209312438965</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G609" t="n">
-        <v>12.9189405441284</v>
+        <v>12.9189395904541</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G611" t="n">
-        <v>12.7999515533447</v>
+        <v>12.7999505996704</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G612" t="n">
-        <v>13.0209321975708</v>
+        <v>13.0209312438965</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G615" t="n">
-        <v>12.9189405441284</v>
+        <v>12.9189395904541</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G616" t="n">
-        <v>13.8028688430786</v>
+        <v>13.8028678894043</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G617" t="n">
-        <v>13.7518720626831</v>
+        <v>13.7518730163574</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G618" t="n">
-        <v>13.5818862915039</v>
+        <v>13.5818853378296</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G620" t="n">
-        <v>13.4798936843872</v>
+        <v>13.4798946380615</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G632" t="n">
-        <v>13.3269090652466</v>
+        <v>13.3269081115723</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G634" t="n">
-        <v>13.2929105758667</v>
+        <v>13.292911529541</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G635" t="n">
-        <v>13.0889253616333</v>
+        <v>13.0889263153076</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G638" t="n">
-        <v>13.2079181671143</v>
+        <v>13.2079172134399</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G639" t="n">
-        <v>13.1399230957031</v>
+        <v>13.1399221420288</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G640" t="n">
-        <v>12.9699363708496</v>
+        <v>12.9699373245239</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G642" t="n">
-        <v>13.071928024292</v>
+        <v>13.0719289779663</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G645" t="n">
-        <v>12.952938079834</v>
+        <v>12.9529371261597</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G647" t="n">
-        <v>13.071928024292</v>
+        <v>13.0719289779663</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G648" t="n">
-        <v>13.1569223403931</v>
+        <v>13.1569213867188</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G651" t="n">
-        <v>13.0039339065552</v>
+        <v>13.0039348602295</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G653" t="n">
-        <v>12.952938079834</v>
+        <v>12.9529371261597</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G654" t="n">
-        <v>13.0209321975708</v>
+        <v>13.0209312438965</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G655" t="n">
-        <v>12.9699363708496</v>
+        <v>12.9699373245239</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G656" t="n">
-        <v>13.0209321975708</v>
+        <v>13.0209312438965</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G657" t="n">
-        <v>13.1059246063232</v>
+        <v>13.1059255599976</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G659" t="n">
-        <v>12.9699363708496</v>
+        <v>12.9699373245239</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G660" t="n">
-        <v>13.0889253616333</v>
+        <v>13.0889263153076</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G665" t="n">
-        <v>12.9189405441284</v>
+        <v>12.9189395904541</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G668" t="n">
-        <v>12.6809606552124</v>
+        <v>12.6809616088867</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G669" t="n">
-        <v>12.7659549713135</v>
+        <v>12.7659540176392</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G682" t="n">
-        <v>12.9189405441284</v>
+        <v>12.9189395904541</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G683" t="n">
-        <v>12.6809606552124</v>
+        <v>12.6809616088867</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G689" t="n">
-        <v>12.6639623641968</v>
+        <v>12.6639614105225</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G690" t="n">
-        <v>12.7149572372437</v>
+        <v>12.714958190918</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G696" t="n">
-        <v>12.6809606552124</v>
+        <v>12.6809616088867</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G707" t="n">
-        <v>10.2331609725952</v>
+        <v>10.2331600189209</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G708" t="n">
-        <v>10.8451108932495</v>
+        <v>10.8451118469238</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G717" t="n">
-        <v>10.9301042556763</v>
+        <v>10.930103302002</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G720" t="n">
-        <v>10.5221366882324</v>
+        <v>10.5221376419067</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G721" t="n">
-        <v>10.6581268310547</v>
+        <v>10.6581258773804</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G722" t="n">
-        <v>10.5221366882324</v>
+        <v>10.5221376419067</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G728" t="n">
-        <v>10.9301042556763</v>
+        <v>10.930103302002</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G730" t="n">
-        <v>11.3040742874146</v>
+        <v>11.3040733337402</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G732" t="n">
-        <v>11.3210725784302</v>
+        <v>11.3210716247559</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G733" t="n">
-        <v>11.3040742874146</v>
+        <v>11.3040733337402</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G740" t="n">
-        <v>10.3691501617432</v>
+        <v>10.3691492080688</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G743" t="n">
-        <v>10.063175201416</v>
+        <v>10.0631761550903</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G746" t="n">
-        <v>10.5561351776123</v>
+        <v>10.556134223938</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G749" t="n">
-        <v>10.8791074752808</v>
+        <v>10.8791084289551</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G750" t="n">
-        <v>10.6071300506592</v>
+        <v>10.6071310043335</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G752" t="n">
-        <v>10.6071300506592</v>
+        <v>10.6071310043335</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G758" t="n">
-        <v>9.06025695800781</v>
+        <v>9.0602560043335</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G759" t="n">
-        <v>9.09425449371338</v>
+        <v>9.09425354003906</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G762" t="n">
-        <v>9.17924690246582</v>
+        <v>9.17924785614014</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G764" t="n">
-        <v>10.3181533813477</v>
+        <v>10.3181552886963</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G768" t="n">
-        <v>10.6581268310547</v>
+        <v>10.6581258773804</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G769" t="n">
-        <v>10.8451108932495</v>
+        <v>10.8451118469238</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G771" t="n">
-        <v>10.5561351776123</v>
+        <v>10.556134223938</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G773" t="n">
-        <v>10.2671585083008</v>
+        <v>10.2671575546265</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G774" t="n">
-        <v>10.2671585083008</v>
+        <v>10.2671575546265</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G775" t="n">
-        <v>10.2671585083008</v>
+        <v>10.2671575546265</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G779" t="n">
-        <v>10.0971727371216</v>
+        <v>10.0971736907959</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G780" t="n">
-        <v>10.1141700744629</v>
+        <v>10.1141710281372</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G781" t="n">
-        <v>10.1821660995483</v>
+        <v>10.182165145874</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G782" t="n">
-        <v>10.3691501617432</v>
+        <v>10.3691492080688</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G784" t="n">
-        <v>10.2671585083008</v>
+        <v>10.2671575546265</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G787" t="n">
-        <v>10.3181533813477</v>
+        <v>10.3181552886963</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G789" t="n">
-        <v>10.2161626815796</v>
+        <v>10.2161636352539</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G790" t="n">
-        <v>10.1651678085327</v>
+        <v>10.1651668548584</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G791" t="n">
-        <v>10.1141700744629</v>
+        <v>10.1141710281372</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G794" t="n">
-        <v>10.1651678085327</v>
+        <v>10.1651668548584</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G795" t="n">
-        <v>10.1821660995483</v>
+        <v>10.182165145874</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G796" t="n">
-        <v>10.1651678085327</v>
+        <v>10.1651668548584</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G797" t="n">
-        <v>10.2671585083008</v>
+        <v>10.2671575546265</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G798" t="n">
-        <v>10.063175201416</v>
+        <v>10.0631761550903</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G799" t="n">
-        <v>9.94418430328369</v>
+        <v>9.94418525695801</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G801" t="n">
-        <v>10.063175201416</v>
+        <v>10.0631761550903</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G809" t="n">
-        <v>10.1141700744629</v>
+        <v>10.1141710281372</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G810" t="n">
-        <v>9.94418430328369</v>
+        <v>9.94418525695801</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G811" t="n">
-        <v>10.0461769104004</v>
+        <v>10.0461759567261</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G812" t="n">
-        <v>10.063175201416</v>
+        <v>10.0631761550903</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G815" t="n">
-        <v>10.0971727371216</v>
+        <v>10.0971736907959</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G818" t="n">
-        <v>10.8451108932495</v>
+        <v>10.8451118469238</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G822" t="n">
-        <v>10.4881391525269</v>
+        <v>10.4881401062012</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G824" t="n">
-        <v>10.6071300506592</v>
+        <v>10.6071310043335</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G826" t="n">
-        <v>10.5051374435425</v>
+        <v>10.5051383972168</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G827" t="n">
-        <v>10.6581268310547</v>
+        <v>10.6581258773804</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G834" t="n">
-        <v>10.8451108932495</v>
+        <v>10.8451118469238</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G835" t="n">
-        <v>10.5731334686279</v>
+        <v>10.5731325149536</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G841" t="n">
-        <v>10.6581268310547</v>
+        <v>10.6581258773804</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G842" t="n">
-        <v>10.6581268310547</v>
+        <v>10.6581258773804</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G843" t="n">
-        <v>10.5731334686279</v>
+        <v>10.5731325149536</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G846" t="n">
-        <v>10.8961067199707</v>
+        <v>10.8961057662964</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G847" t="n">
-        <v>10.8791074752808</v>
+        <v>10.8791084289551</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G852" t="n">
-        <v>10.3056879043579</v>
+        <v>10.3056888580322</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G853" t="n">
-        <v>10.552321434021</v>
+        <v>10.5523204803467</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G857" t="n">
-        <v>9.91812419891357</v>
+        <v>9.91812515258789</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G858" t="n">
-        <v>9.91812419891357</v>
+        <v>9.91812515258789</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G859" t="n">
-        <v>9.51294326782227</v>
+        <v>9.51294422149658</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G860" t="n">
-        <v>9.54817676544189</v>
+        <v>9.54817771911621</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G861" t="n">
-        <v>9.47770977020264</v>
+        <v>9.47771167755127</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G862" t="n">
-        <v>9.33677768707275</v>
+        <v>9.33677864074707</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G865" t="n">
-        <v>9.70672607421875</v>
+        <v>9.70672702789307</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G866" t="n">
-        <v>9.70672607421875</v>
+        <v>9.70672702789307</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G868" t="n">
-        <v>9.56579399108887</v>
+        <v>9.56579303741455</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G871" t="n">
-        <v>9.51294326782227</v>
+        <v>9.51294422149658</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G872" t="n">
-        <v>9.65387630462646</v>
+        <v>9.65387535095215</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G875" t="n">
-        <v>9.75957584381104</v>
+        <v>9.75957489013672</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G877" t="n">
-        <v>9.77719211578369</v>
+        <v>9.77719306945801</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G879" t="n">
-        <v>9.83004188537598</v>
+        <v>9.83004093170166</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G880" t="n">
-        <v>10.0414400100708</v>
+        <v>10.0414409637451</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G883" t="n">
-        <v>9.86527538299561</v>
+        <v>9.86527442932129</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G886" t="n">
-        <v>9.75957584381104</v>
+        <v>9.75957489013672</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G887" t="n">
-        <v>9.75957584381104</v>
+        <v>9.75957489013672</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G888" t="n">
-        <v>9.70672607421875</v>
+        <v>9.70672702789307</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G889" t="n">
-        <v>9.83004188537598</v>
+        <v>9.83004093170166</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G895" t="n">
-        <v>9.88289070129395</v>
+        <v>9.88289165496826</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G897" t="n">
-        <v>10.0590572357178</v>
+        <v>10.0590562820435</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G901" t="n">
-        <v>10.1647567749023</v>
+        <v>10.164755821228</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G902" t="n">
-        <v>10.3409223556519</v>
+        <v>10.3409214019775</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G904" t="n">
-        <v>10.4642381668091</v>
+        <v>10.4642391204834</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G906" t="n">
-        <v>10.3409223556519</v>
+        <v>10.3409214019775</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G908" t="n">
-        <v>10.2880716323853</v>
+        <v>10.2880725860596</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G909" t="n">
-        <v>10.3056879043579</v>
+        <v>10.3056888580322</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G911" t="n">
-        <v>10.3056879043579</v>
+        <v>10.3056888580322</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G912" t="n">
-        <v>10.2880716323853</v>
+        <v>10.2880725860596</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G916" t="n">
-        <v>10.1647567749023</v>
+        <v>10.164755821228</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G919" t="n">
-        <v>10.0414400100708</v>
+        <v>10.0414409637451</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G923" t="n">
-        <v>10.2880716323853</v>
+        <v>10.2880725860596</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G924" t="n">
-        <v>10.2880716323853</v>
+        <v>10.2880725860596</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G926" t="n">
-        <v>10.3056879043579</v>
+        <v>10.3056888580322</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G927" t="n">
-        <v>10.3056879043579</v>
+        <v>10.3056888580322</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G929" t="n">
-        <v>10.2880716323853</v>
+        <v>10.2880725860596</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G931" t="n">
-        <v>10.4818534851074</v>
+        <v>10.4818544387817</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G933" t="n">
-        <v>10.3409223556519</v>
+        <v>10.3409214019775</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G934" t="n">
-        <v>10.552321434021</v>
+        <v>10.5523204803467</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G938" t="n">
-        <v>10.6404037475586</v>
+        <v>10.6404027938843</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G940" t="n">
-        <v>10.8694181442261</v>
+        <v>10.8694190979004</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G943" t="n">
-        <v>10.8870344161987</v>
+        <v>10.887035369873</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G944" t="n">
-        <v>10.9046516418457</v>
+        <v>10.90465259552</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G946" t="n">
-        <v>10.8694181442261</v>
+        <v>10.8694190979004</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G947" t="n">
-        <v>10.9046516418457</v>
+        <v>10.90465259552</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G954" t="n">
-        <v>10.7461032867432</v>
+        <v>10.7461023330688</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G956" t="n">
-        <v>10.4818534851074</v>
+        <v>10.4818544387817</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G961" t="n">
-        <v>10.3409223556519</v>
+        <v>10.3409214019775</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G966" t="n">
-        <v>10.2880716323853</v>
+        <v>10.2880725860596</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G967" t="n">
-        <v>10.3233051300049</v>
+        <v>10.3233060836792</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G968" t="n">
-        <v>10.2880716323853</v>
+        <v>10.2880725860596</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G969" t="n">
-        <v>10.3056879043579</v>
+        <v>10.3056888580322</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G970" t="n">
-        <v>10.3056879043579</v>
+        <v>10.3056888580322</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G971" t="n">
-        <v>10.3056879043579</v>
+        <v>10.3056888580322</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G973" t="n">
-        <v>10.3056879043579</v>
+        <v>10.3056888580322</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G974" t="n">
-        <v>10.3056879043579</v>
+        <v>10.3056888580322</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G976" t="n">
-        <v>10.3056879043579</v>
+        <v>10.3056888580322</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G977" t="n">
-        <v>10.3409223556519</v>
+        <v>10.3409214019775</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G978" t="n">
-        <v>10.3056879043579</v>
+        <v>10.3056888580322</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G985" t="n">
-        <v>10.605170249939</v>
+        <v>10.6051692962646</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G987" t="n">
-        <v>10.5875539779663</v>
+        <v>10.5875549316406</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G988" t="n">
-        <v>10.6404037475586</v>
+        <v>10.6404027938843</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G990" t="n">
-        <v>10.4290046691895</v>
+        <v>10.4290056228638</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G991" t="n">
-        <v>10.5347051620483</v>
+        <v>10.534704208374</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G993" t="n">
-        <v>10.6404037475586</v>
+        <v>10.6404027938843</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G994" t="n">
-        <v>10.7461032867432</v>
+        <v>10.7461023330688</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G995" t="n">
-        <v>10.5875539779663</v>
+        <v>10.5875549316406</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G996" t="n">
-        <v>10.6932525634766</v>
+        <v>10.6932544708252</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1003" t="n">
-        <v>10.5875539779663</v>
+        <v>10.5875549316406</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1010" t="n">
-        <v>10.552321434021</v>
+        <v>10.5523204803467</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1013" t="n">
-        <v>10.605170249939</v>
+        <v>10.6051692962646</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1017" t="n">
-        <v>10.605170249939</v>
+        <v>10.6051692962646</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>10.4818534851074</v>
+        <v>10.4818544387817</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1021" t="n">
-        <v>10.605170249939</v>
+        <v>10.6051692962646</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1022" t="n">
-        <v>10.5875539779663</v>
+        <v>10.5875549316406</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G1023" t="n">
-        <v>10.6404037475586</v>
+        <v>10.6404027938843</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1024" t="n">
-        <v>10.605170249939</v>
+        <v>10.6051692962646</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1029" t="n">
-        <v>10.552321434021</v>
+        <v>10.5523204803467</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G1030" t="n">
-        <v>10.4642381668091</v>
+        <v>10.4642391204834</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G1031" t="n">
-        <v>10.4642381668091</v>
+        <v>10.4642391204834</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1036" t="n">
-        <v>10.2880716323853</v>
+        <v>10.2880725860596</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1045" t="n">
-        <v>10.2880716323853</v>
+        <v>10.2880725860596</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1046" t="n">
-        <v>10.1647567749023</v>
+        <v>10.164755821228</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1049" t="n">
-        <v>10.0414400100708</v>
+        <v>10.0414409637451</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G1052" t="n">
-        <v>9.91812419891357</v>
+        <v>9.91812515258789</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G1055" t="n">
-        <v>9.65387630462646</v>
+        <v>9.65387535095215</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G1061" t="n">
-        <v>7.86579465866089</v>
+        <v>7.86579561233521</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1062" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1064" t="n">
-        <v>6.69429349899292</v>
+        <v>6.69429302215576</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G1066" t="n">
-        <v>5.78704071044922</v>
+        <v>5.78704118728638</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G1068" t="n">
-        <v>6.15698862075806</v>
+        <v>6.1569881439209</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1069" t="n">
-        <v>6.13056373596191</v>
+        <v>6.13056421279907</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G1070" t="n">
-        <v>6.15698862075806</v>
+        <v>6.1569881439209</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1073" t="n">
-        <v>6.74714326858521</v>
+        <v>6.74714279174805</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1077" t="n">
-        <v>7.03781652450562</v>
+        <v>7.03781604766846</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G1078" t="n">
-        <v>6.791184425354</v>
+        <v>6.79118490219116</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1086" t="n">
-        <v>7.09947538375854</v>
+        <v>7.09947490692139</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1090" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1091" t="n">
-        <v>7.41657209396362</v>
+        <v>7.41657257080078</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1099" t="n">
-        <v>7.20517444610596</v>
+        <v>7.2051739692688</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1104" t="n">
-        <v>6.99377489089966</v>
+        <v>6.99377536773682</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1109" t="n">
-        <v>6.8176097869873</v>
+        <v>6.81760931015015</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1117" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1118" t="n">
-        <v>7.24040746688843</v>
+        <v>7.24040699005127</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1121" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1128" t="n">
-        <v>7.69843721389771</v>
+        <v>7.69843769073486</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1129" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1133" t="n">
-        <v>8.22693538665771</v>
+        <v>8.2269344329834</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G1135" t="n">
-        <v>7.89222002029419</v>
+        <v>7.89221954345703</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1137" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1138" t="n">
-        <v>7.76890325546265</v>
+        <v>7.7689037322998</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G1140" t="n">
-        <v>7.85698699951172</v>
+        <v>7.8569860458374</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1141" t="n">
-        <v>7.66320466995239</v>
+        <v>7.66320419311523</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G1142" t="n">
-        <v>7.50465631484985</v>
+        <v>7.5046558380127</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1143" t="n">
-        <v>7.57512140274048</v>
+        <v>7.57512235641479</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1144" t="n">
-        <v>7.46942186355591</v>
+        <v>7.46942234039307</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>8.5</v>
       </c>
       <c r="G1145" t="n">
-        <v>7.48703908920288</v>
+        <v>7.48703956604004</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1146" t="n">
-        <v>7.34610652923584</v>
+        <v>7.346107006073</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1147" t="n">
-        <v>7.45180654525757</v>
+        <v>7.45180606842041</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1148" t="n">
-        <v>7.4341893196106</v>
+        <v>7.43418884277344</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>8.5</v>
       </c>
       <c r="G1149" t="n">
-        <v>7.48703908920288</v>
+        <v>7.48703956604004</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1150" t="n">
-        <v>7.45180654525757</v>
+        <v>7.45180606842041</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1151" t="n">
-        <v>7.46942186355591</v>
+        <v>7.46942234039307</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1153" t="n">
-        <v>7.57512140274048</v>
+        <v>7.57512235641479</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1155" t="n">
-        <v>7.69843721389771</v>
+        <v>7.69843769073486</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>8.5</v>
       </c>
       <c r="G1156" t="n">
-        <v>7.48703908920288</v>
+        <v>7.48703956604004</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1158" t="n">
-        <v>7.46942186355591</v>
+        <v>7.46942234039307</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1159" t="n">
-        <v>7.4341893196106</v>
+        <v>7.43418884277344</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1160" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1161" t="n">
-        <v>7.39895534515381</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1162" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1163" t="n">
-        <v>7.39895534515381</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1165" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1166" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1167" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1168" t="n">
-        <v>7.34610652923584</v>
+        <v>7.346107006073</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1170" t="n">
-        <v>7.46942186355591</v>
+        <v>7.46942234039307</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1172" t="n">
-        <v>7.39895534515381</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1173" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1174" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1184" t="n">
-        <v>6.8176097869873</v>
+        <v>6.81760931015015</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1185" t="n">
-        <v>6.90569305419922</v>
+        <v>6.90569257736206</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1186" t="n">
-        <v>6.78237581253052</v>
+        <v>6.78237628936768</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1187" t="n">
-        <v>6.78237581253052</v>
+        <v>6.78237628936768</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1188" t="n">
-        <v>6.76476001739502</v>
+        <v>6.76475954055786</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1193" t="n">
-        <v>6.39481210708618</v>
+        <v>6.39481258392334</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1194" t="n">
-        <v>6.35957908630371</v>
+        <v>6.35957860946655</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1195" t="n">
-        <v>6.21864652633667</v>
+        <v>6.21864604949951</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1196" t="n">
-        <v>6.21864652633667</v>
+        <v>6.21864604949951</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1198" t="n">
-        <v>6.1129469871521</v>
+        <v>6.11294746398926</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1200" t="n">
-        <v>5.81346559524536</v>
+        <v>5.8134651184082</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1205" t="n">
-        <v>5.81346559524536</v>
+        <v>5.8134651184082</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1206" t="n">
-        <v>5.81346559524536</v>
+        <v>5.8134651184082</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1207" t="n">
-        <v>5.81346559524536</v>
+        <v>5.8134651184082</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1209" t="n">
-        <v>5.81346559524536</v>
+        <v>5.8134651184082</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1210" t="n">
-        <v>5.81346559524536</v>
+        <v>5.8134651184082</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1211" t="n">
-        <v>5.90154790878296</v>
+        <v>5.90154838562012</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1213" t="n">
-        <v>5.90154790878296</v>
+        <v>5.90154838562012</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1214" t="n">
-        <v>5.90154790878296</v>
+        <v>5.90154838562012</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1215" t="n">
-        <v>5.86631536483765</v>
+        <v>5.86631488800049</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G1216" t="n">
-        <v>5.83108139038086</v>
+        <v>5.83108186721802</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1223" t="n">
-        <v>5.44351720809937</v>
+        <v>5.44351768493652</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G1225" t="n">
-        <v>5.30258512496948</v>
+        <v>5.30258464813232</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1226" t="n">
-        <v>5.26735258102417</v>
+        <v>5.26735210418701</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1227" t="n">
-        <v>5.0207200050354</v>
+        <v>5.02072048187256</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1229" t="n">
-        <v>4.91502094268799</v>
+        <v>4.91502046585083</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1230" t="n">
-        <v>5.16165256500244</v>
+        <v>5.1616530418396</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1233" t="n">
-        <v>5.47875118255615</v>
+        <v>5.47875070571899</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1236" t="n">
-        <v>5.81346559524536</v>
+        <v>5.8134651184082</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1240" t="n">
-        <v>6.35957908630371</v>
+        <v>6.35957860946655</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1246" t="n">
-        <v>7.69843721389771</v>
+        <v>7.69843769073486</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1247" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G1250" t="n">
-        <v>7.50465631484985</v>
+        <v>7.5046558380127</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1251" t="n">
-        <v>7.46942186355591</v>
+        <v>7.46942234039307</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1252" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1254" t="n">
-        <v>7.45180654525757</v>
+        <v>7.45180606842041</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G1255" t="n">
-        <v>7.64558887481689</v>
+        <v>7.64558792114258</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1256" t="n">
-        <v>7.68082189559937</v>
+        <v>7.68082141876221</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1257" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1258" t="n">
-        <v>7.57512140274048</v>
+        <v>7.57512235641479</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1259" t="n">
-        <v>7.76890325546265</v>
+        <v>7.7689037322998</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1260" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1261" t="n">
-        <v>7.68082189559937</v>
+        <v>7.68082141876221</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1262" t="n">
-        <v>7.68082189559937</v>
+        <v>7.68082141876221</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1263" t="n">
-        <v>7.80413675308228</v>
+        <v>7.80413722991943</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1265" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1266" t="n">
-        <v>7.39895534515381</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1267" t="n">
-        <v>7.45180654525757</v>
+        <v>7.45180606842041</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1268" t="n">
-        <v>7.46942186355591</v>
+        <v>7.46942234039307</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>8.5</v>
       </c>
       <c r="G1269" t="n">
-        <v>7.48703908920288</v>
+        <v>7.48703956604004</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1270" t="n">
-        <v>7.46942186355591</v>
+        <v>7.46942234039307</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G1272" t="n">
-        <v>7.50465631484985</v>
+        <v>7.5046558380127</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G1273" t="n">
-        <v>7.50465631484985</v>
+        <v>7.5046558380127</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1274" t="n">
-        <v>7.45180654525757</v>
+        <v>7.45180606842041</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1275" t="n">
-        <v>7.34610652923584</v>
+        <v>7.346107006073</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>8.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>7.48703908920288</v>
+        <v>7.48703956604004</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>8.5</v>
       </c>
       <c r="G1277" t="n">
-        <v>7.48703908920288</v>
+        <v>7.48703956604004</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1281" t="n">
-        <v>7.20517444610596</v>
+        <v>7.2051739692688</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1284" t="n">
-        <v>6.99377489089966</v>
+        <v>6.99377536773682</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1286" t="n">
-        <v>6.78237581253052</v>
+        <v>6.78237628936768</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1290" t="n">
-        <v>6.8176097869873</v>
+        <v>6.81760931015015</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1291" t="n">
-        <v>6.74714326858521</v>
+        <v>6.74714279174805</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1292" t="n">
-        <v>6.76476001739502</v>
+        <v>6.76475954055786</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1297" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1298" t="n">
-        <v>7.24040746688843</v>
+        <v>7.24040699005127</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1301" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1303" t="n">
-        <v>7.09947538375854</v>
+        <v>7.09947490692139</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1309" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1310" t="n">
-        <v>7.15232419967651</v>
+        <v>7.15232372283936</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1311" t="n">
-        <v>7.34610652923584</v>
+        <v>7.346107006073</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1312" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1313" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1314" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1317" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1319" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1320" t="n">
-        <v>7.24040746688843</v>
+        <v>7.24040699005127</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1321" t="n">
-        <v>7.34610652923584</v>
+        <v>7.346107006073</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1322" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1323" t="n">
-        <v>7.34610652923584</v>
+        <v>7.346107006073</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G1328" t="n">
-        <v>8.06838607788086</v>
+        <v>8.06838512420654</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G1330" t="n">
-        <v>8.06838607788086</v>
+        <v>8.06838512420654</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1331" t="n">
-        <v>8.19170093536377</v>
+        <v>8.19170188903809</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G1333" t="n">
-        <v>8.61449909210205</v>
+        <v>8.61449813842773</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1338" t="n">
-        <v>8.77304840087891</v>
+        <v>8.77304744720459</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G1342" t="n">
-        <v>8.50879955291748</v>
+        <v>8.50879859924316</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1343" t="n">
-        <v>8.52641582489014</v>
+        <v>8.52641677856445</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1352" t="n">
-        <v>8.52641582489014</v>
+        <v>8.52641677856445</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1356" t="n">
-        <v>8.73781490325928</v>
+        <v>8.73781394958496</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1358" t="n">
-        <v>8.77304840087891</v>
+        <v>8.77304744720459</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1359" t="n">
-        <v>8.79066371917725</v>
+        <v>8.79066467285156</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1360" t="n">
-        <v>8.64973258972168</v>
+        <v>8.64973163604736</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1362" t="n">
-        <v>8.77304840087891</v>
+        <v>8.77304744720459</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1363" t="n">
-        <v>8.73781490325928</v>
+        <v>8.73781394958496</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1364" t="n">
-        <v>8.77304840087891</v>
+        <v>8.77304744720459</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1369" t="n">
-        <v>8.68496417999268</v>
+        <v>8.68496513366699</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1373" t="n">
-        <v>8.79066371917725</v>
+        <v>8.79066467285156</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1376" t="n">
-        <v>9.16061210632324</v>
+        <v>9.16061115264893</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1380" t="n">
-        <v>9.20465278625488</v>
+        <v>9.2046537399292</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1381" t="n">
-        <v>9.42486095428467</v>
+        <v>9.42486000061035</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1382" t="n">
-        <v>10.0414400100708</v>
+        <v>10.0414409637451</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1383" t="n">
-        <v>10.0414400100708</v>
+        <v>10.0414409637451</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1384" t="n">
-        <v>10.0414400100708</v>
+        <v>10.0414409637451</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1387" t="n">
-        <v>9.77719211578369</v>
+        <v>9.77719306945801</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1390" t="n">
-        <v>9.51294326782227</v>
+        <v>9.51294422149658</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1392" t="n">
-        <v>9.42486095428467</v>
+        <v>9.42486000061035</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1395" t="n">
-        <v>9.20465278625488</v>
+        <v>9.2046537399292</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1396" t="n">
-        <v>9.16061210632324</v>
+        <v>9.16061115264893</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1401" t="n">
-        <v>9.16061210632324</v>
+        <v>9.16061115264893</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1403" t="n">
-        <v>9.33677768707275</v>
+        <v>9.33677864074707</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1404" t="n">
-        <v>9.16061210632324</v>
+        <v>9.16061115264893</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1410" t="n">
-        <v>8.68496417999268</v>
+        <v>8.68496513366699</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1421" t="n">
-        <v>8.77304840087891</v>
+        <v>8.77304744720459</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1423" t="n">
-        <v>8.79066371917725</v>
+        <v>8.79066467285156</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1438" t="n">
-        <v>8.79066371917725</v>
+        <v>8.79066467285156</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1440" t="n">
-        <v>8.79066371917725</v>
+        <v>8.79066467285156</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1441" t="n">
-        <v>8.77304840087891</v>
+        <v>8.77304744720459</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1442" t="n">
-        <v>8.73781490325928</v>
+        <v>8.73781394958496</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1443" t="n">
-        <v>8.73781490325928</v>
+        <v>8.73781394958496</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1444" t="n">
-        <v>8.73781490325928</v>
+        <v>8.73781394958496</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1449" t="n">
-        <v>8.73781490325928</v>
+        <v>8.73781394958496</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1460" t="n">
-        <v>8.77304840087891</v>
+        <v>8.77304744720459</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1461" t="n">
-        <v>8.77304840087891</v>
+        <v>8.77304744720459</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1462" t="n">
-        <v>8.64973258972168</v>
+        <v>8.64973163604736</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1464" t="n">
-        <v>8.73781490325928</v>
+        <v>8.73781394958496</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1465" t="n">
-        <v>8.66734886169434</v>
+        <v>8.66734790802002</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1466" t="n">
-        <v>8.68496417999268</v>
+        <v>8.68496513366699</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1467" t="n">
-        <v>8.68496417999268</v>
+        <v>8.68496513366699</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1470" t="n">
-        <v>8.59688282012939</v>
+        <v>8.59688377380371</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G1471" t="n">
-        <v>8.61449909210205</v>
+        <v>8.61449813842773</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1473" t="n">
-        <v>8.77304840087891</v>
+        <v>8.77304744720459</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G1474" t="n">
-        <v>8.61449909210205</v>
+        <v>8.61449813842773</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1476" t="n">
-        <v>8.59688282012939</v>
+        <v>8.59688377380371</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1478" t="n">
-        <v>8.79066371917725</v>
+        <v>8.79066467285156</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G1480" t="n">
-        <v>8.61449909210205</v>
+        <v>8.61449813842773</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1481" t="n">
-        <v>8.59688282012939</v>
+        <v>8.59688377380371</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1482" t="n">
-        <v>8.59688282012939</v>
+        <v>8.59688377380371</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1483" t="n">
-        <v>8.52641582489014</v>
+        <v>8.52641677856445</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1484" t="n">
-        <v>8.64973258972168</v>
+        <v>8.64973163604736</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1485" t="n">
-        <v>8.56164932250977</v>
+        <v>8.56165027618408</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1486" t="n">
-        <v>8.56164932250977</v>
+        <v>8.56165027618408</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1487" t="n">
-        <v>8.59688282012939</v>
+        <v>8.59688377380371</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G1488" t="n">
-        <v>8.50879955291748</v>
+        <v>8.50879859924316</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1489" t="n">
-        <v>8.56164932250977</v>
+        <v>8.56165027618408</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1491" t="n">
-        <v>8.56164932250977</v>
+        <v>8.56165027618408</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1494" t="n">
-        <v>8.52641582489014</v>
+        <v>8.52641677856445</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1495" t="n">
-        <v>8.52641582489014</v>
+        <v>8.52641677856445</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1497" t="n">
-        <v>8.13885116577148</v>
+        <v>8.1388521194458</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G1500" t="n">
-        <v>7.99791860580444</v>
+        <v>7.9979190826416</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G1501" t="n">
-        <v>7.98030233383179</v>
+        <v>7.9803032875061</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1502" t="n">
-        <v>8.12123489379883</v>
+        <v>8.12123584747314</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G1503" t="n">
-        <v>7.89222002029419</v>
+        <v>7.89221954345703</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1505" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G1506" t="n">
-        <v>7.89222002029419</v>
+        <v>7.89221954345703</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1507" t="n">
-        <v>7.80413675308228</v>
+        <v>7.80413722991943</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G1508" t="n">
-        <v>7.89222002029419</v>
+        <v>7.89221954345703</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1509" t="n">
-        <v>7.76890325546265</v>
+        <v>7.7689037322998</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G1510" t="n">
-        <v>7.96268606185913</v>
+        <v>7.96268558502197</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G1511" t="n">
-        <v>7.99791860580444</v>
+        <v>7.9979190826416</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G1513" t="n">
-        <v>8.06838607788086</v>
+        <v>8.06838512420654</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G1514" t="n">
-        <v>7.96268606185913</v>
+        <v>7.96268558502197</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1515" t="n">
-        <v>7.94507026672363</v>
+        <v>7.94506978988647</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G1516" t="n">
-        <v>7.89222002029419</v>
+        <v>7.89221954345703</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G1517" t="n">
-        <v>7.85698699951172</v>
+        <v>7.8569860458374</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1519" t="n">
-        <v>7.82175445556641</v>
+        <v>7.82175397872925</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G1520" t="n">
-        <v>7.89222002029419</v>
+        <v>7.89221954345703</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1521" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1523" t="n">
-        <v>7.76890325546265</v>
+        <v>7.7689037322998</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1524" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1525" t="n">
-        <v>7.59273767471313</v>
+        <v>7.59273862838745</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1526" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G1527" t="n">
-        <v>7.99791860580444</v>
+        <v>7.9979190826416</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1532" t="n">
-        <v>8.22693538665771</v>
+        <v>8.2269344329834</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1536" t="n">
-        <v>8.19170093536377</v>
+        <v>8.19170188903809</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1537" t="n">
-        <v>8.19170093536377</v>
+        <v>8.19170188903809</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1542" t="n">
-        <v>8.0507698059082</v>
+        <v>8.05076885223389</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1544" t="n">
-        <v>8.12123489379883</v>
+        <v>8.12123584747314</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1546" t="n">
-        <v>7.94507026672363</v>
+        <v>7.94506978988647</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1547" t="n">
-        <v>8.0507698059082</v>
+        <v>8.05076885223389</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1548" t="n">
-        <v>8.0507698059082</v>
+        <v>8.05076885223389</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G1552" t="n">
-        <v>7.96268606185913</v>
+        <v>7.96268558502197</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G1553" t="n">
-        <v>7.96268606185913</v>
+        <v>7.96268558502197</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1556" t="n">
-        <v>8.19170093536377</v>
+        <v>8.19170188903809</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1557" t="n">
-        <v>7.94507026672363</v>
+        <v>7.94506978988647</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1559" t="n">
-        <v>8.12123489379883</v>
+        <v>8.12123584747314</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1562" t="n">
-        <v>8.13885116577148</v>
+        <v>8.1388521194458</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G1563" t="n">
-        <v>8.06838607788086</v>
+        <v>8.06838512420654</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G1564" t="n">
-        <v>7.96268606185913</v>
+        <v>7.96268558502197</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G1567" t="n">
-        <v>7.85698699951172</v>
+        <v>7.8569860458374</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1568" t="n">
-        <v>7.68082189559937</v>
+        <v>7.68082141876221</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1571" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1574" t="n">
-        <v>7.39895534515381</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>8.5</v>
       </c>
       <c r="G1575" t="n">
-        <v>7.48703908920288</v>
+        <v>7.48703956604004</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1576" t="n">
-        <v>7.46942186355591</v>
+        <v>7.46942234039307</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1577" t="n">
-        <v>7.4341893196106</v>
+        <v>7.43418884277344</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>8.5</v>
       </c>
       <c r="G1578" t="n">
-        <v>7.48703908920288</v>
+        <v>7.48703956604004</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1580" t="n">
-        <v>7.68082189559937</v>
+        <v>7.68082141876221</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1581" t="n">
-        <v>7.57512140274048</v>
+        <v>7.57512235641479</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1582" t="n">
-        <v>7.4341893196106</v>
+        <v>7.43418884277344</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1583" t="n">
-        <v>7.57512140274048</v>
+        <v>7.57512235641479</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1585" t="n">
-        <v>7.57512140274048</v>
+        <v>7.57512235641479</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1587" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1588" t="n">
-        <v>7.80413675308228</v>
+        <v>7.80413722991943</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1589" t="n">
-        <v>7.80413675308228</v>
+        <v>7.80413722991943</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1592" t="n">
-        <v>7.69843721389771</v>
+        <v>7.69843769073486</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1593" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1594" t="n">
-        <v>7.76890325546265</v>
+        <v>7.7689037322998</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1596" t="n">
-        <v>7.82175445556641</v>
+        <v>7.82175397872925</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1597" t="n">
-        <v>7.69843721389771</v>
+        <v>7.69843769073486</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1598" t="n">
-        <v>7.68082189559937</v>
+        <v>7.68082141876221</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G1601" t="n">
-        <v>7.64558887481689</v>
+        <v>7.64558792114258</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1602" t="n">
-        <v>7.66320466995239</v>
+        <v>7.66320419311523</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1603" t="n">
-        <v>7.59273767471313</v>
+        <v>7.59273862838745</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1604" t="n">
-        <v>7.59273767471313</v>
+        <v>7.59273862838745</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>8.5</v>
       </c>
       <c r="G1606" t="n">
-        <v>7.48703908920288</v>
+        <v>7.48703956604004</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1608" t="n">
-        <v>7.20517444610596</v>
+        <v>7.2051739692688</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1610" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>8.5</v>
       </c>
       <c r="G1612" t="n">
-        <v>7.48703908920288</v>
+        <v>7.48703956604004</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1613" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1614" t="n">
-        <v>7.34610652923584</v>
+        <v>7.346107006073</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1616" t="n">
-        <v>7.59273767471313</v>
+        <v>7.59273862838745</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1617" t="n">
-        <v>7.69843721389771</v>
+        <v>7.69843769073486</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1618" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1620" t="n">
-        <v>7.80413675308228</v>
+        <v>7.80413722991943</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1623" t="n">
-        <v>7.68082189559937</v>
+        <v>7.68082141876221</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1624" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1626" t="n">
-        <v>7.62797164916992</v>
+        <v>7.62797069549561</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1630" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1631" t="n">
-        <v>7.80413675308228</v>
+        <v>7.80413722991943</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1633" t="n">
-        <v>7.94507026672363</v>
+        <v>7.94506978988647</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1634" t="n">
-        <v>8.19170093536377</v>
+        <v>8.19170188903809</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1636" t="n">
-        <v>8.0507698059082</v>
+        <v>8.05076885223389</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G1637" t="n">
-        <v>8.06838607788086</v>
+        <v>8.06838512420654</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1640" t="n">
-        <v>7.57512140274048</v>
+        <v>7.57512235641479</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1642" t="n">
-        <v>7.62797164916992</v>
+        <v>7.62797069549561</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1643" t="n">
-        <v>7.46942186355591</v>
+        <v>7.46942234039307</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>8.5</v>
       </c>
       <c r="G1644" t="n">
-        <v>7.48703908920288</v>
+        <v>7.48703956604004</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1645" t="n">
-        <v>7.45180654525757</v>
+        <v>7.45180606842041</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1647" t="n">
-        <v>7.57512140274048</v>
+        <v>7.57512235641479</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1650" t="n">
-        <v>7.4341893196106</v>
+        <v>7.43418884277344</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>8.5</v>
       </c>
       <c r="G1651" t="n">
-        <v>7.48703908920288</v>
+        <v>7.48703956604004</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1652" t="n">
-        <v>7.45180654525757</v>
+        <v>7.45180606842041</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1653" t="n">
-        <v>7.39895534515381</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1654" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1655" t="n">
-        <v>7.34610652923584</v>
+        <v>7.346107006073</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1658" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1660" t="n">
-        <v>7.41657209396362</v>
+        <v>7.41657257080078</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1662" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1663" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1666" t="n">
-        <v>7.4341893196106</v>
+        <v>7.43418884277344</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1671" t="n">
-        <v>7.39895534515381</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1672" t="n">
-        <v>7.15232419967651</v>
+        <v>7.15232372283936</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1673" t="n">
-        <v>7.39895534515381</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1675" t="n">
-        <v>7.4341893196106</v>
+        <v>7.43418884277344</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1676" t="n">
-        <v>7.46942186355591</v>
+        <v>7.46942234039307</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1677" t="n">
-        <v>7.45180654525757</v>
+        <v>7.45180606842041</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1679" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1680" t="n">
-        <v>7.39895534515381</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1681" t="n">
-        <v>7.39895534515381</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1682" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1683" t="n">
-        <v>7.41657209396362</v>
+        <v>7.41657257080078</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>8.5</v>
       </c>
       <c r="G1684" t="n">
-        <v>7.48703908920288</v>
+        <v>7.48703956604004</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1685" t="n">
-        <v>7.46942186355591</v>
+        <v>7.46942234039307</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1686" t="n">
-        <v>7.46942186355591</v>
+        <v>7.46942234039307</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1687" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1688" t="n">
-        <v>7.24040746688843</v>
+        <v>7.24040699005127</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1689" t="n">
-        <v>7.20517444610596</v>
+        <v>7.2051739692688</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1690" t="n">
-        <v>7.15232419967651</v>
+        <v>7.15232372283936</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1693" t="n">
-        <v>6.87045907974243</v>
+        <v>6.87045955657959</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1694" t="n">
-        <v>6.87045907974243</v>
+        <v>6.87045955657959</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1695" t="n">
-        <v>6.88807582855225</v>
+        <v>6.8880763053894</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1696" t="n">
-        <v>6.76476001739502</v>
+        <v>6.76475954055786</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1697" t="n">
-        <v>6.87045907974243</v>
+        <v>6.87045955657959</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1699" t="n">
-        <v>6.87045907974243</v>
+        <v>6.87045955657959</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1700" t="n">
-        <v>6.87045907974243</v>
+        <v>6.87045955657959</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1701" t="n">
-        <v>6.76476001739502</v>
+        <v>6.76475954055786</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1703" t="n">
-        <v>6.76476001739502</v>
+        <v>6.76475954055786</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1704" t="n">
-        <v>6.87045907974243</v>
+        <v>6.87045955657959</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1705" t="n">
-        <v>6.78237581253052</v>
+        <v>6.78237628936768</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1708" t="n">
-        <v>6.69429349899292</v>
+        <v>6.69429302215576</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1710" t="n">
-        <v>6.27149629592896</v>
+        <v>6.2714958190918</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1713" t="n">
-        <v>6.18341302871704</v>
+        <v>6.1834135055542</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1714" t="n">
-        <v>6.27149629592896</v>
+        <v>6.2714958190918</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1715" t="n">
-        <v>6.39481210708618</v>
+        <v>6.39481258392334</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1718" t="n">
-        <v>6.25387954711914</v>
+        <v>6.25387907028198</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1719" t="n">
-        <v>6.25387954711914</v>
+        <v>6.25387907028198</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G1721" t="n">
-        <v>6.37719488143921</v>
+        <v>6.37719535827637</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1725" t="n">
-        <v>6.46527862548828</v>
+        <v>6.46527814865112</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1732" t="n">
-        <v>6.46527862548828</v>
+        <v>6.46527814865112</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1736" t="n">
-        <v>6.39481210708618</v>
+        <v>6.39481258392334</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1737" t="n">
-        <v>6.39481210708618</v>
+        <v>6.39481258392334</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1742" t="n">
-        <v>6.35957908630371</v>
+        <v>6.35957860946655</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1743" t="n">
-        <v>6.39481210708618</v>
+        <v>6.39481258392334</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1750" t="n">
-        <v>6.74714326858521</v>
+        <v>6.74714279174805</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1751" t="n">
-        <v>6.69429349899292</v>
+        <v>6.69429302215576</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1756" t="n">
-        <v>6.8176097869873</v>
+        <v>6.81760931015015</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1758" t="n">
-        <v>6.90569305419922</v>
+        <v>6.90569257736206</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1759" t="n">
-        <v>6.87045907974243</v>
+        <v>6.87045955657959</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1762" t="n">
-        <v>6.90569305419922</v>
+        <v>6.90569257736206</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1763" t="n">
-        <v>6.99377489089966</v>
+        <v>6.99377536773682</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1764" t="n">
-        <v>6.99377489089966</v>
+        <v>6.99377536773682</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1766" t="n">
-        <v>6.99377489089966</v>
+        <v>6.99377536773682</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1768" t="n">
-        <v>6.99377489089966</v>
+        <v>6.99377536773682</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1769" t="n">
-        <v>6.99377489089966</v>
+        <v>6.99377536773682</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1770" t="n">
-        <v>6.90569305419922</v>
+        <v>6.90569257736206</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1773" t="n">
-        <v>6.8176097869873</v>
+        <v>6.81760931015015</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1774" t="n">
-        <v>6.8176097869873</v>
+        <v>6.81760931015015</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1776" t="n">
-        <v>6.74714326858521</v>
+        <v>6.74714279174805</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1777" t="n">
-        <v>6.90569305419922</v>
+        <v>6.90569257736206</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1778" t="n">
-        <v>6.90569305419922</v>
+        <v>6.90569257736206</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1779" t="n">
-        <v>6.90569305419922</v>
+        <v>6.90569257736206</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1780" t="n">
-        <v>6.90569305419922</v>
+        <v>6.90569257736206</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1781" t="n">
-        <v>6.87045907974243</v>
+        <v>6.87045955657959</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1782" t="n">
-        <v>6.87045907974243</v>
+        <v>6.87045955657959</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1783" t="n">
-        <v>6.8176097869873</v>
+        <v>6.81760931015015</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1784" t="n">
-        <v>6.76476001739502</v>
+        <v>6.76475954055786</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1785" t="n">
-        <v>6.8176097869873</v>
+        <v>6.81760931015015</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1787" t="n">
-        <v>6.87045907974243</v>
+        <v>6.87045955657959</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1796" t="n">
-        <v>6.88807582855225</v>
+        <v>6.8880763053894</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1797" t="n">
-        <v>6.88807582855225</v>
+        <v>6.8880763053894</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1806" t="n">
-        <v>7.09947538375854</v>
+        <v>7.09947490692139</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1808" t="n">
-        <v>7.20517444610596</v>
+        <v>7.2051739692688</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1809" t="n">
-        <v>7.24040746688843</v>
+        <v>7.24040699005127</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1810" t="n">
-        <v>7.24040746688843</v>
+        <v>7.24040699005127</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1811" t="n">
-        <v>7.34610652923584</v>
+        <v>7.346107006073</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G1812" t="n">
-        <v>7.50465631484985</v>
+        <v>7.5046558380127</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G1813" t="n">
-        <v>7.50465631484985</v>
+        <v>7.5046558380127</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1814" t="n">
-        <v>7.24040746688843</v>
+        <v>7.24040699005127</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1816" t="n">
-        <v>7.20517444610596</v>
+        <v>7.2051739692688</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1817" t="n">
-        <v>7.20517444610596</v>
+        <v>7.2051739692688</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1818" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1819" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1821" t="n">
-        <v>7.15232419967651</v>
+        <v>7.15232372283936</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1829" t="n">
-        <v>6.99377489089966</v>
+        <v>6.99377536773682</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1831" t="n">
-        <v>6.90569305419922</v>
+        <v>6.90569257736206</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1833" t="n">
-        <v>6.88807582855225</v>
+        <v>6.8880763053894</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1835" t="n">
-        <v>6.88807582855225</v>
+        <v>6.8880763053894</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1836" t="n">
-        <v>6.90569305419922</v>
+        <v>6.90569257736206</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1838" t="n">
-        <v>6.87045907974243</v>
+        <v>6.87045955657959</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1843" t="n">
-        <v>6.88807582855225</v>
+        <v>6.8880763053894</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1844" t="n">
-        <v>6.87045907974243</v>
+        <v>6.87045955657959</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1850" t="n">
-        <v>7.09947538375854</v>
+        <v>7.09947490692139</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1851" t="n">
-        <v>7.09947538375854</v>
+        <v>7.09947490692139</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1856" t="n">
-        <v>7.09947538375854</v>
+        <v>7.09947490692139</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1857" t="n">
-        <v>7.09947538375854</v>
+        <v>7.09947490692139</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1867" t="n">
-        <v>7.24040746688843</v>
+        <v>7.24040699005127</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1869" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1870" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1871" t="n">
-        <v>7.34610652923584</v>
+        <v>7.346107006073</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1872" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1873" t="n">
-        <v>7.34610652923584</v>
+        <v>7.346107006073</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>8.5</v>
       </c>
       <c r="G1875" t="n">
-        <v>7.48703908920288</v>
+        <v>7.48703956604004</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1877" t="n">
-        <v>7.39895534515381</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1878" t="n">
-        <v>7.57512140274048</v>
+        <v>7.57512235641479</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1879" t="n">
-        <v>7.4341893196106</v>
+        <v>7.43418884277344</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49249,7 +49249,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1880" t="n">
-        <v>7.4341893196106</v>
+        <v>7.43418884277344</v>
       </c>
       <c r="H1880" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1882" t="n">
-        <v>7.4341893196106</v>
+        <v>7.43418884277344</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1883" t="n">
-        <v>7.41657209396362</v>
+        <v>7.41657257080078</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1884" t="n">
-        <v>7.46942186355591</v>
+        <v>7.46942234039307</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>8.5</v>
       </c>
       <c r="G1885" t="n">
-        <v>7.48703908920288</v>
+        <v>7.48703956604004</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1886" t="n">
-        <v>7.46942186355591</v>
+        <v>7.46942234039307</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49431,7 +49431,7 @@
         <v>8.5</v>
       </c>
       <c r="G1887" t="n">
-        <v>7.48703908920288</v>
+        <v>7.48703956604004</v>
       </c>
       <c r="H1887" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1888" t="n">
-        <v>7.39895534515381</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49509,7 +49509,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1890" t="n">
-        <v>7.39895534515381</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1890" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1891" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49561,7 +49561,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1892" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1892" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1893" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1894" t="n">
-        <v>7.39895534515381</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1895" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1896" t="n">
-        <v>7.39895534515381</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1897" t="n">
-        <v>7.41657209396362</v>
+        <v>7.41657257080078</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1898" t="n">
-        <v>7.39895534515381</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1899" t="n">
-        <v>7.39895534515381</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>8.5</v>
       </c>
       <c r="G1901" t="n">
-        <v>7.48703908920288</v>
+        <v>7.48703956604004</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1902" t="n">
-        <v>7.4341893196106</v>
+        <v>7.43418884277344</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1903" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49873,7 +49873,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1904" t="n">
-        <v>7.39895534515381</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1904" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1905" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1906" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -49951,7 +49951,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1907" t="n">
-        <v>7.41657209396362</v>
+        <v>7.41657257080078</v>
       </c>
       <c r="H1907" t="s">
         <v>8</v>
@@ -49977,7 +49977,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1908" t="n">
-        <v>7.41657209396362</v>
+        <v>7.41657257080078</v>
       </c>
       <c r="H1908" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1910" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1911" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1914" t="n">
-        <v>7.34610652923584</v>
+        <v>7.346107006073</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1915" t="n">
-        <v>7.45180654525757</v>
+        <v>7.45180606842041</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1917" t="n">
-        <v>7.46942186355591</v>
+        <v>7.46942234039307</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50237,7 +50237,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1918" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H1918" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1919" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1920" t="n">
-        <v>7.20517444610596</v>
+        <v>7.2051739692688</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50341,7 +50341,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1922" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1922" t="s">
         <v>8</v>
@@ -50367,7 +50367,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1923" t="n">
-        <v>7.24040746688843</v>
+        <v>7.24040699005127</v>
       </c>
       <c r="H1923" t="s">
         <v>8</v>
@@ -50393,7 +50393,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1924" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1924" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1925" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1926" t="n">
-        <v>7.39895534515381</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50471,7 +50471,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1927" t="n">
-        <v>7.34610652923584</v>
+        <v>7.346107006073</v>
       </c>
       <c r="H1927" t="s">
         <v>8</v>
@@ -50497,7 +50497,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1928" t="n">
-        <v>7.39895534515381</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1928" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1930" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1931" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50601,7 +50601,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1932" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1932" t="s">
         <v>8</v>
@@ -50679,7 +50679,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1935" t="n">
-        <v>7.24040746688843</v>
+        <v>7.24040699005127</v>
       </c>
       <c r="H1935" t="s">
         <v>8</v>
@@ -50731,7 +50731,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1937" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1937" t="s">
         <v>8</v>
@@ -50757,7 +50757,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1938" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1938" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1940" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1941" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50861,7 +50861,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1942" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1942" t="s">
         <v>8</v>
@@ -50887,7 +50887,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1943" t="n">
-        <v>7.24040746688843</v>
+        <v>7.24040699005127</v>
       </c>
       <c r="H1943" t="s">
         <v>8</v>
@@ -50965,7 +50965,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1946" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H1946" t="s">
         <v>8</v>
@@ -51017,7 +51017,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1948" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H1948" t="s">
         <v>8</v>
@@ -51043,7 +51043,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1949" t="n">
-        <v>7.41657209396362</v>
+        <v>7.41657257080078</v>
       </c>
       <c r="H1949" t="s">
         <v>8</v>
@@ -51069,7 +51069,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1950" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1950" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1951" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1952" t="n">
-        <v>7.34610652923584</v>
+        <v>7.346107006073</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51199,7 +51199,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1955" t="n">
-        <v>7.39895534515381</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1955" t="s">
         <v>8</v>
@@ -51329,7 +51329,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1960" t="n">
-        <v>7.39895534515381</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1960" t="s">
         <v>8</v>
@@ -51381,7 +51381,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1962" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H1962" t="s">
         <v>8</v>
@@ -51407,7 +51407,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1963" t="n">
-        <v>7.34610652923584</v>
+        <v>7.346107006073</v>
       </c>
       <c r="H1963" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1966" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1970" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51719,7 +51719,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1975" t="n">
-        <v>7.24040746688843</v>
+        <v>7.24040699005127</v>
       </c>
       <c r="H1975" t="s">
         <v>8</v>
@@ -51797,7 +51797,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1978" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1978" t="s">
         <v>8</v>
@@ -51823,7 +51823,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1979" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H1979" t="s">
         <v>8</v>
@@ -51875,7 +51875,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1981" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1981" t="s">
         <v>8</v>
@@ -51901,7 +51901,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1982" t="n">
-        <v>7.39895534515381</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1982" t="s">
         <v>8</v>
@@ -51927,7 +51927,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1983" t="n">
-        <v>7.41657209396362</v>
+        <v>7.41657257080078</v>
       </c>
       <c r="H1983" t="s">
         <v>8</v>
@@ -51979,7 +51979,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1985" t="n">
-        <v>7.15232419967651</v>
+        <v>7.15232372283936</v>
       </c>
       <c r="H1985" t="s">
         <v>8</v>
@@ -52005,7 +52005,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1986" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1986" t="s">
         <v>8</v>
@@ -52083,7 +52083,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1989" t="n">
-        <v>7.09947538375854</v>
+        <v>7.09947490692139</v>
       </c>
       <c r="H1989" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1990" t="n">
-        <v>7.09947538375854</v>
+        <v>7.09947490692139</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52135,7 +52135,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1991" t="n">
-        <v>7.09947538375854</v>
+        <v>7.09947490692139</v>
       </c>
       <c r="H1991" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1994" t="n">
-        <v>7.15232419967651</v>
+        <v>7.15232372283936</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52291,7 +52291,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1997" t="n">
-        <v>7.09947538375854</v>
+        <v>7.09947490692139</v>
       </c>
       <c r="H1997" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2005" t="n">
-        <v>7.15232419967651</v>
+        <v>7.15232372283936</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2006" t="n">
-        <v>7.15232419967651</v>
+        <v>7.15232372283936</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52551,7 +52551,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2007" t="n">
-        <v>7.15232419967651</v>
+        <v>7.15232372283936</v>
       </c>
       <c r="H2007" t="s">
         <v>8</v>
@@ -52577,7 +52577,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2008" t="n">
-        <v>7.15232419967651</v>
+        <v>7.15232372283936</v>
       </c>
       <c r="H2008" t="s">
         <v>8</v>
@@ -52655,7 +52655,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2011" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H2011" t="s">
         <v>8</v>
@@ -52681,7 +52681,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G2012" t="n">
-        <v>7.24040746688843</v>
+        <v>7.24040699005127</v>
       </c>
       <c r="H2012" t="s">
         <v>8</v>
@@ -52811,7 +52811,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2017" t="n">
-        <v>7.09947538375854</v>
+        <v>7.09947490692139</v>
       </c>
       <c r="H2017" t="s">
         <v>8</v>
@@ -52889,7 +52889,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2020" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H2020" t="s">
         <v>8</v>
@@ -52941,7 +52941,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2022" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H2022" t="s">
         <v>8</v>
@@ -52993,7 +52993,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2024" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H2024" t="s">
         <v>8</v>
@@ -53019,7 +53019,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G2025" t="n">
-        <v>7.34610652923584</v>
+        <v>7.346107006073</v>
       </c>
       <c r="H2025" t="s">
         <v>8</v>
@@ -53123,7 +53123,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G2029" t="n">
-        <v>7.20517444610596</v>
+        <v>7.2051739692688</v>
       </c>
       <c r="H2029" t="s">
         <v>8</v>
@@ -53331,7 +53331,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2037" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H2037" t="s">
         <v>8</v>
@@ -53383,7 +53383,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2039" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H2039" t="s">
         <v>8</v>
@@ -53461,7 +53461,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G2042" t="n">
-        <v>7.34610652923584</v>
+        <v>7.346107006073</v>
       </c>
       <c r="H2042" t="s">
         <v>8</v>
@@ -53487,7 +53487,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G2043" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H2043" t="s">
         <v>8</v>
@@ -53513,7 +53513,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G2044" t="n">
-        <v>7.24040746688843</v>
+        <v>7.24040699005127</v>
       </c>
       <c r="H2044" t="s">
         <v>8</v>
@@ -53617,7 +53617,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2048" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H2048" t="s">
         <v>8</v>
@@ -53643,7 +53643,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G2049" t="n">
-        <v>7.34610652923584</v>
+        <v>7.346107006073</v>
       </c>
       <c r="H2049" t="s">
         <v>8</v>
@@ -53695,7 +53695,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2051" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H2051" t="s">
         <v>8</v>
@@ -53721,7 +53721,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G2052" t="n">
-        <v>7.34610652923584</v>
+        <v>7.346107006073</v>
       </c>
       <c r="H2052" t="s">
         <v>8</v>
@@ -53747,7 +53747,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G2053" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H2053" t="s">
         <v>8</v>
@@ -53773,7 +53773,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2054" t="n">
-        <v>7.31087398529053</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H2054" t="s">
         <v>8</v>
@@ -53825,7 +53825,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2056" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H2056" t="s">
         <v>8</v>
@@ -53851,7 +53851,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2057" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H2057" t="s">
         <v>8</v>
@@ -53903,7 +53903,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G2059" t="n">
-        <v>7.24040746688843</v>
+        <v>7.24040699005127</v>
       </c>
       <c r="H2059" t="s">
         <v>8</v>
@@ -53929,7 +53929,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G2060" t="n">
-        <v>7.24040746688843</v>
+        <v>7.24040699005127</v>
       </c>
       <c r="H2060" t="s">
         <v>8</v>
@@ -53981,7 +53981,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G2062" t="n">
-        <v>7.20517444610596</v>
+        <v>7.2051739692688</v>
       </c>
       <c r="H2062" t="s">
         <v>8</v>
@@ -54033,7 +54033,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G2064" t="n">
-        <v>7.20517444610596</v>
+        <v>7.2051739692688</v>
       </c>
       <c r="H2064" t="s">
         <v>8</v>
@@ -54059,7 +54059,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G2065" t="n">
-        <v>7.20517444610596</v>
+        <v>7.2051739692688</v>
       </c>
       <c r="H2065" t="s">
         <v>8</v>
@@ -54345,7 +54345,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2076" t="n">
-        <v>7.09947538375854</v>
+        <v>7.09947490692139</v>
       </c>
       <c r="H2076" t="s">
         <v>8</v>
@@ -54475,7 +54475,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G2081" t="n">
-        <v>6.78237581253052</v>
+        <v>6.78237628936768</v>
       </c>
       <c r="H2081" t="s">
         <v>8</v>
@@ -54787,7 +54787,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2093" t="n">
-        <v>6.90569305419922</v>
+        <v>6.90569257736206</v>
       </c>
       <c r="H2093" t="s">
         <v>8</v>
@@ -55047,7 +55047,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G2103" t="n">
-        <v>6.88807582855225</v>
+        <v>6.8880763053894</v>
       </c>
       <c r="H2103" t="s">
         <v>8</v>
@@ -55359,7 +55359,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G2115" t="n">
-        <v>6.88807582855225</v>
+        <v>6.8880763053894</v>
       </c>
       <c r="H2115" t="s">
         <v>8</v>
@@ -55411,7 +55411,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2117" t="n">
-        <v>6.90569305419922</v>
+        <v>6.90569257736206</v>
       </c>
       <c r="H2117" t="s">
         <v>8</v>
@@ -55541,7 +55541,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2122" t="n">
-        <v>7.09947538375854</v>
+        <v>7.09947490692139</v>
       </c>
       <c r="H2122" t="s">
         <v>8</v>
@@ -55567,7 +55567,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2123" t="n">
-        <v>7.33988857269287</v>
+        <v>7.33988809585571</v>
       </c>
       <c r="H2123" t="s">
         <v>8</v>
@@ -55619,7 +55619,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G2125" t="n">
-        <v>7.23060894012451</v>
+        <v>7.23060941696167</v>
       </c>
       <c r="H2125" t="s">
         <v>8</v>
@@ -55671,7 +55671,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2127" t="n">
-        <v>7.24882221221924</v>
+        <v>7.2488226890564</v>
       </c>
       <c r="H2127" t="s">
         <v>8</v>
@@ -55775,7 +55775,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2131" t="n">
-        <v>7.33988857269287</v>
+        <v>7.33988809585571</v>
       </c>
       <c r="H2131" t="s">
         <v>8</v>
@@ -55853,7 +55853,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2134" t="n">
-        <v>7.24882221221924</v>
+        <v>7.2488226890564</v>
       </c>
       <c r="H2134" t="s">
         <v>8</v>
@@ -55983,7 +55983,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2139" t="n">
-        <v>7.33988857269287</v>
+        <v>7.33988809585571</v>
       </c>
       <c r="H2139" t="s">
         <v>8</v>
@@ -56035,7 +56035,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2141" t="n">
-        <v>7.24882221221924</v>
+        <v>7.2488226890564</v>
       </c>
       <c r="H2141" t="s">
         <v>8</v>
@@ -56113,7 +56113,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G2144" t="n">
-        <v>7.23060894012451</v>
+        <v>7.23060941696167</v>
       </c>
       <c r="H2144" t="s">
         <v>8</v>
@@ -56243,7 +56243,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G2149" t="n">
-        <v>7.32167482376099</v>
+        <v>7.32167434692383</v>
       </c>
       <c r="H2149" t="s">
         <v>8</v>
@@ -56295,7 +56295,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2151" t="n">
-        <v>7.33988857269287</v>
+        <v>7.33988809585571</v>
       </c>
       <c r="H2151" t="s">
         <v>8</v>
@@ -56399,7 +56399,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2155" t="n">
-        <v>7.33988857269287</v>
+        <v>7.33988809585571</v>
       </c>
       <c r="H2155" t="s">
         <v>8</v>
@@ -56425,7 +56425,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G2156" t="n">
-        <v>7.23060894012451</v>
+        <v>7.23060941696167</v>
       </c>
       <c r="H2156" t="s">
         <v>8</v>
@@ -56477,7 +56477,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G2158" t="n">
-        <v>7.23060894012451</v>
+        <v>7.23060941696167</v>
       </c>
       <c r="H2158" t="s">
         <v>8</v>
@@ -56503,7 +56503,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G2159" t="n">
-        <v>7.23060894012451</v>
+        <v>7.23060941696167</v>
       </c>
       <c r="H2159" t="s">
         <v>8</v>
@@ -56659,7 +56659,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2165" t="n">
-        <v>7.1395435333252</v>
+        <v>7.13954401016235</v>
       </c>
       <c r="H2165" t="s">
         <v>8</v>
@@ -56711,7 +56711,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2167" t="n">
-        <v>7.24882221221924</v>
+        <v>7.2488226890564</v>
       </c>
       <c r="H2167" t="s">
         <v>8</v>
@@ -56737,7 +56737,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2168" t="n">
-        <v>7.24882221221924</v>
+        <v>7.2488226890564</v>
       </c>
       <c r="H2168" t="s">
         <v>8</v>
@@ -56763,7 +56763,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G2169" t="n">
-        <v>7.23060894012451</v>
+        <v>7.23060941696167</v>
       </c>
       <c r="H2169" t="s">
         <v>8</v>
@@ -56815,7 +56815,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2171" t="n">
-        <v>7.1395435333252</v>
+        <v>7.13954401016235</v>
       </c>
       <c r="H2171" t="s">
         <v>8</v>
@@ -56867,7 +56867,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2173" t="n">
-        <v>7.24882221221924</v>
+        <v>7.2488226890564</v>
       </c>
       <c r="H2173" t="s">
         <v>8</v>
@@ -56893,7 +56893,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G2174" t="n">
-        <v>7.23060894012451</v>
+        <v>7.23060941696167</v>
       </c>
       <c r="H2174" t="s">
         <v>8</v>
@@ -56919,7 +56919,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2175" t="n">
-        <v>7.1395435333252</v>
+        <v>7.13954401016235</v>
       </c>
       <c r="H2175" t="s">
         <v>8</v>
@@ -56945,7 +56945,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G2176" t="n">
-        <v>7.23060894012451</v>
+        <v>7.23060941696167</v>
       </c>
       <c r="H2176" t="s">
         <v>8</v>
@@ -57023,7 +57023,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2179" t="n">
-        <v>7.24882221221924</v>
+        <v>7.2488226890564</v>
       </c>
       <c r="H2179" t="s">
         <v>8</v>
@@ -57049,7 +57049,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2180" t="n">
-        <v>7.24882221221924</v>
+        <v>7.2488226890564</v>
       </c>
       <c r="H2180" t="s">
         <v>8</v>
@@ -57075,7 +57075,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G2181" t="n">
-        <v>7.23060894012451</v>
+        <v>7.23060941696167</v>
       </c>
       <c r="H2181" t="s">
         <v>8</v>
@@ -57127,7 +57127,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2183" t="n">
-        <v>7.24882221221924</v>
+        <v>7.2488226890564</v>
       </c>
       <c r="H2183" t="s">
         <v>8</v>
@@ -57153,7 +57153,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G2184" t="n">
-        <v>7.17596960067749</v>
+        <v>7.17597007751465</v>
       </c>
       <c r="H2184" t="s">
         <v>8</v>
@@ -57179,7 +57179,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2185" t="n">
-        <v>7.24882221221924</v>
+        <v>7.2488226890564</v>
       </c>
       <c r="H2185" t="s">
         <v>8</v>
@@ -57257,7 +57257,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G2188" t="n">
-        <v>7.17596960067749</v>
+        <v>7.17597007751465</v>
       </c>
       <c r="H2188" t="s">
         <v>8</v>
@@ -57335,7 +57335,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G2191" t="n">
-        <v>7.17596960067749</v>
+        <v>7.17597007751465</v>
       </c>
       <c r="H2191" t="s">
         <v>8</v>
@@ -57517,7 +57517,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2198" t="n">
-        <v>7.1395435333252</v>
+        <v>7.13954401016235</v>
       </c>
       <c r="H2198" t="s">
         <v>8</v>
@@ -57647,7 +57647,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2203" t="n">
-        <v>7.1395435333252</v>
+        <v>7.13954401016235</v>
       </c>
       <c r="H2203" t="s">
         <v>8</v>
@@ -57751,7 +57751,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2207" t="n">
-        <v>7.1395435333252</v>
+        <v>7.13954401016235</v>
       </c>
       <c r="H2207" t="s">
         <v>8</v>
@@ -57829,7 +57829,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2210" t="n">
-        <v>7.04847812652588</v>
+        <v>7.04847764968872</v>
       </c>
       <c r="H2210" t="s">
         <v>8</v>
@@ -57881,7 +57881,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2212" t="n">
-        <v>7.04847812652588</v>
+        <v>7.04847764968872</v>
       </c>
       <c r="H2212" t="s">
         <v>8</v>
@@ -57907,7 +57907,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2213" t="n">
-        <v>7.1395435333252</v>
+        <v>7.13954401016235</v>
       </c>
       <c r="H2213" t="s">
         <v>8</v>
@@ -58167,7 +58167,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G2223" t="n">
-        <v>6.97562551498413</v>
+        <v>6.97562503814697</v>
       </c>
       <c r="H2223" t="s">
         <v>8</v>
@@ -58479,7 +58479,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2235" t="n">
-        <v>7.04847812652588</v>
+        <v>7.04847764968872</v>
       </c>
       <c r="H2235" t="s">
         <v>8</v>
@@ -58557,7 +58557,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2238" t="n">
-        <v>7.04847812652588</v>
+        <v>7.04847764968872</v>
       </c>
       <c r="H2238" t="s">
         <v>8</v>
@@ -58583,7 +58583,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2239" t="n">
-        <v>7.1395435333252</v>
+        <v>7.13954401016235</v>
       </c>
       <c r="H2239" t="s">
         <v>8</v>
@@ -58687,7 +58687,7 @@
         <v>7.5</v>
       </c>
       <c r="G2243" t="n">
-        <v>6.82992076873779</v>
+        <v>6.82992029190063</v>
       </c>
       <c r="H2243" t="s">
         <v>8</v>
@@ -58713,7 +58713,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2244" t="n">
-        <v>6.62957668304443</v>
+        <v>6.62957620620728</v>
       </c>
       <c r="H2244" t="s">
         <v>8</v>
@@ -58739,7 +58739,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2245" t="n">
-        <v>6.79349422454834</v>
+        <v>6.7934947013855</v>
       </c>
       <c r="H2245" t="s">
         <v>8</v>
@@ -58817,7 +58817,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2248" t="n">
-        <v>6.73885488510132</v>
+        <v>6.73885536193848</v>
       </c>
       <c r="H2248" t="s">
         <v>8</v>
@@ -58869,7 +58869,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G2250" t="n">
-        <v>6.75706768035889</v>
+        <v>6.75706815719604</v>
       </c>
       <c r="H2250" t="s">
         <v>8</v>
@@ -58947,7 +58947,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G2253" t="n">
-        <v>6.75706768035889</v>
+        <v>6.75706815719604</v>
       </c>
       <c r="H2253" t="s">
         <v>8</v>
@@ -59025,7 +59025,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G2256" t="n">
-        <v>6.75706768035889</v>
+        <v>6.75706815719604</v>
       </c>
       <c r="H2256" t="s">
         <v>8</v>
@@ -59051,7 +59051,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2257" t="n">
-        <v>6.73885488510132</v>
+        <v>6.73885536193848</v>
       </c>
       <c r="H2257" t="s">
         <v>8</v>
@@ -59129,7 +59129,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2260" t="n">
-        <v>6.79349422454834</v>
+        <v>6.7934947013855</v>
       </c>
       <c r="H2260" t="s">
         <v>8</v>
@@ -59181,7 +59181,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2262" t="n">
-        <v>6.73885488510132</v>
+        <v>6.73885536193848</v>
       </c>
       <c r="H2262" t="s">
         <v>8</v>
@@ -59233,7 +59233,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2264" t="n">
-        <v>6.79349422454834</v>
+        <v>6.7934947013855</v>
       </c>
       <c r="H2264" t="s">
         <v>8</v>
@@ -59311,7 +59311,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G2267" t="n">
-        <v>6.75706768035889</v>
+        <v>6.75706815719604</v>
       </c>
       <c r="H2267" t="s">
         <v>8</v>
@@ -59337,7 +59337,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2268" t="n">
-        <v>6.92098617553711</v>
+        <v>6.92098569869995</v>
       </c>
       <c r="H2268" t="s">
         <v>8</v>
@@ -59363,7 +59363,7 @@
         <v>7.5</v>
       </c>
       <c r="G2269" t="n">
-        <v>6.82992076873779</v>
+        <v>6.82992029190063</v>
       </c>
       <c r="H2269" t="s">
         <v>8</v>
@@ -59389,7 +59389,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2270" t="n">
-        <v>6.86634683609009</v>
+        <v>6.86634635925293</v>
       </c>
       <c r="H2270" t="s">
         <v>8</v>
@@ -59415,7 +59415,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2271" t="n">
-        <v>6.86634683609009</v>
+        <v>6.86634635925293</v>
       </c>
       <c r="H2271" t="s">
         <v>8</v>
@@ -59519,7 +59519,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2275" t="n">
-        <v>6.92098617553711</v>
+        <v>6.92098569869995</v>
       </c>
       <c r="H2275" t="s">
         <v>8</v>
@@ -59805,7 +59805,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2286" t="n">
-        <v>6.73885488510132</v>
+        <v>6.73885536193848</v>
       </c>
       <c r="H2286" t="s">
         <v>8</v>
@@ -59909,7 +59909,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2290" t="n">
-        <v>6.86634683609009</v>
+        <v>6.86634635925293</v>
       </c>
       <c r="H2290" t="s">
         <v>8</v>
@@ -59935,7 +59935,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2291" t="n">
-        <v>6.86634683609009</v>
+        <v>6.86634635925293</v>
       </c>
       <c r="H2291" t="s">
         <v>8</v>
@@ -60013,7 +60013,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2294" t="n">
-        <v>7.04847812652588</v>
+        <v>7.04847764968872</v>
       </c>
       <c r="H2294" t="s">
         <v>8</v>
@@ -60143,7 +60143,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2299" t="n">
-        <v>7.04847812652588</v>
+        <v>7.04847764968872</v>
       </c>
       <c r="H2299" t="s">
         <v>8</v>
@@ -60169,7 +60169,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2300" t="n">
-        <v>7.04847812652588</v>
+        <v>7.04847764968872</v>
       </c>
       <c r="H2300" t="s">
         <v>8</v>
@@ -60221,7 +60221,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2302" t="n">
-        <v>7.04847812652588</v>
+        <v>7.04847764968872</v>
       </c>
       <c r="H2302" t="s">
         <v>8</v>
@@ -60247,7 +60247,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2303" t="n">
-        <v>6.86634683609009</v>
+        <v>6.86634635925293</v>
       </c>
       <c r="H2303" t="s">
         <v>8</v>
@@ -60273,7 +60273,7 @@
         <v>7.5</v>
       </c>
       <c r="G2304" t="n">
-        <v>6.82992076873779</v>
+        <v>6.82992029190063</v>
       </c>
       <c r="H2304" t="s">
         <v>8</v>
@@ -60585,7 +60585,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2316" t="n">
-        <v>7.04847812652588</v>
+        <v>7.04847764968872</v>
       </c>
       <c r="H2316" t="s">
         <v>8</v>
@@ -60819,7 +60819,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G2325" t="n">
-        <v>6.97562551498413</v>
+        <v>6.97562503814697</v>
       </c>
       <c r="H2325" t="s">
         <v>8</v>
@@ -61079,7 +61079,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2335" t="n">
-        <v>7.04847812652588</v>
+        <v>7.04847764968872</v>
       </c>
       <c r="H2335" t="s">
         <v>8</v>
@@ -61131,7 +61131,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2337" t="n">
-        <v>7.04847812652588</v>
+        <v>7.04847764968872</v>
       </c>
       <c r="H2337" t="s">
         <v>8</v>
@@ -61157,7 +61157,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2338" t="n">
-        <v>7.04847812652588</v>
+        <v>7.04847764968872</v>
       </c>
       <c r="H2338" t="s">
         <v>8</v>
@@ -61261,7 +61261,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G2342" t="n">
-        <v>7.32167482376099</v>
+        <v>7.32167434692383</v>
       </c>
       <c r="H2342" t="s">
         <v>8</v>
@@ -61287,7 +61287,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G2343" t="n">
-        <v>7.23060894012451</v>
+        <v>7.23060941696167</v>
       </c>
       <c r="H2343" t="s">
         <v>8</v>
@@ -61365,7 +61365,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2346" t="n">
-        <v>7.33988857269287</v>
+        <v>7.33988809585571</v>
       </c>
       <c r="H2346" t="s">
         <v>8</v>
@@ -61391,7 +61391,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G2347" t="n">
-        <v>7.43095350265503</v>
+        <v>7.43095302581787</v>
       </c>
       <c r="H2347" t="s">
         <v>8</v>
@@ -61417,7 +61417,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G2348" t="n">
-        <v>7.43095350265503</v>
+        <v>7.43095302581787</v>
       </c>
       <c r="H2348" t="s">
         <v>8</v>
@@ -61521,7 +61521,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2352" t="n">
-        <v>7.39452743530273</v>
+        <v>7.39452695846558</v>
       </c>
       <c r="H2352" t="s">
         <v>8</v>
@@ -61547,7 +61547,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2353" t="n">
-        <v>7.39452743530273</v>
+        <v>7.39452695846558</v>
       </c>
       <c r="H2353" t="s">
         <v>8</v>
@@ -61625,7 +61625,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2356" t="n">
-        <v>7.1395435333252</v>
+        <v>7.13954401016235</v>
       </c>
       <c r="H2356" t="s">
         <v>8</v>
@@ -61703,7 +61703,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G2359" t="n">
-        <v>7.32167482376099</v>
+        <v>7.32167434692383</v>
       </c>
       <c r="H2359" t="s">
         <v>8</v>
@@ -61755,7 +61755,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G2361" t="n">
-        <v>7.32167482376099</v>
+        <v>7.32167434692383</v>
       </c>
       <c r="H2361" t="s">
         <v>8</v>
@@ -61833,7 +61833,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2364" t="n">
-        <v>7.39452743530273</v>
+        <v>7.39452695846558</v>
       </c>
       <c r="H2364" t="s">
         <v>8</v>
@@ -62015,7 +62015,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G2371" t="n">
-        <v>7.48559331893921</v>
+        <v>7.48559284210205</v>
       </c>
       <c r="H2371" t="s">
         <v>8</v>
@@ -62119,7 +62119,7 @@
         <v>8.5</v>
       </c>
       <c r="G2375" t="n">
-        <v>7.74057626724243</v>
+        <v>7.74057722091675</v>
       </c>
       <c r="H2375" t="s">
         <v>8</v>
@@ -62145,7 +62145,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G2376" t="n">
-        <v>7.81342935562134</v>
+        <v>7.81342887878418</v>
       </c>
       <c r="H2376" t="s">
         <v>8</v>
@@ -71690,6 +71690,32 @@
         <v>8.88000011444092</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>1007</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>8.96000003814697</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -427,7 +427,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G2" t="n">
-        <v>4.91287708282471</v>
+        <v>4.91287660598755</v>
       </c>
       <c r="H2" t="n">
         <v>9493</v>
@@ -456,7 +456,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>4.91287708282471</v>
+        <v>4.91287660598755</v>
       </c>
       <c r="H3" t="n">
         <v>20399</v>
@@ -485,7 +485,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>4.91287708282471</v>
+        <v>4.91287660598755</v>
       </c>
       <c r="H4" t="n">
         <v>550</v>
@@ -514,7 +514,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G5" t="n">
-        <v>4.96080732345581</v>
+        <v>4.96080780029297</v>
       </c>
       <c r="H5" t="n">
         <v>13699</v>
@@ -543,7 +543,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G6" t="n">
-        <v>4.96080732345581</v>
+        <v>4.96080780029297</v>
       </c>
       <c r="H6" t="n">
         <v>22150</v>
@@ -601,7 +601,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G8" t="n">
-        <v>4.95281887054443</v>
+        <v>4.95281839370728</v>
       </c>
       <c r="H8" t="n">
         <v>5200</v>
@@ -746,7 +746,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G13" t="n">
-        <v>5.04868078231812</v>
+        <v>5.0486798286438</v>
       </c>
       <c r="H13" t="n">
         <v>41577</v>
@@ -775,7 +775,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G14" t="n">
-        <v>5.10459852218628</v>
+        <v>5.10459899902344</v>
       </c>
       <c r="H14" t="n">
         <v>16997</v>
@@ -804,7 +804,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G15" t="n">
-        <v>5.11258697509766</v>
+        <v>5.11258792877197</v>
       </c>
       <c r="H15" t="n">
         <v>29415</v>
@@ -833,7 +833,7 @@
         <v>6.40500020980835</v>
       </c>
       <c r="G16" t="n">
-        <v>5.11658191680908</v>
+        <v>5.11658143997192</v>
       </c>
       <c r="H16" t="n">
         <v>8017</v>
@@ -891,7 +891,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G18" t="n">
-        <v>5.18448305130005</v>
+        <v>5.18448257446289</v>
       </c>
       <c r="H18" t="n">
         <v>2671</v>
@@ -920,7 +920,7 @@
         <v>6.44500017166138</v>
       </c>
       <c r="G19" t="n">
-        <v>5.14853525161743</v>
+        <v>5.14853572845459</v>
       </c>
       <c r="H19" t="n">
         <v>4391</v>
@@ -949,7 +949,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G20" t="n">
-        <v>5.11258697509766</v>
+        <v>5.11258792877197</v>
       </c>
       <c r="H20" t="n">
         <v>3489</v>
@@ -1036,7 +1036,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G23" t="n">
-        <v>5.16850566864014</v>
+        <v>5.16850614547729</v>
       </c>
       <c r="H23" t="n">
         <v>1883</v>
@@ -1152,7 +1152,7 @@
         <v>6.5</v>
       </c>
       <c r="G27" t="n">
-        <v>5.19247102737427</v>
+        <v>5.19247150421143</v>
       </c>
       <c r="H27" t="n">
         <v>11644</v>
@@ -1210,7 +1210,7 @@
         <v>6.5</v>
       </c>
       <c r="G29" t="n">
-        <v>5.19247102737427</v>
+        <v>5.19247150421143</v>
       </c>
       <c r="H29" t="n">
         <v>13504</v>
@@ -1268,7 +1268,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G31" t="n">
-        <v>5.27235555648804</v>
+        <v>5.2723560333252</v>
       </c>
       <c r="H31" t="n">
         <v>6912</v>
@@ -1297,7 +1297,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>5.2763500213623</v>
+        <v>5.27634954452515</v>
       </c>
       <c r="H32" t="n">
         <v>3215</v>
@@ -1355,7 +1355,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G34" t="n">
-        <v>5.71171808242798</v>
+        <v>5.71171855926514</v>
       </c>
       <c r="H34" t="n">
         <v>20799</v>
@@ -1384,7 +1384,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G35" t="n">
-        <v>5.67177629470825</v>
+        <v>5.67177581787109</v>
       </c>
       <c r="H35" t="n">
         <v>17521</v>
@@ -1442,7 +1442,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G37" t="n">
-        <v>5.63982200622559</v>
+        <v>5.6398229598999</v>
       </c>
       <c r="H37" t="n">
         <v>8243</v>
@@ -1500,7 +1500,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G39" t="n">
-        <v>5.7436728477478</v>
+        <v>5.74367237091064</v>
       </c>
       <c r="H39" t="n">
         <v>7628</v>
@@ -1529,7 +1529,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G40" t="n">
-        <v>5.67976570129395</v>
+        <v>5.67976474761963</v>
       </c>
       <c r="H40" t="n">
         <v>8522</v>
@@ -1558,7 +1558,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G41" t="n">
-        <v>5.71171808242798</v>
+        <v>5.71171855926514</v>
       </c>
       <c r="H41" t="n">
         <v>4672</v>
@@ -1587,7 +1587,7 @@
         <v>7.18499994277954</v>
       </c>
       <c r="G42" t="n">
-        <v>5.73967790603638</v>
+        <v>5.73967838287354</v>
       </c>
       <c r="H42" t="n">
         <v>7589</v>
@@ -1645,7 +1645,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G44" t="n">
-        <v>5.67177629470825</v>
+        <v>5.67177581787109</v>
       </c>
       <c r="H44" t="n">
         <v>17200</v>
@@ -1703,7 +1703,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G46" t="n">
-        <v>5.72370100021362</v>
+        <v>5.72370147705078</v>
       </c>
       <c r="H46" t="n">
         <v>2398</v>
@@ -1732,7 +1732,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>5.6557993888855</v>
+        <v>5.65579986572266</v>
       </c>
       <c r="H47" t="n">
         <v>3372</v>
@@ -1790,7 +1790,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G49" t="n">
-        <v>5.82755136489868</v>
+        <v>5.82755041122437</v>
       </c>
       <c r="H49" t="n">
         <v>15519</v>
@@ -1819,7 +1819,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G50" t="n">
-        <v>5.81556844711304</v>
+        <v>5.81556797027588</v>
       </c>
       <c r="H50" t="n">
         <v>3160</v>
@@ -1877,7 +1877,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G52" t="n">
-        <v>5.82355690002441</v>
+        <v>5.82355642318726</v>
       </c>
       <c r="H52" t="n">
         <v>4780</v>
@@ -1906,7 +1906,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G53" t="n">
-        <v>5.90344047546387</v>
+        <v>5.90343999862671</v>
       </c>
       <c r="H53" t="n">
         <v>21076</v>
@@ -1964,7 +1964,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G55" t="n">
-        <v>6.23096561431885</v>
+        <v>6.23096609115601</v>
       </c>
       <c r="H55" t="n">
         <v>5741</v>
@@ -2051,7 +2051,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G58" t="n">
-        <v>6.32682657241821</v>
+        <v>6.32682704925537</v>
       </c>
       <c r="H58" t="n">
         <v>5452</v>
@@ -2080,7 +2080,7 @@
         <v>7.90500020980835</v>
       </c>
       <c r="G59" t="n">
-        <v>6.31484460830688</v>
+        <v>6.31484365463257</v>
       </c>
       <c r="H59" t="n">
         <v>3075</v>
@@ -2138,7 +2138,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G61" t="n">
-        <v>6.29487276077271</v>
+        <v>6.29487323760986</v>
       </c>
       <c r="H61" t="n">
         <v>7217</v>
@@ -2167,7 +2167,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G62" t="n">
-        <v>6.34679841995239</v>
+        <v>6.34679794311523</v>
       </c>
       <c r="H62" t="n">
         <v>5109</v>
@@ -2225,7 +2225,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G64" t="n">
-        <v>6.35079193115234</v>
+        <v>6.35079145431519</v>
       </c>
       <c r="H64" t="n">
         <v>17796</v>
@@ -2370,7 +2370,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G69" t="n">
-        <v>6.75021314620972</v>
+        <v>6.75021266937256</v>
       </c>
       <c r="H69" t="n">
         <v>26144</v>
@@ -2428,7 +2428,7 @@
         <v>8.5</v>
       </c>
       <c r="G71" t="n">
-        <v>6.79015445709229</v>
+        <v>6.79015588760376</v>
       </c>
       <c r="H71" t="n">
         <v>9688</v>
@@ -2457,7 +2457,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G72" t="n">
-        <v>6.86205053329468</v>
+        <v>6.86205148696899</v>
       </c>
       <c r="H72" t="n">
         <v>9488</v>
@@ -2486,7 +2486,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G73" t="n">
-        <v>7.02980756759644</v>
+        <v>7.02980804443359</v>
       </c>
       <c r="H73" t="n">
         <v>19379</v>
@@ -2544,7 +2544,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G75" t="n">
-        <v>7.69284725189209</v>
+        <v>7.69284629821777</v>
       </c>
       <c r="H75" t="n">
         <v>42958</v>
@@ -2573,7 +2573,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G76" t="n">
-        <v>8.34789562225342</v>
+        <v>8.34789657592773</v>
       </c>
       <c r="H76" t="n">
         <v>85982</v>
@@ -2602,7 +2602,7 @@
         <v>9.79500007629395</v>
       </c>
       <c r="G77" t="n">
-        <v>7.82465553283691</v>
+        <v>7.82465505599976</v>
       </c>
       <c r="H77" t="n">
         <v>137248</v>
@@ -2631,7 +2631,7 @@
         <v>9.24499988555908</v>
       </c>
       <c r="G78" t="n">
-        <v>7.3852915763855</v>
+        <v>7.38529205322266</v>
       </c>
       <c r="H78" t="n">
         <v>64285</v>
@@ -2689,7 +2689,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G80" t="n">
-        <v>7.14963483810425</v>
+        <v>7.14963293075562</v>
       </c>
       <c r="H80" t="n">
         <v>11155</v>
@@ -2718,7 +2718,7 @@
         <v>8.875</v>
       </c>
       <c r="G81" t="n">
-        <v>7.08972024917603</v>
+        <v>7.08972072601318</v>
       </c>
       <c r="H81" t="n">
         <v>23079</v>
@@ -2747,7 +2747,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G82" t="n">
-        <v>7.02980756759644</v>
+        <v>7.02980804443359</v>
       </c>
       <c r="H82" t="n">
         <v>18244</v>
@@ -2805,7 +2805,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G84" t="n">
-        <v>6.94592905044556</v>
+        <v>6.94592809677124</v>
       </c>
       <c r="H84" t="n">
         <v>5593</v>
@@ -2834,7 +2834,7 @@
         <v>8.78499984741211</v>
       </c>
       <c r="G85" t="n">
-        <v>7.15776968002319</v>
+        <v>7.15776920318604</v>
       </c>
       <c r="H85" t="n">
         <v>12088</v>
@@ -2921,7 +2921,7 @@
         <v>8.14500045776367</v>
       </c>
       <c r="G88" t="n">
-        <v>6.63631629943848</v>
+        <v>6.63631582260132</v>
       </c>
       <c r="H88" t="n">
         <v>11875</v>
@@ -2950,7 +2950,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G89" t="n">
-        <v>6.47743511199951</v>
+        <v>6.47743558883667</v>
       </c>
       <c r="H89" t="n">
         <v>51574</v>
@@ -3008,7 +3008,7 @@
         <v>8.25</v>
       </c>
       <c r="G91" t="n">
-        <v>6.72186708450317</v>
+        <v>6.72186660766602</v>
       </c>
       <c r="H91" t="n">
         <v>8811</v>
@@ -3066,7 +3066,7 @@
         <v>8.00500011444092</v>
       </c>
       <c r="G93" t="n">
-        <v>6.52224731445312</v>
+        <v>6.52224779129028</v>
       </c>
       <c r="H93" t="n">
         <v>3608</v>
@@ -3095,7 +3095,7 @@
         <v>8.24499988555908</v>
       </c>
       <c r="G94" t="n">
-        <v>6.71779251098633</v>
+        <v>6.71779298782349</v>
       </c>
       <c r="H94" t="n">
         <v>2103</v>
@@ -3240,7 +3240,7 @@
         <v>8.61499977111816</v>
       </c>
       <c r="G99" t="n">
-        <v>7.01925897598267</v>
+        <v>7.01925849914551</v>
       </c>
       <c r="H99" t="n">
         <v>10326</v>
@@ -3269,7 +3269,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G100" t="n">
-        <v>7.0233325958252</v>
+        <v>7.02333164215088</v>
       </c>
       <c r="H100" t="n">
         <v>4258</v>
@@ -3298,7 +3298,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G101" t="n">
-        <v>6.99074172973633</v>
+        <v>6.99074125289917</v>
       </c>
       <c r="H101" t="n">
         <v>8488</v>
@@ -3356,7 +3356,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G103" t="n">
-        <v>7.0233325958252</v>
+        <v>7.02333164215088</v>
       </c>
       <c r="H103" t="n">
         <v>1598</v>
@@ -3385,7 +3385,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G104" t="n">
-        <v>7.03148078918457</v>
+        <v>7.03147983551025</v>
       </c>
       <c r="H104" t="n">
         <v>4477</v>
@@ -3443,7 +3443,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G106" t="n">
-        <v>7.08851385116577</v>
+        <v>7.08851432800293</v>
       </c>
       <c r="H106" t="n">
         <v>16393</v>
@@ -3472,7 +3472,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G107" t="n">
-        <v>6.92963409423828</v>
+        <v>6.92963361740112</v>
       </c>
       <c r="H107" t="n">
         <v>14082</v>
@@ -3501,7 +3501,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G108" t="n">
-        <v>7.01518392562866</v>
+        <v>7.01518487930298</v>
       </c>
       <c r="H108" t="n">
         <v>3672</v>
@@ -3530,7 +3530,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G109" t="n">
-        <v>6.96629858016968</v>
+        <v>6.96629905700684</v>
       </c>
       <c r="H109" t="n">
         <v>3803</v>
@@ -3559,7 +3559,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>6.89296865463257</v>
+        <v>6.89296960830688</v>
       </c>
       <c r="H110" t="n">
         <v>13645</v>
@@ -3588,7 +3588,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G111" t="n">
-        <v>6.80334424972534</v>
+        <v>6.8033447265625</v>
       </c>
       <c r="H111" t="n">
         <v>4897</v>
@@ -3617,7 +3617,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G112" t="n">
-        <v>6.89296865463257</v>
+        <v>6.89296960830688</v>
       </c>
       <c r="H112" t="n">
         <v>4368</v>
@@ -3675,7 +3675,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G114" t="n">
-        <v>6.61594676971436</v>
+        <v>6.61594581604004</v>
       </c>
       <c r="H114" t="n">
         <v>2440</v>
@@ -3704,7 +3704,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G115" t="n">
-        <v>6.43669652938843</v>
+        <v>6.43669700622559</v>
       </c>
       <c r="H115" t="n">
         <v>6182</v>
@@ -3762,7 +3762,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G117" t="n">
-        <v>6.42040109634399</v>
+        <v>6.42040157318115</v>
       </c>
       <c r="H117" t="n">
         <v>6253</v>
@@ -3791,7 +3791,7 @@
         <v>7.75</v>
       </c>
       <c r="G118" t="n">
-        <v>6.31448030471802</v>
+        <v>6.31448125839233</v>
       </c>
       <c r="H118" t="n">
         <v>4631</v>
@@ -3820,7 +3820,7 @@
         <v>8.24499988555908</v>
       </c>
       <c r="G119" t="n">
-        <v>6.71779251098633</v>
+        <v>6.71779298782349</v>
       </c>
       <c r="H119" t="n">
         <v>5214</v>
@@ -3849,7 +3849,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>6.88482141494751</v>
+        <v>6.88482093811035</v>
       </c>
       <c r="H120" t="n">
         <v>5304</v>
@@ -3907,7 +3907,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G122" t="n">
-        <v>6.70557069778442</v>
+        <v>6.70557117462158</v>
       </c>
       <c r="H122" t="n">
         <v>3705</v>
@@ -3936,7 +3936,7 @@
         <v>8.26500034332275</v>
       </c>
       <c r="G123" t="n">
-        <v>6.73408794403076</v>
+        <v>6.73408842086792</v>
       </c>
       <c r="H123" t="n">
         <v>2839</v>
@@ -3994,7 +3994,7 @@
         <v>8</v>
       </c>
       <c r="G125" t="n">
-        <v>6.51817417144775</v>
+        <v>6.5181736946106</v>
       </c>
       <c r="H125" t="n">
         <v>6788</v>
@@ -4023,7 +4023,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G126" t="n">
-        <v>6.59150314331055</v>
+        <v>6.59150409698486</v>
       </c>
       <c r="H126" t="n">
         <v>3711</v>
@@ -4052,7 +4052,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G127" t="n">
-        <v>6.6281681060791</v>
+        <v>6.62816905975342</v>
       </c>
       <c r="H127" t="n">
         <v>2765</v>
@@ -4139,7 +4139,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G130" t="n">
-        <v>6.84408187866211</v>
+        <v>6.84408235549927</v>
       </c>
       <c r="H130" t="n">
         <v>5336</v>
@@ -4197,7 +4197,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G132" t="n">
-        <v>6.78704786300659</v>
+        <v>6.78704881668091</v>
       </c>
       <c r="H132" t="n">
         <v>2310</v>
@@ -4226,7 +4226,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G133" t="n">
-        <v>6.84408187866211</v>
+        <v>6.84408235549927</v>
       </c>
       <c r="H133" t="n">
         <v>988</v>
@@ -4255,7 +4255,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G134" t="n">
-        <v>6.84408187866211</v>
+        <v>6.84408235549927</v>
       </c>
       <c r="H134" t="n">
         <v>3155</v>
@@ -4284,7 +4284,7 @@
         <v>8.4350004196167</v>
       </c>
       <c r="G135" t="n">
-        <v>6.87260007858276</v>
+        <v>6.87259960174561</v>
       </c>
       <c r="H135" t="n">
         <v>1346</v>
@@ -4313,7 +4313,7 @@
         <v>8.4350004196167</v>
       </c>
       <c r="G136" t="n">
-        <v>6.87260007858276</v>
+        <v>6.87259960174561</v>
       </c>
       <c r="H136" t="n">
         <v>1346</v>
@@ -4342,7 +4342,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G137" t="n">
-        <v>6.84000968933105</v>
+        <v>6.8400092124939</v>
       </c>
       <c r="H137" t="n">
         <v>270</v>
@@ -4371,7 +4371,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G138" t="n">
-        <v>6.84408187866211</v>
+        <v>6.84408235549927</v>
       </c>
       <c r="H138" t="n">
         <v>6014</v>
@@ -4400,7 +4400,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G139" t="n">
-        <v>6.82778739929199</v>
+        <v>6.82778692245483</v>
       </c>
       <c r="H139" t="n">
         <v>5165</v>
@@ -4516,7 +4516,7 @@
         <v>8.32499980926514</v>
       </c>
       <c r="G143" t="n">
-        <v>6.78297424316406</v>
+        <v>6.7829737663269</v>
       </c>
       <c r="H143" t="n">
         <v>3906</v>
@@ -4661,7 +4661,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G148" t="n">
-        <v>6.80334424972534</v>
+        <v>6.8033447265625</v>
       </c>
       <c r="H148" t="n">
         <v>8280</v>
@@ -4719,7 +4719,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G150" t="n">
-        <v>6.82778739929199</v>
+        <v>6.82778692245483</v>
       </c>
       <c r="H150" t="n">
         <v>8840</v>
@@ -4748,7 +4748,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>6.7911229133606</v>
+        <v>6.79112243652344</v>
       </c>
       <c r="H151" t="n">
         <v>2739</v>
@@ -4806,7 +4806,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G153" t="n">
-        <v>6.83186101913452</v>
+        <v>6.83186054229736</v>
       </c>
       <c r="H153" t="n">
         <v>6046</v>
@@ -4835,7 +4835,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G154" t="n">
-        <v>6.84408187866211</v>
+        <v>6.84408235549927</v>
       </c>
       <c r="H154" t="n">
         <v>3182</v>
@@ -4893,7 +4893,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G156" t="n">
-        <v>6.84000968933105</v>
+        <v>6.8400092124939</v>
       </c>
       <c r="H156" t="n">
         <v>960</v>
@@ -5038,7 +5038,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G161" t="n">
-        <v>6.85223007202148</v>
+        <v>6.85223054885864</v>
       </c>
       <c r="H161" t="n">
         <v>916</v>
@@ -5067,7 +5067,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G162" t="n">
-        <v>6.85223007202148</v>
+        <v>6.85223054885864</v>
       </c>
       <c r="H162" t="n">
         <v>3754</v>
@@ -5125,7 +5125,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G164" t="n">
-        <v>6.74631023406982</v>
+        <v>6.74630975723267</v>
       </c>
       <c r="H164" t="n">
         <v>2913</v>
@@ -5154,7 +5154,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G165" t="n">
-        <v>6.85223007202148</v>
+        <v>6.85223054885864</v>
       </c>
       <c r="H165" t="n">
         <v>6349</v>
@@ -5183,7 +5183,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G166" t="n">
-        <v>6.84408187866211</v>
+        <v>6.84408235549927</v>
       </c>
       <c r="H166" t="n">
         <v>859</v>
@@ -5241,7 +5241,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G168" t="n">
-        <v>6.83593416213989</v>
+        <v>6.83593559265137</v>
       </c>
       <c r="H168" t="n">
         <v>1264</v>
@@ -5299,7 +5299,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G170" t="n">
-        <v>7.11295700073242</v>
+        <v>7.11295652389526</v>
       </c>
       <c r="H170" t="n">
         <v>62180</v>
@@ -5328,7 +5328,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G171" t="n">
-        <v>6.93370819091797</v>
+        <v>6.93370771408081</v>
       </c>
       <c r="H171" t="n">
         <v>33132</v>
@@ -5386,7 +5386,7 @@
         <v>8.47500038146973</v>
       </c>
       <c r="G173" t="n">
-        <v>6.90519094467163</v>
+        <v>6.90519046783447</v>
       </c>
       <c r="H173" t="n">
         <v>6175</v>
@@ -5415,7 +5415,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G174" t="n">
-        <v>6.94185543060303</v>
+        <v>6.94185590744019</v>
       </c>
       <c r="H174" t="n">
         <v>4184</v>
@@ -5502,7 +5502,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G177" t="n">
-        <v>7.15369606018066</v>
+        <v>7.15369510650635</v>
       </c>
       <c r="H177" t="n">
         <v>13716</v>
@@ -5560,7 +5560,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G179" t="n">
-        <v>7.14554882049561</v>
+        <v>7.14554834365845</v>
       </c>
       <c r="H179" t="n">
         <v>9000</v>
@@ -5589,7 +5589,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G180" t="n">
-        <v>7.10480928421021</v>
+        <v>7.10480976104736</v>
       </c>
       <c r="H180" t="n">
         <v>3695</v>
@@ -5618,7 +5618,7 @@
         <v>8.60499954223633</v>
       </c>
       <c r="G181" t="n">
-        <v>7.01111030578613</v>
+        <v>7.01111125946045</v>
       </c>
       <c r="H181" t="n">
         <v>2628</v>
@@ -5705,7 +5705,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G184" t="n">
-        <v>7.19443464279175</v>
+        <v>7.19443416595459</v>
       </c>
       <c r="H184" t="n">
         <v>11223</v>
@@ -5734,7 +5734,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G185" t="n">
-        <v>7.35738897323608</v>
+        <v>7.35738849639893</v>
       </c>
       <c r="H185" t="n">
         <v>56641</v>
@@ -5763,7 +5763,7 @@
         <v>9.25</v>
       </c>
       <c r="G186" t="n">
-        <v>7.5366382598877</v>
+        <v>7.53663873672485</v>
       </c>
       <c r="H186" t="n">
         <v>43231</v>
@@ -5821,7 +5821,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G188" t="n">
-        <v>7.49182653427124</v>
+        <v>7.49182605743408</v>
       </c>
       <c r="H188" t="n">
         <v>21680</v>
@@ -5908,7 +5908,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G191" t="n">
-        <v>7.25146913528442</v>
+        <v>7.25146818161011</v>
       </c>
       <c r="H191" t="n">
         <v>8242</v>
@@ -5966,7 +5966,7 @@
         <v>8.96500015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>7.30442905426025</v>
+        <v>7.3044285774231</v>
       </c>
       <c r="H193" t="n">
         <v>3147</v>
@@ -6111,7 +6111,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G198" t="n">
-        <v>7.45516061782837</v>
+        <v>7.45516109466553</v>
       </c>
       <c r="H198" t="n">
         <v>27066</v>
@@ -6169,7 +6169,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G200" t="n">
-        <v>7.63441181182861</v>
+        <v>7.6344108581543</v>
       </c>
       <c r="H200" t="n">
         <v>15518</v>
@@ -6198,7 +6198,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G201" t="n">
-        <v>7.62626361846924</v>
+        <v>7.62626314163208</v>
       </c>
       <c r="H201" t="n">
         <v>8007</v>
@@ -6227,7 +6227,7 @@
         <v>9.24499988555908</v>
       </c>
       <c r="G202" t="n">
-        <v>7.53256464004517</v>
+        <v>7.53256511688232</v>
       </c>
       <c r="H202" t="n">
         <v>7128</v>
@@ -6256,7 +6256,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G203" t="n">
-        <v>7.63441181182861</v>
+        <v>7.6344108581543</v>
       </c>
       <c r="H203" t="n">
         <v>4985</v>
@@ -6314,7 +6314,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G205" t="n">
-        <v>7.61811542510986</v>
+        <v>7.61811637878418</v>
       </c>
       <c r="H205" t="n">
         <v>4407</v>
@@ -6372,7 +6372,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G207" t="n">
-        <v>7.65070676803589</v>
+        <v>7.65070629119873</v>
       </c>
       <c r="H207" t="n">
         <v>2927</v>
@@ -6401,7 +6401,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>7.77292251586914</v>
+        <v>7.7729229927063</v>
       </c>
       <c r="H208" t="n">
         <v>6320</v>
@@ -6459,7 +6459,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G210" t="n">
-        <v>7.4144229888916</v>
+        <v>7.41442441940308</v>
       </c>
       <c r="H210" t="n">
         <v>28708</v>
@@ -6488,7 +6488,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G211" t="n">
-        <v>7.4144229888916</v>
+        <v>7.41442441940308</v>
       </c>
       <c r="H211" t="n">
         <v>6682</v>
@@ -6517,7 +6517,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G212" t="n">
-        <v>7.35738897323608</v>
+        <v>7.35738849639893</v>
       </c>
       <c r="H212" t="n">
         <v>911</v>
@@ -6546,7 +6546,7 @@
         <v>8.99499988555908</v>
       </c>
       <c r="G213" t="n">
-        <v>7.32887125015259</v>
+        <v>7.32887172698975</v>
       </c>
       <c r="H213" t="n">
         <v>47666</v>
@@ -6575,7 +6575,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G214" t="n">
-        <v>7.19443464279175</v>
+        <v>7.19443416595459</v>
       </c>
       <c r="H214" t="n">
         <v>7414</v>
@@ -6691,7 +6691,7 @@
         <v>8.5649995803833</v>
       </c>
       <c r="G218" t="n">
-        <v>6.97852039337158</v>
+        <v>6.97851991653442</v>
       </c>
       <c r="H218" t="n">
         <v>5000</v>
@@ -6720,7 +6720,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G219" t="n">
-        <v>7.01518392562866</v>
+        <v>7.01518487930298</v>
       </c>
       <c r="H219" t="n">
         <v>3968</v>
@@ -6749,7 +6749,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G220" t="n">
-        <v>6.84000968933105</v>
+        <v>6.8400092124939</v>
       </c>
       <c r="H220" t="n">
         <v>11363</v>
@@ -6778,7 +6778,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G221" t="n">
-        <v>6.83593416213989</v>
+        <v>6.83593559265137</v>
       </c>
       <c r="H221" t="n">
         <v>11021</v>
@@ -6894,7 +6894,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G225" t="n">
-        <v>7.34924221038818</v>
+        <v>7.34924125671387</v>
       </c>
       <c r="H225" t="n">
         <v>34117</v>
@@ -6923,7 +6923,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G226" t="n">
-        <v>7.44701433181763</v>
+        <v>7.44701385498047</v>
       </c>
       <c r="H226" t="n">
         <v>3064</v>
@@ -6952,7 +6952,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G227" t="n">
-        <v>7.23517274856567</v>
+        <v>7.23517322540283</v>
       </c>
       <c r="H227" t="n">
         <v>26085</v>
@@ -6981,7 +6981,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G228" t="n">
-        <v>7.10480928421021</v>
+        <v>7.10480976104736</v>
       </c>
       <c r="H228" t="n">
         <v>8424</v>
@@ -7010,7 +7010,7 @@
         <v>8.63500022888184</v>
       </c>
       <c r="G229" t="n">
-        <v>7.03555393218994</v>
+        <v>7.0355544090271</v>
       </c>
       <c r="H229" t="n">
         <v>2732</v>
@@ -7068,7 +7068,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G231" t="n">
-        <v>7.10480928421021</v>
+        <v>7.10480976104736</v>
       </c>
       <c r="H231" t="n">
         <v>1189</v>
@@ -7155,7 +7155,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G234" t="n">
-        <v>6.99888944625854</v>
+        <v>6.9988899230957</v>
       </c>
       <c r="H234" t="n">
         <v>4106</v>
@@ -7184,7 +7184,7 @@
         <v>8.52499961853027</v>
       </c>
       <c r="G235" t="n">
-        <v>6.94592905044556</v>
+        <v>6.94592809677124</v>
       </c>
       <c r="H235" t="n">
         <v>5717</v>
@@ -7358,7 +7358,7 @@
         <v>9.24499988555908</v>
       </c>
       <c r="G241" t="n">
-        <v>7.53256464004517</v>
+        <v>7.53256511688232</v>
       </c>
       <c r="H241" t="n">
         <v>71341</v>
@@ -7387,7 +7387,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G242" t="n">
-        <v>7.65885496139526</v>
+        <v>7.65885400772095</v>
       </c>
       <c r="H242" t="n">
         <v>14906</v>
@@ -7416,7 +7416,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G243" t="n">
-        <v>7.71181440353394</v>
+        <v>7.71181488037109</v>
       </c>
       <c r="H243" t="n">
         <v>30935</v>
@@ -7445,7 +7445,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G244" t="n">
-        <v>7.72403573989868</v>
+        <v>7.72403478622437</v>
       </c>
       <c r="H244" t="n">
         <v>19310</v>
@@ -7503,7 +7503,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G246" t="n">
-        <v>7.90328598022461</v>
+        <v>7.90328645706177</v>
       </c>
       <c r="H246" t="n">
         <v>20713</v>
@@ -7532,7 +7532,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G247" t="n">
-        <v>7.96031904220581</v>
+        <v>7.96032047271729</v>
       </c>
       <c r="H247" t="n">
         <v>10737</v>
@@ -7561,7 +7561,7 @@
         <v>9.9350004196167</v>
       </c>
       <c r="G248" t="n">
-        <v>8.09475708007812</v>
+        <v>8.09475612640381</v>
       </c>
       <c r="H248" t="n">
         <v>11336</v>
@@ -7590,7 +7590,7 @@
         <v>9.98499965667725</v>
       </c>
       <c r="G249" t="n">
-        <v>8.13549423217773</v>
+        <v>8.13549518585205</v>
       </c>
       <c r="H249" t="n">
         <v>10061</v>
@@ -7619,7 +7619,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G250" t="n">
-        <v>8.09068393707275</v>
+        <v>8.09068298339844</v>
       </c>
       <c r="H250" t="n">
         <v>10923</v>
@@ -7677,7 +7677,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G252" t="n">
-        <v>7.90328598022461</v>
+        <v>7.90328645706177</v>
       </c>
       <c r="H252" t="n">
         <v>7899</v>
@@ -7706,7 +7706,7 @@
         <v>9.72500038146973</v>
       </c>
       <c r="G253" t="n">
-        <v>7.92365503311157</v>
+        <v>7.92365598678589</v>
       </c>
       <c r="H253" t="n">
         <v>7258</v>
@@ -7735,7 +7735,7 @@
         <v>9.8149995803833</v>
       </c>
       <c r="G254" t="n">
-        <v>7.99698448181152</v>
+        <v>7.99698400497437</v>
       </c>
       <c r="H254" t="n">
         <v>8073</v>
@@ -7793,7 +7793,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G256" t="n">
-        <v>8.06624126434326</v>
+        <v>8.06623935699463</v>
       </c>
       <c r="H256" t="n">
         <v>16787</v>
@@ -7822,7 +7822,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G257" t="n">
-        <v>8.06624126434326</v>
+        <v>8.06623935699463</v>
       </c>
       <c r="H257" t="n">
         <v>5473</v>
@@ -7851,7 +7851,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G258" t="n">
-        <v>8.38400173187256</v>
+        <v>8.38400077819824</v>
       </c>
       <c r="H258" t="n">
         <v>18321</v>
@@ -7880,7 +7880,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G259" t="n">
-        <v>8.54695510864258</v>
+        <v>8.54695606231689</v>
       </c>
       <c r="H259" t="n">
         <v>13981</v>
@@ -7909,7 +7909,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G260" t="n">
-        <v>8.77509117126465</v>
+        <v>8.77509212493896</v>
       </c>
       <c r="H260" t="n">
         <v>16781</v>
@@ -7967,7 +7967,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G262" t="n">
-        <v>8.66102409362793</v>
+        <v>8.6610221862793</v>
       </c>
       <c r="H262" t="n">
         <v>4089</v>
@@ -8025,7 +8025,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G264" t="n">
-        <v>8.68546676635742</v>
+        <v>8.68546772003174</v>
       </c>
       <c r="H264" t="n">
         <v>11212</v>
@@ -8083,7 +8083,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G266" t="n">
-        <v>8.83212661743164</v>
+        <v>8.83212566375732</v>
       </c>
       <c r="H266" t="n">
         <v>14439</v>
@@ -8199,7 +8199,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G270" t="n">
-        <v>10.0624322891235</v>
+        <v>10.0624313354492</v>
       </c>
       <c r="H270" t="n">
         <v>158289</v>
@@ -8257,7 +8257,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G272" t="n">
-        <v>9.75281810760498</v>
+        <v>9.75281715393066</v>
       </c>
       <c r="H272" t="n">
         <v>62164</v>
@@ -8286,7 +8286,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G273" t="n">
-        <v>9.53282928466797</v>
+        <v>9.53282833099365</v>
       </c>
       <c r="H273" t="n">
         <v>30099</v>
@@ -8344,7 +8344,7 @@
         <v>12.75</v>
       </c>
       <c r="G275" t="n">
-        <v>10.3883409500122</v>
+        <v>10.3883419036865</v>
       </c>
       <c r="H275" t="n">
         <v>79740</v>
@@ -8373,7 +8373,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G276" t="n">
-        <v>10.5349988937378</v>
+        <v>10.5349979400635</v>
       </c>
       <c r="H276" t="n">
         <v>85635</v>
@@ -8431,7 +8431,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G278" t="n">
-        <v>10.6409187316895</v>
+        <v>10.6409196853638</v>
       </c>
       <c r="H278" t="n">
         <v>55113</v>
@@ -8489,7 +8489,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G280" t="n">
-        <v>11.1542253494263</v>
+        <v>11.154224395752</v>
       </c>
       <c r="H280" t="n">
         <v>48845</v>
@@ -8518,7 +8518,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G281" t="n">
-        <v>11.2845878601074</v>
+        <v>11.2845907211304</v>
       </c>
       <c r="H281" t="n">
         <v>75384</v>
@@ -8547,7 +8547,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G282" t="n">
-        <v>11.3253269195557</v>
+        <v>11.3253259658813</v>
       </c>
       <c r="H282" t="n">
         <v>37053</v>
@@ -8576,7 +8576,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G283" t="n">
-        <v>11.48828125</v>
+        <v>11.4882822036743</v>
       </c>
       <c r="H283" t="n">
         <v>40824</v>
@@ -8634,7 +8634,7 @@
         <v>15</v>
       </c>
       <c r="G285" t="n">
-        <v>12.2215757369995</v>
+        <v>12.2215747833252</v>
       </c>
       <c r="H285" t="n">
         <v>78638</v>
@@ -8692,7 +8692,7 @@
         <v>15.7700004577637</v>
       </c>
       <c r="G287" t="n">
-        <v>12.8489513397217</v>
+        <v>12.8489503860474</v>
       </c>
       <c r="H287" t="n">
         <v>117545</v>
@@ -8721,7 +8721,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G288" t="n">
-        <v>13.7289037704468</v>
+        <v>13.7289056777954</v>
       </c>
       <c r="H288" t="n">
         <v>143297</v>
@@ -8866,7 +8866,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G293" t="n">
-        <v>14.0955495834351</v>
+        <v>14.0955514907837</v>
       </c>
       <c r="H293" t="n">
         <v>249868</v>
@@ -8895,7 +8895,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G294" t="n">
-        <v>13.5659484863281</v>
+        <v>13.5659475326538</v>
       </c>
       <c r="H294" t="n">
         <v>359273</v>
@@ -8924,7 +8924,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G295" t="n">
-        <v>13.9733362197876</v>
+        <v>13.973334312439</v>
       </c>
       <c r="H295" t="n">
         <v>102080</v>
@@ -9011,7 +9011,7 @@
         <v>15.5</v>
       </c>
       <c r="G298" t="n">
-        <v>12.628960609436</v>
+        <v>12.6289625167847</v>
       </c>
       <c r="H298" t="n">
         <v>63861</v>
@@ -9156,7 +9156,7 @@
         <v>16</v>
       </c>
       <c r="G303" t="n">
-        <v>13.0363483428955</v>
+        <v>13.0363473892212</v>
       </c>
       <c r="H303" t="n">
         <v>23424</v>
@@ -9185,7 +9185,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G304" t="n">
-        <v>13.0037565231323</v>
+        <v>13.0037574768066</v>
       </c>
       <c r="H304" t="n">
         <v>68169</v>
@@ -9214,7 +9214,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G305" t="n">
-        <v>13.0119037628174</v>
+        <v>13.0119047164917</v>
       </c>
       <c r="H305" t="n">
         <v>32421</v>
@@ -9243,7 +9243,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G306" t="n">
-        <v>12.9874610900879</v>
+        <v>12.9874620437622</v>
       </c>
       <c r="H306" t="n">
         <v>16171</v>
@@ -9272,7 +9272,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G307" t="n">
-        <v>13.0119037628174</v>
+        <v>13.0119047164917</v>
       </c>
       <c r="H307" t="n">
         <v>30877</v>
@@ -9301,7 +9301,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G308" t="n">
-        <v>13.2481889724731</v>
+        <v>13.2481880187988</v>
       </c>
       <c r="H308" t="n">
         <v>27779</v>
@@ -9388,7 +9388,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G311" t="n">
-        <v>13.769642829895</v>
+        <v>13.7696418762207</v>
       </c>
       <c r="H311" t="n">
         <v>55505</v>
@@ -9417,7 +9417,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G312" t="n">
-        <v>13.8103818893433</v>
+        <v>13.8103809356689</v>
       </c>
       <c r="H312" t="n">
         <v>37474</v>
@@ -9475,7 +9475,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G314" t="n">
-        <v>14.0059261322021</v>
+        <v>14.0059270858765</v>
       </c>
       <c r="H314" t="n">
         <v>61864</v>
@@ -9533,7 +9533,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G316" t="n">
-        <v>13.9651880264282</v>
+        <v>13.9651870727539</v>
       </c>
       <c r="H316" t="n">
         <v>41577</v>
@@ -9562,7 +9562,7 @@
         <v>17.1299991607666</v>
       </c>
       <c r="G317" t="n">
-        <v>13.9570407867432</v>
+        <v>13.9570398330688</v>
       </c>
       <c r="H317" t="n">
         <v>38749</v>
@@ -9591,7 +9591,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G318" t="n">
-        <v>13.8674163818359</v>
+        <v>13.8674154281616</v>
       </c>
       <c r="H318" t="n">
         <v>22927</v>
@@ -9707,7 +9707,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G322" t="n">
-        <v>13.6311311721802</v>
+        <v>13.6311302185059</v>
       </c>
       <c r="H322" t="n">
         <v>17626</v>
@@ -9736,7 +9736,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G323" t="n">
-        <v>13.3459606170654</v>
+        <v>13.3459596633911</v>
       </c>
       <c r="H323" t="n">
         <v>50087</v>
@@ -9765,7 +9765,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G324" t="n">
-        <v>13.2807779312134</v>
+        <v>13.2807788848877</v>
       </c>
       <c r="H324" t="n">
         <v>25110</v>
@@ -9823,7 +9823,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G326" t="n">
-        <v>13.3785524368286</v>
+        <v>13.3785514831543</v>
       </c>
       <c r="H326" t="n">
         <v>13988</v>
@@ -9852,7 +9852,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G327" t="n">
-        <v>13.223744392395</v>
+        <v>13.2237453460693</v>
       </c>
       <c r="H327" t="n">
         <v>11118</v>
@@ -9881,7 +9881,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G328" t="n">
-        <v>13.3785524368286</v>
+        <v>13.3785514831543</v>
       </c>
       <c r="H328" t="n">
         <v>19232</v>
@@ -9910,7 +9910,7 @@
         <v>16</v>
       </c>
       <c r="G329" t="n">
-        <v>13.0363483428955</v>
+        <v>13.0363473892212</v>
       </c>
       <c r="H329" t="n">
         <v>33023</v>
@@ -10084,7 +10084,7 @@
         <v>15</v>
       </c>
       <c r="G335" t="n">
-        <v>12.2215757369995</v>
+        <v>12.2215747833252</v>
       </c>
       <c r="H335" t="n">
         <v>24693</v>
@@ -10113,7 +10113,7 @@
         <v>15.3900003433228</v>
       </c>
       <c r="G336" t="n">
-        <v>12.5393371582031</v>
+        <v>12.5393381118774</v>
       </c>
       <c r="H336" t="n">
         <v>16213</v>
@@ -10142,7 +10142,7 @@
         <v>15.5</v>
       </c>
       <c r="G337" t="n">
-        <v>12.628960609436</v>
+        <v>12.6289625167847</v>
       </c>
       <c r="H337" t="n">
         <v>20705</v>
@@ -10171,7 +10171,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G338" t="n">
-        <v>13.0200529098511</v>
+        <v>13.0200519561768</v>
       </c>
       <c r="H338" t="n">
         <v>72522</v>
@@ -10200,7 +10200,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G339" t="n">
-        <v>13.0444946289062</v>
+        <v>13.0444955825806</v>
       </c>
       <c r="H339" t="n">
         <v>29767</v>
@@ -10258,7 +10258,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G341" t="n">
-        <v>13.0355949401855</v>
+        <v>13.0355958938599</v>
       </c>
       <c r="H341" t="n">
         <v>14592</v>
@@ -10287,7 +10287,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G342" t="n">
-        <v>12.7121934890747</v>
+        <v>12.7121915817261</v>
       </c>
       <c r="H342" t="n">
         <v>36835</v>
@@ -10316,7 +10316,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G343" t="n">
-        <v>12.5463447570801</v>
+        <v>12.5463466644287</v>
       </c>
       <c r="H343" t="n">
         <v>30309</v>
@@ -10345,7 +10345,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G344" t="n">
-        <v>12.5546388626099</v>
+        <v>12.5546379089355</v>
       </c>
       <c r="H344" t="n">
         <v>21822</v>
@@ -10374,7 +10374,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G345" t="n">
-        <v>12.4551296234131</v>
+        <v>12.4551305770874</v>
       </c>
       <c r="H345" t="n">
         <v>24964</v>
@@ -10403,7 +10403,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G346" t="n">
-        <v>12.9360876083374</v>
+        <v>12.9360885620117</v>
       </c>
       <c r="H346" t="n">
         <v>38295</v>
@@ -10432,7 +10432,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G347" t="n">
-        <v>12.6790237426758</v>
+        <v>12.6790246963501</v>
       </c>
       <c r="H347" t="n">
         <v>28075</v>
@@ -10490,7 +10490,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G349" t="n">
-        <v>12.803409576416</v>
+        <v>12.8034086227417</v>
       </c>
       <c r="H349" t="n">
         <v>47915</v>
@@ -10577,7 +10577,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G352" t="n">
-        <v>12.3970823287964</v>
+        <v>12.397084236145</v>
       </c>
       <c r="H352" t="n">
         <v>21257</v>
@@ -10722,7 +10722,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G357" t="n">
-        <v>12.6292695999146</v>
+        <v>12.6292686462402</v>
       </c>
       <c r="H357" t="n">
         <v>11678</v>
@@ -10780,7 +10780,7 @@
         <v>15</v>
       </c>
       <c r="G359" t="n">
-        <v>12.4385452270508</v>
+        <v>12.4385442733765</v>
       </c>
       <c r="H359" t="n">
         <v>12449</v>
@@ -10838,7 +10838,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G361" t="n">
-        <v>12.6209764480591</v>
+        <v>12.6209774017334</v>
       </c>
       <c r="H361" t="n">
         <v>41002</v>
@@ -10867,7 +10867,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G362" t="n">
-        <v>12.5546388626099</v>
+        <v>12.5546379089355</v>
       </c>
       <c r="H362" t="n">
         <v>26774</v>
@@ -10925,7 +10925,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G364" t="n">
-        <v>12.7785310745239</v>
+        <v>12.7785320281982</v>
       </c>
       <c r="H364" t="n">
         <v>6011</v>
@@ -10954,7 +10954,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G365" t="n">
-        <v>12.7536554336548</v>
+        <v>12.7536544799805</v>
       </c>
       <c r="H365" t="n">
         <v>4595</v>
@@ -10983,7 +10983,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G366" t="n">
-        <v>12.803409576416</v>
+        <v>12.8034086227417</v>
       </c>
       <c r="H366" t="n">
         <v>13374</v>
@@ -11012,7 +11012,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G367" t="n">
-        <v>12.7785310745239</v>
+        <v>12.7785320281982</v>
       </c>
       <c r="H367" t="n">
         <v>18865</v>
@@ -11041,7 +11041,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G368" t="n">
-        <v>12.5712232589722</v>
+        <v>12.5712223052979</v>
       </c>
       <c r="H368" t="n">
         <v>4589</v>
@@ -11099,7 +11099,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G370" t="n">
-        <v>12.3390369415283</v>
+        <v>12.3390378952026</v>
       </c>
       <c r="H370" t="n">
         <v>10317</v>
@@ -11128,7 +11128,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G371" t="n">
-        <v>12.0156345367432</v>
+        <v>12.0156335830688</v>
       </c>
       <c r="H371" t="n">
         <v>17510</v>
@@ -11186,7 +11186,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G373" t="n">
-        <v>11.8746643066406</v>
+        <v>11.8746633529663</v>
       </c>
       <c r="H373" t="n">
         <v>16874</v>
@@ -11215,7 +11215,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G374" t="n">
-        <v>11.5844316482544</v>
+        <v>11.5844326019287</v>
       </c>
       <c r="H374" t="n">
         <v>14355</v>
@@ -11273,7 +11273,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G376" t="n">
-        <v>11.6922340393066</v>
+        <v>11.6922330856323</v>
       </c>
       <c r="H376" t="n">
         <v>34667</v>
@@ -11302,7 +11302,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G377" t="n">
-        <v>11.6922340393066</v>
+        <v>11.6922330856323</v>
       </c>
       <c r="H377" t="n">
         <v>12470</v>
@@ -11331,7 +11331,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G378" t="n">
-        <v>11.8912487030029</v>
+        <v>11.8912496566772</v>
       </c>
       <c r="H378" t="n">
         <v>12393</v>
@@ -11360,7 +11360,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G379" t="n">
-        <v>11.8000335693359</v>
+        <v>11.8000326156616</v>
       </c>
       <c r="H379" t="n">
         <v>4581</v>
@@ -11418,7 +11418,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>11.8580799102783</v>
+        <v>11.858078956604</v>
       </c>
       <c r="H381" t="n">
         <v>7017</v>
@@ -11447,7 +11447,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G382" t="n">
-        <v>11.67564868927</v>
+        <v>11.6756477355957</v>
       </c>
       <c r="H382" t="n">
         <v>6885</v>
@@ -11476,7 +11476,7 @@
         <v>14.1099996566772</v>
       </c>
       <c r="G383" t="n">
-        <v>11.7005243301392</v>
+        <v>11.7005252838135</v>
       </c>
       <c r="H383" t="n">
         <v>12173</v>
@@ -11505,7 +11505,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G384" t="n">
-        <v>11.5346784591675</v>
+        <v>11.5346765518188</v>
       </c>
       <c r="H384" t="n">
         <v>6657</v>
@@ -11592,7 +11592,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G387" t="n">
-        <v>11.3439540863037</v>
+        <v>11.3439531326294</v>
       </c>
       <c r="H387" t="n">
         <v>8433</v>
@@ -11621,7 +11621,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G388" t="n">
-        <v>11.2776155471802</v>
+        <v>11.2776145935059</v>
       </c>
       <c r="H388" t="n">
         <v>12024</v>
@@ -11766,7 +11766,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G393" t="n">
-        <v>11.3356609344482</v>
+        <v>11.3356618881226</v>
       </c>
       <c r="H393" t="n">
         <v>9178</v>
@@ -11795,7 +11795,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G394" t="n">
-        <v>11.3107852935791</v>
+        <v>11.3107843399048</v>
       </c>
       <c r="H394" t="n">
         <v>5662</v>
@@ -11882,7 +11882,7 @@
         <v>13.5</v>
       </c>
       <c r="G397" t="n">
-        <v>11.1946897506714</v>
+        <v>11.1946907043457</v>
       </c>
       <c r="H397" t="n">
         <v>8673</v>
@@ -11940,7 +11940,7 @@
         <v>14</v>
       </c>
       <c r="G399" t="n">
-        <v>11.6093091964722</v>
+        <v>11.6093082427979</v>
       </c>
       <c r="H399" t="n">
         <v>8182</v>
@@ -11969,7 +11969,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G400" t="n">
-        <v>11.6258935928345</v>
+        <v>11.6258945465088</v>
       </c>
       <c r="H400" t="n">
         <v>6992</v>
@@ -12027,7 +12027,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G402" t="n">
-        <v>11.6839399337769</v>
+        <v>11.6839408874512</v>
       </c>
       <c r="H402" t="n">
         <v>6860</v>
@@ -12056,7 +12056,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G403" t="n">
-        <v>11.6258935928345</v>
+        <v>11.6258945465088</v>
       </c>
       <c r="H403" t="n">
         <v>7152</v>
@@ -12114,7 +12114,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G405" t="n">
-        <v>11.6839399337769</v>
+        <v>11.6839408874512</v>
       </c>
       <c r="H405" t="n">
         <v>7252</v>
@@ -12201,7 +12201,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G408" t="n">
-        <v>12.7785310745239</v>
+        <v>12.7785320281982</v>
       </c>
       <c r="H408" t="n">
         <v>149181</v>
@@ -12259,7 +12259,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G410" t="n">
-        <v>12.6790237426758</v>
+        <v>12.6790246963501</v>
       </c>
       <c r="H410" t="n">
         <v>13482</v>
@@ -12288,7 +12288,7 @@
         <v>15.210000038147</v>
       </c>
       <c r="G411" t="n">
-        <v>12.6126852035522</v>
+        <v>12.6126842498779</v>
       </c>
       <c r="H411" t="n">
         <v>8603</v>
@@ -12317,7 +12317,7 @@
         <v>15</v>
       </c>
       <c r="G412" t="n">
-        <v>12.4385452270508</v>
+        <v>12.4385442733765</v>
       </c>
       <c r="H412" t="n">
         <v>25552</v>
@@ -12346,7 +12346,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G413" t="n">
-        <v>12.2229442596436</v>
+        <v>12.2229433059692</v>
       </c>
       <c r="H413" t="n">
         <v>15093</v>
@@ -12375,7 +12375,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G414" t="n">
-        <v>12.0322189331055</v>
+        <v>12.0322198867798</v>
       </c>
       <c r="H414" t="n">
         <v>15763</v>
@@ -12433,7 +12433,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G416" t="n">
-        <v>12.2809915542603</v>
+        <v>12.2809906005859</v>
       </c>
       <c r="H416" t="n">
         <v>18494</v>
@@ -12462,7 +12462,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G417" t="n">
-        <v>12.2395286560059</v>
+        <v>12.2395296096802</v>
       </c>
       <c r="H417" t="n">
         <v>7412</v>
@@ -12491,7 +12491,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G418" t="n">
-        <v>11.9575891494751</v>
+        <v>11.9575881958008</v>
       </c>
       <c r="H418" t="n">
         <v>15347</v>
@@ -12520,7 +12520,7 @@
         <v>14.5</v>
       </c>
       <c r="G419" t="n">
-        <v>12.0239276885986</v>
+        <v>12.0239267349243</v>
       </c>
       <c r="H419" t="n">
         <v>9220</v>
@@ -12549,7 +12549,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G420" t="n">
-        <v>11.9990491867065</v>
+        <v>11.9990510940552</v>
       </c>
       <c r="H420" t="n">
         <v>8947</v>
@@ -12665,7 +12665,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G424" t="n">
-        <v>12.15660572052</v>
+        <v>12.1566047668457</v>
       </c>
       <c r="H424" t="n">
         <v>15306</v>
@@ -12694,7 +12694,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G425" t="n">
-        <v>12.0653886795044</v>
+        <v>12.0653896331787</v>
       </c>
       <c r="H425" t="n">
         <v>13711</v>
@@ -12723,7 +12723,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G426" t="n">
-        <v>12.0570974349976</v>
+        <v>12.0570955276489</v>
       </c>
       <c r="H426" t="n">
         <v>4562</v>
@@ -12781,7 +12781,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G428" t="n">
-        <v>12.3058671951294</v>
+        <v>12.3058681488037</v>
       </c>
       <c r="H428" t="n">
         <v>16024</v>
@@ -12926,7 +12926,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G433" t="n">
-        <v>12.4053764343262</v>
+        <v>12.4053754806519</v>
       </c>
       <c r="H433" t="n">
         <v>4750</v>
@@ -12955,7 +12955,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G434" t="n">
-        <v>12.3722076416016</v>
+        <v>12.3722057342529</v>
       </c>
       <c r="H434" t="n">
         <v>7940</v>
@@ -12984,7 +12984,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G435" t="n">
-        <v>12.4053764343262</v>
+        <v>12.4053754806519</v>
       </c>
       <c r="H435" t="n">
         <v>22095</v>
@@ -13013,7 +13013,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G436" t="n">
-        <v>12.173189163208</v>
+        <v>12.1731901168823</v>
       </c>
       <c r="H436" t="n">
         <v>38036</v>
@@ -13042,7 +13042,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G437" t="n">
-        <v>12.15660572052</v>
+        <v>12.1566047668457</v>
       </c>
       <c r="H437" t="n">
         <v>23483</v>
@@ -13071,7 +13071,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G438" t="n">
-        <v>12.3722076416016</v>
+        <v>12.3722057342529</v>
       </c>
       <c r="H438" t="n">
         <v>100631</v>
@@ -13100,7 +13100,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G439" t="n">
-        <v>12.3722076416016</v>
+        <v>12.3722057342529</v>
       </c>
       <c r="H439" t="n">
         <v>15556</v>
@@ -13158,7 +13158,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G441" t="n">
-        <v>12.1897745132446</v>
+        <v>12.1897735595703</v>
       </c>
       <c r="H441" t="n">
         <v>3927</v>
@@ -13187,7 +13187,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G442" t="n">
-        <v>12.15660572052</v>
+        <v>12.1566047668457</v>
       </c>
       <c r="H442" t="n">
         <v>5869</v>
@@ -13216,7 +13216,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G443" t="n">
-        <v>12.2726974487305</v>
+        <v>12.2726984024048</v>
       </c>
       <c r="H443" t="n">
         <v>14042</v>
@@ -13245,7 +13245,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G444" t="n">
-        <v>12.1151428222656</v>
+        <v>12.1151418685913</v>
       </c>
       <c r="H444" t="n">
         <v>17089</v>
@@ -13274,7 +13274,7 @@
         <v>14.75</v>
       </c>
       <c r="G445" t="n">
-        <v>12.2312364578247</v>
+        <v>12.2312355041504</v>
       </c>
       <c r="H445" t="n">
         <v>13439</v>
@@ -13332,7 +13332,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G447" t="n">
-        <v>12.2726974487305</v>
+        <v>12.2726984024048</v>
       </c>
       <c r="H447" t="n">
         <v>7518</v>
@@ -13361,7 +13361,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G448" t="n">
-        <v>12.2229442596436</v>
+        <v>12.2229433059692</v>
       </c>
       <c r="H448" t="n">
         <v>13038</v>
@@ -13419,7 +13419,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G450" t="n">
-        <v>12.2229442596436</v>
+        <v>12.2229433059692</v>
       </c>
       <c r="H450" t="n">
         <v>6397</v>
@@ -13477,7 +13477,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G452" t="n">
-        <v>12.3141613006592</v>
+        <v>12.3141603469849</v>
       </c>
       <c r="H452" t="n">
         <v>7915</v>
@@ -13506,7 +13506,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G453" t="n">
-        <v>12.3473300933838</v>
+        <v>12.3473291397095</v>
       </c>
       <c r="H453" t="n">
         <v>6380</v>
@@ -13535,7 +13535,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G454" t="n">
-        <v>12.2644052505493</v>
+        <v>12.2644062042236</v>
       </c>
       <c r="H454" t="n">
         <v>6141</v>
@@ -13593,7 +13593,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G456" t="n">
-        <v>12.5048856735229</v>
+        <v>12.5048847198486</v>
       </c>
       <c r="H456" t="n">
         <v>12039</v>
@@ -13651,7 +13651,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G458" t="n">
-        <v>12.5214700698853</v>
+        <v>12.5214691162109</v>
       </c>
       <c r="H458" t="n">
         <v>7823</v>
@@ -13680,7 +13680,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G459" t="n">
-        <v>12.5463447570801</v>
+        <v>12.5463466644287</v>
       </c>
       <c r="H459" t="n">
         <v>8305</v>
@@ -13709,7 +13709,7 @@
         <v>15</v>
       </c>
       <c r="G460" t="n">
-        <v>12.4385452270508</v>
+        <v>12.4385442733765</v>
       </c>
       <c r="H460" t="n">
         <v>18506</v>
@@ -13738,7 +13738,7 @@
         <v>15</v>
       </c>
       <c r="G461" t="n">
-        <v>12.4385452270508</v>
+        <v>12.4385442733765</v>
       </c>
       <c r="H461" t="n">
         <v>8683</v>
@@ -13854,7 +13854,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G465" t="n">
-        <v>12.5048856735229</v>
+        <v>12.5048847198486</v>
       </c>
       <c r="H465" t="n">
         <v>2531</v>
@@ -13883,7 +13883,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G466" t="n">
-        <v>12.5214700698853</v>
+        <v>12.5214691162109</v>
       </c>
       <c r="H466" t="n">
         <v>8349</v>
@@ -13912,7 +13912,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G467" t="n">
-        <v>12.5546388626099</v>
+        <v>12.5546379089355</v>
       </c>
       <c r="H467" t="n">
         <v>9941</v>
@@ -13941,7 +13941,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G468" t="n">
-        <v>12.5629301071167</v>
+        <v>12.562931060791</v>
       </c>
       <c r="H468" t="n">
         <v>8313</v>
@@ -13970,7 +13970,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G469" t="n">
-        <v>12.5878076553345</v>
+        <v>12.5878086090088</v>
       </c>
       <c r="H469" t="n">
         <v>8180</v>
@@ -14028,7 +14028,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G471" t="n">
-        <v>12.6292695999146</v>
+        <v>12.6292686462402</v>
       </c>
       <c r="H471" t="n">
         <v>6021</v>
@@ -14086,7 +14086,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G473" t="n">
-        <v>12.6790237426758</v>
+        <v>12.6790246963501</v>
       </c>
       <c r="H473" t="n">
         <v>10931</v>
@@ -14144,7 +14144,7 @@
         <v>15.25</v>
       </c>
       <c r="G475" t="n">
-        <v>12.6458549499512</v>
+        <v>12.6458539962769</v>
       </c>
       <c r="H475" t="n">
         <v>5117</v>
@@ -14173,7 +14173,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G476" t="n">
-        <v>12.6790237426758</v>
+        <v>12.6790246963501</v>
       </c>
       <c r="H476" t="n">
         <v>7899</v>
@@ -14289,7 +14289,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G480" t="n">
-        <v>12.7039012908936</v>
+        <v>12.7039003372192</v>
       </c>
       <c r="H480" t="n">
         <v>79987</v>
@@ -14405,7 +14405,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G484" t="n">
-        <v>13.1433963775635</v>
+        <v>13.1433973312378</v>
       </c>
       <c r="H484" t="n">
         <v>64007</v>
@@ -14463,7 +14463,7 @@
         <v>16</v>
       </c>
       <c r="G486" t="n">
-        <v>13.2677822113037</v>
+        <v>13.2677812576294</v>
       </c>
       <c r="H486" t="n">
         <v>48007</v>
@@ -14492,7 +14492,7 @@
         <v>16</v>
       </c>
       <c r="G487" t="n">
-        <v>13.2677822113037</v>
+        <v>13.2677812576294</v>
       </c>
       <c r="H487" t="n">
         <v>21644</v>
@@ -14608,7 +14608,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>13.9726324081421</v>
+        <v>13.9726343154907</v>
       </c>
       <c r="H491" t="n">
         <v>54222</v>
@@ -14666,7 +14666,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G493" t="n">
-        <v>13.1848573684692</v>
+        <v>13.1848583221436</v>
       </c>
       <c r="H493" t="n">
         <v>39092</v>
@@ -14724,7 +14724,7 @@
         <v>16.0900001525879</v>
       </c>
       <c r="G495" t="n">
-        <v>13.3424139022827</v>
+        <v>13.3424129486084</v>
       </c>
       <c r="H495" t="n">
         <v>11108</v>
@@ -14869,7 +14869,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G500" t="n">
-        <v>13.8067846298218</v>
+        <v>13.8067836761475</v>
       </c>
       <c r="H500" t="n">
         <v>53133</v>
@@ -14927,7 +14927,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G502" t="n">
-        <v>13.4170436859131</v>
+        <v>13.4170455932617</v>
       </c>
       <c r="H502" t="n">
         <v>10237</v>
@@ -15101,7 +15101,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G508" t="n">
-        <v>13.1102275848389</v>
+        <v>13.1102266311646</v>
       </c>
       <c r="H508" t="n">
         <v>9747</v>
@@ -15217,7 +15217,7 @@
         <v>16</v>
       </c>
       <c r="G512" t="n">
-        <v>13.2677822113037</v>
+        <v>13.2677812576294</v>
       </c>
       <c r="H512" t="n">
         <v>8800</v>
@@ -15246,7 +15246,7 @@
         <v>16</v>
       </c>
       <c r="G513" t="n">
-        <v>13.2677822113037</v>
+        <v>13.2677812576294</v>
       </c>
       <c r="H513" t="n">
         <v>4453</v>
@@ -15304,7 +15304,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>13.3507051467896</v>
+        <v>13.3507061004639</v>
       </c>
       <c r="H515" t="n">
         <v>18264</v>
@@ -15391,7 +15391,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G518" t="n">
-        <v>13.2843675613403</v>
+        <v>13.284366607666</v>
       </c>
       <c r="H518" t="n">
         <v>13632</v>
@@ -15449,7 +15449,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G520" t="n">
-        <v>13.2014436721802</v>
+        <v>13.2014427185059</v>
       </c>
       <c r="H520" t="n">
         <v>23672</v>
@@ -15507,7 +15507,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G522" t="n">
-        <v>13.2843675613403</v>
+        <v>13.284366607666</v>
       </c>
       <c r="H522" t="n">
         <v>12088</v>
@@ -15739,7 +15739,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G530" t="n">
-        <v>13.3507051467896</v>
+        <v>13.3507061004639</v>
       </c>
       <c r="H530" t="n">
         <v>9782</v>
@@ -15768,7 +15768,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G531" t="n">
-        <v>13.1848573684692</v>
+        <v>13.1848583221436</v>
       </c>
       <c r="H531" t="n">
         <v>15426</v>
@@ -15826,7 +15826,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G533" t="n">
-        <v>13.1019344329834</v>
+        <v>13.1019353866577</v>
       </c>
       <c r="H533" t="n">
         <v>17732</v>
@@ -15913,7 +15913,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>12.9360876083374</v>
+        <v>12.9360885620117</v>
       </c>
       <c r="H536" t="n">
         <v>64407</v>
@@ -15942,7 +15942,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G537" t="n">
-        <v>12.9360876083374</v>
+        <v>12.9360885620117</v>
       </c>
       <c r="H537" t="n">
         <v>69811</v>
@@ -16087,7 +16087,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G542" t="n">
-        <v>12.8199939727783</v>
+        <v>12.8199949264526</v>
       </c>
       <c r="H542" t="n">
         <v>13425</v>
@@ -16145,7 +16145,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G544" t="n">
-        <v>12.8863334655762</v>
+        <v>12.8863325119019</v>
       </c>
       <c r="H544" t="n">
         <v>10751</v>
@@ -16203,7 +16203,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G546" t="n">
-        <v>13.2511978149414</v>
+        <v>13.2511968612671</v>
       </c>
       <c r="H546" t="n">
         <v>29544</v>
@@ -16232,7 +16232,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G547" t="n">
-        <v>13.11851978302</v>
+        <v>13.1185178756714</v>
       </c>
       <c r="H547" t="n">
         <v>11521</v>
@@ -16261,7 +16261,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G548" t="n">
-        <v>13.0355949401855</v>
+        <v>13.0355958938599</v>
       </c>
       <c r="H548" t="n">
         <v>5330</v>
@@ -16377,7 +16377,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G552" t="n">
-        <v>12.8199939727783</v>
+        <v>12.8199949264526</v>
       </c>
       <c r="H552" t="n">
         <v>9029</v>
@@ -16406,7 +16406,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G553" t="n">
-        <v>12.7868251800537</v>
+        <v>12.7868232727051</v>
       </c>
       <c r="H553" t="n">
         <v>12202</v>
@@ -16638,7 +16638,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G561" t="n">
-        <v>13.0521802902222</v>
+        <v>13.0521793365479</v>
       </c>
       <c r="H561" t="n">
         <v>6186</v>
@@ -16725,7 +16725,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G564" t="n">
-        <v>13.1019344329834</v>
+        <v>13.1019353866577</v>
       </c>
       <c r="H564" t="n">
         <v>22720</v>
@@ -16754,7 +16754,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G565" t="n">
-        <v>12.8365783691406</v>
+        <v>12.8365793228149</v>
       </c>
       <c r="H565" t="n">
         <v>10281</v>
@@ -16870,7 +16870,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G569" t="n">
-        <v>13.0521802902222</v>
+        <v>13.0521793365479</v>
       </c>
       <c r="H569" t="n">
         <v>12181</v>
@@ -16899,7 +16899,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G570" t="n">
-        <v>13.0355949401855</v>
+        <v>13.0355958938599</v>
       </c>
       <c r="H570" t="n">
         <v>14678</v>
@@ -17015,7 +17015,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G574" t="n">
-        <v>13.0190105438232</v>
+        <v>13.0190114974976</v>
       </c>
       <c r="H574" t="n">
         <v>2693</v>
@@ -17044,7 +17044,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G575" t="n">
-        <v>13.0355949401855</v>
+        <v>13.0355958938599</v>
       </c>
       <c r="H575" t="n">
         <v>6605</v>
@@ -17073,7 +17073,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G576" t="n">
-        <v>12.9360876083374</v>
+        <v>12.9360885620117</v>
       </c>
       <c r="H576" t="n">
         <v>7063</v>
@@ -17131,7 +17131,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G578" t="n">
-        <v>13.1019344329834</v>
+        <v>13.1019353866577</v>
       </c>
       <c r="H578" t="n">
         <v>3820</v>
@@ -17160,7 +17160,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G579" t="n">
-        <v>13.0521802902222</v>
+        <v>13.0521793365479</v>
       </c>
       <c r="H579" t="n">
         <v>6568</v>
@@ -17218,7 +17218,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G581" t="n">
-        <v>13.0024251937866</v>
+        <v>13.0024271011353</v>
       </c>
       <c r="H581" t="n">
         <v>2866</v>
@@ -17247,7 +17247,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G582" t="n">
-        <v>13.0521802902222</v>
+        <v>13.0521793365479</v>
       </c>
       <c r="H582" t="n">
         <v>3784</v>
@@ -17276,7 +17276,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G583" t="n">
-        <v>13.0355949401855</v>
+        <v>13.0355958938599</v>
       </c>
       <c r="H583" t="n">
         <v>5685</v>
@@ -17305,7 +17305,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>12.9360876083374</v>
+        <v>12.9360885620117</v>
       </c>
       <c r="H584" t="n">
         <v>6280</v>
@@ -17334,7 +17334,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G585" t="n">
-        <v>13.0024251937866</v>
+        <v>13.0024271011353</v>
       </c>
       <c r="H585" t="n">
         <v>3549</v>
@@ -17363,7 +17363,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G586" t="n">
-        <v>13.2014436721802</v>
+        <v>13.2014427185059</v>
       </c>
       <c r="H586" t="n">
         <v>11401</v>
@@ -17421,7 +17421,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G588" t="n">
-        <v>13.1019344329834</v>
+        <v>13.1019353866577</v>
       </c>
       <c r="H588" t="n">
         <v>4013</v>
@@ -17450,7 +17450,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G589" t="n">
-        <v>13.1019344329834</v>
+        <v>13.1019353866577</v>
       </c>
       <c r="H589" t="n">
         <v>4473</v>
@@ -17479,7 +17479,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G590" t="n">
-        <v>13.2014436721802</v>
+        <v>13.2014427185059</v>
       </c>
       <c r="H590" t="n">
         <v>7153</v>
@@ -17537,7 +17537,7 @@
         <v>16</v>
       </c>
       <c r="G592" t="n">
-        <v>13.2677822113037</v>
+        <v>13.2677812576294</v>
       </c>
       <c r="H592" t="n">
         <v>9379</v>
@@ -17566,7 +17566,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G593" t="n">
-        <v>13.2843675613403</v>
+        <v>13.284366607666</v>
       </c>
       <c r="H593" t="n">
         <v>8278</v>
@@ -17653,7 +17653,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G596" t="n">
-        <v>13.2843675613403</v>
+        <v>13.284366607666</v>
       </c>
       <c r="H596" t="n">
         <v>15741</v>
@@ -17682,7 +17682,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>13.3507051467896</v>
+        <v>13.3507061004639</v>
       </c>
       <c r="H597" t="n">
         <v>7278</v>
@@ -17711,7 +17711,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G598" t="n">
-        <v>13.4968938827515</v>
+        <v>13.4968929290771</v>
       </c>
       <c r="H598" t="n">
         <v>4547</v>
@@ -17769,7 +17769,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G600" t="n">
-        <v>13.4288988113403</v>
+        <v>13.4288997650146</v>
       </c>
       <c r="H600" t="n">
         <v>4016</v>
@@ -17798,7 +17798,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G601" t="n">
-        <v>13.4458980560303</v>
+        <v>13.445897102356</v>
       </c>
       <c r="H601" t="n">
         <v>9348</v>
@@ -17856,7 +17856,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G603" t="n">
-        <v>13.5818872451782</v>
+        <v>13.5818862915039</v>
       </c>
       <c r="H603" t="n">
         <v>11082</v>
@@ -17943,7 +17943,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G606" t="n">
-        <v>13.4288988113403</v>
+        <v>13.4288997650146</v>
       </c>
       <c r="H606" t="n">
         <v>10655</v>
@@ -17972,7 +17972,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G607" t="n">
-        <v>13.1059255599976</v>
+        <v>13.1059246063232</v>
       </c>
       <c r="H607" t="n">
         <v>29495</v>
@@ -18001,7 +18001,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G608" t="n">
-        <v>13.0209331512451</v>
+        <v>13.0209321975708</v>
       </c>
       <c r="H608" t="n">
         <v>18632</v>
@@ -18059,7 +18059,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G610" t="n">
-        <v>12.5959663391113</v>
+        <v>12.5959672927856</v>
       </c>
       <c r="H610" t="n">
         <v>11692</v>
@@ -18088,7 +18088,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G611" t="n">
-        <v>12.7999505996704</v>
+        <v>12.7999515533447</v>
       </c>
       <c r="H611" t="n">
         <v>5742</v>
@@ -18117,7 +18117,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G612" t="n">
-        <v>13.0209331512451</v>
+        <v>13.0209321975708</v>
       </c>
       <c r="H612" t="n">
         <v>8035</v>
@@ -18175,7 +18175,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G614" t="n">
-        <v>12.5789680480957</v>
+        <v>12.5789699554443</v>
       </c>
       <c r="H614" t="n">
         <v>27324</v>
@@ -18233,7 +18233,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G616" t="n">
-        <v>13.8028688430786</v>
+        <v>13.8028678894043</v>
       </c>
       <c r="H616" t="n">
         <v>30653</v>
@@ -18262,7 +18262,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G617" t="n">
-        <v>13.7518720626831</v>
+        <v>13.7518730163574</v>
       </c>
       <c r="H617" t="n">
         <v>42337</v>
@@ -18291,7 +18291,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G618" t="n">
-        <v>13.5818872451782</v>
+        <v>13.5818862915039</v>
       </c>
       <c r="H618" t="n">
         <v>4207</v>
@@ -18436,7 +18436,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G623" t="n">
-        <v>13.3609046936035</v>
+        <v>13.3609056472778</v>
       </c>
       <c r="H623" t="n">
         <v>2632</v>
@@ -18465,7 +18465,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G624" t="n">
-        <v>13.4288988113403</v>
+        <v>13.4288997650146</v>
       </c>
       <c r="H624" t="n">
         <v>3232</v>
@@ -18494,7 +18494,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G625" t="n">
-        <v>13.3609046936035</v>
+        <v>13.3609056472778</v>
       </c>
       <c r="H625" t="n">
         <v>3083</v>
@@ -18668,7 +18668,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G631" t="n">
-        <v>13.4628953933716</v>
+        <v>13.4628963470459</v>
       </c>
       <c r="H631" t="n">
         <v>3970</v>
@@ -18697,7 +18697,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G632" t="n">
-        <v>13.3269071578979</v>
+        <v>13.3269081115723</v>
       </c>
       <c r="H632" t="n">
         <v>2271</v>
@@ -18784,7 +18784,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G635" t="n">
-        <v>13.0889263153076</v>
+        <v>13.0889253616333</v>
       </c>
       <c r="H635" t="n">
         <v>6319</v>
@@ -18813,7 +18813,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G636" t="n">
-        <v>12.8849439620972</v>
+        <v>12.8849430084229</v>
       </c>
       <c r="H636" t="n">
         <v>6634</v>
@@ -18900,7 +18900,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G639" t="n">
-        <v>13.1399221420288</v>
+        <v>13.1399230957031</v>
       </c>
       <c r="H639" t="n">
         <v>1580</v>
@@ -18929,7 +18929,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G640" t="n">
-        <v>12.9699373245239</v>
+        <v>12.9699363708496</v>
       </c>
       <c r="H640" t="n">
         <v>3125</v>
@@ -18958,7 +18958,7 @@
         <v>15.5</v>
       </c>
       <c r="G641" t="n">
-        <v>13.1739196777344</v>
+        <v>13.1739206314087</v>
       </c>
       <c r="H641" t="n">
         <v>6584</v>
@@ -18987,7 +18987,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G642" t="n">
-        <v>13.0719289779663</v>
+        <v>13.0719270706177</v>
       </c>
       <c r="H642" t="n">
         <v>10854</v>
@@ -19016,7 +19016,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G643" t="n">
-        <v>13.1229238510132</v>
+        <v>13.1229228973389</v>
       </c>
       <c r="H643" t="n">
         <v>4708</v>
@@ -19045,7 +19045,7 @@
         <v>15.5</v>
       </c>
       <c r="G644" t="n">
-        <v>13.1739196777344</v>
+        <v>13.1739206314087</v>
       </c>
       <c r="H644" t="n">
         <v>6247</v>
@@ -19103,7 +19103,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G646" t="n">
-        <v>12.9869356155396</v>
+        <v>12.9869346618652</v>
       </c>
       <c r="H646" t="n">
         <v>3681</v>
@@ -19132,7 +19132,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G647" t="n">
-        <v>13.0719289779663</v>
+        <v>13.0719270706177</v>
       </c>
       <c r="H647" t="n">
         <v>2506</v>
@@ -19161,7 +19161,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G648" t="n">
-        <v>13.1569204330444</v>
+        <v>13.1569223403931</v>
       </c>
       <c r="H648" t="n">
         <v>3677</v>
@@ -19335,7 +19335,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G654" t="n">
-        <v>13.0209331512451</v>
+        <v>13.0209321975708</v>
       </c>
       <c r="H654" t="n">
         <v>2203</v>
@@ -19364,7 +19364,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G655" t="n">
-        <v>12.9699373245239</v>
+        <v>12.9699363708496</v>
       </c>
       <c r="H655" t="n">
         <v>1831</v>
@@ -19393,7 +19393,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G656" t="n">
-        <v>13.0209331512451</v>
+        <v>13.0209321975708</v>
       </c>
       <c r="H656" t="n">
         <v>9822</v>
@@ -19422,7 +19422,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G657" t="n">
-        <v>13.1059255599976</v>
+        <v>13.1059246063232</v>
       </c>
       <c r="H657" t="n">
         <v>1798</v>
@@ -19451,7 +19451,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G658" t="n">
-        <v>12.9869356155396</v>
+        <v>12.9869346618652</v>
       </c>
       <c r="H658" t="n">
         <v>1229</v>
@@ -19480,7 +19480,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G659" t="n">
-        <v>12.9699373245239</v>
+        <v>12.9699363708496</v>
       </c>
       <c r="H659" t="n">
         <v>4278</v>
@@ -19509,7 +19509,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G660" t="n">
-        <v>13.0889263153076</v>
+        <v>13.0889253616333</v>
       </c>
       <c r="H660" t="n">
         <v>3774</v>
@@ -19683,7 +19683,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G666" t="n">
-        <v>12.8679456710815</v>
+        <v>12.8679447174072</v>
       </c>
       <c r="H666" t="n">
         <v>5831</v>
@@ -19741,7 +19741,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G668" t="n">
-        <v>12.6809616088867</v>
+        <v>12.6809606552124</v>
       </c>
       <c r="H668" t="n">
         <v>2882</v>
@@ -19770,7 +19770,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G669" t="n">
-        <v>12.7659530639648</v>
+        <v>12.7659540176392</v>
       </c>
       <c r="H669" t="n">
         <v>2986</v>
@@ -19799,7 +19799,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G670" t="n">
-        <v>12.4939765930176</v>
+        <v>12.4939756393433</v>
       </c>
       <c r="H670" t="n">
         <v>18477</v>
@@ -19857,7 +19857,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G672" t="n">
-        <v>12.0350122451782</v>
+        <v>12.0350141525269</v>
       </c>
       <c r="H672" t="n">
         <v>4976</v>
@@ -19886,7 +19886,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G673" t="n">
-        <v>12.4939765930176</v>
+        <v>12.4939756393433</v>
       </c>
       <c r="H673" t="n">
         <v>3249</v>
@@ -19915,7 +19915,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G674" t="n">
-        <v>12.5959663391113</v>
+        <v>12.5959672927856</v>
       </c>
       <c r="H674" t="n">
         <v>1792</v>
@@ -19973,7 +19973,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G676" t="n">
-        <v>12.5959663391113</v>
+        <v>12.5959672927856</v>
       </c>
       <c r="H676" t="n">
         <v>927</v>
@@ -20002,7 +20002,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G677" t="n">
-        <v>12.9869356155396</v>
+        <v>12.9869346618652</v>
       </c>
       <c r="H677" t="n">
         <v>3964</v>
@@ -20118,7 +20118,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G681" t="n">
-        <v>12.5789680480957</v>
+        <v>12.5789699554443</v>
       </c>
       <c r="H681" t="n">
         <v>9741</v>
@@ -20176,7 +20176,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G683" t="n">
-        <v>12.6809616088867</v>
+        <v>12.6809606552124</v>
       </c>
       <c r="H683" t="n">
         <v>4306</v>
@@ -20263,7 +20263,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G686" t="n">
-        <v>12.3579874038696</v>
+        <v>12.357985496521</v>
       </c>
       <c r="H686" t="n">
         <v>6124</v>
@@ -20292,7 +20292,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G687" t="n">
-        <v>12.5449714660645</v>
+        <v>12.5449724197388</v>
       </c>
       <c r="H687" t="n">
         <v>6669</v>
@@ -20321,7 +20321,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G688" t="n">
-        <v>12.5449714660645</v>
+        <v>12.5449724197388</v>
       </c>
       <c r="H688" t="n">
         <v>8177</v>
@@ -20379,7 +20379,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G690" t="n">
-        <v>12.714958190918</v>
+        <v>12.7149572372437</v>
       </c>
       <c r="H690" t="n">
         <v>3034</v>
@@ -20495,7 +20495,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G694" t="n">
-        <v>12.6469631195068</v>
+        <v>12.6469640731812</v>
       </c>
       <c r="H694" t="n">
         <v>3256</v>
@@ -20524,7 +20524,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G695" t="n">
-        <v>12.6299638748169</v>
+        <v>12.6299648284912</v>
       </c>
       <c r="H695" t="n">
         <v>767</v>
@@ -20553,7 +20553,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G696" t="n">
-        <v>12.6809616088867</v>
+        <v>12.6809606552124</v>
       </c>
       <c r="H696" t="n">
         <v>3412</v>
@@ -20611,7 +20611,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G698" t="n">
-        <v>12.5789680480957</v>
+        <v>12.5789699554443</v>
       </c>
       <c r="H698" t="n">
         <v>544</v>
@@ -20640,7 +20640,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G699" t="n">
-        <v>12.5789680480957</v>
+        <v>12.5789699554443</v>
       </c>
       <c r="H699" t="n">
         <v>1193</v>
@@ -20727,7 +20727,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G702" t="n">
-        <v>12.3749856948853</v>
+        <v>12.3749847412109</v>
       </c>
       <c r="H702" t="n">
         <v>2009</v>
@@ -20785,7 +20785,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G704" t="n">
-        <v>12.3579874038696</v>
+        <v>12.357985496521</v>
       </c>
       <c r="H704" t="n">
         <v>4542</v>
@@ -20843,7 +20843,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G706" t="n">
-        <v>11.7800340652466</v>
+        <v>11.7800331115723</v>
       </c>
       <c r="H706" t="n">
         <v>7420</v>
@@ -20930,7 +20930,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G709" t="n">
-        <v>10.9131050109863</v>
+        <v>10.9131059646606</v>
       </c>
       <c r="H709" t="n">
         <v>13875</v>
@@ -20988,7 +20988,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G711" t="n">
-        <v>11.0320959091187</v>
+        <v>11.03209400177</v>
       </c>
       <c r="H711" t="n">
         <v>10783</v>
@@ -21017,7 +21017,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G712" t="n">
-        <v>10.7601175308228</v>
+        <v>10.7601184844971</v>
       </c>
       <c r="H712" t="n">
         <v>3711</v>
@@ -21075,7 +21075,7 @@
         <v>12.5</v>
       </c>
       <c r="G714" t="n">
-        <v>10.6241283416748</v>
+        <v>10.6241292953491</v>
       </c>
       <c r="H714" t="n">
         <v>4353</v>
@@ -21104,7 +21104,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G715" t="n">
-        <v>10.5901308059692</v>
+        <v>10.5901327133179</v>
       </c>
       <c r="H715" t="n">
         <v>12512</v>
@@ -21220,7 +21220,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G719" t="n">
-        <v>10.4711418151855</v>
+        <v>10.4711408615112</v>
       </c>
       <c r="H719" t="n">
         <v>11515</v>
@@ -21249,7 +21249,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G720" t="n">
-        <v>10.5221376419067</v>
+        <v>10.5221366882324</v>
       </c>
       <c r="H720" t="n">
         <v>14593</v>
@@ -21278,7 +21278,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G721" t="n">
-        <v>10.6581258773804</v>
+        <v>10.6581268310547</v>
       </c>
       <c r="H721" t="n">
         <v>2544</v>
@@ -21307,7 +21307,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G722" t="n">
-        <v>10.5221376419067</v>
+        <v>10.5221366882324</v>
       </c>
       <c r="H722" t="n">
         <v>4192</v>
@@ -21336,7 +21336,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G723" t="n">
-        <v>10.7601175308228</v>
+        <v>10.7601184844971</v>
       </c>
       <c r="H723" t="n">
         <v>3418</v>
@@ -21394,7 +21394,7 @@
         <v>12.5</v>
       </c>
       <c r="G725" t="n">
-        <v>10.6241283416748</v>
+        <v>10.6241292953491</v>
       </c>
       <c r="H725" t="n">
         <v>618</v>
@@ -21510,7 +21510,7 @@
         <v>13</v>
       </c>
       <c r="G729" t="n">
-        <v>11.0490942001343</v>
+        <v>11.04909324646</v>
       </c>
       <c r="H729" t="n">
         <v>1235</v>
@@ -21597,7 +21597,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G732" t="n">
-        <v>11.3210716247559</v>
+        <v>11.3210725784302</v>
       </c>
       <c r="H732" t="n">
         <v>2650</v>
@@ -21655,7 +21655,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G734" t="n">
-        <v>11.2870740890503</v>
+        <v>11.2870750427246</v>
       </c>
       <c r="H734" t="n">
         <v>1704</v>
@@ -21713,7 +21713,7 @@
         <v>13</v>
       </c>
       <c r="G736" t="n">
-        <v>11.0490942001343</v>
+        <v>11.04909324646</v>
       </c>
       <c r="H736" t="n">
         <v>1901</v>
@@ -21800,7 +21800,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G739" t="n">
-        <v>10.8281126022339</v>
+        <v>10.8281116485596</v>
       </c>
       <c r="H739" t="n">
         <v>1908</v>
@@ -21916,7 +21916,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G743" t="n">
-        <v>10.0631742477417</v>
+        <v>10.063175201416</v>
       </c>
       <c r="H743" t="n">
         <v>1807</v>
@@ -22003,7 +22003,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G746" t="n">
-        <v>10.5561351776123</v>
+        <v>10.556134223938</v>
       </c>
       <c r="H746" t="n">
         <v>12940</v>
@@ -22032,7 +22032,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G747" t="n">
-        <v>11.0150966644287</v>
+        <v>11.015097618103</v>
       </c>
       <c r="H747" t="n">
         <v>7239</v>
@@ -22061,7 +22061,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G748" t="n">
-        <v>10.8281126022339</v>
+        <v>10.8281116485596</v>
       </c>
       <c r="H748" t="n">
         <v>12059</v>
@@ -22119,7 +22119,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G750" t="n">
-        <v>10.6071300506592</v>
+        <v>10.6071310043335</v>
       </c>
       <c r="H750" t="n">
         <v>955</v>
@@ -22148,7 +22148,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G751" t="n">
-        <v>10.7601175308228</v>
+        <v>10.7601184844971</v>
       </c>
       <c r="H751" t="n">
         <v>1943</v>
@@ -22177,7 +22177,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G752" t="n">
-        <v>10.6071300506592</v>
+        <v>10.6071310043335</v>
       </c>
       <c r="H752" t="n">
         <v>1850</v>
@@ -22206,7 +22206,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G753" t="n">
-        <v>10.4711418151855</v>
+        <v>10.4711408615112</v>
       </c>
       <c r="H753" t="n">
         <v>1160</v>
@@ -22380,7 +22380,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G759" t="n">
-        <v>9.0942554473877</v>
+        <v>9.09425449371338</v>
       </c>
       <c r="H759" t="n">
         <v>4520</v>
@@ -22467,7 +22467,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G762" t="n">
-        <v>9.17924785614014</v>
+        <v>9.17924690246582</v>
       </c>
       <c r="H762" t="n">
         <v>11417</v>
@@ -22525,7 +22525,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G764" t="n">
-        <v>10.318154335022</v>
+        <v>10.3181533813477</v>
       </c>
       <c r="H764" t="n">
         <v>2548</v>
@@ -22554,7 +22554,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G765" t="n">
-        <v>10.8281126022339</v>
+        <v>10.8281116485596</v>
       </c>
       <c r="H765" t="n">
         <v>8865</v>
@@ -22583,7 +22583,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G766" t="n">
-        <v>10.9131050109863</v>
+        <v>10.9131059646606</v>
       </c>
       <c r="H766" t="n">
         <v>6619</v>
@@ -22612,7 +22612,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G767" t="n">
-        <v>10.7771167755127</v>
+        <v>10.777117729187</v>
       </c>
       <c r="H767" t="n">
         <v>4276</v>
@@ -22641,7 +22641,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G768" t="n">
-        <v>10.6581258773804</v>
+        <v>10.6581268310547</v>
       </c>
       <c r="H768" t="n">
         <v>5651</v>
@@ -22699,7 +22699,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G770" t="n">
-        <v>10.9131050109863</v>
+        <v>10.9131059646606</v>
       </c>
       <c r="H770" t="n">
         <v>2821</v>
@@ -22728,7 +22728,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G771" t="n">
-        <v>10.5561351776123</v>
+        <v>10.556134223938</v>
       </c>
       <c r="H771" t="n">
         <v>4676</v>
@@ -22757,7 +22757,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G772" t="n">
-        <v>10.3521509170532</v>
+        <v>10.3521518707275</v>
       </c>
       <c r="H772" t="n">
         <v>4347</v>
@@ -22902,7 +22902,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G777" t="n">
-        <v>9.89318943023682</v>
+        <v>9.8931884765625</v>
       </c>
       <c r="H777" t="n">
         <v>8808</v>
@@ -22931,7 +22931,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>9.85919094085693</v>
+        <v>9.85919189453125</v>
       </c>
       <c r="H778" t="n">
         <v>5115</v>
@@ -22960,7 +22960,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G779" t="n">
-        <v>10.0971717834473</v>
+        <v>10.0971727371216</v>
       </c>
       <c r="H779" t="n">
         <v>4452</v>
@@ -23018,7 +23018,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G781" t="n">
-        <v>10.1821660995483</v>
+        <v>10.182165145874</v>
       </c>
       <c r="H781" t="n">
         <v>1732</v>
@@ -23076,7 +23076,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>10.2841567993164</v>
+        <v>10.2841577529907</v>
       </c>
       <c r="H783" t="n">
         <v>1967</v>
@@ -23134,7 +23134,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G785" t="n">
-        <v>10.3351526260376</v>
+        <v>10.3351516723633</v>
       </c>
       <c r="H785" t="n">
         <v>3117</v>
@@ -23192,7 +23192,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G787" t="n">
-        <v>10.318154335022</v>
+        <v>10.3181533813477</v>
       </c>
       <c r="H787" t="n">
         <v>1444</v>
@@ -23221,7 +23221,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>10.2841567993164</v>
+        <v>10.2841577529907</v>
       </c>
       <c r="H788" t="n">
         <v>1385</v>
@@ -23424,7 +23424,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G795" t="n">
-        <v>10.1821660995483</v>
+        <v>10.182165145874</v>
       </c>
       <c r="H795" t="n">
         <v>1668</v>
@@ -23511,7 +23511,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G798" t="n">
-        <v>10.0631742477417</v>
+        <v>10.063175201416</v>
       </c>
       <c r="H798" t="n">
         <v>4835</v>
@@ -23540,7 +23540,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G799" t="n">
-        <v>9.94418525695801</v>
+        <v>9.94418430328369</v>
       </c>
       <c r="H799" t="n">
         <v>3445</v>
@@ -23569,7 +23569,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G800" t="n">
-        <v>9.89318943023682</v>
+        <v>9.8931884765625</v>
       </c>
       <c r="H800" t="n">
         <v>3975</v>
@@ -23598,7 +23598,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G801" t="n">
-        <v>10.0631742477417</v>
+        <v>10.063175201416</v>
       </c>
       <c r="H801" t="n">
         <v>3813</v>
@@ -23627,7 +23627,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G802" t="n">
-        <v>9.89318943023682</v>
+        <v>9.8931884765625</v>
       </c>
       <c r="H802" t="n">
         <v>1415</v>
@@ -23656,7 +23656,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G803" t="n">
-        <v>10.1481685638428</v>
+        <v>10.1481676101685</v>
       </c>
       <c r="H803" t="n">
         <v>2714</v>
@@ -23743,7 +23743,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G806" t="n">
-        <v>10.0291776657104</v>
+        <v>10.0291786193848</v>
       </c>
       <c r="H806" t="n">
         <v>9149</v>
@@ -23772,7 +23772,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G807" t="n">
-        <v>10.0291776657104</v>
+        <v>10.0291786193848</v>
       </c>
       <c r="H807" t="n">
         <v>4574</v>
@@ -23859,7 +23859,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G810" t="n">
-        <v>9.94418525695801</v>
+        <v>9.94418430328369</v>
       </c>
       <c r="H810" t="n">
         <v>5595</v>
@@ -23888,7 +23888,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G811" t="n">
-        <v>10.0461759567261</v>
+        <v>10.0461769104004</v>
       </c>
       <c r="H811" t="n">
         <v>1756</v>
@@ -23917,7 +23917,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G812" t="n">
-        <v>10.0631742477417</v>
+        <v>10.063175201416</v>
       </c>
       <c r="H812" t="n">
         <v>1848</v>
@@ -23946,7 +23946,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G813" t="n">
-        <v>10.0291776657104</v>
+        <v>10.0291786193848</v>
       </c>
       <c r="H813" t="n">
         <v>1690</v>
@@ -24004,7 +24004,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G815" t="n">
-        <v>10.0971717834473</v>
+        <v>10.0971727371216</v>
       </c>
       <c r="H815" t="n">
         <v>1326</v>
@@ -24033,7 +24033,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G816" t="n">
-        <v>10.43714427948</v>
+        <v>10.4371433258057</v>
       </c>
       <c r="H816" t="n">
         <v>20119</v>
@@ -24149,7 +24149,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G820" t="n">
-        <v>10.7771167755127</v>
+        <v>10.777117729187</v>
       </c>
       <c r="H820" t="n">
         <v>2139</v>
@@ -24178,7 +24178,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G821" t="n">
-        <v>10.5901308059692</v>
+        <v>10.5901327133179</v>
       </c>
       <c r="H821" t="n">
         <v>4370</v>
@@ -24265,7 +24265,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G824" t="n">
-        <v>10.6071300506592</v>
+        <v>10.6071310043335</v>
       </c>
       <c r="H824" t="n">
         <v>5188</v>
@@ -24294,7 +24294,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G825" t="n">
-        <v>10.5901308059692</v>
+        <v>10.5901327133179</v>
       </c>
       <c r="H825" t="n">
         <v>1639</v>
@@ -24323,7 +24323,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G826" t="n">
-        <v>10.5051393508911</v>
+        <v>10.5051383972168</v>
       </c>
       <c r="H826" t="n">
         <v>1678</v>
@@ -24352,7 +24352,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G827" t="n">
-        <v>10.6581258773804</v>
+        <v>10.6581268310547</v>
       </c>
       <c r="H827" t="n">
         <v>6703</v>
@@ -24439,7 +24439,7 @@
         <v>12.5</v>
       </c>
       <c r="G830" t="n">
-        <v>10.6241283416748</v>
+        <v>10.6241292953491</v>
       </c>
       <c r="H830" t="n">
         <v>2256</v>
@@ -24729,7 +24729,7 @@
         <v>12.5</v>
       </c>
       <c r="G840" t="n">
-        <v>10.6241283416748</v>
+        <v>10.6241292953491</v>
       </c>
       <c r="H840" t="n">
         <v>5241</v>
@@ -24758,7 +24758,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G841" t="n">
-        <v>10.6581258773804</v>
+        <v>10.6581268310547</v>
       </c>
       <c r="H841" t="n">
         <v>2748</v>
@@ -24787,7 +24787,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G842" t="n">
-        <v>10.6581258773804</v>
+        <v>10.6581268310547</v>
       </c>
       <c r="H842" t="n">
         <v>5980</v>
@@ -24874,7 +24874,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G845" t="n">
-        <v>10.9131050109863</v>
+        <v>10.9131059646606</v>
       </c>
       <c r="H845" t="n">
         <v>11428</v>
@@ -24903,7 +24903,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G846" t="n">
-        <v>10.8961067199707</v>
+        <v>10.896107673645</v>
       </c>
       <c r="H846" t="n">
         <v>10666</v>
@@ -25077,7 +25077,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G852" t="n">
-        <v>10.3056888580322</v>
+        <v>10.3056879043579</v>
       </c>
       <c r="H852" t="n">
         <v>11347</v>
@@ -25338,7 +25338,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G861" t="n">
-        <v>9.47771167755127</v>
+        <v>9.47771072387695</v>
       </c>
       <c r="H861" t="n">
         <v>22858</v>
@@ -25367,7 +25367,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G862" t="n">
-        <v>9.33677864074707</v>
+        <v>9.33677768707275</v>
       </c>
       <c r="H862" t="n">
         <v>17370</v>
@@ -25425,7 +25425,7 @@
         <v>11</v>
       </c>
       <c r="G864" t="n">
-        <v>9.68910980224609</v>
+        <v>9.68910884857178</v>
       </c>
       <c r="H864" t="n">
         <v>18151</v>
@@ -25454,7 +25454,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G865" t="n">
-        <v>9.70672702789307</v>
+        <v>9.70672607421875</v>
       </c>
       <c r="H865" t="n">
         <v>127666</v>
@@ -25483,7 +25483,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G866" t="n">
-        <v>9.70672702789307</v>
+        <v>9.70672607421875</v>
       </c>
       <c r="H866" t="n">
         <v>12913</v>
@@ -25686,7 +25686,7 @@
         <v>11</v>
       </c>
       <c r="G873" t="n">
-        <v>9.68910980224609</v>
+        <v>9.68910884857178</v>
       </c>
       <c r="H873" t="n">
         <v>4194</v>
@@ -25744,7 +25744,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G875" t="n">
-        <v>9.75957489013672</v>
+        <v>9.75957584381104</v>
       </c>
       <c r="H875" t="n">
         <v>4354</v>
@@ -25802,7 +25802,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G877" t="n">
-        <v>9.77719211578369</v>
+        <v>9.77719306945801</v>
       </c>
       <c r="H877" t="n">
         <v>11030</v>
@@ -25831,7 +25831,7 @@
         <v>11</v>
       </c>
       <c r="G878" t="n">
-        <v>9.68910980224609</v>
+        <v>9.68910884857178</v>
       </c>
       <c r="H878" t="n">
         <v>3446</v>
@@ -25918,7 +25918,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G881" t="n">
-        <v>10.1119070053101</v>
+        <v>10.1119060516357</v>
       </c>
       <c r="H881" t="n">
         <v>9542</v>
@@ -26063,7 +26063,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G886" t="n">
-        <v>9.75957489013672</v>
+        <v>9.75957584381104</v>
       </c>
       <c r="H886" t="n">
         <v>23233</v>
@@ -26092,7 +26092,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G887" t="n">
-        <v>9.75957489013672</v>
+        <v>9.75957584381104</v>
       </c>
       <c r="H887" t="n">
         <v>2857</v>
@@ -26121,7 +26121,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G888" t="n">
-        <v>9.70672702789307</v>
+        <v>9.70672607421875</v>
       </c>
       <c r="H888" t="n">
         <v>4450</v>
@@ -26295,7 +26295,7 @@
         <v>11.5</v>
       </c>
       <c r="G894" t="n">
-        <v>10.129524230957</v>
+        <v>10.1295232772827</v>
       </c>
       <c r="H894" t="n">
         <v>3524</v>
@@ -26440,7 +26440,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G899" t="n">
-        <v>10.1119070053101</v>
+        <v>10.1119060516357</v>
       </c>
       <c r="H899" t="n">
         <v>14293</v>
@@ -26498,7 +26498,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G901" t="n">
-        <v>10.164755821228</v>
+        <v>10.1647567749023</v>
       </c>
       <c r="H901" t="n">
         <v>4467</v>
@@ -26730,7 +26730,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G909" t="n">
-        <v>10.3056888580322</v>
+        <v>10.3056879043579</v>
       </c>
       <c r="H909" t="n">
         <v>6017</v>
@@ -26788,7 +26788,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G911" t="n">
-        <v>10.3056888580322</v>
+        <v>10.3056879043579</v>
       </c>
       <c r="H911" t="n">
         <v>1589</v>
@@ -26846,7 +26846,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G913" t="n">
-        <v>10.2704544067383</v>
+        <v>10.2704553604126</v>
       </c>
       <c r="H913" t="n">
         <v>12358</v>
@@ -26933,7 +26933,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G916" t="n">
-        <v>10.164755821228</v>
+        <v>10.1647567749023</v>
       </c>
       <c r="H916" t="n">
         <v>5059</v>
@@ -26962,7 +26962,7 @@
         <v>11.5</v>
       </c>
       <c r="G917" t="n">
-        <v>10.129524230957</v>
+        <v>10.1295232772827</v>
       </c>
       <c r="H917" t="n">
         <v>2244</v>
@@ -26991,7 +26991,7 @@
         <v>11.5</v>
       </c>
       <c r="G918" t="n">
-        <v>10.129524230957</v>
+        <v>10.1295232772827</v>
       </c>
       <c r="H918" t="n">
         <v>10186</v>
@@ -27078,7 +27078,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G921" t="n">
-        <v>10.1119070053101</v>
+        <v>10.1119060516357</v>
       </c>
       <c r="H921" t="n">
         <v>5139</v>
@@ -27194,7 +27194,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G925" t="n">
-        <v>10.2704544067383</v>
+        <v>10.2704553604126</v>
       </c>
       <c r="H925" t="n">
         <v>771</v>
@@ -27223,7 +27223,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G926" t="n">
-        <v>10.3056888580322</v>
+        <v>10.3056879043579</v>
       </c>
       <c r="H926" t="n">
         <v>483</v>
@@ -27252,7 +27252,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G927" t="n">
-        <v>10.3056888580322</v>
+        <v>10.3056879043579</v>
       </c>
       <c r="H927" t="n">
         <v>4193</v>
@@ -27339,7 +27339,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G930" t="n">
-        <v>10.3937711715698</v>
+        <v>10.3937721252441</v>
       </c>
       <c r="H930" t="n">
         <v>8467</v>
@@ -27368,7 +27368,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G931" t="n">
-        <v>10.4818544387817</v>
+        <v>10.4818534851074</v>
       </c>
       <c r="H931" t="n">
         <v>3073</v>
@@ -27658,7 +27658,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G941" t="n">
-        <v>10.7989530563354</v>
+        <v>10.7989521026611</v>
       </c>
       <c r="H941" t="n">
         <v>3811</v>
@@ -28035,7 +28035,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G954" t="n">
-        <v>10.7461023330688</v>
+        <v>10.7461032867432</v>
       </c>
       <c r="H954" t="n">
         <v>3959</v>
@@ -28064,7 +28064,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G955" t="n">
-        <v>10.4466218948364</v>
+        <v>10.4466209411621</v>
       </c>
       <c r="H955" t="n">
         <v>13523</v>
@@ -28093,7 +28093,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G956" t="n">
-        <v>10.4818544387817</v>
+        <v>10.4818534851074</v>
       </c>
       <c r="H956" t="n">
         <v>1585</v>
@@ -28151,7 +28151,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G958" t="n">
-        <v>10.3937711715698</v>
+        <v>10.3937721252441</v>
       </c>
       <c r="H958" t="n">
         <v>5503</v>
@@ -28412,7 +28412,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G967" t="n">
-        <v>10.3233060836792</v>
+        <v>10.3233051300049</v>
       </c>
       <c r="H967" t="n">
         <v>4355</v>
@@ -28470,7 +28470,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G969" t="n">
-        <v>10.3056888580322</v>
+        <v>10.3056879043579</v>
       </c>
       <c r="H969" t="n">
         <v>4656</v>
@@ -28499,7 +28499,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G970" t="n">
-        <v>10.3056888580322</v>
+        <v>10.3056879043579</v>
       </c>
       <c r="H970" t="n">
         <v>1759</v>
@@ -28528,7 +28528,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G971" t="n">
-        <v>10.3056888580322</v>
+        <v>10.3056879043579</v>
       </c>
       <c r="H971" t="n">
         <v>1282</v>
@@ -28586,7 +28586,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G973" t="n">
-        <v>10.3056888580322</v>
+        <v>10.3056879043579</v>
       </c>
       <c r="H973" t="n">
         <v>9834</v>
@@ -28615,7 +28615,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G974" t="n">
-        <v>10.3056888580322</v>
+        <v>10.3056879043579</v>
       </c>
       <c r="H974" t="n">
         <v>6576</v>
@@ -28673,7 +28673,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G976" t="n">
-        <v>10.3056888580322</v>
+        <v>10.3056879043579</v>
       </c>
       <c r="H976" t="n">
         <v>7738</v>
@@ -28731,7 +28731,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G978" t="n">
-        <v>10.3056888580322</v>
+        <v>10.3056879043579</v>
       </c>
       <c r="H978" t="n">
         <v>3553</v>
@@ -28789,7 +28789,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G980" t="n">
-        <v>10.3937711715698</v>
+        <v>10.3937721252441</v>
       </c>
       <c r="H980" t="n">
         <v>6587</v>
@@ -29108,7 +29108,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G991" t="n">
-        <v>10.534704208374</v>
+        <v>10.5347051620483</v>
       </c>
       <c r="H991" t="n">
         <v>1588</v>
@@ -29195,7 +29195,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G994" t="n">
-        <v>10.7461023330688</v>
+        <v>10.7461032867432</v>
       </c>
       <c r="H994" t="n">
         <v>20163</v>
@@ -29253,7 +29253,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G996" t="n">
-        <v>10.6932535171509</v>
+        <v>10.6932525634766</v>
       </c>
       <c r="H996" t="n">
         <v>7115</v>
@@ -29282,7 +29282,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G997" t="n">
-        <v>10.7284860610962</v>
+        <v>10.7284870147705</v>
       </c>
       <c r="H997" t="n">
         <v>19210</v>
@@ -29891,7 +29891,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>10.4818544387817</v>
+        <v>10.4818534851074</v>
       </c>
       <c r="H1018" t="n">
         <v>1506</v>
@@ -30297,7 +30297,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1032" t="n">
-        <v>10.4466218948364</v>
+        <v>10.4466209411621</v>
       </c>
       <c r="H1032" t="n">
         <v>16605</v>
@@ -30529,7 +30529,7 @@
         <v>11.5</v>
       </c>
       <c r="G1040" t="n">
-        <v>10.129524230957</v>
+        <v>10.1295232772827</v>
       </c>
       <c r="H1040" t="n">
         <v>5403</v>
@@ -30558,7 +30558,7 @@
         <v>11.5</v>
       </c>
       <c r="G1041" t="n">
-        <v>10.129524230957</v>
+        <v>10.1295232772827</v>
       </c>
       <c r="H1041" t="n">
         <v>2612</v>
@@ -30587,7 +30587,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G1042" t="n">
-        <v>10.2704544067383</v>
+        <v>10.2704553604126</v>
       </c>
       <c r="H1042" t="n">
         <v>741</v>
@@ -30703,7 +30703,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1046" t="n">
-        <v>10.164755821228</v>
+        <v>10.1647567749023</v>
       </c>
       <c r="H1046" t="n">
         <v>4234</v>
@@ -30819,7 +30819,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1050" t="n">
-        <v>10.1119070053101</v>
+        <v>10.1119060516357</v>
       </c>
       <c r="H1050" t="n">
         <v>8520</v>
@@ -31051,7 +31051,7 @@
         <v>9</v>
       </c>
       <c r="G1058" t="n">
-        <v>7.92745351791382</v>
+        <v>7.9274525642395</v>
       </c>
       <c r="H1058" t="n">
         <v>50046</v>
@@ -31080,7 +31080,7 @@
         <v>9</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.92745351791382</v>
+        <v>7.9274525642395</v>
       </c>
       <c r="H1059" t="n">
         <v>41153</v>
@@ -31138,7 +31138,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G1061" t="n">
-        <v>7.86579561233521</v>
+        <v>7.86579465866089</v>
       </c>
       <c r="H1061" t="n">
         <v>13588</v>
@@ -31167,7 +31167,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1062" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1062" t="n">
         <v>20843</v>
@@ -31283,7 +31283,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G1066" t="n">
-        <v>5.78704118728638</v>
+        <v>5.78704071044922</v>
       </c>
       <c r="H1066" t="n">
         <v>39491</v>
@@ -31486,7 +31486,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1073" t="n">
-        <v>6.74714279174805</v>
+        <v>6.74714326858521</v>
       </c>
       <c r="H1073" t="n">
         <v>6635</v>
@@ -31631,7 +31631,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G1078" t="n">
-        <v>6.79118490219116</v>
+        <v>6.791184425354</v>
       </c>
       <c r="H1078" t="n">
         <v>5745</v>
@@ -31921,7 +31921,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1088" t="n">
-        <v>7.13470792770386</v>
+        <v>7.13470840454102</v>
       </c>
       <c r="H1088" t="n">
         <v>6794</v>
@@ -31979,7 +31979,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1090" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1090" t="n">
         <v>9003</v>
@@ -32008,7 +32008,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1091" t="n">
-        <v>7.41657257080078</v>
+        <v>7.41657209396362</v>
       </c>
       <c r="H1091" t="n">
         <v>11099</v>
@@ -32240,7 +32240,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1099" t="n">
-        <v>7.2051739692688</v>
+        <v>7.20517444610596</v>
       </c>
       <c r="H1099" t="n">
         <v>4563</v>
@@ -32501,7 +32501,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1108" t="n">
-        <v>6.43004512786865</v>
+        <v>6.43004560470581</v>
       </c>
       <c r="H1108" t="n">
         <v>13424</v>
@@ -32530,7 +32530,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1109" t="n">
-        <v>6.81760931015015</v>
+        <v>6.8176097869873</v>
       </c>
       <c r="H1109" t="n">
         <v>5340</v>
@@ -32588,7 +32588,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1111" t="n">
-        <v>7.13470792770386</v>
+        <v>7.13470840454102</v>
       </c>
       <c r="H1111" t="n">
         <v>3525</v>
@@ -32762,7 +32762,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1117" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1117" t="n">
         <v>19155</v>
@@ -32791,7 +32791,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1118" t="n">
-        <v>7.24040699005127</v>
+        <v>7.24040746688843</v>
       </c>
       <c r="H1118" t="n">
         <v>9119</v>
@@ -32878,7 +32878,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1121" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1121" t="n">
         <v>5107</v>
@@ -32907,7 +32907,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1122" t="n">
-        <v>7.83936882019043</v>
+        <v>7.83936977386475</v>
       </c>
       <c r="H1122" t="n">
         <v>42458</v>
@@ -32936,7 +32936,7 @@
         <v>9.5</v>
       </c>
       <c r="G1123" t="n">
-        <v>8.3678674697876</v>
+        <v>8.36786651611328</v>
       </c>
       <c r="H1123" t="n">
         <v>39790</v>
@@ -32994,7 +32994,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1125" t="n">
-        <v>8.63211536407471</v>
+        <v>8.63211631774902</v>
       </c>
       <c r="H1125" t="n">
         <v>34492</v>
@@ -33052,7 +33052,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G1127" t="n">
-        <v>8.29740047454834</v>
+        <v>8.29740142822266</v>
       </c>
       <c r="H1127" t="n">
         <v>15947</v>
@@ -33313,7 +33313,7 @@
         <v>9</v>
       </c>
       <c r="G1136" t="n">
-        <v>7.92745351791382</v>
+        <v>7.9274525642395</v>
       </c>
       <c r="H1136" t="n">
         <v>3365</v>
@@ -33400,7 +33400,7 @@
         <v>9</v>
       </c>
       <c r="G1139" t="n">
-        <v>7.92745351791382</v>
+        <v>7.9274525642395</v>
       </c>
       <c r="H1139" t="n">
         <v>3778</v>
@@ -33487,7 +33487,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G1142" t="n">
-        <v>7.5046558380127</v>
+        <v>7.50465631484985</v>
       </c>
       <c r="H1142" t="n">
         <v>4006</v>
@@ -33516,7 +33516,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1143" t="n">
-        <v>7.57512235641479</v>
+        <v>7.57512187957764</v>
       </c>
       <c r="H1143" t="n">
         <v>14330</v>
@@ -33574,7 +33574,7 @@
         <v>8.5</v>
       </c>
       <c r="G1145" t="n">
-        <v>7.48703956604004</v>
+        <v>7.48703908920288</v>
       </c>
       <c r="H1145" t="n">
         <v>4972</v>
@@ -33603,7 +33603,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1146" t="n">
-        <v>7.346107006073</v>
+        <v>7.34610652923584</v>
       </c>
       <c r="H1146" t="n">
         <v>3269</v>
@@ -33632,7 +33632,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1147" t="n">
-        <v>7.45180606842041</v>
+        <v>7.45180654525757</v>
       </c>
       <c r="H1147" t="n">
         <v>1581</v>
@@ -33661,7 +33661,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1148" t="n">
-        <v>7.43418884277344</v>
+        <v>7.4341893196106</v>
       </c>
       <c r="H1148" t="n">
         <v>3309</v>
@@ -33690,7 +33690,7 @@
         <v>8.5</v>
       </c>
       <c r="G1149" t="n">
-        <v>7.48703956604004</v>
+        <v>7.48703908920288</v>
       </c>
       <c r="H1149" t="n">
         <v>3485</v>
@@ -33719,7 +33719,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1150" t="n">
-        <v>7.45180606842041</v>
+        <v>7.45180654525757</v>
       </c>
       <c r="H1150" t="n">
         <v>4736</v>
@@ -33806,7 +33806,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1153" t="n">
-        <v>7.57512235641479</v>
+        <v>7.57512187957764</v>
       </c>
       <c r="H1153" t="n">
         <v>5313</v>
@@ -33893,7 +33893,7 @@
         <v>8.5</v>
       </c>
       <c r="G1156" t="n">
-        <v>7.48703956604004</v>
+        <v>7.48703908920288</v>
       </c>
       <c r="H1156" t="n">
         <v>3635</v>
@@ -33980,7 +33980,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1159" t="n">
-        <v>7.43418884277344</v>
+        <v>7.4341893196106</v>
       </c>
       <c r="H1159" t="n">
         <v>863</v>
@@ -34009,7 +34009,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1160" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1160" t="n">
         <v>4869</v>
@@ -34183,7 +34183,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1166" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1166" t="n">
         <v>1337</v>
@@ -34241,7 +34241,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1168" t="n">
-        <v>7.346107006073</v>
+        <v>7.34610652923584</v>
       </c>
       <c r="H1168" t="n">
         <v>1028</v>
@@ -34705,7 +34705,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1184" t="n">
-        <v>6.81760931015015</v>
+        <v>6.8176097869873</v>
       </c>
       <c r="H1184" t="n">
         <v>3985</v>
@@ -34763,7 +34763,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1186" t="n">
-        <v>6.78237628936768</v>
+        <v>6.78237581253052</v>
       </c>
       <c r="H1186" t="n">
         <v>5258</v>
@@ -34792,7 +34792,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1187" t="n">
-        <v>6.78237628936768</v>
+        <v>6.78237581253052</v>
       </c>
       <c r="H1187" t="n">
         <v>9395</v>
@@ -34850,7 +34850,7 @@
         <v>7.5</v>
       </c>
       <c r="G1189" t="n">
-        <v>6.60621118545532</v>
+        <v>6.60621070861816</v>
       </c>
       <c r="H1189" t="n">
         <v>5048</v>
@@ -34937,7 +34937,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1192" t="n">
-        <v>6.43004512786865</v>
+        <v>6.43004560470581</v>
       </c>
       <c r="H1192" t="n">
         <v>12522</v>
@@ -35024,7 +35024,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1195" t="n">
-        <v>6.21864652633667</v>
+        <v>6.21864604949951</v>
       </c>
       <c r="H1195" t="n">
         <v>17403</v>
@@ -35053,7 +35053,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1196" t="n">
-        <v>6.21864652633667</v>
+        <v>6.21864604949951</v>
       </c>
       <c r="H1196" t="n">
         <v>14235</v>
@@ -35082,7 +35082,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1197" t="n">
-        <v>6.07771396636963</v>
+        <v>6.07771444320679</v>
       </c>
       <c r="H1197" t="n">
         <v>12852</v>
@@ -35111,7 +35111,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1198" t="n">
-        <v>6.11294746398926</v>
+        <v>6.1129469871521</v>
       </c>
       <c r="H1198" t="n">
         <v>10016</v>
@@ -35227,7 +35227,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1202" t="n">
-        <v>5.79584932327271</v>
+        <v>5.79584884643555</v>
       </c>
       <c r="H1202" t="n">
         <v>23567</v>
@@ -35256,7 +35256,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1203" t="n">
-        <v>5.79584932327271</v>
+        <v>5.79584884643555</v>
       </c>
       <c r="H1203" t="n">
         <v>4392</v>
@@ -35285,7 +35285,7 @@
         <v>6.5</v>
       </c>
       <c r="G1204" t="n">
-        <v>5.72538280487061</v>
+        <v>5.72538232803345</v>
       </c>
       <c r="H1204" t="n">
         <v>3100</v>
@@ -35488,7 +35488,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1211" t="n">
-        <v>5.90154838562012</v>
+        <v>5.90154790878296</v>
       </c>
       <c r="H1211" t="n">
         <v>6159</v>
@@ -35546,7 +35546,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1213" t="n">
-        <v>5.90154838562012</v>
+        <v>5.90154790878296</v>
       </c>
       <c r="H1213" t="n">
         <v>4505</v>
@@ -35575,7 +35575,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1214" t="n">
-        <v>5.90154838562012</v>
+        <v>5.90154790878296</v>
       </c>
       <c r="H1214" t="n">
         <v>5958</v>
@@ -35662,7 +35662,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1217" t="n">
-        <v>5.79584932327271</v>
+        <v>5.79584884643555</v>
       </c>
       <c r="H1217" t="n">
         <v>1205</v>
@@ -35691,7 +35691,7 @@
         <v>6.5</v>
       </c>
       <c r="G1218" t="n">
-        <v>5.72538280487061</v>
+        <v>5.72538232803345</v>
       </c>
       <c r="H1218" t="n">
         <v>6775</v>
@@ -35720,7 +35720,7 @@
         <v>6.5</v>
       </c>
       <c r="G1219" t="n">
-        <v>5.72538280487061</v>
+        <v>5.72538232803345</v>
       </c>
       <c r="H1219" t="n">
         <v>1169</v>
@@ -35923,7 +35923,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1226" t="n">
-        <v>5.26735210418701</v>
+        <v>5.26735258102417</v>
       </c>
       <c r="H1226" t="n">
         <v>2131</v>
@@ -35981,7 +35981,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1228" t="n">
-        <v>5.05595350265503</v>
+        <v>5.05595302581787</v>
       </c>
       <c r="H1228" t="n">
         <v>10666</v>
@@ -36039,7 +36039,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1230" t="n">
-        <v>5.1616530418396</v>
+        <v>5.16165256500244</v>
       </c>
       <c r="H1230" t="n">
         <v>32693</v>
@@ -36097,7 +36097,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1232" t="n">
-        <v>5.40828466415405</v>
+        <v>5.40828418731689</v>
       </c>
       <c r="H1232" t="n">
         <v>22678</v>
@@ -36184,7 +36184,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1235" t="n">
-        <v>6.07771396636963</v>
+        <v>6.07771444320679</v>
       </c>
       <c r="H1235" t="n">
         <v>99215</v>
@@ -36242,7 +36242,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1237" t="n">
-        <v>5.79584932327271</v>
+        <v>5.79584884643555</v>
       </c>
       <c r="H1237" t="n">
         <v>20235</v>
@@ -36358,7 +36358,7 @@
         <v>7.5</v>
       </c>
       <c r="G1241" t="n">
-        <v>6.60621118545532</v>
+        <v>6.60621070861816</v>
       </c>
       <c r="H1241" t="n">
         <v>59776</v>
@@ -36445,7 +36445,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1244" t="n">
-        <v>7.16994142532349</v>
+        <v>7.16994094848633</v>
       </c>
       <c r="H1244" t="n">
         <v>37865</v>
@@ -36561,7 +36561,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1248" t="n">
-        <v>7.83936882019043</v>
+        <v>7.83936977386475</v>
       </c>
       <c r="H1248" t="n">
         <v>21091</v>
@@ -36619,7 +36619,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G1250" t="n">
-        <v>7.5046558380127</v>
+        <v>7.50465631484985</v>
       </c>
       <c r="H1250" t="n">
         <v>62658</v>
@@ -36735,7 +36735,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1254" t="n">
-        <v>7.45180606842041</v>
+        <v>7.45180654525757</v>
       </c>
       <c r="H1254" t="n">
         <v>10064</v>
@@ -36764,7 +36764,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G1255" t="n">
-        <v>7.64558792114258</v>
+        <v>7.64558839797974</v>
       </c>
       <c r="H1255" t="n">
         <v>8245</v>
@@ -36851,7 +36851,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1258" t="n">
-        <v>7.57512235641479</v>
+        <v>7.57512187957764</v>
       </c>
       <c r="H1258" t="n">
         <v>4457</v>
@@ -37025,7 +37025,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1264" t="n">
-        <v>7.83936882019043</v>
+        <v>7.83936977386475</v>
       </c>
       <c r="H1264" t="n">
         <v>12133</v>
@@ -37054,7 +37054,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1265" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1265" t="n">
         <v>30312</v>
@@ -37112,7 +37112,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1267" t="n">
-        <v>7.45180606842041</v>
+        <v>7.45180654525757</v>
       </c>
       <c r="H1267" t="n">
         <v>3762</v>
@@ -37170,7 +37170,7 @@
         <v>8.5</v>
       </c>
       <c r="G1269" t="n">
-        <v>7.48703956604004</v>
+        <v>7.48703908920288</v>
       </c>
       <c r="H1269" t="n">
         <v>1238</v>
@@ -37257,7 +37257,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G1272" t="n">
-        <v>7.5046558380127</v>
+        <v>7.50465631484985</v>
       </c>
       <c r="H1272" t="n">
         <v>10662</v>
@@ -37286,7 +37286,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G1273" t="n">
-        <v>7.5046558380127</v>
+        <v>7.50465631484985</v>
       </c>
       <c r="H1273" t="n">
         <v>10110</v>
@@ -37315,7 +37315,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1274" t="n">
-        <v>7.45180606842041</v>
+        <v>7.45180654525757</v>
       </c>
       <c r="H1274" t="n">
         <v>5725</v>
@@ -37344,7 +37344,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1275" t="n">
-        <v>7.346107006073</v>
+        <v>7.34610652923584</v>
       </c>
       <c r="H1275" t="n">
         <v>5406</v>
@@ -37373,7 +37373,7 @@
         <v>8.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>7.48703956604004</v>
+        <v>7.48703908920288</v>
       </c>
       <c r="H1276" t="n">
         <v>3025</v>
@@ -37402,7 +37402,7 @@
         <v>8.5</v>
       </c>
       <c r="G1277" t="n">
-        <v>7.48703956604004</v>
+        <v>7.48703908920288</v>
       </c>
       <c r="H1277" t="n">
         <v>7016</v>
@@ -37518,7 +37518,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1281" t="n">
-        <v>7.2051739692688</v>
+        <v>7.20517444610596</v>
       </c>
       <c r="H1281" t="n">
         <v>10404</v>
@@ -37547,7 +37547,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1282" t="n">
-        <v>7.13470792770386</v>
+        <v>7.13470840454102</v>
       </c>
       <c r="H1282" t="n">
         <v>5578</v>
@@ -37576,7 +37576,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1283" t="n">
-        <v>7.13470792770386</v>
+        <v>7.13470840454102</v>
       </c>
       <c r="H1283" t="n">
         <v>6211</v>
@@ -37663,7 +37663,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1286" t="n">
-        <v>6.78237628936768</v>
+        <v>6.78237581253052</v>
       </c>
       <c r="H1286" t="n">
         <v>11939</v>
@@ -37779,7 +37779,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1290" t="n">
-        <v>6.81760931015015</v>
+        <v>6.8176097869873</v>
       </c>
       <c r="H1290" t="n">
         <v>2365</v>
@@ -37808,7 +37808,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1291" t="n">
-        <v>6.74714279174805</v>
+        <v>6.74714326858521</v>
       </c>
       <c r="H1291" t="n">
         <v>2639</v>
@@ -37953,7 +37953,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1296" t="n">
-        <v>7.16994142532349</v>
+        <v>7.16994094848633</v>
       </c>
       <c r="H1296" t="n">
         <v>19552</v>
@@ -37982,7 +37982,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1297" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1297" t="n">
         <v>8484</v>
@@ -38011,7 +38011,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1298" t="n">
-        <v>7.24040699005127</v>
+        <v>7.24040746688843</v>
       </c>
       <c r="H1298" t="n">
         <v>21087</v>
@@ -38040,7 +38040,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1299" t="n">
-        <v>7.13470792770386</v>
+        <v>7.13470840454102</v>
       </c>
       <c r="H1299" t="n">
         <v>11313</v>
@@ -38098,7 +38098,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1301" t="n">
-        <v>7.2756404876709</v>
+        <v>7.27564001083374</v>
       </c>
       <c r="H1301" t="n">
         <v>19981</v>
@@ -38127,7 +38127,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1302" t="n">
-        <v>7.13470792770386</v>
+        <v>7.13470840454102</v>
       </c>
       <c r="H1302" t="n">
         <v>8032</v>
@@ -38301,7 +38301,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1308" t="n">
-        <v>7.16994142532349</v>
+        <v>7.16994094848633</v>
       </c>
       <c r="H1308" t="n">
         <v>5647</v>
@@ -38388,7 +38388,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1311" t="n">
-        <v>7.346107006073</v>
+        <v>7.34610652923584</v>
       </c>
       <c r="H1311" t="n">
         <v>17733</v>
@@ -38417,7 +38417,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1312" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1312" t="n">
         <v>27792</v>
@@ -38475,7 +38475,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1314" t="n">
-        <v>7.2756404876709</v>
+        <v>7.27564001083374</v>
       </c>
       <c r="H1314" t="n">
         <v>24116</v>
@@ -38649,7 +38649,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1320" t="n">
-        <v>7.24040699005127</v>
+        <v>7.24040746688843</v>
       </c>
       <c r="H1320" t="n">
         <v>6678</v>
@@ -38678,7 +38678,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1321" t="n">
-        <v>7.346107006073</v>
+        <v>7.34610652923584</v>
       </c>
       <c r="H1321" t="n">
         <v>20967</v>
@@ -38707,7 +38707,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1322" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1322" t="n">
         <v>21351</v>
@@ -38736,7 +38736,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1323" t="n">
-        <v>7.346107006073</v>
+        <v>7.34610652923584</v>
       </c>
       <c r="H1323" t="n">
         <v>17781</v>
@@ -38968,7 +38968,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1331" t="n">
-        <v>8.19170188903809</v>
+        <v>8.19170093536377</v>
       </c>
       <c r="H1331" t="n">
         <v>19337</v>
@@ -38997,7 +38997,7 @@
         <v>9.5</v>
       </c>
       <c r="G1332" t="n">
-        <v>8.3678674697876</v>
+        <v>8.36786651611328</v>
       </c>
       <c r="H1332" t="n">
         <v>29234</v>
@@ -39026,7 +39026,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G1333" t="n">
-        <v>8.61449813842773</v>
+        <v>8.61449909210205</v>
       </c>
       <c r="H1333" t="n">
         <v>41033</v>
@@ -39055,7 +39055,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1334" t="n">
-        <v>8.70258235931396</v>
+        <v>8.70258140563965</v>
       </c>
       <c r="H1334" t="n">
         <v>35246</v>
@@ -39084,7 +39084,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1335" t="n">
-        <v>8.94040393829346</v>
+        <v>8.94040489196777</v>
       </c>
       <c r="H1335" t="n">
         <v>32730</v>
@@ -39113,7 +39113,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1336" t="n">
-        <v>9.2927360534668</v>
+        <v>9.29273700714111</v>
       </c>
       <c r="H1336" t="n">
         <v>49007</v>
@@ -39142,7 +39142,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1337" t="n">
-        <v>8.94040393829346</v>
+        <v>8.94040489196777</v>
       </c>
       <c r="H1337" t="n">
         <v>43189</v>
@@ -39200,7 +39200,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G1339" t="n">
-        <v>8.40310001373291</v>
+        <v>8.40310096740723</v>
       </c>
       <c r="H1339" t="n">
         <v>50615</v>
@@ -39258,7 +39258,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1341" t="n">
-        <v>8.70258235931396</v>
+        <v>8.70258140563965</v>
       </c>
       <c r="H1341" t="n">
         <v>33920</v>
@@ -39345,7 +39345,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1344" t="n">
-        <v>8.94040393829346</v>
+        <v>8.94040489196777</v>
       </c>
       <c r="H1344" t="n">
         <v>30292</v>
@@ -39461,7 +39461,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1348" t="n">
-        <v>8.94040393829346</v>
+        <v>8.94040489196777</v>
       </c>
       <c r="H1348" t="n">
         <v>15289</v>
@@ -39548,7 +39548,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1351" t="n">
-        <v>8.63211536407471</v>
+        <v>8.63211631774902</v>
       </c>
       <c r="H1351" t="n">
         <v>14156</v>
@@ -39606,7 +39606,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G1353" t="n">
-        <v>8.49118232727051</v>
+        <v>8.49118328094482</v>
       </c>
       <c r="H1353" t="n">
         <v>9159</v>
@@ -39780,7 +39780,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1359" t="n">
-        <v>8.79066371917725</v>
+        <v>8.79066467285156</v>
       </c>
       <c r="H1359" t="n">
         <v>13792</v>
@@ -39809,7 +39809,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1360" t="n">
-        <v>8.64973163604736</v>
+        <v>8.64973258972168</v>
       </c>
       <c r="H1360" t="n">
         <v>10496</v>
@@ -40070,7 +40070,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1369" t="n">
-        <v>8.68496513366699</v>
+        <v>8.68496417999268</v>
       </c>
       <c r="H1369" t="n">
         <v>6982</v>
@@ -40186,7 +40186,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1373" t="n">
-        <v>8.79066371917725</v>
+        <v>8.79066467285156</v>
       </c>
       <c r="H1373" t="n">
         <v>19472</v>
@@ -40215,7 +40215,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1374" t="n">
-        <v>8.94040393829346</v>
+        <v>8.94040489196777</v>
       </c>
       <c r="H1374" t="n">
         <v>42527</v>
@@ -40418,7 +40418,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1381" t="n">
-        <v>9.42486000061035</v>
+        <v>9.42486095428467</v>
       </c>
       <c r="H1381" t="n">
         <v>34373</v>
@@ -40563,7 +40563,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G1386" t="n">
-        <v>9.99739933013916</v>
+        <v>9.99739837646484</v>
       </c>
       <c r="H1386" t="n">
         <v>25969</v>
@@ -40592,7 +40592,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1387" t="n">
-        <v>9.77719211578369</v>
+        <v>9.77719306945801</v>
       </c>
       <c r="H1387" t="n">
         <v>15068</v>
@@ -40737,7 +40737,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1392" t="n">
-        <v>9.42486000061035</v>
+        <v>9.42486095428467</v>
       </c>
       <c r="H1392" t="n">
         <v>8501</v>
@@ -41056,7 +41056,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1403" t="n">
-        <v>9.33677864074707</v>
+        <v>9.33677768707275</v>
       </c>
       <c r="H1403" t="n">
         <v>10638</v>
@@ -41259,7 +41259,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1410" t="n">
-        <v>8.68496513366699</v>
+        <v>8.68496417999268</v>
       </c>
       <c r="H1410" t="n">
         <v>24712</v>
@@ -41288,7 +41288,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1411" t="n">
-        <v>8.94040393829346</v>
+        <v>8.94040489196777</v>
       </c>
       <c r="H1411" t="n">
         <v>8453</v>
@@ -41346,7 +41346,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1413" t="n">
-        <v>8.94040393829346</v>
+        <v>8.94040489196777</v>
       </c>
       <c r="H1413" t="n">
         <v>8818</v>
@@ -41375,7 +41375,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1414" t="n">
-        <v>8.94040393829346</v>
+        <v>8.94040489196777</v>
       </c>
       <c r="H1414" t="n">
         <v>3602</v>
@@ -41433,7 +41433,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1416" t="n">
-        <v>8.94040393829346</v>
+        <v>8.94040489196777</v>
       </c>
       <c r="H1416" t="n">
         <v>5606</v>
@@ -41462,7 +41462,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1417" t="n">
-        <v>8.94040393829346</v>
+        <v>8.94040489196777</v>
       </c>
       <c r="H1417" t="n">
         <v>3651</v>
@@ -41636,7 +41636,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1423" t="n">
-        <v>8.79066371917725</v>
+        <v>8.79066467285156</v>
       </c>
       <c r="H1423" t="n">
         <v>3057</v>
@@ -41781,7 +41781,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1428" t="n">
-        <v>8.94040393829346</v>
+        <v>8.94040489196777</v>
       </c>
       <c r="H1428" t="n">
         <v>6172</v>
@@ -41897,7 +41897,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1432" t="n">
-        <v>8.94040393829346</v>
+        <v>8.94040489196777</v>
       </c>
       <c r="H1432" t="n">
         <v>3388</v>
@@ -41955,7 +41955,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1434" t="n">
-        <v>8.94040393829346</v>
+        <v>8.94040489196777</v>
       </c>
       <c r="H1434" t="n">
         <v>4954</v>
@@ -42071,7 +42071,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1438" t="n">
-        <v>8.79066371917725</v>
+        <v>8.79066467285156</v>
       </c>
       <c r="H1438" t="n">
         <v>7874</v>
@@ -42129,7 +42129,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1440" t="n">
-        <v>8.79066371917725</v>
+        <v>8.79066467285156</v>
       </c>
       <c r="H1440" t="n">
         <v>4460</v>
@@ -42767,7 +42767,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1462" t="n">
-        <v>8.64973163604736</v>
+        <v>8.64973258972168</v>
       </c>
       <c r="H1462" t="n">
         <v>7641</v>
@@ -42883,7 +42883,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1466" t="n">
-        <v>8.68496513366699</v>
+        <v>8.68496417999268</v>
       </c>
       <c r="H1466" t="n">
         <v>7884</v>
@@ -42912,7 +42912,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1467" t="n">
-        <v>8.68496513366699</v>
+        <v>8.68496417999268</v>
       </c>
       <c r="H1467" t="n">
         <v>7736</v>
@@ -43028,7 +43028,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G1471" t="n">
-        <v>8.61449813842773</v>
+        <v>8.61449909210205</v>
       </c>
       <c r="H1471" t="n">
         <v>3350</v>
@@ -43115,7 +43115,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G1474" t="n">
-        <v>8.61449813842773</v>
+        <v>8.61449909210205</v>
       </c>
       <c r="H1474" t="n">
         <v>5643</v>
@@ -43144,7 +43144,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1475" t="n">
-        <v>8.63211536407471</v>
+        <v>8.63211631774902</v>
       </c>
       <c r="H1475" t="n">
         <v>4598</v>
@@ -43202,7 +43202,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1477" t="n">
-        <v>8.63211536407471</v>
+        <v>8.63211631774902</v>
       </c>
       <c r="H1477" t="n">
         <v>1389</v>
@@ -43231,7 +43231,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1478" t="n">
-        <v>8.79066371917725</v>
+        <v>8.79066467285156</v>
       </c>
       <c r="H1478" t="n">
         <v>9036</v>
@@ -43260,7 +43260,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1479" t="n">
-        <v>8.63211536407471</v>
+        <v>8.63211631774902</v>
       </c>
       <c r="H1479" t="n">
         <v>7922</v>
@@ -43289,7 +43289,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G1480" t="n">
-        <v>8.61449813842773</v>
+        <v>8.61449909210205</v>
       </c>
       <c r="H1480" t="n">
         <v>5621</v>
@@ -43405,7 +43405,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1484" t="n">
-        <v>8.64973163604736</v>
+        <v>8.64973258972168</v>
       </c>
       <c r="H1484" t="n">
         <v>5148</v>
@@ -43434,7 +43434,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1485" t="n">
-        <v>8.56164932250977</v>
+        <v>8.56164836883545</v>
       </c>
       <c r="H1485" t="n">
         <v>4070</v>
@@ -43463,7 +43463,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1486" t="n">
-        <v>8.56164932250977</v>
+        <v>8.56164836883545</v>
       </c>
       <c r="H1486" t="n">
         <v>1980</v>
@@ -43550,7 +43550,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1489" t="n">
-        <v>8.56164932250977</v>
+        <v>8.56164836883545</v>
       </c>
       <c r="H1489" t="n">
         <v>6819</v>
@@ -43579,7 +43579,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1490" t="n">
-        <v>8.63211536407471</v>
+        <v>8.63211631774902</v>
       </c>
       <c r="H1490" t="n">
         <v>7334</v>
@@ -43608,7 +43608,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1491" t="n">
-        <v>8.56164932250977</v>
+        <v>8.56164836883545</v>
       </c>
       <c r="H1491" t="n">
         <v>5763</v>
@@ -43753,7 +43753,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G1496" t="n">
-        <v>8.40310001373291</v>
+        <v>8.40310096740723</v>
       </c>
       <c r="H1496" t="n">
         <v>10254</v>
@@ -43811,7 +43811,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1498" t="n">
-        <v>7.83936882019043</v>
+        <v>7.83936977386475</v>
       </c>
       <c r="H1498" t="n">
         <v>31204</v>
@@ -43985,7 +43985,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1504" t="n">
-        <v>7.83936882019043</v>
+        <v>7.83936977386475</v>
       </c>
       <c r="H1504" t="n">
         <v>9399</v>
@@ -44594,7 +44594,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1525" t="n">
-        <v>7.59273862838745</v>
+        <v>7.59273767471313</v>
       </c>
       <c r="H1525" t="n">
         <v>3711</v>
@@ -44768,7 +44768,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G1531" t="n">
-        <v>8.29740047454834</v>
+        <v>8.29740142822266</v>
       </c>
       <c r="H1531" t="n">
         <v>6056</v>
@@ -44826,7 +44826,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G1533" t="n">
-        <v>8.15646743774414</v>
+        <v>8.15646839141846</v>
       </c>
       <c r="H1533" t="n">
         <v>2086</v>
@@ -44913,7 +44913,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1536" t="n">
-        <v>8.19170188903809</v>
+        <v>8.19170093536377</v>
       </c>
       <c r="H1536" t="n">
         <v>3436</v>
@@ -44942,7 +44942,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1537" t="n">
-        <v>8.19170188903809</v>
+        <v>8.19170093536377</v>
       </c>
       <c r="H1537" t="n">
         <v>6326</v>
@@ -45116,7 +45116,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G1543" t="n">
-        <v>8.15646743774414</v>
+        <v>8.15646839141846</v>
       </c>
       <c r="H1543" t="n">
         <v>5357</v>
@@ -45174,7 +45174,7 @@
         <v>9</v>
       </c>
       <c r="G1545" t="n">
-        <v>7.92745351791382</v>
+        <v>7.9274525642395</v>
       </c>
       <c r="H1545" t="n">
         <v>3128</v>
@@ -45493,7 +45493,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1556" t="n">
-        <v>8.19170188903809</v>
+        <v>8.19170093536377</v>
       </c>
       <c r="H1556" t="n">
         <v>6365</v>
@@ -45783,7 +45783,7 @@
         <v>9</v>
       </c>
       <c r="G1566" t="n">
-        <v>7.92745351791382</v>
+        <v>7.9274525642395</v>
       </c>
       <c r="H1566" t="n">
         <v>2179</v>
@@ -45928,7 +45928,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1571" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1571" t="n">
         <v>8105</v>
@@ -45957,7 +45957,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1572" t="n">
-        <v>7.16994142532349</v>
+        <v>7.16994094848633</v>
       </c>
       <c r="H1572" t="n">
         <v>19994</v>
@@ -46044,7 +46044,7 @@
         <v>8.5</v>
       </c>
       <c r="G1575" t="n">
-        <v>7.48703956604004</v>
+        <v>7.48703908920288</v>
       </c>
       <c r="H1575" t="n">
         <v>11680</v>
@@ -46102,7 +46102,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1577" t="n">
-        <v>7.43418884277344</v>
+        <v>7.4341893196106</v>
       </c>
       <c r="H1577" t="n">
         <v>1349</v>
@@ -46131,7 +46131,7 @@
         <v>8.5</v>
       </c>
       <c r="G1578" t="n">
-        <v>7.48703956604004</v>
+        <v>7.48703908920288</v>
       </c>
       <c r="H1578" t="n">
         <v>5686</v>
@@ -46218,7 +46218,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1581" t="n">
-        <v>7.57512235641479</v>
+        <v>7.57512187957764</v>
       </c>
       <c r="H1581" t="n">
         <v>2233</v>
@@ -46247,7 +46247,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1582" t="n">
-        <v>7.43418884277344</v>
+        <v>7.4341893196106</v>
       </c>
       <c r="H1582" t="n">
         <v>2145</v>
@@ -46276,7 +46276,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1583" t="n">
-        <v>7.57512235641479</v>
+        <v>7.57512187957764</v>
       </c>
       <c r="H1583" t="n">
         <v>4255</v>
@@ -46334,7 +46334,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1585" t="n">
-        <v>7.57512235641479</v>
+        <v>7.57512187957764</v>
       </c>
       <c r="H1585" t="n">
         <v>8359</v>
@@ -46798,7 +46798,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G1601" t="n">
-        <v>7.64558792114258</v>
+        <v>7.64558839797974</v>
       </c>
       <c r="H1601" t="n">
         <v>9877</v>
@@ -46856,7 +46856,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1603" t="n">
-        <v>7.59273862838745</v>
+        <v>7.59273767471313</v>
       </c>
       <c r="H1603" t="n">
         <v>6068</v>
@@ -46885,7 +46885,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1604" t="n">
-        <v>7.59273862838745</v>
+        <v>7.59273767471313</v>
       </c>
       <c r="H1604" t="n">
         <v>2080</v>
@@ -46943,7 +46943,7 @@
         <v>8.5</v>
       </c>
       <c r="G1606" t="n">
-        <v>7.48703956604004</v>
+        <v>7.48703908920288</v>
       </c>
       <c r="H1606" t="n">
         <v>5619</v>
@@ -47001,7 +47001,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1608" t="n">
-        <v>7.2051739692688</v>
+        <v>7.20517444610596</v>
       </c>
       <c r="H1608" t="n">
         <v>4057</v>
@@ -47059,7 +47059,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1610" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1610" t="n">
         <v>2528</v>
@@ -47117,7 +47117,7 @@
         <v>8.5</v>
       </c>
       <c r="G1612" t="n">
-        <v>7.48703956604004</v>
+        <v>7.48703908920288</v>
       </c>
       <c r="H1612" t="n">
         <v>1690</v>
@@ -47175,7 +47175,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1614" t="n">
-        <v>7.346107006073</v>
+        <v>7.34610652923584</v>
       </c>
       <c r="H1614" t="n">
         <v>3772</v>
@@ -47233,7 +47233,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1616" t="n">
-        <v>7.59273862838745</v>
+        <v>7.59273767471313</v>
       </c>
       <c r="H1616" t="n">
         <v>5720</v>
@@ -47523,7 +47523,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1626" t="n">
-        <v>7.62797069549561</v>
+        <v>7.62797164916992</v>
       </c>
       <c r="H1626" t="n">
         <v>1536</v>
@@ -47755,7 +47755,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1634" t="n">
-        <v>8.19170188903809</v>
+        <v>8.19170093536377</v>
       </c>
       <c r="H1634" t="n">
         <v>16021</v>
@@ -47784,7 +47784,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G1635" t="n">
-        <v>8.15646743774414</v>
+        <v>8.15646839141846</v>
       </c>
       <c r="H1635" t="n">
         <v>9328</v>
@@ -47900,7 +47900,7 @@
         <v>9</v>
       </c>
       <c r="G1639" t="n">
-        <v>7.92745351791382</v>
+        <v>7.9274525642395</v>
       </c>
       <c r="H1639" t="n">
         <v>9295</v>
@@ -47929,7 +47929,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1640" t="n">
-        <v>7.57512235641479</v>
+        <v>7.57512187957764</v>
       </c>
       <c r="H1640" t="n">
         <v>10405</v>
@@ -47987,7 +47987,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1642" t="n">
-        <v>7.62797069549561</v>
+        <v>7.62797164916992</v>
       </c>
       <c r="H1642" t="n">
         <v>17226</v>
@@ -48045,7 +48045,7 @@
         <v>8.5</v>
       </c>
       <c r="G1644" t="n">
-        <v>7.48703956604004</v>
+        <v>7.48703908920288</v>
       </c>
       <c r="H1644" t="n">
         <v>3090</v>
@@ -48074,7 +48074,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1645" t="n">
-        <v>7.45180606842041</v>
+        <v>7.45180654525757</v>
       </c>
       <c r="H1645" t="n">
         <v>6814</v>
@@ -48132,7 +48132,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1647" t="n">
-        <v>7.57512235641479</v>
+        <v>7.57512187957764</v>
       </c>
       <c r="H1647" t="n">
         <v>1209</v>
@@ -48219,7 +48219,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1650" t="n">
-        <v>7.43418884277344</v>
+        <v>7.4341893196106</v>
       </c>
       <c r="H1650" t="n">
         <v>1997</v>
@@ -48248,7 +48248,7 @@
         <v>8.5</v>
       </c>
       <c r="G1651" t="n">
-        <v>7.48703956604004</v>
+        <v>7.48703908920288</v>
       </c>
       <c r="H1651" t="n">
         <v>2370</v>
@@ -48277,7 +48277,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1652" t="n">
-        <v>7.45180606842041</v>
+        <v>7.45180654525757</v>
       </c>
       <c r="H1652" t="n">
         <v>2682</v>
@@ -48364,7 +48364,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1655" t="n">
-        <v>7.346107006073</v>
+        <v>7.34610652923584</v>
       </c>
       <c r="H1655" t="n">
         <v>168</v>
@@ -48393,7 +48393,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1656" t="n">
-        <v>7.16994142532349</v>
+        <v>7.16994094848633</v>
       </c>
       <c r="H1656" t="n">
         <v>2765</v>
@@ -48451,7 +48451,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1658" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1658" t="n">
         <v>2529</v>
@@ -48509,7 +48509,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1660" t="n">
-        <v>7.41657257080078</v>
+        <v>7.41657209396362</v>
       </c>
       <c r="H1660" t="n">
         <v>1125</v>
@@ -48567,7 +48567,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1662" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1662" t="n">
         <v>2095</v>
@@ -48596,7 +48596,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1663" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1663" t="n">
         <v>1508</v>
@@ -48683,7 +48683,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1666" t="n">
-        <v>7.43418884277344</v>
+        <v>7.4341893196106</v>
       </c>
       <c r="H1666" t="n">
         <v>18</v>
@@ -48712,7 +48712,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1667" t="n">
-        <v>7.13470792770386</v>
+        <v>7.13470840454102</v>
       </c>
       <c r="H1667" t="n">
         <v>3306</v>
@@ -48741,7 +48741,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1668" t="n">
-        <v>7.16994142532349</v>
+        <v>7.16994094848633</v>
       </c>
       <c r="H1668" t="n">
         <v>155</v>
@@ -48944,7 +48944,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1675" t="n">
-        <v>7.43418884277344</v>
+        <v>7.4341893196106</v>
       </c>
       <c r="H1675" t="n">
         <v>1564</v>
@@ -49002,7 +49002,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1677" t="n">
-        <v>7.45180606842041</v>
+        <v>7.45180654525757</v>
       </c>
       <c r="H1677" t="n">
         <v>487</v>
@@ -49147,7 +49147,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1682" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1682" t="n">
         <v>3350</v>
@@ -49176,7 +49176,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1683" t="n">
-        <v>7.41657257080078</v>
+        <v>7.41657209396362</v>
       </c>
       <c r="H1683" t="n">
         <v>1400</v>
@@ -49205,7 +49205,7 @@
         <v>8.5</v>
       </c>
       <c r="G1684" t="n">
-        <v>7.48703956604004</v>
+        <v>7.48703908920288</v>
       </c>
       <c r="H1684" t="n">
         <v>2997</v>
@@ -49321,7 +49321,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1688" t="n">
-        <v>7.24040699005127</v>
+        <v>7.24040746688843</v>
       </c>
       <c r="H1688" t="n">
         <v>5720</v>
@@ -49350,7 +49350,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1689" t="n">
-        <v>7.2051739692688</v>
+        <v>7.20517444610596</v>
       </c>
       <c r="H1689" t="n">
         <v>1707</v>
@@ -49408,7 +49408,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1691" t="n">
-        <v>7.16994142532349</v>
+        <v>7.16994094848633</v>
       </c>
       <c r="H1691" t="n">
         <v>3239</v>
@@ -49727,7 +49727,7 @@
         <v>7.5</v>
       </c>
       <c r="G1702" t="n">
-        <v>6.60621118545532</v>
+        <v>6.60621070861816</v>
       </c>
       <c r="H1702" t="n">
         <v>894</v>
@@ -49814,7 +49814,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1705" t="n">
-        <v>6.78237628936768</v>
+        <v>6.78237581253052</v>
       </c>
       <c r="H1705" t="n">
         <v>16158</v>
@@ -50162,7 +50162,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1717" t="n">
-        <v>6.32434558868408</v>
+        <v>6.32434606552124</v>
       </c>
       <c r="H1717" t="n">
         <v>3021</v>
@@ -50191,7 +50191,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1718" t="n">
-        <v>6.25387907028198</v>
+        <v>6.25387954711914</v>
       </c>
       <c r="H1718" t="n">
         <v>1986</v>
@@ -50220,7 +50220,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1719" t="n">
-        <v>6.25387907028198</v>
+        <v>6.25387954711914</v>
       </c>
       <c r="H1719" t="n">
         <v>3572</v>
@@ -50626,7 +50626,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1733" t="n">
-        <v>6.43004512786865</v>
+        <v>6.43004560470581</v>
       </c>
       <c r="H1733" t="n">
         <v>1793</v>
@@ -50655,7 +50655,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1734" t="n">
-        <v>6.43004512786865</v>
+        <v>6.43004560470581</v>
       </c>
       <c r="H1734" t="n">
         <v>2928</v>
@@ -50829,7 +50829,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1740" t="n">
-        <v>6.43004512786865</v>
+        <v>6.43004560470581</v>
       </c>
       <c r="H1740" t="n">
         <v>897</v>
@@ -50974,7 +50974,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1745" t="n">
-        <v>6.32434558868408</v>
+        <v>6.32434606552124</v>
       </c>
       <c r="H1745" t="n">
         <v>2018</v>
@@ -51003,7 +51003,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G1746" t="n">
-        <v>6.28911304473877</v>
+        <v>6.28911256790161</v>
       </c>
       <c r="H1746" t="n">
         <v>4981</v>
@@ -51119,7 +51119,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1750" t="n">
-        <v>6.74714279174805</v>
+        <v>6.74714326858521</v>
       </c>
       <c r="H1750" t="n">
         <v>18859</v>
@@ -51206,7 +51206,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1753" t="n">
-        <v>6.43004512786865</v>
+        <v>6.43004560470581</v>
       </c>
       <c r="H1753" t="n">
         <v>2663</v>
@@ -51293,7 +51293,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1756" t="n">
-        <v>6.81760931015015</v>
+        <v>6.8176097869873</v>
       </c>
       <c r="H1756" t="n">
         <v>9527</v>
@@ -51786,7 +51786,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1773" t="n">
-        <v>6.81760931015015</v>
+        <v>6.8176097869873</v>
       </c>
       <c r="H1773" t="n">
         <v>2673</v>
@@ -51815,7 +51815,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1774" t="n">
-        <v>6.81760931015015</v>
+        <v>6.8176097869873</v>
       </c>
       <c r="H1774" t="n">
         <v>1069</v>
@@ -51844,7 +51844,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1775" t="n">
-        <v>6.67667722702026</v>
+        <v>6.67667675018311</v>
       </c>
       <c r="H1775" t="n">
         <v>1012</v>
@@ -51873,7 +51873,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1776" t="n">
-        <v>6.74714279174805</v>
+        <v>6.74714326858521</v>
       </c>
       <c r="H1776" t="n">
         <v>1358</v>
@@ -52076,7 +52076,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1783" t="n">
-        <v>6.81760931015015</v>
+        <v>6.8176097869873</v>
       </c>
       <c r="H1783" t="n">
         <v>135</v>
@@ -52134,7 +52134,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1785" t="n">
-        <v>6.81760931015015</v>
+        <v>6.8176097869873</v>
       </c>
       <c r="H1785" t="n">
         <v>5058</v>
@@ -52540,7 +52540,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1799" t="n">
-        <v>7.13470792770386</v>
+        <v>7.13470840454102</v>
       </c>
       <c r="H1799" t="n">
         <v>2975</v>
@@ -52627,7 +52627,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1802" t="n">
-        <v>7.16994142532349</v>
+        <v>7.16994094848633</v>
       </c>
       <c r="H1802" t="n">
         <v>1141</v>
@@ -52656,7 +52656,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1803" t="n">
-        <v>7.13470792770386</v>
+        <v>7.13470840454102</v>
       </c>
       <c r="H1803" t="n">
         <v>4010</v>
@@ -52801,7 +52801,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1808" t="n">
-        <v>7.2051739692688</v>
+        <v>7.20517444610596</v>
       </c>
       <c r="H1808" t="n">
         <v>14143</v>
@@ -52830,7 +52830,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1809" t="n">
-        <v>7.24040699005127</v>
+        <v>7.24040746688843</v>
       </c>
       <c r="H1809" t="n">
         <v>10563</v>
@@ -52859,7 +52859,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1810" t="n">
-        <v>7.24040699005127</v>
+        <v>7.24040746688843</v>
       </c>
       <c r="H1810" t="n">
         <v>4697</v>
@@ -52888,7 +52888,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1811" t="n">
-        <v>7.346107006073</v>
+        <v>7.34610652923584</v>
       </c>
       <c r="H1811" t="n">
         <v>5102</v>
@@ -52917,7 +52917,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G1812" t="n">
-        <v>7.5046558380127</v>
+        <v>7.50465631484985</v>
       </c>
       <c r="H1812" t="n">
         <v>16995</v>
@@ -52946,7 +52946,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G1813" t="n">
-        <v>7.5046558380127</v>
+        <v>7.50465631484985</v>
       </c>
       <c r="H1813" t="n">
         <v>5578</v>
@@ -52975,7 +52975,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1814" t="n">
-        <v>7.24040699005127</v>
+        <v>7.24040746688843</v>
       </c>
       <c r="H1814" t="n">
         <v>6960</v>
@@ -53004,7 +53004,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1815" t="n">
-        <v>7.13470792770386</v>
+        <v>7.13470840454102</v>
       </c>
       <c r="H1815" t="n">
         <v>3537</v>
@@ -53033,7 +53033,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1816" t="n">
-        <v>7.2051739692688</v>
+        <v>7.20517444610596</v>
       </c>
       <c r="H1816" t="n">
         <v>217</v>
@@ -53062,7 +53062,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1817" t="n">
-        <v>7.2051739692688</v>
+        <v>7.20517444610596</v>
       </c>
       <c r="H1817" t="n">
         <v>2479</v>
@@ -53091,7 +53091,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1818" t="n">
-        <v>7.2756404876709</v>
+        <v>7.27564001083374</v>
       </c>
       <c r="H1818" t="n">
         <v>2903</v>
@@ -53120,7 +53120,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1819" t="n">
-        <v>7.2756404876709</v>
+        <v>7.27564001083374</v>
       </c>
       <c r="H1819" t="n">
         <v>3901</v>
@@ -53149,7 +53149,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1820" t="n">
-        <v>7.16994142532349</v>
+        <v>7.16994094848633</v>
       </c>
       <c r="H1820" t="n">
         <v>2760</v>
@@ -53207,7 +53207,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1822" t="n">
-        <v>7.16994142532349</v>
+        <v>7.16994094848633</v>
       </c>
       <c r="H1822" t="n">
         <v>162</v>
@@ -53265,7 +53265,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1824" t="n">
-        <v>7.13470792770386</v>
+        <v>7.13470840454102</v>
       </c>
       <c r="H1824" t="n">
         <v>10492</v>
@@ -53555,7 +53555,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1834" t="n">
-        <v>7.13470792770386</v>
+        <v>7.13470840454102</v>
       </c>
       <c r="H1834" t="n">
         <v>7544</v>
@@ -54164,7 +54164,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1855" t="n">
-        <v>7.13470792770386</v>
+        <v>7.13470840454102</v>
       </c>
       <c r="H1855" t="n">
         <v>1452</v>
@@ -54251,7 +54251,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1858" t="n">
-        <v>7.13470792770386</v>
+        <v>7.13470840454102</v>
       </c>
       <c r="H1858" t="n">
         <v>5028</v>
@@ -54280,7 +54280,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1859" t="n">
-        <v>7.13470792770386</v>
+        <v>7.13470840454102</v>
       </c>
       <c r="H1859" t="n">
         <v>520</v>
@@ -54309,7 +54309,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1860" t="n">
-        <v>7.13470792770386</v>
+        <v>7.13470840454102</v>
       </c>
       <c r="H1860" t="n">
         <v>425</v>
@@ -54367,7 +54367,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1862" t="n">
-        <v>7.16994142532349</v>
+        <v>7.16994094848633</v>
       </c>
       <c r="H1862" t="n">
         <v>859</v>
@@ -54425,7 +54425,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1864" t="n">
-        <v>7.16994142532349</v>
+        <v>7.16994094848633</v>
       </c>
       <c r="H1864" t="n">
         <v>14616</v>
@@ -54512,7 +54512,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1867" t="n">
-        <v>7.24040699005127</v>
+        <v>7.24040746688843</v>
       </c>
       <c r="H1867" t="n">
         <v>2849</v>
@@ -54628,7 +54628,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1871" t="n">
-        <v>7.346107006073</v>
+        <v>7.34610652923584</v>
       </c>
       <c r="H1871" t="n">
         <v>1487</v>
@@ -54657,7 +54657,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1872" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1872" t="n">
         <v>2299</v>
@@ -54686,7 +54686,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1873" t="n">
-        <v>7.346107006073</v>
+        <v>7.34610652923584</v>
       </c>
       <c r="H1873" t="n">
         <v>3578</v>
@@ -54744,7 +54744,7 @@
         <v>8.5</v>
       </c>
       <c r="G1875" t="n">
-        <v>7.48703956604004</v>
+        <v>7.48703908920288</v>
       </c>
       <c r="H1875" t="n">
         <v>23739</v>
@@ -54831,7 +54831,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1878" t="n">
-        <v>7.57512235641479</v>
+        <v>7.57512187957764</v>
       </c>
       <c r="H1878" t="n">
         <v>11078</v>
@@ -54860,7 +54860,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1879" t="n">
-        <v>7.43418884277344</v>
+        <v>7.4341893196106</v>
       </c>
       <c r="H1879" t="n">
         <v>3292</v>
@@ -54889,7 +54889,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1880" t="n">
-        <v>7.43418884277344</v>
+        <v>7.4341893196106</v>
       </c>
       <c r="H1880" t="n">
         <v>1570</v>
@@ -54947,7 +54947,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1882" t="n">
-        <v>7.43418884277344</v>
+        <v>7.4341893196106</v>
       </c>
       <c r="H1882" t="n">
         <v>911</v>
@@ -54976,7 +54976,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1883" t="n">
-        <v>7.41657257080078</v>
+        <v>7.41657209396362</v>
       </c>
       <c r="H1883" t="n">
         <v>3071</v>
@@ -55034,7 +55034,7 @@
         <v>8.5</v>
       </c>
       <c r="G1885" t="n">
-        <v>7.48703956604004</v>
+        <v>7.48703908920288</v>
       </c>
       <c r="H1885" t="n">
         <v>369</v>
@@ -55092,7 +55092,7 @@
         <v>8.5</v>
       </c>
       <c r="G1887" t="n">
-        <v>7.48703956604004</v>
+        <v>7.48703908920288</v>
       </c>
       <c r="H1887" t="n">
         <v>4842</v>
@@ -55266,7 +55266,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1893" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1893" t="n">
         <v>7253</v>
@@ -55324,7 +55324,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1895" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1895" t="n">
         <v>5501</v>
@@ -55382,7 +55382,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1897" t="n">
-        <v>7.41657257080078</v>
+        <v>7.41657209396362</v>
       </c>
       <c r="H1897" t="n">
         <v>2058</v>
@@ -55498,7 +55498,7 @@
         <v>8.5</v>
       </c>
       <c r="G1901" t="n">
-        <v>7.48703956604004</v>
+        <v>7.48703908920288</v>
       </c>
       <c r="H1901" t="n">
         <v>3789</v>
@@ -55527,7 +55527,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1902" t="n">
-        <v>7.43418884277344</v>
+        <v>7.4341893196106</v>
       </c>
       <c r="H1902" t="n">
         <v>3866</v>
@@ -55614,7 +55614,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1905" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1905" t="n">
         <v>406</v>
@@ -55643,7 +55643,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1906" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1906" t="n">
         <v>550</v>
@@ -55672,7 +55672,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1907" t="n">
-        <v>7.41657257080078</v>
+        <v>7.41657209396362</v>
       </c>
       <c r="H1907" t="n">
         <v>478</v>
@@ -55701,7 +55701,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1908" t="n">
-        <v>7.41657257080078</v>
+        <v>7.41657209396362</v>
       </c>
       <c r="H1908" t="n">
         <v>0</v>
@@ -55759,7 +55759,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1910" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1910" t="n">
         <v>3360</v>
@@ -55846,7 +55846,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1913" t="n">
-        <v>7.13470792770386</v>
+        <v>7.13470840454102</v>
       </c>
       <c r="H1913" t="n">
         <v>4836</v>
@@ -55875,7 +55875,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1914" t="n">
-        <v>7.346107006073</v>
+        <v>7.34610652923584</v>
       </c>
       <c r="H1914" t="n">
         <v>2395</v>
@@ -55904,7 +55904,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1915" t="n">
-        <v>7.45180606842041</v>
+        <v>7.45180654525757</v>
       </c>
       <c r="H1915" t="n">
         <v>2656</v>
@@ -55991,7 +55991,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1918" t="n">
-        <v>7.2756404876709</v>
+        <v>7.27564001083374</v>
       </c>
       <c r="H1918" t="n">
         <v>13617</v>
@@ -56020,7 +56020,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1919" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1919" t="n">
         <v>1055</v>
@@ -56049,7 +56049,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1920" t="n">
-        <v>7.2051739692688</v>
+        <v>7.20517444610596</v>
       </c>
       <c r="H1920" t="n">
         <v>2167</v>
@@ -56107,7 +56107,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1922" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1922" t="n">
         <v>18143</v>
@@ -56136,7 +56136,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1923" t="n">
-        <v>7.24040699005127</v>
+        <v>7.24040746688843</v>
       </c>
       <c r="H1923" t="n">
         <v>3630</v>
@@ -56165,7 +56165,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1924" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1924" t="n">
         <v>10941</v>
@@ -56194,7 +56194,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1925" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1925" t="n">
         <v>4893</v>
@@ -56252,7 +56252,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1927" t="n">
-        <v>7.346107006073</v>
+        <v>7.34610652923584</v>
       </c>
       <c r="H1927" t="n">
         <v>9457</v>
@@ -56339,7 +56339,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1930" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1930" t="n">
         <v>6373</v>
@@ -56368,7 +56368,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1931" t="n">
-        <v>7.2756404876709</v>
+        <v>7.27564001083374</v>
       </c>
       <c r="H1931" t="n">
         <v>20231</v>
@@ -56484,7 +56484,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1935" t="n">
-        <v>7.24040699005127</v>
+        <v>7.24040746688843</v>
       </c>
       <c r="H1935" t="n">
         <v>2114</v>
@@ -56542,7 +56542,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1937" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1937" t="n">
         <v>1661</v>
@@ -56571,7 +56571,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1938" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1938" t="n">
         <v>0</v>
@@ -56629,7 +56629,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1940" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1940" t="n">
         <v>2749</v>
@@ -56658,7 +56658,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1941" t="n">
-        <v>7.2756404876709</v>
+        <v>7.27564001083374</v>
       </c>
       <c r="H1941" t="n">
         <v>1400</v>
@@ -56716,7 +56716,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1943" t="n">
-        <v>7.24040699005127</v>
+        <v>7.24040746688843</v>
       </c>
       <c r="H1943" t="n">
         <v>4153</v>
@@ -56803,7 +56803,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1946" t="n">
-        <v>7.2756404876709</v>
+        <v>7.27564001083374</v>
       </c>
       <c r="H1946" t="n">
         <v>2069</v>
@@ -56861,7 +56861,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1948" t="n">
-        <v>7.2756404876709</v>
+        <v>7.27564001083374</v>
       </c>
       <c r="H1948" t="n">
         <v>981</v>
@@ -56890,7 +56890,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1949" t="n">
-        <v>7.41657257080078</v>
+        <v>7.41657209396362</v>
       </c>
       <c r="H1949" t="n">
         <v>19988</v>
@@ -56919,7 +56919,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1950" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1950" t="n">
         <v>7167</v>
@@ -56948,7 +56948,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1951" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1951" t="n">
         <v>3959</v>
@@ -56977,7 +56977,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1952" t="n">
-        <v>7.346107006073</v>
+        <v>7.34610652923584</v>
       </c>
       <c r="H1952" t="n">
         <v>2320</v>
@@ -57267,7 +57267,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1962" t="n">
-        <v>7.2756404876709</v>
+        <v>7.27564001083374</v>
       </c>
       <c r="H1962" t="n">
         <v>1313</v>
@@ -57296,7 +57296,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1963" t="n">
-        <v>7.346107006073</v>
+        <v>7.34610652923584</v>
       </c>
       <c r="H1963" t="n">
         <v>5482</v>
@@ -57383,7 +57383,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1966" t="n">
-        <v>7.2756404876709</v>
+        <v>7.27564001083374</v>
       </c>
       <c r="H1966" t="n">
         <v>3431</v>
@@ -57644,7 +57644,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1975" t="n">
-        <v>7.24040699005127</v>
+        <v>7.24040746688843</v>
       </c>
       <c r="H1975" t="n">
         <v>11036</v>
@@ -57731,7 +57731,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1978" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1978" t="n">
         <v>7891</v>
@@ -57760,7 +57760,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1979" t="n">
-        <v>7.2756404876709</v>
+        <v>7.27564001083374</v>
       </c>
       <c r="H1979" t="n">
         <v>2912</v>
@@ -57876,7 +57876,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1983" t="n">
-        <v>7.41657257080078</v>
+        <v>7.41657209396362</v>
       </c>
       <c r="H1983" t="n">
         <v>2985</v>
@@ -57963,7 +57963,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1986" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H1986" t="n">
         <v>8304</v>
@@ -58166,7 +58166,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1993" t="n">
-        <v>7.13470792770386</v>
+        <v>7.13470840454102</v>
       </c>
       <c r="H1993" t="n">
         <v>666</v>
@@ -58224,7 +58224,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1995" t="n">
-        <v>7.13470792770386</v>
+        <v>7.13470840454102</v>
       </c>
       <c r="H1995" t="n">
         <v>1806</v>
@@ -58253,7 +58253,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1996" t="n">
-        <v>7.16994142532349</v>
+        <v>7.16994094848633</v>
       </c>
       <c r="H1996" t="n">
         <v>2257</v>
@@ -58311,7 +58311,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1998" t="n">
-        <v>7.13470792770386</v>
+        <v>7.13470840454102</v>
       </c>
       <c r="H1998" t="n">
         <v>5054</v>
@@ -58485,7 +58485,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G2004" t="n">
-        <v>7.13470792770386</v>
+        <v>7.13470840454102</v>
       </c>
       <c r="H2004" t="n">
         <v>6254</v>
@@ -58630,7 +58630,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G2009" t="n">
-        <v>7.13470792770386</v>
+        <v>7.13470840454102</v>
       </c>
       <c r="H2009" t="n">
         <v>6844</v>
@@ -58688,7 +58688,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2011" t="n">
-        <v>7.2756404876709</v>
+        <v>7.27564001083374</v>
       </c>
       <c r="H2011" t="n">
         <v>3465</v>
@@ -58717,7 +58717,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G2012" t="n">
-        <v>7.24040699005127</v>
+        <v>7.24040746688843</v>
       </c>
       <c r="H2012" t="n">
         <v>4624</v>
@@ -58949,7 +58949,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2020" t="n">
-        <v>7.2756404876709</v>
+        <v>7.27564001083374</v>
       </c>
       <c r="H2020" t="n">
         <v>7520</v>
@@ -59007,7 +59007,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2022" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H2022" t="n">
         <v>2232</v>
@@ -59065,7 +59065,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2024" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H2024" t="n">
         <v>2063</v>
@@ -59094,7 +59094,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G2025" t="n">
-        <v>7.346107006073</v>
+        <v>7.34610652923584</v>
       </c>
       <c r="H2025" t="n">
         <v>2584</v>
@@ -59210,7 +59210,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G2029" t="n">
-        <v>7.2051739692688</v>
+        <v>7.20517444610596</v>
       </c>
       <c r="H2029" t="n">
         <v>4378</v>
@@ -59297,7 +59297,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G2032" t="n">
-        <v>7.16994142532349</v>
+        <v>7.16994094848633</v>
       </c>
       <c r="H2032" t="n">
         <v>4699</v>
@@ -59442,7 +59442,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2037" t="n">
-        <v>7.2756404876709</v>
+        <v>7.27564001083374</v>
       </c>
       <c r="H2037" t="n">
         <v>910</v>
@@ -59500,7 +59500,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2039" t="n">
-        <v>7.2756404876709</v>
+        <v>7.27564001083374</v>
       </c>
       <c r="H2039" t="n">
         <v>2378</v>
@@ -59587,7 +59587,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G2042" t="n">
-        <v>7.346107006073</v>
+        <v>7.34610652923584</v>
       </c>
       <c r="H2042" t="n">
         <v>4459</v>
@@ -59645,7 +59645,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G2044" t="n">
-        <v>7.24040699005127</v>
+        <v>7.24040746688843</v>
       </c>
       <c r="H2044" t="n">
         <v>4898</v>
@@ -59761,7 +59761,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2048" t="n">
-        <v>7.2756404876709</v>
+        <v>7.27564001083374</v>
       </c>
       <c r="H2048" t="n">
         <v>315</v>
@@ -59790,7 +59790,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G2049" t="n">
-        <v>7.346107006073</v>
+        <v>7.34610652923584</v>
       </c>
       <c r="H2049" t="n">
         <v>11449</v>
@@ -59848,7 +59848,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2051" t="n">
-        <v>7.2756404876709</v>
+        <v>7.27564001083374</v>
       </c>
       <c r="H2051" t="n">
         <v>865</v>
@@ -59877,7 +59877,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G2052" t="n">
-        <v>7.346107006073</v>
+        <v>7.34610652923584</v>
       </c>
       <c r="H2052" t="n">
         <v>725</v>
@@ -59935,7 +59935,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2054" t="n">
-        <v>7.31087303161621</v>
+        <v>7.31087350845337</v>
       </c>
       <c r="H2054" t="n">
         <v>3021</v>
@@ -59993,7 +59993,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2056" t="n">
-        <v>7.2756404876709</v>
+        <v>7.27564001083374</v>
       </c>
       <c r="H2056" t="n">
         <v>353</v>
@@ -60022,7 +60022,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2057" t="n">
-        <v>7.2756404876709</v>
+        <v>7.27564001083374</v>
       </c>
       <c r="H2057" t="n">
         <v>2950</v>
@@ -60080,7 +60080,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G2059" t="n">
-        <v>7.24040699005127</v>
+        <v>7.24040746688843</v>
       </c>
       <c r="H2059" t="n">
         <v>2526</v>
@@ -60109,7 +60109,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G2060" t="n">
-        <v>7.24040699005127</v>
+        <v>7.24040746688843</v>
       </c>
       <c r="H2060" t="n">
         <v>1178</v>
@@ -60167,7 +60167,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G2062" t="n">
-        <v>7.2051739692688</v>
+        <v>7.20517444610596</v>
       </c>
       <c r="H2062" t="n">
         <v>4899</v>
@@ -60225,7 +60225,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G2064" t="n">
-        <v>7.2051739692688</v>
+        <v>7.20517444610596</v>
       </c>
       <c r="H2064" t="n">
         <v>2958</v>
@@ -60254,7 +60254,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G2065" t="n">
-        <v>7.2051739692688</v>
+        <v>7.20517444610596</v>
       </c>
       <c r="H2065" t="n">
         <v>3192</v>
@@ -60428,7 +60428,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G2071" t="n">
-        <v>7.13470792770386</v>
+        <v>7.13470840454102</v>
       </c>
       <c r="H2071" t="n">
         <v>659</v>
@@ -60718,7 +60718,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G2081" t="n">
-        <v>6.78237628936768</v>
+        <v>6.78237581253052</v>
       </c>
       <c r="H2081" t="n">
         <v>25460</v>
@@ -61849,7 +61849,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G2120" t="n">
-        <v>7.13470792770386</v>
+        <v>7.13470840454102</v>
       </c>
       <c r="H2120" t="n">
         <v>22492</v>
@@ -61878,7 +61878,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G2121" t="n">
-        <v>7.16994142532349</v>
+        <v>7.16994094848633</v>
       </c>
       <c r="H2121" t="n">
         <v>5584</v>
@@ -79980,6 +79980,35 @@
         <v>2154</v>
       </c>
       <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>8.80000019073486</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>9.14000034332275</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>8.68000030517578</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>8.89999961853027</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>8.89999961853027</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>6359</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -427,7 +427,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G2" t="n">
-        <v>4.91287660598755</v>
+        <v>4.91287708282471</v>
       </c>
       <c r="H2" t="n">
         <v>9493</v>
@@ -456,7 +456,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>4.91287660598755</v>
+        <v>4.91287708282471</v>
       </c>
       <c r="H3" t="n">
         <v>20399</v>
@@ -485,7 +485,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>4.91287660598755</v>
+        <v>4.91287708282471</v>
       </c>
       <c r="H4" t="n">
         <v>550</v>
@@ -514,7 +514,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G5" t="n">
-        <v>4.96080780029297</v>
+        <v>4.96080684661865</v>
       </c>
       <c r="H5" t="n">
         <v>13699</v>
@@ -543,7 +543,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G6" t="n">
-        <v>4.96080780029297</v>
+        <v>4.96080684661865</v>
       </c>
       <c r="H6" t="n">
         <v>22150</v>
@@ -630,7 +630,7 @@
         <v>6.25</v>
       </c>
       <c r="G9" t="n">
-        <v>4.99276065826416</v>
+        <v>4.99276113510132</v>
       </c>
       <c r="H9" t="n">
         <v>6824</v>
@@ -688,7 +688,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G11" t="n">
-        <v>4.96879529953003</v>
+        <v>4.96879625320435</v>
       </c>
       <c r="H11" t="n">
         <v>14400</v>
@@ -717,7 +717,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G12" t="n">
-        <v>5.00474405288696</v>
+        <v>5.0047435760498</v>
       </c>
       <c r="H12" t="n">
         <v>4765</v>
@@ -775,7 +775,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G14" t="n">
-        <v>5.10459899902344</v>
+        <v>5.10459852218628</v>
       </c>
       <c r="H14" t="n">
         <v>16997</v>
@@ -804,7 +804,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G15" t="n">
-        <v>5.11258792877197</v>
+        <v>5.11258745193481</v>
       </c>
       <c r="H15" t="n">
         <v>29415</v>
@@ -862,7 +862,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G17" t="n">
-        <v>5.14454078674316</v>
+        <v>5.14454126358032</v>
       </c>
       <c r="H17" t="n">
         <v>3580</v>
@@ -891,7 +891,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G18" t="n">
-        <v>5.18448257446289</v>
+        <v>5.18448305130005</v>
       </c>
       <c r="H18" t="n">
         <v>2671</v>
@@ -920,7 +920,7 @@
         <v>6.44500017166138</v>
       </c>
       <c r="G19" t="n">
-        <v>5.14853572845459</v>
+        <v>5.14853525161743</v>
       </c>
       <c r="H19" t="n">
         <v>4391</v>
@@ -949,7 +949,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G20" t="n">
-        <v>5.11258792877197</v>
+        <v>5.11258745193481</v>
       </c>
       <c r="H20" t="n">
         <v>3489</v>
@@ -978,7 +978,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G21" t="n">
-        <v>5.14454078674316</v>
+        <v>5.14454126358032</v>
       </c>
       <c r="H21" t="n">
         <v>1561</v>
@@ -1036,7 +1036,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G23" t="n">
-        <v>5.16850614547729</v>
+        <v>5.16850566864014</v>
       </c>
       <c r="H23" t="n">
         <v>1883</v>
@@ -1065,7 +1065,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G24" t="n">
-        <v>5.20844841003418</v>
+        <v>5.20844793319702</v>
       </c>
       <c r="H24" t="n">
         <v>11938</v>
@@ -1094,7 +1094,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G25" t="n">
-        <v>5.14454078674316</v>
+        <v>5.14454126358032</v>
       </c>
       <c r="H25" t="n">
         <v>2193</v>
@@ -1123,7 +1123,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G26" t="n">
-        <v>5.14054679870605</v>
+        <v>5.14054727554321</v>
       </c>
       <c r="H26" t="n">
         <v>1611</v>
@@ -1152,7 +1152,7 @@
         <v>6.5</v>
       </c>
       <c r="G27" t="n">
-        <v>5.19247150421143</v>
+        <v>5.19247198104858</v>
       </c>
       <c r="H27" t="n">
         <v>11644</v>
@@ -1210,7 +1210,7 @@
         <v>6.5</v>
       </c>
       <c r="G29" t="n">
-        <v>5.19247150421143</v>
+        <v>5.19247198104858</v>
       </c>
       <c r="H29" t="n">
         <v>13504</v>
@@ -1268,7 +1268,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G31" t="n">
-        <v>5.2723560333252</v>
+        <v>5.27235555648804</v>
       </c>
       <c r="H31" t="n">
         <v>6912</v>
@@ -1297,7 +1297,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>5.27634954452515</v>
+        <v>5.2763500213623</v>
       </c>
       <c r="H32" t="n">
         <v>3215</v>
@@ -1326,7 +1326,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G33" t="n">
-        <v>5.49603176116943</v>
+        <v>5.49603080749512</v>
       </c>
       <c r="H33" t="n">
         <v>10346</v>
@@ -1384,7 +1384,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G35" t="n">
-        <v>5.67177581787109</v>
+        <v>5.67177629470825</v>
       </c>
       <c r="H35" t="n">
         <v>17521</v>
@@ -1500,7 +1500,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G39" t="n">
-        <v>5.74367237091064</v>
+        <v>5.7436728477478</v>
       </c>
       <c r="H39" t="n">
         <v>7628</v>
@@ -1529,7 +1529,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G40" t="n">
-        <v>5.67976474761963</v>
+        <v>5.67976522445679</v>
       </c>
       <c r="H40" t="n">
         <v>8522</v>
@@ -1616,7 +1616,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>5.72769546508789</v>
+        <v>5.72769451141357</v>
       </c>
       <c r="H43" t="n">
         <v>2200</v>
@@ -1645,7 +1645,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G44" t="n">
-        <v>5.67177581787109</v>
+        <v>5.67177629470825</v>
       </c>
       <c r="H44" t="n">
         <v>17200</v>
@@ -1674,7 +1674,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G45" t="n">
-        <v>5.72769546508789</v>
+        <v>5.72769451141357</v>
       </c>
       <c r="H45" t="n">
         <v>2704</v>
@@ -1703,7 +1703,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G46" t="n">
-        <v>5.72370147705078</v>
+        <v>5.72370100021362</v>
       </c>
       <c r="H46" t="n">
         <v>2398</v>
@@ -1761,7 +1761,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G48" t="n">
-        <v>5.64781188964844</v>
+        <v>5.64781141281128</v>
       </c>
       <c r="H48" t="n">
         <v>166</v>
@@ -1790,7 +1790,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G49" t="n">
-        <v>5.82755041122437</v>
+        <v>5.82755136489868</v>
       </c>
       <c r="H49" t="n">
         <v>15519</v>
@@ -1848,7 +1848,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G51" t="n">
-        <v>5.83154535293579</v>
+        <v>5.83154439926147</v>
       </c>
       <c r="H51" t="n">
         <v>1781</v>
@@ -1877,7 +1877,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G52" t="n">
-        <v>5.82355642318726</v>
+        <v>5.8235559463501</v>
       </c>
       <c r="H52" t="n">
         <v>4780</v>
@@ -1906,7 +1906,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G53" t="n">
-        <v>5.90343999862671</v>
+        <v>5.90344095230103</v>
       </c>
       <c r="H53" t="n">
         <v>21076</v>
@@ -1935,7 +1935,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G54" t="n">
-        <v>5.95935964584351</v>
+        <v>5.95936012268066</v>
       </c>
       <c r="H54" t="n">
         <v>7298</v>
@@ -1993,7 +1993,7 @@
         <v>7.66499996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>6.123122215271</v>
+        <v>6.12312269210815</v>
       </c>
       <c r="H56" t="n">
         <v>9750</v>
@@ -2022,7 +2022,7 @@
         <v>7.89499998092651</v>
       </c>
       <c r="G57" t="n">
-        <v>6.30685567855835</v>
+        <v>6.30685615539551</v>
       </c>
       <c r="H57" t="n">
         <v>20694</v>
@@ -2051,7 +2051,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G58" t="n">
-        <v>6.32682704925537</v>
+        <v>6.32682657241821</v>
       </c>
       <c r="H58" t="n">
         <v>5452</v>
@@ -2109,7 +2109,7 @@
         <v>7.75</v>
       </c>
       <c r="G60" t="n">
-        <v>6.19102382659912</v>
+        <v>6.19102334976196</v>
       </c>
       <c r="H60" t="n">
         <v>12470</v>
@@ -2167,7 +2167,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G62" t="n">
-        <v>6.34679794311523</v>
+        <v>6.34679841995239</v>
       </c>
       <c r="H62" t="n">
         <v>5109</v>
@@ -2225,7 +2225,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G64" t="n">
-        <v>6.35079145431519</v>
+        <v>6.3507924079895</v>
       </c>
       <c r="H64" t="n">
         <v>17796</v>
@@ -2370,7 +2370,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G69" t="n">
-        <v>6.75021266937256</v>
+        <v>6.7502121925354</v>
       </c>
       <c r="H69" t="n">
         <v>26144</v>
@@ -2399,7 +2399,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G70" t="n">
-        <v>6.76619052886963</v>
+        <v>6.76619005203247</v>
       </c>
       <c r="H70" t="n">
         <v>14318</v>
@@ -2428,7 +2428,7 @@
         <v>8.5</v>
       </c>
       <c r="G71" t="n">
-        <v>6.79015588760376</v>
+        <v>6.7901554107666</v>
       </c>
       <c r="H71" t="n">
         <v>9688</v>
@@ -2486,7 +2486,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G73" t="n">
-        <v>7.02980804443359</v>
+        <v>7.02980709075928</v>
       </c>
       <c r="H73" t="n">
         <v>19379</v>
@@ -2515,7 +2515,7 @@
         <v>9</v>
       </c>
       <c r="G74" t="n">
-        <v>7.1895751953125</v>
+        <v>7.18957614898682</v>
       </c>
       <c r="H74" t="n">
         <v>45752</v>
@@ -2602,7 +2602,7 @@
         <v>9.79500007629395</v>
       </c>
       <c r="G77" t="n">
-        <v>7.82465505599976</v>
+        <v>7.8246545791626</v>
       </c>
       <c r="H77" t="n">
         <v>137248</v>
@@ -2631,7 +2631,7 @@
         <v>9.24499988555908</v>
       </c>
       <c r="G78" t="n">
-        <v>7.38529205322266</v>
+        <v>7.3852915763855</v>
       </c>
       <c r="H78" t="n">
         <v>64285</v>
@@ -2747,7 +2747,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G82" t="n">
-        <v>7.02980804443359</v>
+        <v>7.02980709075928</v>
       </c>
       <c r="H82" t="n">
         <v>18244</v>
@@ -2805,7 +2805,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G84" t="n">
-        <v>6.94592809677124</v>
+        <v>6.94592905044556</v>
       </c>
       <c r="H84" t="n">
         <v>5593</v>
@@ -2834,7 +2834,7 @@
         <v>8.78499984741211</v>
       </c>
       <c r="G85" t="n">
-        <v>7.15776920318604</v>
+        <v>7.15776968002319</v>
       </c>
       <c r="H85" t="n">
         <v>12088</v>
@@ -2863,7 +2863,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G86" t="n">
-        <v>6.95000267028809</v>
+        <v>6.95000314712524</v>
       </c>
       <c r="H86" t="n">
         <v>12383</v>
@@ -2892,7 +2892,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G87" t="n">
-        <v>6.9377818107605</v>
+        <v>6.93778133392334</v>
       </c>
       <c r="H87" t="n">
         <v>11708</v>
@@ -2921,7 +2921,7 @@
         <v>8.14500045776367</v>
       </c>
       <c r="G88" t="n">
-        <v>6.63631582260132</v>
+        <v>6.63631629943848</v>
       </c>
       <c r="H88" t="n">
         <v>11875</v>
@@ -3066,7 +3066,7 @@
         <v>8.00500011444092</v>
       </c>
       <c r="G93" t="n">
-        <v>6.52224779129028</v>
+        <v>6.52224731445312</v>
       </c>
       <c r="H93" t="n">
         <v>3608</v>
@@ -3211,7 +3211,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G98" t="n">
-        <v>7.00703716278076</v>
+        <v>7.00703763961792</v>
       </c>
       <c r="H98" t="n">
         <v>8280</v>
@@ -3240,7 +3240,7 @@
         <v>8.61499977111816</v>
       </c>
       <c r="G99" t="n">
-        <v>7.01925849914551</v>
+        <v>7.01925802230835</v>
       </c>
       <c r="H99" t="n">
         <v>10326</v>
@@ -3269,7 +3269,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G100" t="n">
-        <v>7.02333164215088</v>
+        <v>7.0233325958252</v>
       </c>
       <c r="H100" t="n">
         <v>4258</v>
@@ -3298,7 +3298,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G101" t="n">
-        <v>6.99074125289917</v>
+        <v>6.99074077606201</v>
       </c>
       <c r="H101" t="n">
         <v>8488</v>
@@ -3327,7 +3327,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G102" t="n">
-        <v>7.00703716278076</v>
+        <v>7.00703763961792</v>
       </c>
       <c r="H102" t="n">
         <v>4621</v>
@@ -3356,7 +3356,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G103" t="n">
-        <v>7.02333164215088</v>
+        <v>7.0233325958252</v>
       </c>
       <c r="H103" t="n">
         <v>1598</v>
@@ -3385,7 +3385,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G104" t="n">
-        <v>7.03147983551025</v>
+        <v>7.03148031234741</v>
       </c>
       <c r="H104" t="n">
         <v>4477</v>
@@ -3414,7 +3414,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G105" t="n">
-        <v>7.00703716278076</v>
+        <v>7.00703763961792</v>
       </c>
       <c r="H105" t="n">
         <v>1698</v>
@@ -3443,7 +3443,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G106" t="n">
-        <v>7.08851432800293</v>
+        <v>7.08851385116577</v>
       </c>
       <c r="H106" t="n">
         <v>16393</v>
@@ -3472,7 +3472,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G107" t="n">
-        <v>6.92963361740112</v>
+        <v>6.92963314056396</v>
       </c>
       <c r="H107" t="n">
         <v>14082</v>
@@ -3501,7 +3501,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G108" t="n">
-        <v>7.01518487930298</v>
+        <v>7.01518440246582</v>
       </c>
       <c r="H108" t="n">
         <v>3672</v>
@@ -3530,7 +3530,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G109" t="n">
-        <v>6.96629905700684</v>
+        <v>6.96629858016968</v>
       </c>
       <c r="H109" t="n">
         <v>3803</v>
@@ -3559,7 +3559,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>6.89296960830688</v>
+        <v>6.89296865463257</v>
       </c>
       <c r="H110" t="n">
         <v>13645</v>
@@ -3588,7 +3588,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G111" t="n">
-        <v>6.8033447265625</v>
+        <v>6.80334424972534</v>
       </c>
       <c r="H111" t="n">
         <v>4897</v>
@@ -3617,7 +3617,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G112" t="n">
-        <v>6.89296960830688</v>
+        <v>6.89296865463257</v>
       </c>
       <c r="H112" t="n">
         <v>4368</v>
@@ -3646,7 +3646,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G113" t="n">
-        <v>6.76260614395142</v>
+        <v>6.76260566711426</v>
       </c>
       <c r="H113" t="n">
         <v>8780</v>
@@ -3675,7 +3675,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G114" t="n">
-        <v>6.61594581604004</v>
+        <v>6.6159462928772</v>
       </c>
       <c r="H114" t="n">
         <v>2440</v>
@@ -3704,7 +3704,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G115" t="n">
-        <v>6.43669700622559</v>
+        <v>6.43669652938843</v>
       </c>
       <c r="H115" t="n">
         <v>6182</v>
@@ -3733,7 +3733,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>6.20856046676636</v>
+        <v>6.2085599899292</v>
       </c>
       <c r="H116" t="n">
         <v>28419</v>
@@ -3762,7 +3762,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G117" t="n">
-        <v>6.42040157318115</v>
+        <v>6.42040109634399</v>
       </c>
       <c r="H117" t="n">
         <v>6253</v>
@@ -3791,7 +3791,7 @@
         <v>7.75</v>
       </c>
       <c r="G118" t="n">
-        <v>6.31448125839233</v>
+        <v>6.31448078155518</v>
       </c>
       <c r="H118" t="n">
         <v>4631</v>
@@ -3849,7 +3849,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>6.88482093811035</v>
+        <v>6.88482046127319</v>
       </c>
       <c r="H120" t="n">
         <v>5304</v>
@@ -3878,7 +3878,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G121" t="n">
-        <v>6.81963920593262</v>
+        <v>6.81963872909546</v>
       </c>
       <c r="H121" t="n">
         <v>10422</v>
@@ -3907,7 +3907,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G122" t="n">
-        <v>6.70557117462158</v>
+        <v>6.70557069778442</v>
       </c>
       <c r="H122" t="n">
         <v>3705</v>
@@ -3936,7 +3936,7 @@
         <v>8.26500034332275</v>
       </c>
       <c r="G123" t="n">
-        <v>6.73408842086792</v>
+        <v>6.73408889770508</v>
       </c>
       <c r="H123" t="n">
         <v>2839</v>
@@ -3994,7 +3994,7 @@
         <v>8</v>
       </c>
       <c r="G125" t="n">
-        <v>6.5181736946106</v>
+        <v>6.51817417144775</v>
       </c>
       <c r="H125" t="n">
         <v>6788</v>
@@ -4023,7 +4023,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G126" t="n">
-        <v>6.59150409698486</v>
+        <v>6.59150362014771</v>
       </c>
       <c r="H126" t="n">
         <v>3711</v>
@@ -4052,7 +4052,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G127" t="n">
-        <v>6.62816905975342</v>
+        <v>6.62816858291626</v>
       </c>
       <c r="H127" t="n">
         <v>2765</v>
@@ -4081,7 +4081,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G128" t="n">
-        <v>6.91741132736206</v>
+        <v>6.91741275787354</v>
       </c>
       <c r="H128" t="n">
         <v>5734</v>
@@ -4110,7 +4110,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G129" t="n">
-        <v>6.91741132736206</v>
+        <v>6.91741275787354</v>
       </c>
       <c r="H129" t="n">
         <v>758</v>
@@ -4139,7 +4139,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G130" t="n">
-        <v>6.84408235549927</v>
+        <v>6.84408283233643</v>
       </c>
       <c r="H130" t="n">
         <v>5336</v>
@@ -4168,7 +4168,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G131" t="n">
-        <v>6.91741132736206</v>
+        <v>6.91741275787354</v>
       </c>
       <c r="H131" t="n">
         <v>2685</v>
@@ -4197,7 +4197,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G132" t="n">
-        <v>6.78704881668091</v>
+        <v>6.78704833984375</v>
       </c>
       <c r="H132" t="n">
         <v>2310</v>
@@ -4226,7 +4226,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G133" t="n">
-        <v>6.84408235549927</v>
+        <v>6.84408283233643</v>
       </c>
       <c r="H133" t="n">
         <v>988</v>
@@ -4255,7 +4255,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G134" t="n">
-        <v>6.84408235549927</v>
+        <v>6.84408283233643</v>
       </c>
       <c r="H134" t="n">
         <v>3155</v>
@@ -4284,7 +4284,7 @@
         <v>8.4350004196167</v>
       </c>
       <c r="G135" t="n">
-        <v>6.87259960174561</v>
+        <v>6.87260055541992</v>
       </c>
       <c r="H135" t="n">
         <v>1346</v>
@@ -4313,7 +4313,7 @@
         <v>8.4350004196167</v>
       </c>
       <c r="G136" t="n">
-        <v>6.87259960174561</v>
+        <v>6.87260055541992</v>
       </c>
       <c r="H136" t="n">
         <v>1346</v>
@@ -4371,7 +4371,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G138" t="n">
-        <v>6.84408235549927</v>
+        <v>6.84408283233643</v>
       </c>
       <c r="H138" t="n">
         <v>6014</v>
@@ -4400,7 +4400,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G139" t="n">
-        <v>6.82778692245483</v>
+        <v>6.82778787612915</v>
       </c>
       <c r="H139" t="n">
         <v>5165</v>
@@ -4429,7 +4429,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G140" t="n">
-        <v>6.76260614395142</v>
+        <v>6.76260566711426</v>
       </c>
       <c r="H140" t="n">
         <v>4748</v>
@@ -4516,7 +4516,7 @@
         <v>8.32499980926514</v>
       </c>
       <c r="G143" t="n">
-        <v>6.7829737663269</v>
+        <v>6.78297424316406</v>
       </c>
       <c r="H143" t="n">
         <v>3906</v>
@@ -4574,7 +4574,7 @@
         <v>8.23499965667725</v>
       </c>
       <c r="G145" t="n">
-        <v>6.70964479446411</v>
+        <v>6.70964574813843</v>
       </c>
       <c r="H145" t="n">
         <v>2061</v>
@@ -4603,7 +4603,7 @@
         <v>8.3149995803833</v>
       </c>
       <c r="G146" t="n">
-        <v>6.774827003479</v>
+        <v>6.77482604980469</v>
       </c>
       <c r="H146" t="n">
         <v>6371</v>
@@ -4632,7 +4632,7 @@
         <v>8.30500030517578</v>
       </c>
       <c r="G147" t="n">
-        <v>6.76667976379395</v>
+        <v>6.76667928695679</v>
       </c>
       <c r="H147" t="n">
         <v>5309</v>
@@ -4661,7 +4661,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G148" t="n">
-        <v>6.8033447265625</v>
+        <v>6.80334424972534</v>
       </c>
       <c r="H148" t="n">
         <v>8280</v>
@@ -4719,7 +4719,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G150" t="n">
-        <v>6.82778692245483</v>
+        <v>6.82778787612915</v>
       </c>
       <c r="H150" t="n">
         <v>8840</v>
@@ -4777,7 +4777,7 @@
         <v>8.3149995803833</v>
       </c>
       <c r="G152" t="n">
-        <v>6.774827003479</v>
+        <v>6.77482604980469</v>
       </c>
       <c r="H152" t="n">
         <v>1406</v>
@@ -4806,7 +4806,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G153" t="n">
-        <v>6.83186054229736</v>
+        <v>6.83186149597168</v>
       </c>
       <c r="H153" t="n">
         <v>6046</v>
@@ -4835,7 +4835,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G154" t="n">
-        <v>6.84408235549927</v>
+        <v>6.84408283233643</v>
       </c>
       <c r="H154" t="n">
         <v>3182</v>
@@ -5038,7 +5038,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G161" t="n">
-        <v>6.85223054885864</v>
+        <v>6.85223007202148</v>
       </c>
       <c r="H161" t="n">
         <v>916</v>
@@ -5067,7 +5067,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G162" t="n">
-        <v>6.85223054885864</v>
+        <v>6.85223007202148</v>
       </c>
       <c r="H162" t="n">
         <v>3754</v>
@@ -5096,7 +5096,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>6.81963920593262</v>
+        <v>6.81963872909546</v>
       </c>
       <c r="H163" t="n">
         <v>670</v>
@@ -5125,7 +5125,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G164" t="n">
-        <v>6.74630975723267</v>
+        <v>6.74631023406982</v>
       </c>
       <c r="H164" t="n">
         <v>2913</v>
@@ -5154,7 +5154,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G165" t="n">
-        <v>6.85223054885864</v>
+        <v>6.85223007202148</v>
       </c>
       <c r="H165" t="n">
         <v>6349</v>
@@ -5183,7 +5183,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G166" t="n">
-        <v>6.84408235549927</v>
+        <v>6.84408283233643</v>
       </c>
       <c r="H166" t="n">
         <v>859</v>
@@ -5241,7 +5241,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G168" t="n">
-        <v>6.83593559265137</v>
+        <v>6.83593511581421</v>
       </c>
       <c r="H168" t="n">
         <v>1264</v>
@@ -5328,7 +5328,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G171" t="n">
-        <v>6.93370771408081</v>
+        <v>6.93370866775513</v>
       </c>
       <c r="H171" t="n">
         <v>33132</v>
@@ -5357,7 +5357,7 @@
         <v>8.54500007629395</v>
       </c>
       <c r="G172" t="n">
-        <v>6.96222448348999</v>
+        <v>6.96222496032715</v>
       </c>
       <c r="H172" t="n">
         <v>15150</v>
@@ -5386,7 +5386,7 @@
         <v>8.47500038146973</v>
       </c>
       <c r="G173" t="n">
-        <v>6.90519046783447</v>
+        <v>6.90519142150879</v>
       </c>
       <c r="H173" t="n">
         <v>6175</v>
@@ -5444,7 +5444,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G175" t="n">
-        <v>6.97444677352905</v>
+        <v>6.97444581985474</v>
       </c>
       <c r="H175" t="n">
         <v>7055</v>
@@ -5473,7 +5473,7 @@
         <v>8.75</v>
       </c>
       <c r="G176" t="n">
-        <v>7.12925243377686</v>
+        <v>7.12925291061401</v>
       </c>
       <c r="H176" t="n">
         <v>35957</v>
@@ -5560,7 +5560,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G179" t="n">
-        <v>7.14554834365845</v>
+        <v>7.14554929733276</v>
       </c>
       <c r="H179" t="n">
         <v>9000</v>
@@ -5589,7 +5589,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G180" t="n">
-        <v>7.10480976104736</v>
+        <v>7.10481023788452</v>
       </c>
       <c r="H180" t="n">
         <v>3695</v>
@@ -5618,7 +5618,7 @@
         <v>8.60499954223633</v>
       </c>
       <c r="G181" t="n">
-        <v>7.01111125946045</v>
+        <v>7.01111030578613</v>
       </c>
       <c r="H181" t="n">
         <v>2628</v>
@@ -5705,7 +5705,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G184" t="n">
-        <v>7.19443416595459</v>
+        <v>7.19443464279175</v>
       </c>
       <c r="H184" t="n">
         <v>11223</v>
@@ -5734,7 +5734,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G185" t="n">
-        <v>7.35738849639893</v>
+        <v>7.35738897323608</v>
       </c>
       <c r="H185" t="n">
         <v>56641</v>
@@ -5763,7 +5763,7 @@
         <v>9.25</v>
       </c>
       <c r="G186" t="n">
-        <v>7.53663873672485</v>
+        <v>7.5366382598877</v>
       </c>
       <c r="H186" t="n">
         <v>43231</v>
@@ -5792,7 +5792,7 @@
         <v>9.04500007629395</v>
       </c>
       <c r="G187" t="n">
-        <v>7.36961030960083</v>
+        <v>7.36960983276367</v>
       </c>
       <c r="H187" t="n">
         <v>46365</v>
@@ -5850,7 +5850,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G189" t="n">
-        <v>7.30035495758057</v>
+        <v>7.30035448074341</v>
       </c>
       <c r="H189" t="n">
         <v>13518</v>
@@ -5879,7 +5879,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G190" t="n">
-        <v>7.1699914932251</v>
+        <v>7.16999101638794</v>
       </c>
       <c r="H190" t="n">
         <v>6307</v>
@@ -5908,7 +5908,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G191" t="n">
-        <v>7.25146818161011</v>
+        <v>7.25146770477295</v>
       </c>
       <c r="H191" t="n">
         <v>8242</v>
@@ -5937,7 +5937,7 @@
         <v>9</v>
       </c>
       <c r="G192" t="n">
-        <v>7.33294486999512</v>
+        <v>7.33294534683228</v>
       </c>
       <c r="H192" t="n">
         <v>6767</v>
@@ -5966,7 +5966,7 @@
         <v>8.96500015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>7.3044285774231</v>
+        <v>7.30442905426025</v>
       </c>
       <c r="H193" t="n">
         <v>3147</v>
@@ -5995,7 +5995,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>7.36553573608398</v>
+        <v>7.36553621292114</v>
       </c>
       <c r="H194" t="n">
         <v>7497</v>
@@ -6024,7 +6024,7 @@
         <v>9</v>
       </c>
       <c r="G195" t="n">
-        <v>7.33294486999512</v>
+        <v>7.33294534683228</v>
       </c>
       <c r="H195" t="n">
         <v>2353</v>
@@ -6053,7 +6053,7 @@
         <v>9</v>
       </c>
       <c r="G196" t="n">
-        <v>7.33294486999512</v>
+        <v>7.33294534683228</v>
       </c>
       <c r="H196" t="n">
         <v>5394</v>
@@ -6082,7 +6082,7 @@
         <v>9.09500026702881</v>
       </c>
       <c r="G197" t="n">
-        <v>7.41034889221191</v>
+        <v>7.41034936904907</v>
       </c>
       <c r="H197" t="n">
         <v>12723</v>
@@ -6111,7 +6111,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G198" t="n">
-        <v>7.45516109466553</v>
+        <v>7.45516204833984</v>
       </c>
       <c r="H198" t="n">
         <v>27066</v>
@@ -6169,7 +6169,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G200" t="n">
-        <v>7.6344108581543</v>
+        <v>7.63441181182861</v>
       </c>
       <c r="H200" t="n">
         <v>15518</v>
@@ -6198,7 +6198,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G201" t="n">
-        <v>7.62626314163208</v>
+        <v>7.62626361846924</v>
       </c>
       <c r="H201" t="n">
         <v>8007</v>
@@ -6256,7 +6256,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G203" t="n">
-        <v>7.6344108581543</v>
+        <v>7.63441181182861</v>
       </c>
       <c r="H203" t="n">
         <v>4985</v>
@@ -6285,7 +6285,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G204" t="n">
-        <v>7.59367227554321</v>
+        <v>7.59367179870605</v>
       </c>
       <c r="H204" t="n">
         <v>4547</v>
@@ -6343,7 +6343,7 @@
         <v>9.39500045776367</v>
       </c>
       <c r="G206" t="n">
-        <v>7.65478134155273</v>
+        <v>7.65478086471558</v>
       </c>
       <c r="H206" t="n">
         <v>30815</v>
@@ -6372,7 +6372,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G207" t="n">
-        <v>7.65070629119873</v>
+        <v>7.65070724487305</v>
       </c>
       <c r="H207" t="n">
         <v>2927</v>
@@ -6401,7 +6401,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>7.7729229927063</v>
+        <v>7.77292251586914</v>
       </c>
       <c r="H208" t="n">
         <v>6320</v>
@@ -6430,7 +6430,7 @@
         <v>9.39500045776367</v>
       </c>
       <c r="G209" t="n">
-        <v>7.65478134155273</v>
+        <v>7.65478086471558</v>
       </c>
       <c r="H209" t="n">
         <v>12571</v>
@@ -6459,7 +6459,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G210" t="n">
-        <v>7.41442441940308</v>
+        <v>7.4144229888916</v>
       </c>
       <c r="H210" t="n">
         <v>28708</v>
@@ -6488,7 +6488,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G211" t="n">
-        <v>7.41442441940308</v>
+        <v>7.4144229888916</v>
       </c>
       <c r="H211" t="n">
         <v>6682</v>
@@ -6517,7 +6517,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G212" t="n">
-        <v>7.35738849639893</v>
+        <v>7.35738897323608</v>
       </c>
       <c r="H212" t="n">
         <v>911</v>
@@ -6546,7 +6546,7 @@
         <v>8.99499988555908</v>
       </c>
       <c r="G213" t="n">
-        <v>7.32887172698975</v>
+        <v>7.3288722038269</v>
       </c>
       <c r="H213" t="n">
         <v>47666</v>
@@ -6575,7 +6575,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G214" t="n">
-        <v>7.19443416595459</v>
+        <v>7.19443464279175</v>
       </c>
       <c r="H214" t="n">
         <v>7414</v>
@@ -6604,7 +6604,7 @@
         <v>8.77499961853027</v>
       </c>
       <c r="G215" t="n">
-        <v>7.14962148666382</v>
+        <v>7.14962196350098</v>
       </c>
       <c r="H215" t="n">
         <v>2727</v>
@@ -6691,7 +6691,7 @@
         <v>8.5649995803833</v>
       </c>
       <c r="G218" t="n">
-        <v>6.97851991653442</v>
+        <v>6.97852039337158</v>
       </c>
       <c r="H218" t="n">
         <v>5000</v>
@@ -6720,7 +6720,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G219" t="n">
-        <v>7.01518487930298</v>
+        <v>7.01518440246582</v>
       </c>
       <c r="H219" t="n">
         <v>3968</v>
@@ -6778,7 +6778,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G221" t="n">
-        <v>6.83593559265137</v>
+        <v>6.83593511581421</v>
       </c>
       <c r="H221" t="n">
         <v>11021</v>
@@ -6807,7 +6807,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G222" t="n">
-        <v>6.91741132736206</v>
+        <v>6.91741275787354</v>
       </c>
       <c r="H222" t="n">
         <v>3920</v>
@@ -6836,7 +6836,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G223" t="n">
-        <v>6.91741132736206</v>
+        <v>6.91741275787354</v>
       </c>
       <c r="H223" t="n">
         <v>2610</v>
@@ -6894,7 +6894,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G225" t="n">
-        <v>7.34924125671387</v>
+        <v>7.34924221038818</v>
       </c>
       <c r="H225" t="n">
         <v>34117</v>
@@ -6923,7 +6923,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G226" t="n">
-        <v>7.44701385498047</v>
+        <v>7.44701433181763</v>
       </c>
       <c r="H226" t="n">
         <v>3064</v>
@@ -6981,7 +6981,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G228" t="n">
-        <v>7.10480976104736</v>
+        <v>7.10481023788452</v>
       </c>
       <c r="H228" t="n">
         <v>8424</v>
@@ -7010,7 +7010,7 @@
         <v>8.63500022888184</v>
       </c>
       <c r="G229" t="n">
-        <v>7.0355544090271</v>
+        <v>7.03555345535278</v>
       </c>
       <c r="H229" t="n">
         <v>2732</v>
@@ -7039,7 +7039,7 @@
         <v>8.74499988555908</v>
       </c>
       <c r="G230" t="n">
-        <v>7.12517881393433</v>
+        <v>7.12517786026001</v>
       </c>
       <c r="H230" t="n">
         <v>4890</v>
@@ -7068,7 +7068,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G231" t="n">
-        <v>7.10480976104736</v>
+        <v>7.10481023788452</v>
       </c>
       <c r="H231" t="n">
         <v>1189</v>
@@ -7126,7 +7126,7 @@
         <v>8.77499961853027</v>
       </c>
       <c r="G233" t="n">
-        <v>7.14962148666382</v>
+        <v>7.14962196350098</v>
       </c>
       <c r="H233" t="n">
         <v>1494</v>
@@ -7213,7 +7213,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G236" t="n">
-        <v>7.00703716278076</v>
+        <v>7.00703763961792</v>
       </c>
       <c r="H236" t="n">
         <v>5066</v>
@@ -7329,7 +7329,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G240" t="n">
-        <v>7.22702550888062</v>
+        <v>7.2270245552063</v>
       </c>
       <c r="H240" t="n">
         <v>4198</v>
@@ -7387,7 +7387,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G242" t="n">
-        <v>7.65885400772095</v>
+        <v>7.65885448455811</v>
       </c>
       <c r="H242" t="n">
         <v>14906</v>
@@ -7416,7 +7416,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G243" t="n">
-        <v>7.71181488037109</v>
+        <v>7.71181440353394</v>
       </c>
       <c r="H243" t="n">
         <v>30935</v>
@@ -7445,7 +7445,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G244" t="n">
-        <v>7.72403478622437</v>
+        <v>7.72403573989868</v>
       </c>
       <c r="H244" t="n">
         <v>19310</v>
@@ -7474,7 +7474,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G245" t="n">
-        <v>7.76477479934692</v>
+        <v>7.76477384567261</v>
       </c>
       <c r="H245" t="n">
         <v>17242</v>
@@ -7503,7 +7503,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G246" t="n">
-        <v>7.90328645706177</v>
+        <v>7.90328693389893</v>
       </c>
       <c r="H246" t="n">
         <v>20713</v>
@@ -7532,7 +7532,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G247" t="n">
-        <v>7.96032047271729</v>
+        <v>7.96031999588013</v>
       </c>
       <c r="H247" t="n">
         <v>10737</v>
@@ -7561,7 +7561,7 @@
         <v>9.9350004196167</v>
       </c>
       <c r="G248" t="n">
-        <v>8.09475612640381</v>
+        <v>8.09475708007812</v>
       </c>
       <c r="H248" t="n">
         <v>11336</v>
@@ -7619,7 +7619,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G250" t="n">
-        <v>8.09068298339844</v>
+        <v>8.09068393707275</v>
       </c>
       <c r="H250" t="n">
         <v>10923</v>
@@ -7648,7 +7648,7 @@
         <v>9.76500034332275</v>
       </c>
       <c r="G251" t="n">
-        <v>7.9562463760376</v>
+        <v>7.95624732971191</v>
       </c>
       <c r="H251" t="n">
         <v>6054</v>
@@ -7677,7 +7677,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G252" t="n">
-        <v>7.90328645706177</v>
+        <v>7.90328693389893</v>
       </c>
       <c r="H252" t="n">
         <v>7899</v>
@@ -7735,7 +7735,7 @@
         <v>9.8149995803833</v>
       </c>
       <c r="G254" t="n">
-        <v>7.99698400497437</v>
+        <v>7.99698543548584</v>
       </c>
       <c r="H254" t="n">
         <v>8073</v>
@@ -7764,7 +7764,7 @@
         <v>9.83500003814697</v>
       </c>
       <c r="G255" t="n">
-        <v>8.01327991485596</v>
+        <v>8.01328182220459</v>
       </c>
       <c r="H255" t="n">
         <v>5376</v>
@@ -7793,7 +7793,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G256" t="n">
-        <v>8.06623935699463</v>
+        <v>8.06624031066895</v>
       </c>
       <c r="H256" t="n">
         <v>16787</v>
@@ -7822,7 +7822,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G257" t="n">
-        <v>8.06623935699463</v>
+        <v>8.06624031066895</v>
       </c>
       <c r="H257" t="n">
         <v>5473</v>
@@ -7880,7 +7880,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G259" t="n">
-        <v>8.54695606231689</v>
+        <v>8.54695510864258</v>
       </c>
       <c r="H259" t="n">
         <v>13981</v>
@@ -7909,7 +7909,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G260" t="n">
-        <v>8.77509212493896</v>
+        <v>8.77509307861328</v>
       </c>
       <c r="H260" t="n">
         <v>16781</v>
@@ -7938,7 +7938,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G261" t="n">
-        <v>8.67731761932373</v>
+        <v>8.67731857299805</v>
       </c>
       <c r="H261" t="n">
         <v>11679</v>
@@ -7967,7 +7967,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G262" t="n">
-        <v>8.6610221862793</v>
+        <v>8.66102409362793</v>
       </c>
       <c r="H262" t="n">
         <v>4089</v>
@@ -8025,7 +8025,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G264" t="n">
-        <v>8.68546772003174</v>
+        <v>8.68546676635742</v>
       </c>
       <c r="H264" t="n">
         <v>11212</v>
@@ -8083,7 +8083,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G266" t="n">
-        <v>8.83212566375732</v>
+        <v>8.83212661743164</v>
       </c>
       <c r="H266" t="n">
         <v>14439</v>
@@ -8112,7 +8112,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G267" t="n">
-        <v>8.94619369506836</v>
+        <v>8.94619274139404</v>
       </c>
       <c r="H267" t="n">
         <v>16735</v>
@@ -8199,7 +8199,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G270" t="n">
-        <v>10.0624313354492</v>
+        <v>10.0624322891235</v>
       </c>
       <c r="H270" t="n">
         <v>158289</v>
@@ -8228,7 +8228,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G271" t="n">
-        <v>9.35357856750488</v>
+        <v>9.3535795211792</v>
       </c>
       <c r="H271" t="n">
         <v>148658</v>
@@ -8286,7 +8286,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G273" t="n">
-        <v>9.53282833099365</v>
+        <v>9.53283023834229</v>
       </c>
       <c r="H273" t="n">
         <v>30099</v>
@@ -8344,7 +8344,7 @@
         <v>12.75</v>
       </c>
       <c r="G275" t="n">
-        <v>10.3883419036865</v>
+        <v>10.3883399963379</v>
       </c>
       <c r="H275" t="n">
         <v>79740</v>
@@ -8373,7 +8373,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G276" t="n">
-        <v>10.5349979400635</v>
+        <v>10.5349998474121</v>
       </c>
       <c r="H276" t="n">
         <v>85635</v>
@@ -8518,7 +8518,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G281" t="n">
-        <v>11.2845907211304</v>
+        <v>11.2845878601074</v>
       </c>
       <c r="H281" t="n">
         <v>75384</v>
@@ -8547,7 +8547,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G282" t="n">
-        <v>11.3253259658813</v>
+        <v>11.3253269195557</v>
       </c>
       <c r="H282" t="n">
         <v>37053</v>
@@ -8576,7 +8576,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G283" t="n">
-        <v>11.4882822036743</v>
+        <v>11.48828125</v>
       </c>
       <c r="H283" t="n">
         <v>40824</v>
@@ -8634,7 +8634,7 @@
         <v>15</v>
       </c>
       <c r="G285" t="n">
-        <v>12.2215747833252</v>
+        <v>12.2215766906738</v>
       </c>
       <c r="H285" t="n">
         <v>78638</v>
@@ -8663,7 +8663,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>12.6697006225586</v>
+        <v>12.6696996688843</v>
       </c>
       <c r="H286" t="n">
         <v>95711</v>
@@ -8721,7 +8721,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G288" t="n">
-        <v>13.7289056777954</v>
+        <v>13.7289028167725</v>
       </c>
       <c r="H288" t="n">
         <v>143297</v>
@@ -8779,7 +8779,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G290" t="n">
-        <v>13.5252122879028</v>
+        <v>13.5252113342285</v>
       </c>
       <c r="H290" t="n">
         <v>372464</v>
@@ -8866,7 +8866,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G293" t="n">
-        <v>14.0955514907837</v>
+        <v>14.0955495834351</v>
       </c>
       <c r="H293" t="n">
         <v>249868</v>
@@ -8895,7 +8895,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G294" t="n">
-        <v>13.5659475326538</v>
+        <v>13.5659484863281</v>
       </c>
       <c r="H294" t="n">
         <v>359273</v>
@@ -8924,7 +8924,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G295" t="n">
-        <v>13.973334312439</v>
+        <v>13.9733352661133</v>
       </c>
       <c r="H295" t="n">
         <v>102080</v>
@@ -8982,7 +8982,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G297" t="n">
-        <v>12.6697006225586</v>
+        <v>12.6696996688843</v>
       </c>
       <c r="H297" t="n">
         <v>112555</v>
@@ -9011,7 +9011,7 @@
         <v>15.5</v>
       </c>
       <c r="G298" t="n">
-        <v>12.6289625167847</v>
+        <v>12.6289615631104</v>
       </c>
       <c r="H298" t="n">
         <v>63861</v>
@@ -9040,7 +9040,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>12.3437919616699</v>
+        <v>12.3437910079956</v>
       </c>
       <c r="H299" t="n">
         <v>42661</v>
@@ -9069,7 +9069,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G300" t="n">
-        <v>12.9141330718994</v>
+        <v>12.9141321182251</v>
       </c>
       <c r="H300" t="n">
         <v>113230</v>
@@ -9156,7 +9156,7 @@
         <v>16</v>
       </c>
       <c r="G303" t="n">
-        <v>13.0363473892212</v>
+        <v>13.0363483428955</v>
       </c>
       <c r="H303" t="n">
         <v>23424</v>
@@ -9214,7 +9214,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G305" t="n">
-        <v>13.0119047164917</v>
+        <v>13.011905670166</v>
       </c>
       <c r="H305" t="n">
         <v>32421</v>
@@ -9243,7 +9243,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G306" t="n">
-        <v>12.9874620437622</v>
+        <v>12.9874601364136</v>
       </c>
       <c r="H306" t="n">
         <v>16171</v>
@@ -9272,7 +9272,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G307" t="n">
-        <v>13.0119047164917</v>
+        <v>13.011905670166</v>
       </c>
       <c r="H307" t="n">
         <v>30877</v>
@@ -9301,7 +9301,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G308" t="n">
-        <v>13.2481880187988</v>
+        <v>13.2481889724731</v>
       </c>
       <c r="H308" t="n">
         <v>27779</v>
@@ -9359,7 +9359,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G310" t="n">
-        <v>13.5252122879028</v>
+        <v>13.5252113342285</v>
       </c>
       <c r="H310" t="n">
         <v>28868</v>
@@ -9388,7 +9388,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G311" t="n">
-        <v>13.7696418762207</v>
+        <v>13.7696409225464</v>
       </c>
       <c r="H311" t="n">
         <v>55505</v>
@@ -9417,7 +9417,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G312" t="n">
-        <v>13.8103809356689</v>
+        <v>13.8103828430176</v>
       </c>
       <c r="H312" t="n">
         <v>37474</v>
@@ -9446,7 +9446,7 @@
         <v>17.25</v>
       </c>
       <c r="G313" t="n">
-        <v>14.0548124313354</v>
+        <v>14.0548114776611</v>
       </c>
       <c r="H313" t="n">
         <v>107618</v>
@@ -9475,7 +9475,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G314" t="n">
-        <v>14.0059270858765</v>
+        <v>14.0059251785278</v>
       </c>
       <c r="H314" t="n">
         <v>61864</v>
@@ -9504,7 +9504,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G315" t="n">
-        <v>14.0140743255615</v>
+        <v>14.0140752792358</v>
       </c>
       <c r="H315" t="n">
         <v>63826</v>
@@ -9533,7 +9533,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G316" t="n">
-        <v>13.9651870727539</v>
+        <v>13.9651861190796</v>
       </c>
       <c r="H316" t="n">
         <v>41577</v>
@@ -9562,7 +9562,7 @@
         <v>17.1299991607666</v>
       </c>
       <c r="G317" t="n">
-        <v>13.9570398330688</v>
+        <v>13.9570407867432</v>
       </c>
       <c r="H317" t="n">
         <v>38749</v>
@@ -9591,7 +9591,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G318" t="n">
-        <v>13.8674154281616</v>
+        <v>13.8674173355103</v>
       </c>
       <c r="H318" t="n">
         <v>22927</v>
@@ -9620,7 +9620,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G319" t="n">
-        <v>13.875563621521</v>
+        <v>13.8755626678467</v>
       </c>
       <c r="H319" t="n">
         <v>25048</v>
@@ -9707,7 +9707,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G322" t="n">
-        <v>13.6311302185059</v>
+        <v>13.6311321258545</v>
       </c>
       <c r="H322" t="n">
         <v>17626</v>
@@ -9736,7 +9736,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G323" t="n">
-        <v>13.3459596633911</v>
+        <v>13.3459606170654</v>
       </c>
       <c r="H323" t="n">
         <v>50087</v>
@@ -9765,7 +9765,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G324" t="n">
-        <v>13.2807788848877</v>
+        <v>13.2807779312134</v>
       </c>
       <c r="H324" t="n">
         <v>25110</v>
@@ -9823,7 +9823,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G326" t="n">
-        <v>13.3785514831543</v>
+        <v>13.3785524368286</v>
       </c>
       <c r="H326" t="n">
         <v>13988</v>
@@ -9852,7 +9852,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G327" t="n">
-        <v>13.2237453460693</v>
+        <v>13.223744392395</v>
       </c>
       <c r="H327" t="n">
         <v>11118</v>
@@ -9881,7 +9881,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G328" t="n">
-        <v>13.3785514831543</v>
+        <v>13.3785524368286</v>
       </c>
       <c r="H328" t="n">
         <v>19232</v>
@@ -9910,7 +9910,7 @@
         <v>16</v>
       </c>
       <c r="G329" t="n">
-        <v>13.0363473892212</v>
+        <v>13.0363483428955</v>
       </c>
       <c r="H329" t="n">
         <v>33023</v>
@@ -9968,7 +9968,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G331" t="n">
-        <v>12.6371097564697</v>
+        <v>12.6371088027954</v>
       </c>
       <c r="H331" t="n">
         <v>22060</v>
@@ -10084,7 +10084,7 @@
         <v>15</v>
       </c>
       <c r="G335" t="n">
-        <v>12.2215747833252</v>
+        <v>12.2215766906738</v>
       </c>
       <c r="H335" t="n">
         <v>24693</v>
@@ -10113,7 +10113,7 @@
         <v>15.3900003433228</v>
       </c>
       <c r="G336" t="n">
-        <v>12.5393381118774</v>
+        <v>12.5393371582031</v>
       </c>
       <c r="H336" t="n">
         <v>16213</v>
@@ -10142,7 +10142,7 @@
         <v>15.5</v>
       </c>
       <c r="G337" t="n">
-        <v>12.6289625167847</v>
+        <v>12.6289615631104</v>
       </c>
       <c r="H337" t="n">
         <v>20705</v>
@@ -10171,7 +10171,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G338" t="n">
-        <v>13.0200519561768</v>
+        <v>13.0200529098511</v>
       </c>
       <c r="H338" t="n">
         <v>72522</v>
@@ -10200,7 +10200,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G339" t="n">
-        <v>13.0444955825806</v>
+        <v>13.0444946289062</v>
       </c>
       <c r="H339" t="n">
         <v>29767</v>
@@ -10229,7 +10229,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G340" t="n">
-        <v>12.9385747909546</v>
+        <v>12.9385757446289</v>
       </c>
       <c r="H340" t="n">
         <v>28319</v>
@@ -10287,7 +10287,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G342" t="n">
-        <v>12.7121915817261</v>
+        <v>12.7121934890747</v>
       </c>
       <c r="H342" t="n">
         <v>36835</v>
@@ -10316,7 +10316,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G343" t="n">
-        <v>12.5463466644287</v>
+        <v>12.546347618103</v>
       </c>
       <c r="H343" t="n">
         <v>30309</v>
@@ -10374,7 +10374,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G345" t="n">
-        <v>12.4551305770874</v>
+        <v>12.4551315307617</v>
       </c>
       <c r="H345" t="n">
         <v>24964</v>
@@ -10403,7 +10403,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G346" t="n">
-        <v>12.9360885620117</v>
+        <v>12.9360876083374</v>
       </c>
       <c r="H346" t="n">
         <v>38295</v>
@@ -10432,7 +10432,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G347" t="n">
-        <v>12.6790246963501</v>
+        <v>12.6790237426758</v>
       </c>
       <c r="H347" t="n">
         <v>28075</v>
@@ -10577,7 +10577,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G352" t="n">
-        <v>12.397084236145</v>
+        <v>12.3970832824707</v>
       </c>
       <c r="H352" t="n">
         <v>21257</v>
@@ -10606,7 +10606,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G353" t="n">
-        <v>12.2146511077881</v>
+        <v>12.2146520614624</v>
       </c>
       <c r="H353" t="n">
         <v>42518</v>
@@ -10693,7 +10693,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G356" t="n">
-        <v>12.6873159408569</v>
+        <v>12.6873168945312</v>
       </c>
       <c r="H356" t="n">
         <v>17586</v>
@@ -10722,7 +10722,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G357" t="n">
-        <v>12.6292686462402</v>
+        <v>12.6292695999146</v>
       </c>
       <c r="H357" t="n">
         <v>11678</v>
@@ -10780,7 +10780,7 @@
         <v>15</v>
       </c>
       <c r="G359" t="n">
-        <v>12.4385442733765</v>
+        <v>12.4385452270508</v>
       </c>
       <c r="H359" t="n">
         <v>12449</v>
@@ -10954,7 +10954,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G365" t="n">
-        <v>12.7536544799805</v>
+        <v>12.7536554336548</v>
       </c>
       <c r="H365" t="n">
         <v>4595</v>
@@ -11070,7 +11070,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G369" t="n">
-        <v>12.4468383789062</v>
+        <v>12.4468374252319</v>
       </c>
       <c r="H369" t="n">
         <v>14509</v>
@@ -11099,7 +11099,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G370" t="n">
-        <v>12.3390378952026</v>
+        <v>12.3390369415283</v>
       </c>
       <c r="H370" t="n">
         <v>10317</v>
@@ -11128,7 +11128,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G371" t="n">
-        <v>12.0156335830688</v>
+        <v>12.0156345367432</v>
       </c>
       <c r="H371" t="n">
         <v>17510</v>
@@ -11157,7 +11157,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G372" t="n">
-        <v>11.7751560211182</v>
+        <v>11.7751569747925</v>
       </c>
       <c r="H372" t="n">
         <v>14434</v>
@@ -11215,7 +11215,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G374" t="n">
-        <v>11.5844326019287</v>
+        <v>11.5844316482544</v>
       </c>
       <c r="H374" t="n">
         <v>14355</v>
@@ -11389,7 +11389,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>11.7751560211182</v>
+        <v>11.7751569747925</v>
       </c>
       <c r="H380" t="n">
         <v>13544</v>
@@ -11476,7 +11476,7 @@
         <v>14.1099996566772</v>
       </c>
       <c r="G383" t="n">
-        <v>11.7005252838135</v>
+        <v>11.7005243301392</v>
       </c>
       <c r="H383" t="n">
         <v>12173</v>
@@ -11505,7 +11505,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G384" t="n">
-        <v>11.5346765518188</v>
+        <v>11.5346775054932</v>
       </c>
       <c r="H384" t="n">
         <v>6657</v>
@@ -11621,7 +11621,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G388" t="n">
-        <v>11.2776145935059</v>
+        <v>11.2776155471802</v>
       </c>
       <c r="H388" t="n">
         <v>12024</v>
@@ -11708,7 +11708,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>11.3190755844116</v>
+        <v>11.3190765380859</v>
       </c>
       <c r="H391" t="n">
         <v>9695</v>
@@ -11737,7 +11737,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G392" t="n">
-        <v>11.3771228790283</v>
+        <v>11.3771238327026</v>
       </c>
       <c r="H392" t="n">
         <v>6969</v>
@@ -11766,7 +11766,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G393" t="n">
-        <v>11.3356618881226</v>
+        <v>11.3356609344482</v>
       </c>
       <c r="H393" t="n">
         <v>9178</v>
@@ -11824,7 +11824,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>11.2941989898682</v>
+        <v>11.2941999435425</v>
       </c>
       <c r="H395" t="n">
         <v>3799</v>
@@ -11882,7 +11882,7 @@
         <v>13.5</v>
       </c>
       <c r="G397" t="n">
-        <v>11.1946907043457</v>
+        <v>11.19469165802</v>
       </c>
       <c r="H397" t="n">
         <v>8673</v>
@@ -11998,7 +11998,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G401" t="n">
-        <v>11.7751560211182</v>
+        <v>11.7751569747925</v>
       </c>
       <c r="H401" t="n">
         <v>45663</v>
@@ -12172,7 +12172,7 @@
         <v>14.0299997329712</v>
       </c>
       <c r="G407" t="n">
-        <v>11.6341857910156</v>
+        <v>11.6341848373413</v>
       </c>
       <c r="H407" t="n">
         <v>3908</v>
@@ -12259,7 +12259,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G410" t="n">
-        <v>12.6790246963501</v>
+        <v>12.6790237426758</v>
       </c>
       <c r="H410" t="n">
         <v>13482</v>
@@ -12317,7 +12317,7 @@
         <v>15</v>
       </c>
       <c r="G412" t="n">
-        <v>12.4385442733765</v>
+        <v>12.4385452270508</v>
       </c>
       <c r="H412" t="n">
         <v>25552</v>
@@ -12346,7 +12346,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G413" t="n">
-        <v>12.2229433059692</v>
+        <v>12.2229423522949</v>
       </c>
       <c r="H413" t="n">
         <v>15093</v>
@@ -12433,7 +12433,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G416" t="n">
-        <v>12.2809906005859</v>
+        <v>12.2809915542603</v>
       </c>
       <c r="H416" t="n">
         <v>18494</v>
@@ -12462,7 +12462,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G417" t="n">
-        <v>12.2395296096802</v>
+        <v>12.2395286560059</v>
       </c>
       <c r="H417" t="n">
         <v>7412</v>
@@ -12520,7 +12520,7 @@
         <v>14.5</v>
       </c>
       <c r="G419" t="n">
-        <v>12.0239267349243</v>
+        <v>12.0239276885986</v>
       </c>
       <c r="H419" t="n">
         <v>9220</v>
@@ -12549,7 +12549,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G420" t="n">
-        <v>11.9990510940552</v>
+        <v>11.9990501403809</v>
       </c>
       <c r="H420" t="n">
         <v>8947</v>
@@ -12578,7 +12578,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G421" t="n">
-        <v>11.8995428085327</v>
+        <v>11.8995418548584</v>
       </c>
       <c r="H421" t="n">
         <v>6358</v>
@@ -12607,7 +12607,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G422" t="n">
-        <v>11.8995428085327</v>
+        <v>11.8995418548584</v>
       </c>
       <c r="H422" t="n">
         <v>6838</v>
@@ -12665,7 +12665,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G424" t="n">
-        <v>12.1566047668457</v>
+        <v>12.15660572052</v>
       </c>
       <c r="H424" t="n">
         <v>15306</v>
@@ -12694,7 +12694,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G425" t="n">
-        <v>12.0653896331787</v>
+        <v>12.0653886795044</v>
       </c>
       <c r="H425" t="n">
         <v>13711</v>
@@ -12723,7 +12723,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G426" t="n">
-        <v>12.0570955276489</v>
+        <v>12.0570964813232</v>
       </c>
       <c r="H426" t="n">
         <v>4562</v>
@@ -12781,7 +12781,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G428" t="n">
-        <v>12.3058681488037</v>
+        <v>12.3058671951294</v>
       </c>
       <c r="H428" t="n">
         <v>16024</v>
@@ -12810,7 +12810,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G429" t="n">
-        <v>12.4302530288696</v>
+        <v>12.4302520751953</v>
       </c>
       <c r="H429" t="n">
         <v>18527</v>
@@ -12868,7 +12868,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G431" t="n">
-        <v>12.3556203842163</v>
+        <v>12.3556213378906</v>
       </c>
       <c r="H431" t="n">
         <v>20472</v>
@@ -12897,7 +12897,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G432" t="n">
-        <v>12.4302530288696</v>
+        <v>12.4302520751953</v>
       </c>
       <c r="H432" t="n">
         <v>28371</v>
@@ -12955,7 +12955,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G434" t="n">
-        <v>12.3722057342529</v>
+        <v>12.3722066879272</v>
       </c>
       <c r="H434" t="n">
         <v>7940</v>
@@ -13013,7 +13013,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G436" t="n">
-        <v>12.1731901168823</v>
+        <v>12.173189163208</v>
       </c>
       <c r="H436" t="n">
         <v>38036</v>
@@ -13042,7 +13042,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G437" t="n">
-        <v>12.1566047668457</v>
+        <v>12.15660572052</v>
       </c>
       <c r="H437" t="n">
         <v>23483</v>
@@ -13071,7 +13071,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G438" t="n">
-        <v>12.3722057342529</v>
+        <v>12.3722066879272</v>
       </c>
       <c r="H438" t="n">
         <v>100631</v>
@@ -13100,7 +13100,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G439" t="n">
-        <v>12.3722057342529</v>
+        <v>12.3722066879272</v>
       </c>
       <c r="H439" t="n">
         <v>15556</v>
@@ -13129,7 +13129,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G440" t="n">
-        <v>12.2146511077881</v>
+        <v>12.2146520614624</v>
       </c>
       <c r="H440" t="n">
         <v>10898</v>
@@ -13187,7 +13187,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G442" t="n">
-        <v>12.1566047668457</v>
+        <v>12.15660572052</v>
       </c>
       <c r="H442" t="n">
         <v>5869</v>
@@ -13216,7 +13216,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G443" t="n">
-        <v>12.2726984024048</v>
+        <v>12.2726993560791</v>
       </c>
       <c r="H443" t="n">
         <v>14042</v>
@@ -13245,7 +13245,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G444" t="n">
-        <v>12.1151418685913</v>
+        <v>12.1151428222656</v>
       </c>
       <c r="H444" t="n">
         <v>17089</v>
@@ -13274,7 +13274,7 @@
         <v>14.75</v>
       </c>
       <c r="G445" t="n">
-        <v>12.2312355041504</v>
+        <v>12.2312364578247</v>
       </c>
       <c r="H445" t="n">
         <v>13439</v>
@@ -13332,7 +13332,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G447" t="n">
-        <v>12.2726984024048</v>
+        <v>12.2726993560791</v>
       </c>
       <c r="H447" t="n">
         <v>7518</v>
@@ -13361,7 +13361,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G448" t="n">
-        <v>12.2229433059692</v>
+        <v>12.2229423522949</v>
       </c>
       <c r="H448" t="n">
         <v>13038</v>
@@ -13419,7 +13419,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G450" t="n">
-        <v>12.2229433059692</v>
+        <v>12.2229423522949</v>
       </c>
       <c r="H450" t="n">
         <v>6397</v>
@@ -13448,7 +13448,7 @@
         <v>14.7700004577637</v>
       </c>
       <c r="G451" t="n">
-        <v>12.2478218078613</v>
+        <v>12.247820854187</v>
       </c>
       <c r="H451" t="n">
         <v>12129</v>
@@ -13535,7 +13535,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G454" t="n">
-        <v>12.2644062042236</v>
+        <v>12.2644052505493</v>
       </c>
       <c r="H454" t="n">
         <v>6141</v>
@@ -13593,7 +13593,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G456" t="n">
-        <v>12.5048847198486</v>
+        <v>12.5048856735229</v>
       </c>
       <c r="H456" t="n">
         <v>12039</v>
@@ -13680,7 +13680,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G459" t="n">
-        <v>12.5463466644287</v>
+        <v>12.546347618103</v>
       </c>
       <c r="H459" t="n">
         <v>8305</v>
@@ -13709,7 +13709,7 @@
         <v>15</v>
       </c>
       <c r="G460" t="n">
-        <v>12.4385442733765</v>
+        <v>12.4385452270508</v>
       </c>
       <c r="H460" t="n">
         <v>18506</v>
@@ -13738,7 +13738,7 @@
         <v>15</v>
       </c>
       <c r="G461" t="n">
-        <v>12.4385442733765</v>
+        <v>12.4385452270508</v>
       </c>
       <c r="H461" t="n">
         <v>8683</v>
@@ -13825,7 +13825,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G464" t="n">
-        <v>12.3556203842163</v>
+        <v>12.3556213378906</v>
       </c>
       <c r="H464" t="n">
         <v>10716</v>
@@ -13854,7 +13854,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G465" t="n">
-        <v>12.5048847198486</v>
+        <v>12.5048856735229</v>
       </c>
       <c r="H465" t="n">
         <v>2531</v>
@@ -13970,7 +13970,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G469" t="n">
-        <v>12.5878086090088</v>
+        <v>12.5878076553345</v>
       </c>
       <c r="H469" t="n">
         <v>8180</v>
@@ -14028,7 +14028,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G471" t="n">
-        <v>12.6292686462402</v>
+        <v>12.6292695999146</v>
       </c>
       <c r="H471" t="n">
         <v>6021</v>
@@ -14086,7 +14086,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G473" t="n">
-        <v>12.6790246963501</v>
+        <v>12.6790237426758</v>
       </c>
       <c r="H473" t="n">
         <v>10931</v>
@@ -14144,7 +14144,7 @@
         <v>15.25</v>
       </c>
       <c r="G475" t="n">
-        <v>12.6458539962769</v>
+        <v>12.6458549499512</v>
       </c>
       <c r="H475" t="n">
         <v>5117</v>
@@ -14173,7 +14173,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G476" t="n">
-        <v>12.6790246963501</v>
+        <v>12.6790237426758</v>
       </c>
       <c r="H476" t="n">
         <v>7899</v>
@@ -14231,7 +14231,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G478" t="n">
-        <v>12.4468383789062</v>
+        <v>12.4468374252319</v>
       </c>
       <c r="H478" t="n">
         <v>10899</v>
@@ -14260,7 +14260,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G479" t="n">
-        <v>12.4302530288696</v>
+        <v>12.4302520751953</v>
       </c>
       <c r="H479" t="n">
         <v>12669</v>
@@ -14289,7 +14289,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G480" t="n">
-        <v>12.7039003372192</v>
+        <v>12.7039012908936</v>
       </c>
       <c r="H480" t="n">
         <v>79987</v>
@@ -14405,7 +14405,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G484" t="n">
-        <v>13.1433973312378</v>
+        <v>13.1433963775635</v>
       </c>
       <c r="H484" t="n">
         <v>64007</v>
@@ -14579,7 +14579,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G490" t="n">
-        <v>13.9477558135986</v>
+        <v>13.9477548599243</v>
       </c>
       <c r="H490" t="n">
         <v>117106</v>
@@ -14608,7 +14608,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>13.9726343154907</v>
+        <v>13.9726333618164</v>
       </c>
       <c r="H491" t="n">
         <v>54222</v>
@@ -14637,7 +14637,7 @@
         <v>16.5</v>
       </c>
       <c r="G492" t="n">
-        <v>13.6823997497559</v>
+        <v>13.6824007034302</v>
       </c>
       <c r="H492" t="n">
         <v>235031</v>
@@ -14724,7 +14724,7 @@
         <v>16.0900001525879</v>
       </c>
       <c r="G495" t="n">
-        <v>13.3424129486084</v>
+        <v>13.3424139022827</v>
       </c>
       <c r="H495" t="n">
         <v>11108</v>
@@ -14869,7 +14869,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G500" t="n">
-        <v>13.8067836761475</v>
+        <v>13.8067846298218</v>
       </c>
       <c r="H500" t="n">
         <v>53133</v>
@@ -14898,7 +14898,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G501" t="n">
-        <v>13.4999685287476</v>
+        <v>13.4999675750732</v>
       </c>
       <c r="H501" t="n">
         <v>15452</v>
@@ -14927,7 +14927,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G502" t="n">
-        <v>13.4170455932617</v>
+        <v>13.4170446395874</v>
       </c>
       <c r="H502" t="n">
         <v>10237</v>
@@ -14985,7 +14985,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G504" t="n">
-        <v>13.3258275985718</v>
+        <v>13.3258285522461</v>
       </c>
       <c r="H504" t="n">
         <v>8839</v>
@@ -15101,7 +15101,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G508" t="n">
-        <v>13.1102266311646</v>
+        <v>13.1102275848389</v>
       </c>
       <c r="H508" t="n">
         <v>9747</v>
@@ -15159,7 +15159,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G510" t="n">
-        <v>13.1516885757446</v>
+        <v>13.1516876220703</v>
       </c>
       <c r="H510" t="n">
         <v>25855</v>
@@ -15188,7 +15188,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G511" t="n">
-        <v>13.3009519577026</v>
+        <v>13.300952911377</v>
       </c>
       <c r="H511" t="n">
         <v>9571</v>
@@ -15275,7 +15275,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G514" t="n">
-        <v>13.3672904968262</v>
+        <v>13.3672914505005</v>
       </c>
       <c r="H514" t="n">
         <v>18072</v>
@@ -15304,7 +15304,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>13.3507061004639</v>
+        <v>13.3507041931152</v>
       </c>
       <c r="H515" t="n">
         <v>18264</v>
@@ -15362,7 +15362,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G517" t="n">
-        <v>13.3672904968262</v>
+        <v>13.3672914505005</v>
       </c>
       <c r="H517" t="n">
         <v>16407</v>
@@ -15391,7 +15391,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G518" t="n">
-        <v>13.284366607666</v>
+        <v>13.2843675613403</v>
       </c>
       <c r="H518" t="n">
         <v>13632</v>
@@ -15449,7 +15449,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G520" t="n">
-        <v>13.2014427185059</v>
+        <v>13.2014436721802</v>
       </c>
       <c r="H520" t="n">
         <v>23672</v>
@@ -15507,7 +15507,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G522" t="n">
-        <v>13.284366607666</v>
+        <v>13.2843675613403</v>
       </c>
       <c r="H522" t="n">
         <v>12088</v>
@@ -15536,7 +15536,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G523" t="n">
-        <v>13.3009519577026</v>
+        <v>13.300952911377</v>
       </c>
       <c r="H523" t="n">
         <v>5777</v>
@@ -15623,7 +15623,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G526" t="n">
-        <v>13.3009519577026</v>
+        <v>13.300952911377</v>
       </c>
       <c r="H526" t="n">
         <v>22442</v>
@@ -15681,7 +15681,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G528" t="n">
-        <v>13.3009519577026</v>
+        <v>13.300952911377</v>
       </c>
       <c r="H528" t="n">
         <v>25522</v>
@@ -15739,7 +15739,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G530" t="n">
-        <v>13.3507061004639</v>
+        <v>13.3507041931152</v>
       </c>
       <c r="H530" t="n">
         <v>9782</v>
@@ -15826,7 +15826,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G533" t="n">
-        <v>13.1019353866577</v>
+        <v>13.1019344329834</v>
       </c>
       <c r="H533" t="n">
         <v>17732</v>
@@ -15855,7 +15855,7 @@
         <v>15.5</v>
       </c>
       <c r="G534" t="n">
-        <v>12.8531637191772</v>
+        <v>12.8531646728516</v>
       </c>
       <c r="H534" t="n">
         <v>16868</v>
@@ -15913,7 +15913,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>12.9360885620117</v>
+        <v>12.9360876083374</v>
       </c>
       <c r="H536" t="n">
         <v>64407</v>
@@ -15942,7 +15942,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G537" t="n">
-        <v>12.9360885620117</v>
+        <v>12.9360876083374</v>
       </c>
       <c r="H537" t="n">
         <v>69811</v>
@@ -16058,7 +16058,7 @@
         <v>15.5</v>
       </c>
       <c r="G541" t="n">
-        <v>12.8531637191772</v>
+        <v>12.8531646728516</v>
       </c>
       <c r="H541" t="n">
         <v>7128</v>
@@ -16145,7 +16145,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G544" t="n">
-        <v>12.8863325119019</v>
+        <v>12.8863334655762</v>
       </c>
       <c r="H544" t="n">
         <v>10751</v>
@@ -16232,7 +16232,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G547" t="n">
-        <v>13.1185178756714</v>
+        <v>13.1185188293457</v>
       </c>
       <c r="H547" t="n">
         <v>11521</v>
@@ -16290,7 +16290,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G549" t="n">
-        <v>12.8697481155396</v>
+        <v>12.8697490692139</v>
       </c>
       <c r="H549" t="n">
         <v>6432</v>
@@ -16406,7 +16406,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G553" t="n">
-        <v>12.7868232727051</v>
+        <v>12.7868242263794</v>
       </c>
       <c r="H553" t="n">
         <v>12202</v>
@@ -16609,7 +16609,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G560" t="n">
-        <v>12.8697481155396</v>
+        <v>12.8697490692139</v>
       </c>
       <c r="H560" t="n">
         <v>2545</v>
@@ -16638,7 +16638,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G561" t="n">
-        <v>13.0521793365479</v>
+        <v>13.0521802902222</v>
       </c>
       <c r="H561" t="n">
         <v>6186</v>
@@ -16667,7 +16667,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G562" t="n">
-        <v>13.1516885757446</v>
+        <v>13.1516876220703</v>
       </c>
       <c r="H562" t="n">
         <v>9363</v>
@@ -16725,7 +16725,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G564" t="n">
-        <v>13.1019353866577</v>
+        <v>13.1019344329834</v>
       </c>
       <c r="H564" t="n">
         <v>22720</v>
@@ -16754,7 +16754,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G565" t="n">
-        <v>12.8365793228149</v>
+        <v>12.8365783691406</v>
       </c>
       <c r="H565" t="n">
         <v>10281</v>
@@ -16870,7 +16870,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G569" t="n">
-        <v>13.0521793365479</v>
+        <v>13.0521802902222</v>
       </c>
       <c r="H569" t="n">
         <v>12181</v>
@@ -16986,7 +16986,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G573" t="n">
-        <v>12.8697481155396</v>
+        <v>12.8697490692139</v>
       </c>
       <c r="H573" t="n">
         <v>10113</v>
@@ -17015,7 +17015,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G574" t="n">
-        <v>13.0190114974976</v>
+        <v>13.0190105438232</v>
       </c>
       <c r="H574" t="n">
         <v>2693</v>
@@ -17073,7 +17073,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G576" t="n">
-        <v>12.9360885620117</v>
+        <v>12.9360876083374</v>
       </c>
       <c r="H576" t="n">
         <v>7063</v>
@@ -17102,7 +17102,7 @@
         <v>15.5</v>
       </c>
       <c r="G577" t="n">
-        <v>12.8531637191772</v>
+        <v>12.8531646728516</v>
       </c>
       <c r="H577" t="n">
         <v>8970</v>
@@ -17131,7 +17131,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G578" t="n">
-        <v>13.1019353866577</v>
+        <v>13.1019344329834</v>
       </c>
       <c r="H578" t="n">
         <v>3820</v>
@@ -17160,7 +17160,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G579" t="n">
-        <v>13.0521793365479</v>
+        <v>13.0521802902222</v>
       </c>
       <c r="H579" t="n">
         <v>6568</v>
@@ -17218,7 +17218,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G581" t="n">
-        <v>13.0024271011353</v>
+        <v>13.0024261474609</v>
       </c>
       <c r="H581" t="n">
         <v>2866</v>
@@ -17247,7 +17247,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G582" t="n">
-        <v>13.0521793365479</v>
+        <v>13.0521802902222</v>
       </c>
       <c r="H582" t="n">
         <v>3784</v>
@@ -17305,7 +17305,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>12.9360885620117</v>
+        <v>12.9360876083374</v>
       </c>
       <c r="H584" t="n">
         <v>6280</v>
@@ -17334,7 +17334,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G585" t="n">
-        <v>13.0024271011353</v>
+        <v>13.0024261474609</v>
       </c>
       <c r="H585" t="n">
         <v>3549</v>
@@ -17363,7 +17363,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G586" t="n">
-        <v>13.2014427185059</v>
+        <v>13.2014436721802</v>
       </c>
       <c r="H586" t="n">
         <v>11401</v>
@@ -17421,7 +17421,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G588" t="n">
-        <v>13.1019353866577</v>
+        <v>13.1019344329834</v>
       </c>
       <c r="H588" t="n">
         <v>4013</v>
@@ -17450,7 +17450,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G589" t="n">
-        <v>13.1019353866577</v>
+        <v>13.1019344329834</v>
       </c>
       <c r="H589" t="n">
         <v>4473</v>
@@ -17479,7 +17479,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G590" t="n">
-        <v>13.2014427185059</v>
+        <v>13.2014436721802</v>
       </c>
       <c r="H590" t="n">
         <v>7153</v>
@@ -17508,7 +17508,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G591" t="n">
-        <v>13.1516885757446</v>
+        <v>13.1516876220703</v>
       </c>
       <c r="H591" t="n">
         <v>2070</v>
@@ -17566,7 +17566,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G593" t="n">
-        <v>13.284366607666</v>
+        <v>13.2843675613403</v>
       </c>
       <c r="H593" t="n">
         <v>8278</v>
@@ -17653,7 +17653,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G596" t="n">
-        <v>13.284366607666</v>
+        <v>13.2843675613403</v>
       </c>
       <c r="H596" t="n">
         <v>15741</v>
@@ -17682,7 +17682,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>13.3507061004639</v>
+        <v>13.3507041931152</v>
       </c>
       <c r="H597" t="n">
         <v>7278</v>
@@ -17711,7 +17711,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G598" t="n">
-        <v>13.4968929290771</v>
+        <v>13.4968938827515</v>
       </c>
       <c r="H598" t="n">
         <v>4547</v>
@@ -17798,7 +17798,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G601" t="n">
-        <v>13.445897102356</v>
+        <v>13.4458961486816</v>
       </c>
       <c r="H601" t="n">
         <v>9348</v>
@@ -18059,7 +18059,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G610" t="n">
-        <v>12.5959672927856</v>
+        <v>12.5959663391113</v>
       </c>
       <c r="H610" t="n">
         <v>11692</v>
@@ -18436,7 +18436,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G623" t="n">
-        <v>13.3609056472778</v>
+        <v>13.3609046936035</v>
       </c>
       <c r="H623" t="n">
         <v>2632</v>
@@ -18494,7 +18494,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G625" t="n">
-        <v>13.3609056472778</v>
+        <v>13.3609046936035</v>
       </c>
       <c r="H625" t="n">
         <v>3083</v>
@@ -18668,7 +18668,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G631" t="n">
-        <v>13.4628963470459</v>
+        <v>13.4628953933716</v>
       </c>
       <c r="H631" t="n">
         <v>3970</v>
@@ -18784,7 +18784,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G635" t="n">
-        <v>13.0889253616333</v>
+        <v>13.0889263153076</v>
       </c>
       <c r="H635" t="n">
         <v>6319</v>
@@ -18929,7 +18929,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G640" t="n">
-        <v>12.9699363708496</v>
+        <v>12.9699373245239</v>
       </c>
       <c r="H640" t="n">
         <v>3125</v>
@@ -18987,7 +18987,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G642" t="n">
-        <v>13.0719270706177</v>
+        <v>13.071928024292</v>
       </c>
       <c r="H642" t="n">
         <v>10854</v>
@@ -19103,7 +19103,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G646" t="n">
-        <v>12.9869346618652</v>
+        <v>12.9869356155396</v>
       </c>
       <c r="H646" t="n">
         <v>3681</v>
@@ -19132,7 +19132,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G647" t="n">
-        <v>13.0719270706177</v>
+        <v>13.071928024292</v>
       </c>
       <c r="H647" t="n">
         <v>2506</v>
@@ -19161,7 +19161,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G648" t="n">
-        <v>13.1569223403931</v>
+        <v>13.1569213867188</v>
       </c>
       <c r="H648" t="n">
         <v>3677</v>
@@ -19248,7 +19248,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G651" t="n">
-        <v>13.0039339065552</v>
+        <v>13.0039348602295</v>
       </c>
       <c r="H651" t="n">
         <v>3947</v>
@@ -19364,7 +19364,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G655" t="n">
-        <v>12.9699363708496</v>
+        <v>12.9699373245239</v>
       </c>
       <c r="H655" t="n">
         <v>1831</v>
@@ -19451,7 +19451,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G658" t="n">
-        <v>12.9869346618652</v>
+        <v>12.9869356155396</v>
       </c>
       <c r="H658" t="n">
         <v>1229</v>
@@ -19480,7 +19480,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G659" t="n">
-        <v>12.9699363708496</v>
+        <v>12.9699373245239</v>
       </c>
       <c r="H659" t="n">
         <v>4278</v>
@@ -19509,7 +19509,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G660" t="n">
-        <v>13.0889253616333</v>
+        <v>13.0889263153076</v>
       </c>
       <c r="H660" t="n">
         <v>3774</v>
@@ -19538,7 +19538,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G661" t="n">
-        <v>12.8509464263916</v>
+        <v>12.8509454727173</v>
       </c>
       <c r="H661" t="n">
         <v>3907</v>
@@ -19857,7 +19857,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G672" t="n">
-        <v>12.0350141525269</v>
+        <v>12.0350131988525</v>
       </c>
       <c r="H672" t="n">
         <v>4976</v>
@@ -19915,7 +19915,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G674" t="n">
-        <v>12.5959672927856</v>
+        <v>12.5959663391113</v>
       </c>
       <c r="H674" t="n">
         <v>1792</v>
@@ -19944,7 +19944,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G675" t="n">
-        <v>12.5279731750488</v>
+        <v>12.5279722213745</v>
       </c>
       <c r="H675" t="n">
         <v>4068</v>
@@ -19973,7 +19973,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G676" t="n">
-        <v>12.5959672927856</v>
+        <v>12.5959663391113</v>
       </c>
       <c r="H676" t="n">
         <v>927</v>
@@ -20002,7 +20002,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G677" t="n">
-        <v>12.9869346618652</v>
+        <v>12.9869356155396</v>
       </c>
       <c r="H677" t="n">
         <v>3964</v>
@@ -20089,7 +20089,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G680" t="n">
-        <v>12.5109748840332</v>
+        <v>12.5109739303589</v>
       </c>
       <c r="H680" t="n">
         <v>2858</v>
@@ -20292,7 +20292,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G687" t="n">
-        <v>12.5449724197388</v>
+        <v>12.5449714660645</v>
       </c>
       <c r="H687" t="n">
         <v>6669</v>
@@ -20321,7 +20321,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G688" t="n">
-        <v>12.5449724197388</v>
+        <v>12.5449714660645</v>
       </c>
       <c r="H688" t="n">
         <v>8177</v>
@@ -20350,7 +20350,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G689" t="n">
-        <v>12.6639614105225</v>
+        <v>12.6639623641968</v>
       </c>
       <c r="H689" t="n">
         <v>3151</v>
@@ -20466,7 +20466,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G693" t="n">
-        <v>12.4089832305908</v>
+        <v>12.4089841842651</v>
       </c>
       <c r="H693" t="n">
         <v>2666</v>
@@ -20495,7 +20495,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G694" t="n">
-        <v>12.6469640731812</v>
+        <v>12.6469631195068</v>
       </c>
       <c r="H694" t="n">
         <v>3256</v>
@@ -20524,7 +20524,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G695" t="n">
-        <v>12.6299648284912</v>
+        <v>12.6299638748169</v>
       </c>
       <c r="H695" t="n">
         <v>767</v>
@@ -20727,7 +20727,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G702" t="n">
-        <v>12.3749847412109</v>
+        <v>12.3749856948853</v>
       </c>
       <c r="H702" t="n">
         <v>2009</v>
@@ -20814,7 +20814,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G705" t="n">
-        <v>12.4089832305908</v>
+        <v>12.4089841842651</v>
       </c>
       <c r="H705" t="n">
         <v>8953</v>
@@ -20930,7 +20930,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G709" t="n">
-        <v>10.9131059646606</v>
+        <v>10.9131050109863</v>
       </c>
       <c r="H709" t="n">
         <v>13875</v>
@@ -20988,7 +20988,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G711" t="n">
-        <v>11.03209400177</v>
+        <v>11.0320949554443</v>
       </c>
       <c r="H711" t="n">
         <v>10783</v>
@@ -21104,7 +21104,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G715" t="n">
-        <v>10.5901327133179</v>
+        <v>10.5901317596436</v>
       </c>
       <c r="H715" t="n">
         <v>12512</v>
@@ -21191,7 +21191,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G718" t="n">
-        <v>10.6751251220703</v>
+        <v>10.675124168396</v>
       </c>
       <c r="H718" t="n">
         <v>14791</v>
@@ -21220,7 +21220,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G719" t="n">
-        <v>10.4711408615112</v>
+        <v>10.4711418151855</v>
       </c>
       <c r="H719" t="n">
         <v>11515</v>
@@ -21249,7 +21249,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G720" t="n">
-        <v>10.5221366882324</v>
+        <v>10.5221376419067</v>
       </c>
       <c r="H720" t="n">
         <v>14593</v>
@@ -21278,7 +21278,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G721" t="n">
-        <v>10.6581268310547</v>
+        <v>10.6581258773804</v>
       </c>
       <c r="H721" t="n">
         <v>2544</v>
@@ -21307,7 +21307,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G722" t="n">
-        <v>10.5221366882324</v>
+        <v>10.5221376419067</v>
       </c>
       <c r="H722" t="n">
         <v>4192</v>
@@ -21510,7 +21510,7 @@
         <v>13</v>
       </c>
       <c r="G729" t="n">
-        <v>11.04909324646</v>
+        <v>11.0490942001343</v>
       </c>
       <c r="H729" t="n">
         <v>1235</v>
@@ -21597,7 +21597,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G732" t="n">
-        <v>11.3210725784302</v>
+        <v>11.3210716247559</v>
       </c>
       <c r="H732" t="n">
         <v>2650</v>
@@ -21713,7 +21713,7 @@
         <v>13</v>
       </c>
       <c r="G736" t="n">
-        <v>11.04909324646</v>
+        <v>11.0490942001343</v>
       </c>
       <c r="H736" t="n">
         <v>1901</v>
@@ -21916,7 +21916,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G743" t="n">
-        <v>10.063175201416</v>
+        <v>10.0631742477417</v>
       </c>
       <c r="H743" t="n">
         <v>1807</v>
@@ -22003,7 +22003,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G746" t="n">
-        <v>10.556134223938</v>
+        <v>10.5561351776123</v>
       </c>
       <c r="H746" t="n">
         <v>12940</v>
@@ -22119,7 +22119,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G750" t="n">
-        <v>10.6071310043335</v>
+        <v>10.6071300506592</v>
       </c>
       <c r="H750" t="n">
         <v>955</v>
@@ -22177,7 +22177,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G752" t="n">
-        <v>10.6071310043335</v>
+        <v>10.6071300506592</v>
       </c>
       <c r="H752" t="n">
         <v>1850</v>
@@ -22206,7 +22206,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G753" t="n">
-        <v>10.4711408615112</v>
+        <v>10.4711418151855</v>
       </c>
       <c r="H753" t="n">
         <v>1160</v>
@@ -22235,7 +22235,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G754" t="n">
-        <v>10.5391359329224</v>
+        <v>10.5391368865967</v>
       </c>
       <c r="H754" t="n">
         <v>1779</v>
@@ -22380,7 +22380,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G759" t="n">
-        <v>9.09425449371338</v>
+        <v>9.0942554473877</v>
       </c>
       <c r="H759" t="n">
         <v>4520</v>
@@ -22467,7 +22467,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G762" t="n">
-        <v>9.17924690246582</v>
+        <v>9.17924785614014</v>
       </c>
       <c r="H762" t="n">
         <v>11417</v>
@@ -22583,7 +22583,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G766" t="n">
-        <v>10.9131059646606</v>
+        <v>10.9131050109863</v>
       </c>
       <c r="H766" t="n">
         <v>6619</v>
@@ -22641,7 +22641,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G768" t="n">
-        <v>10.6581268310547</v>
+        <v>10.6581258773804</v>
       </c>
       <c r="H768" t="n">
         <v>5651</v>
@@ -22699,7 +22699,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G770" t="n">
-        <v>10.9131059646606</v>
+        <v>10.9131050109863</v>
       </c>
       <c r="H770" t="n">
         <v>2821</v>
@@ -22728,7 +22728,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G771" t="n">
-        <v>10.556134223938</v>
+        <v>10.5561351776123</v>
       </c>
       <c r="H771" t="n">
         <v>4676</v>
@@ -22902,7 +22902,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G777" t="n">
-        <v>9.8931884765625</v>
+        <v>9.89318943023682</v>
       </c>
       <c r="H777" t="n">
         <v>8808</v>
@@ -22960,7 +22960,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G779" t="n">
-        <v>10.0971727371216</v>
+        <v>10.0971717834473</v>
       </c>
       <c r="H779" t="n">
         <v>4452</v>
@@ -23250,7 +23250,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G789" t="n">
-        <v>10.2161626815796</v>
+        <v>10.2161636352539</v>
       </c>
       <c r="H789" t="n">
         <v>2973</v>
@@ -23337,7 +23337,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G792" t="n">
-        <v>9.87619018554688</v>
+        <v>9.87619113922119</v>
       </c>
       <c r="H792" t="n">
         <v>5141</v>
@@ -23511,7 +23511,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G798" t="n">
-        <v>10.063175201416</v>
+        <v>10.0631742477417</v>
       </c>
       <c r="H798" t="n">
         <v>4835</v>
@@ -23569,7 +23569,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G800" t="n">
-        <v>9.8931884765625</v>
+        <v>9.89318943023682</v>
       </c>
       <c r="H800" t="n">
         <v>3975</v>
@@ -23598,7 +23598,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G801" t="n">
-        <v>10.063175201416</v>
+        <v>10.0631742477417</v>
       </c>
       <c r="H801" t="n">
         <v>3813</v>
@@ -23627,7 +23627,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G802" t="n">
-        <v>9.8931884765625</v>
+        <v>9.89318943023682</v>
       </c>
       <c r="H802" t="n">
         <v>1415</v>
@@ -23917,7 +23917,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G812" t="n">
-        <v>10.063175201416</v>
+        <v>10.0631742477417</v>
       </c>
       <c r="H812" t="n">
         <v>1848</v>
@@ -24004,7 +24004,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G815" t="n">
-        <v>10.0971727371216</v>
+        <v>10.0971717834473</v>
       </c>
       <c r="H815" t="n">
         <v>1326</v>
@@ -24033,7 +24033,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G816" t="n">
-        <v>10.4371433258057</v>
+        <v>10.43714427948</v>
       </c>
       <c r="H816" t="n">
         <v>20119</v>
@@ -24120,7 +24120,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G819" t="n">
-        <v>10.6751251220703</v>
+        <v>10.675124168396</v>
       </c>
       <c r="H819" t="n">
         <v>6541</v>
@@ -24178,7 +24178,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G821" t="n">
-        <v>10.5901327133179</v>
+        <v>10.5901317596436</v>
       </c>
       <c r="H821" t="n">
         <v>4370</v>
@@ -24265,7 +24265,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G824" t="n">
-        <v>10.6071310043335</v>
+        <v>10.6071300506592</v>
       </c>
       <c r="H824" t="n">
         <v>5188</v>
@@ -24294,7 +24294,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G825" t="n">
-        <v>10.5901327133179</v>
+        <v>10.5901317596436</v>
       </c>
       <c r="H825" t="n">
         <v>1639</v>
@@ -24352,7 +24352,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G827" t="n">
-        <v>10.6581268310547</v>
+        <v>10.6581258773804</v>
       </c>
       <c r="H827" t="n">
         <v>6703</v>
@@ -24381,7 +24381,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>10.5391359329224</v>
+        <v>10.5391368865967</v>
       </c>
       <c r="H828" t="n">
         <v>4015</v>
@@ -24410,7 +24410,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G829" t="n">
-        <v>10.6411285400391</v>
+        <v>10.6411275863647</v>
       </c>
       <c r="H829" t="n">
         <v>1596</v>
@@ -24468,7 +24468,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G831" t="n">
-        <v>10.6411285400391</v>
+        <v>10.6411275863647</v>
       </c>
       <c r="H831" t="n">
         <v>13500</v>
@@ -24497,7 +24497,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G832" t="n">
-        <v>10.6751251220703</v>
+        <v>10.675124168396</v>
       </c>
       <c r="H832" t="n">
         <v>4510</v>
@@ -24526,7 +24526,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G833" t="n">
-        <v>10.6751251220703</v>
+        <v>10.675124168396</v>
       </c>
       <c r="H833" t="n">
         <v>6889</v>
@@ -24613,7 +24613,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G836" t="n">
-        <v>10.5391359329224</v>
+        <v>10.5391368865967</v>
       </c>
       <c r="H836" t="n">
         <v>3307</v>
@@ -24642,7 +24642,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G837" t="n">
-        <v>10.6411285400391</v>
+        <v>10.6411275863647</v>
       </c>
       <c r="H837" t="n">
         <v>2527</v>
@@ -24671,7 +24671,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G838" t="n">
-        <v>10.5391359329224</v>
+        <v>10.5391368865967</v>
       </c>
       <c r="H838" t="n">
         <v>1927</v>
@@ -24758,7 +24758,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G841" t="n">
-        <v>10.6581268310547</v>
+        <v>10.6581258773804</v>
       </c>
       <c r="H841" t="n">
         <v>2748</v>
@@ -24787,7 +24787,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G842" t="n">
-        <v>10.6581268310547</v>
+        <v>10.6581258773804</v>
       </c>
       <c r="H842" t="n">
         <v>5980</v>
@@ -24874,7 +24874,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G845" t="n">
-        <v>10.9131059646606</v>
+        <v>10.9131050109863</v>
       </c>
       <c r="H845" t="n">
         <v>11428</v>
@@ -24903,7 +24903,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G846" t="n">
-        <v>10.896107673645</v>
+        <v>10.8961067199707</v>
       </c>
       <c r="H846" t="n">
         <v>10666</v>
@@ -79994,7 +79994,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="D2746" t="n">
-        <v>9.14000034332275</v>
+        <v>9.26000022888184</v>
       </c>
       <c r="E2746" t="n">
         <v>8.68000030517578</v>
@@ -80009,6 +80009,35 @@
         <v>6359</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>9.02000045776367</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>9.07999992370605</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>8.89999961853027</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>9.02000045776367</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>9.02000045776367</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>4649</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -427,7 +427,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G2" t="n">
-        <v>4.91287708282471</v>
+        <v>4.91287660598755</v>
       </c>
       <c r="H2" t="n">
         <v>9493</v>
@@ -456,7 +456,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>4.91287708282471</v>
+        <v>4.91287660598755</v>
       </c>
       <c r="H3" t="n">
         <v>20399</v>
@@ -485,7 +485,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>4.91287708282471</v>
+        <v>4.91287660598755</v>
       </c>
       <c r="H4" t="n">
         <v>550</v>
@@ -601,7 +601,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G8" t="n">
-        <v>4.95281887054443</v>
+        <v>4.95281934738159</v>
       </c>
       <c r="H8" t="n">
         <v>5200</v>
@@ -630,7 +630,7 @@
         <v>6.25</v>
       </c>
       <c r="G9" t="n">
-        <v>4.99276113510132</v>
+        <v>4.99276065826416</v>
       </c>
       <c r="H9" t="n">
         <v>6824</v>
@@ -717,7 +717,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G12" t="n">
-        <v>5.0047435760498</v>
+        <v>5.00474309921265</v>
       </c>
       <c r="H12" t="n">
         <v>4765</v>
@@ -746,7 +746,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G13" t="n">
-        <v>5.04868030548096</v>
+        <v>5.0486798286438</v>
       </c>
       <c r="H13" t="n">
         <v>41577</v>
@@ -775,7 +775,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G14" t="n">
-        <v>5.10459852218628</v>
+        <v>5.10459899902344</v>
       </c>
       <c r="H14" t="n">
         <v>16997</v>
@@ -833,7 +833,7 @@
         <v>6.40500020980835</v>
       </c>
       <c r="G16" t="n">
-        <v>5.11658191680908</v>
+        <v>5.11658143997192</v>
       </c>
       <c r="H16" t="n">
         <v>8017</v>
@@ -891,7 +891,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G18" t="n">
-        <v>5.18448257446289</v>
+        <v>5.18448352813721</v>
       </c>
       <c r="H18" t="n">
         <v>2671</v>
@@ -920,7 +920,7 @@
         <v>6.44500017166138</v>
       </c>
       <c r="G19" t="n">
-        <v>5.14853477478027</v>
+        <v>5.14853572845459</v>
       </c>
       <c r="H19" t="n">
         <v>4391</v>
@@ -1007,7 +1007,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G22" t="n">
-        <v>5.15252923965454</v>
+        <v>5.15252876281738</v>
       </c>
       <c r="H22" t="n">
         <v>2276</v>
@@ -1181,7 +1181,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G28" t="n">
-        <v>5.15252923965454</v>
+        <v>5.15252876281738</v>
       </c>
       <c r="H28" t="n">
         <v>18305</v>
@@ -1239,7 +1239,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>5.15252923965454</v>
+        <v>5.15252876281738</v>
       </c>
       <c r="H30" t="n">
         <v>7910</v>
@@ -1326,7 +1326,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G33" t="n">
-        <v>5.49603080749512</v>
+        <v>5.49603176116943</v>
       </c>
       <c r="H33" t="n">
         <v>10346</v>
@@ -1413,7 +1413,7 @@
         <v>6.88500022888184</v>
       </c>
       <c r="G36" t="n">
-        <v>5.50002574920654</v>
+        <v>5.5000262260437</v>
       </c>
       <c r="H36" t="n">
         <v>5041</v>
@@ -1442,7 +1442,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G37" t="n">
-        <v>5.63982343673706</v>
+        <v>5.6398229598999</v>
       </c>
       <c r="H37" t="n">
         <v>8243</v>
@@ -1471,7 +1471,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G38" t="n">
-        <v>5.75166082382202</v>
+        <v>5.75165987014771</v>
       </c>
       <c r="H38" t="n">
         <v>19828</v>
@@ -1500,7 +1500,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G39" t="n">
-        <v>5.74367189407349</v>
+        <v>5.74367237091064</v>
       </c>
       <c r="H39" t="n">
         <v>7628</v>
@@ -1587,7 +1587,7 @@
         <v>7.18499994277954</v>
       </c>
       <c r="G42" t="n">
-        <v>5.73967742919922</v>
+        <v>5.73967838287354</v>
       </c>
       <c r="H42" t="n">
         <v>7589</v>
@@ -1616,7 +1616,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>5.72769546508789</v>
+        <v>5.72769498825073</v>
       </c>
       <c r="H43" t="n">
         <v>2200</v>
@@ -1674,7 +1674,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G45" t="n">
-        <v>5.72769546508789</v>
+        <v>5.72769498825073</v>
       </c>
       <c r="H45" t="n">
         <v>2704</v>
@@ -1790,7 +1790,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G49" t="n">
-        <v>5.82755041122437</v>
+        <v>5.82755088806152</v>
       </c>
       <c r="H49" t="n">
         <v>15519</v>
@@ -1819,7 +1819,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G50" t="n">
-        <v>5.81556844711304</v>
+        <v>5.81556749343872</v>
       </c>
       <c r="H50" t="n">
         <v>3160</v>
@@ -1877,7 +1877,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G52" t="n">
-        <v>5.82355642318726</v>
+        <v>5.82355690002441</v>
       </c>
       <c r="H52" t="n">
         <v>4780</v>
@@ -1906,7 +1906,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G53" t="n">
-        <v>5.90344095230103</v>
+        <v>5.90344047546387</v>
       </c>
       <c r="H53" t="n">
         <v>21076</v>
@@ -1935,7 +1935,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G54" t="n">
-        <v>5.95935964584351</v>
+        <v>5.95935916900635</v>
       </c>
       <c r="H54" t="n">
         <v>7298</v>
@@ -1964,7 +1964,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G55" t="n">
-        <v>6.23096561431885</v>
+        <v>6.23096609115601</v>
       </c>
       <c r="H55" t="n">
         <v>5741</v>
@@ -2080,7 +2080,7 @@
         <v>7.90500020980835</v>
       </c>
       <c r="G59" t="n">
-        <v>6.31484508514404</v>
+        <v>6.31484413146973</v>
       </c>
       <c r="H59" t="n">
         <v>3075</v>
@@ -2109,7 +2109,7 @@
         <v>7.75</v>
       </c>
       <c r="G60" t="n">
-        <v>6.19102382659912</v>
+        <v>6.19102334976196</v>
       </c>
       <c r="H60" t="n">
         <v>12470</v>
@@ -2196,7 +2196,7 @@
         <v>7.93499994277954</v>
       </c>
       <c r="G63" t="n">
-        <v>6.3388090133667</v>
+        <v>6.33880996704102</v>
       </c>
       <c r="H63" t="n">
         <v>5580</v>
@@ -2312,7 +2312,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G67" t="n">
-        <v>6.55050277709961</v>
+        <v>6.55050230026245</v>
       </c>
       <c r="H67" t="n">
         <v>7377</v>
@@ -2399,7 +2399,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G70" t="n">
-        <v>6.76619005203247</v>
+        <v>6.76618957519531</v>
       </c>
       <c r="H70" t="n">
         <v>14318</v>
@@ -2428,7 +2428,7 @@
         <v>8.5</v>
       </c>
       <c r="G71" t="n">
-        <v>6.79015493392944</v>
+        <v>6.7901554107666</v>
       </c>
       <c r="H71" t="n">
         <v>9688</v>
@@ -2457,7 +2457,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G72" t="n">
-        <v>6.86205101013184</v>
+        <v>6.86205148696899</v>
       </c>
       <c r="H72" t="n">
         <v>9488</v>
@@ -2515,7 +2515,7 @@
         <v>9</v>
       </c>
       <c r="G74" t="n">
-        <v>7.1895751953125</v>
+        <v>7.18957614898682</v>
       </c>
       <c r="H74" t="n">
         <v>45752</v>
@@ -2602,7 +2602,7 @@
         <v>9.79500007629395</v>
       </c>
       <c r="G77" t="n">
-        <v>7.8246545791626</v>
+        <v>7.82465553283691</v>
       </c>
       <c r="H77" t="n">
         <v>137248</v>
@@ -2660,7 +2660,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G79" t="n">
-        <v>7.10969209671021</v>
+        <v>7.10969066619873</v>
       </c>
       <c r="H79" t="n">
         <v>67199</v>
@@ -2689,7 +2689,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G80" t="n">
-        <v>7.14963340759277</v>
+        <v>7.14963388442993</v>
       </c>
       <c r="H80" t="n">
         <v>11155</v>
@@ -2718,7 +2718,7 @@
         <v>8.875</v>
       </c>
       <c r="G81" t="n">
-        <v>7.08972120285034</v>
+        <v>7.08972024917603</v>
       </c>
       <c r="H81" t="n">
         <v>23079</v>
@@ -2805,7 +2805,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G84" t="n">
-        <v>6.9459285736084</v>
+        <v>6.94592905044556</v>
       </c>
       <c r="H84" t="n">
         <v>5593</v>
@@ -2834,7 +2834,7 @@
         <v>8.78499984741211</v>
       </c>
       <c r="G85" t="n">
-        <v>7.15776968002319</v>
+        <v>7.15777015686035</v>
       </c>
       <c r="H85" t="n">
         <v>12088</v>
@@ -2863,7 +2863,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G86" t="n">
-        <v>6.95000267028809</v>
+        <v>6.95000314712524</v>
       </c>
       <c r="H86" t="n">
         <v>12383</v>
@@ -2892,7 +2892,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G87" t="n">
-        <v>6.93778228759766</v>
+        <v>6.9377818107605</v>
       </c>
       <c r="H87" t="n">
         <v>11708</v>
@@ -2921,7 +2921,7 @@
         <v>8.14500045776367</v>
       </c>
       <c r="G88" t="n">
-        <v>6.63631677627563</v>
+        <v>6.63631629943848</v>
       </c>
       <c r="H88" t="n">
         <v>11875</v>
@@ -2979,7 +2979,7 @@
         <v>8.03499984741211</v>
       </c>
       <c r="G90" t="n">
-        <v>6.54668998718262</v>
+        <v>6.54669094085693</v>
       </c>
       <c r="H90" t="n">
         <v>13317</v>
@@ -3037,7 +3037,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G92" t="n">
-        <v>6.68112850189209</v>
+        <v>6.68112802505493</v>
       </c>
       <c r="H92" t="n">
         <v>2266</v>
@@ -3066,7 +3066,7 @@
         <v>8.00500011444092</v>
       </c>
       <c r="G93" t="n">
-        <v>6.52224779129028</v>
+        <v>6.52224826812744</v>
       </c>
       <c r="H93" t="n">
         <v>3608</v>
@@ -3095,7 +3095,7 @@
         <v>8.24499988555908</v>
       </c>
       <c r="G94" t="n">
-        <v>6.71779298782349</v>
+        <v>6.71779346466064</v>
       </c>
       <c r="H94" t="n">
         <v>2103</v>
@@ -3124,7 +3124,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G95" t="n">
-        <v>6.73001432418823</v>
+        <v>6.73001480102539</v>
       </c>
       <c r="H95" t="n">
         <v>4983</v>
@@ -3153,7 +3153,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G96" t="n">
-        <v>7.21073055267334</v>
+        <v>7.21072959899902</v>
       </c>
       <c r="H96" t="n">
         <v>29339</v>
@@ -3211,7 +3211,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G98" t="n">
-        <v>7.00703763961792</v>
+        <v>7.00703716278076</v>
       </c>
       <c r="H98" t="n">
         <v>8280</v>
@@ -3240,7 +3240,7 @@
         <v>8.61499977111816</v>
       </c>
       <c r="G99" t="n">
-        <v>7.01925897598267</v>
+        <v>7.01925754547119</v>
       </c>
       <c r="H99" t="n">
         <v>10326</v>
@@ -3298,7 +3298,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G101" t="n">
-        <v>6.99074220657349</v>
+        <v>6.99074125289917</v>
       </c>
       <c r="H101" t="n">
         <v>8488</v>
@@ -3327,7 +3327,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G102" t="n">
-        <v>7.00703763961792</v>
+        <v>7.00703716278076</v>
       </c>
       <c r="H102" t="n">
         <v>4621</v>
@@ -3385,7 +3385,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G104" t="n">
-        <v>7.03148031234741</v>
+        <v>7.03147983551025</v>
       </c>
       <c r="H104" t="n">
         <v>4477</v>
@@ -3414,7 +3414,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G105" t="n">
-        <v>7.00703763961792</v>
+        <v>7.00703716278076</v>
       </c>
       <c r="H105" t="n">
         <v>1698</v>
@@ -3443,7 +3443,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G106" t="n">
-        <v>7.08851432800293</v>
+        <v>7.08851480484009</v>
       </c>
       <c r="H106" t="n">
         <v>16393</v>
@@ -3472,7 +3472,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G107" t="n">
-        <v>6.92963457107544</v>
+        <v>6.92963314056396</v>
       </c>
       <c r="H107" t="n">
         <v>14082</v>
@@ -3530,7 +3530,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G109" t="n">
-        <v>6.96629905700684</v>
+        <v>6.96629858016968</v>
       </c>
       <c r="H109" t="n">
         <v>3803</v>
@@ -3646,7 +3646,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G113" t="n">
-        <v>6.7626051902771</v>
+        <v>6.76260566711426</v>
       </c>
       <c r="H113" t="n">
         <v>8780</v>
@@ -3762,7 +3762,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G117" t="n">
-        <v>6.42040157318115</v>
+        <v>6.42040109634399</v>
       </c>
       <c r="H117" t="n">
         <v>6253</v>
@@ -3791,7 +3791,7 @@
         <v>7.75</v>
       </c>
       <c r="G118" t="n">
-        <v>6.31448125839233</v>
+        <v>6.31448078155518</v>
       </c>
       <c r="H118" t="n">
         <v>4631</v>
@@ -3820,7 +3820,7 @@
         <v>8.24499988555908</v>
       </c>
       <c r="G119" t="n">
-        <v>6.71779298782349</v>
+        <v>6.71779346466064</v>
       </c>
       <c r="H119" t="n">
         <v>5214</v>
@@ -3878,7 +3878,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G121" t="n">
-        <v>6.81963872909546</v>
+        <v>6.81963920593262</v>
       </c>
       <c r="H121" t="n">
         <v>10422</v>
@@ -3936,7 +3936,7 @@
         <v>8.26500034332275</v>
       </c>
       <c r="G123" t="n">
-        <v>6.73408889770508</v>
+        <v>6.73408842086792</v>
       </c>
       <c r="H123" t="n">
         <v>2839</v>
@@ -4023,7 +4023,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G126" t="n">
-        <v>6.59150314331055</v>
+        <v>6.59150362014771</v>
       </c>
       <c r="H126" t="n">
         <v>3711</v>
@@ -4052,7 +4052,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G127" t="n">
-        <v>6.62816858291626</v>
+        <v>6.62816762924194</v>
       </c>
       <c r="H127" t="n">
         <v>2765</v>
@@ -4284,7 +4284,7 @@
         <v>8.4350004196167</v>
       </c>
       <c r="G135" t="n">
-        <v>6.87259960174561</v>
+        <v>6.87260007858276</v>
       </c>
       <c r="H135" t="n">
         <v>1346</v>
@@ -4313,7 +4313,7 @@
         <v>8.4350004196167</v>
       </c>
       <c r="G136" t="n">
-        <v>6.87259960174561</v>
+        <v>6.87260007858276</v>
       </c>
       <c r="H136" t="n">
         <v>1346</v>
@@ -4342,7 +4342,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G137" t="n">
-        <v>6.8400092124939</v>
+        <v>6.84000873565674</v>
       </c>
       <c r="H137" t="n">
         <v>270</v>
@@ -4400,7 +4400,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G139" t="n">
-        <v>6.82778644561768</v>
+        <v>6.82778787612915</v>
       </c>
       <c r="H139" t="n">
         <v>5165</v>
@@ -4429,7 +4429,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G140" t="n">
-        <v>6.7626051902771</v>
+        <v>6.76260566711426</v>
       </c>
       <c r="H140" t="n">
         <v>4748</v>
@@ -4458,7 +4458,7 @@
         <v>8.375</v>
       </c>
       <c r="G141" t="n">
-        <v>6.8237133026123</v>
+        <v>6.82371282577515</v>
       </c>
       <c r="H141" t="n">
         <v>3351</v>
@@ -4574,7 +4574,7 @@
         <v>8.23499965667725</v>
       </c>
       <c r="G145" t="n">
-        <v>6.70964479446411</v>
+        <v>6.70964527130127</v>
       </c>
       <c r="H145" t="n">
         <v>2061</v>
@@ -4603,7 +4603,7 @@
         <v>8.3149995803833</v>
       </c>
       <c r="G146" t="n">
-        <v>6.774827003479</v>
+        <v>6.77482604980469</v>
       </c>
       <c r="H146" t="n">
         <v>6371</v>
@@ -4632,7 +4632,7 @@
         <v>8.30500030517578</v>
       </c>
       <c r="G147" t="n">
-        <v>6.76667928695679</v>
+        <v>6.76667976379395</v>
       </c>
       <c r="H147" t="n">
         <v>5309</v>
@@ -4719,7 +4719,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G150" t="n">
-        <v>6.82778644561768</v>
+        <v>6.82778787612915</v>
       </c>
       <c r="H150" t="n">
         <v>8840</v>
@@ -4748,7 +4748,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>6.79112243652344</v>
+        <v>6.7911229133606</v>
       </c>
       <c r="H151" t="n">
         <v>2739</v>
@@ -4777,7 +4777,7 @@
         <v>8.3149995803833</v>
       </c>
       <c r="G152" t="n">
-        <v>6.774827003479</v>
+        <v>6.77482604980469</v>
       </c>
       <c r="H152" t="n">
         <v>1406</v>
@@ -4806,7 +4806,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G153" t="n">
-        <v>6.83186149597168</v>
+        <v>6.83186101913452</v>
       </c>
       <c r="H153" t="n">
         <v>6046</v>
@@ -4864,7 +4864,7 @@
         <v>8.375</v>
       </c>
       <c r="G155" t="n">
-        <v>6.8237133026123</v>
+        <v>6.82371282577515</v>
       </c>
       <c r="H155" t="n">
         <v>869</v>
@@ -4893,7 +4893,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G156" t="n">
-        <v>6.8400092124939</v>
+        <v>6.84000873565674</v>
       </c>
       <c r="H156" t="n">
         <v>960</v>
@@ -4951,7 +4951,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G158" t="n">
-        <v>6.73816251754761</v>
+        <v>6.73816299438477</v>
       </c>
       <c r="H158" t="n">
         <v>834</v>
@@ -5096,7 +5096,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>6.81963872909546</v>
+        <v>6.81963920593262</v>
       </c>
       <c r="H163" t="n">
         <v>670</v>
@@ -5241,7 +5241,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G168" t="n">
-        <v>6.83593559265137</v>
+        <v>6.83593511581421</v>
       </c>
       <c r="H168" t="n">
         <v>1264</v>
@@ -5328,7 +5328,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G171" t="n">
-        <v>6.93370771408081</v>
+        <v>6.93370723724365</v>
       </c>
       <c r="H171" t="n">
         <v>33132</v>
@@ -5357,7 +5357,7 @@
         <v>8.54500007629395</v>
       </c>
       <c r="G172" t="n">
-        <v>6.96222448348999</v>
+        <v>6.96222496032715</v>
       </c>
       <c r="H172" t="n">
         <v>15150</v>
@@ -5415,7 +5415,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G174" t="n">
-        <v>6.94185543060303</v>
+        <v>6.94185590744019</v>
       </c>
       <c r="H174" t="n">
         <v>4184</v>
@@ -5444,7 +5444,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G175" t="n">
-        <v>6.97444725036621</v>
+        <v>6.97444629669189</v>
       </c>
       <c r="H175" t="n">
         <v>7055</v>
@@ -5473,7 +5473,7 @@
         <v>8.75</v>
       </c>
       <c r="G176" t="n">
-        <v>7.12925291061401</v>
+        <v>7.12925243377686</v>
       </c>
       <c r="H176" t="n">
         <v>35957</v>
@@ -5531,7 +5531,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G178" t="n">
-        <v>7.2188777923584</v>
+        <v>7.21887731552124</v>
       </c>
       <c r="H178" t="n">
         <v>13040</v>
@@ -5560,7 +5560,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G179" t="n">
-        <v>7.14554834365845</v>
+        <v>7.14554786682129</v>
       </c>
       <c r="H179" t="n">
         <v>9000</v>
@@ -5589,7 +5589,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G180" t="n">
-        <v>7.10481023788452</v>
+        <v>7.10480976104736</v>
       </c>
       <c r="H180" t="n">
         <v>3695</v>
@@ -5647,7 +5647,7 @@
         <v>8.79500007629395</v>
       </c>
       <c r="G182" t="n">
-        <v>7.16591739654541</v>
+        <v>7.16591787338257</v>
       </c>
       <c r="H182" t="n">
         <v>1991</v>
@@ -5676,7 +5676,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G183" t="n">
-        <v>7.1211051940918</v>
+        <v>7.12110471725464</v>
       </c>
       <c r="H183" t="n">
         <v>18864</v>
@@ -5705,7 +5705,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G184" t="n">
-        <v>7.19443368911743</v>
+        <v>7.19443464279175</v>
       </c>
       <c r="H184" t="n">
         <v>11223</v>
@@ -5734,7 +5734,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G185" t="n">
-        <v>7.35738945007324</v>
+        <v>7.35738897323608</v>
       </c>
       <c r="H185" t="n">
         <v>56641</v>
@@ -5821,7 +5821,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G188" t="n">
-        <v>7.49182510375977</v>
+        <v>7.49182605743408</v>
       </c>
       <c r="H188" t="n">
         <v>21680</v>
@@ -5850,7 +5850,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G189" t="n">
-        <v>7.30035495758057</v>
+        <v>7.30035448074341</v>
       </c>
       <c r="H189" t="n">
         <v>13518</v>
@@ -5908,7 +5908,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G191" t="n">
-        <v>7.25146865844727</v>
+        <v>7.25146770477295</v>
       </c>
       <c r="H191" t="n">
         <v>8242</v>
@@ -5937,7 +5937,7 @@
         <v>9</v>
       </c>
       <c r="G192" t="n">
-        <v>7.33294486999512</v>
+        <v>7.33294582366943</v>
       </c>
       <c r="H192" t="n">
         <v>6767</v>
@@ -5966,7 +5966,7 @@
         <v>8.96500015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>7.30442905426025</v>
+        <v>7.3044285774231</v>
       </c>
       <c r="H193" t="n">
         <v>3147</v>
@@ -6024,7 +6024,7 @@
         <v>9</v>
       </c>
       <c r="G195" t="n">
-        <v>7.33294486999512</v>
+        <v>7.33294582366943</v>
       </c>
       <c r="H195" t="n">
         <v>2353</v>
@@ -6053,7 +6053,7 @@
         <v>9</v>
       </c>
       <c r="G196" t="n">
-        <v>7.33294486999512</v>
+        <v>7.33294582366943</v>
       </c>
       <c r="H196" t="n">
         <v>5394</v>
@@ -6082,7 +6082,7 @@
         <v>9.09500026702881</v>
       </c>
       <c r="G197" t="n">
-        <v>7.41034984588623</v>
+        <v>7.41034889221191</v>
       </c>
       <c r="H197" t="n">
         <v>12723</v>
@@ -6111,7 +6111,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G198" t="n">
-        <v>7.45516109466553</v>
+        <v>7.45516157150269</v>
       </c>
       <c r="H198" t="n">
         <v>27066</v>
@@ -6140,7 +6140,7 @@
         <v>9.29500007629395</v>
       </c>
       <c r="G199" t="n">
-        <v>7.57330274581909</v>
+        <v>7.57330369949341</v>
       </c>
       <c r="H199" t="n">
         <v>9185</v>
@@ -6198,7 +6198,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G201" t="n">
-        <v>7.62626314163208</v>
+        <v>7.6262640953064</v>
       </c>
       <c r="H201" t="n">
         <v>8007</v>
@@ -6285,7 +6285,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G204" t="n">
-        <v>7.59367275238037</v>
+        <v>7.59367179870605</v>
       </c>
       <c r="H204" t="n">
         <v>4547</v>
@@ -6314,7 +6314,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G205" t="n">
-        <v>7.61811637878418</v>
+        <v>7.61811542510986</v>
       </c>
       <c r="H205" t="n">
         <v>4407</v>
@@ -6372,7 +6372,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G207" t="n">
-        <v>7.65070772171021</v>
+        <v>7.65070724487305</v>
       </c>
       <c r="H207" t="n">
         <v>2927</v>
@@ -6459,7 +6459,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G210" t="n">
-        <v>7.4144229888916</v>
+        <v>7.41442251205444</v>
       </c>
       <c r="H210" t="n">
         <v>28708</v>
@@ -6488,7 +6488,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G211" t="n">
-        <v>7.4144229888916</v>
+        <v>7.41442251205444</v>
       </c>
       <c r="H211" t="n">
         <v>6682</v>
@@ -6517,7 +6517,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G212" t="n">
-        <v>7.35738945007324</v>
+        <v>7.35738897323608</v>
       </c>
       <c r="H212" t="n">
         <v>911</v>
@@ -6546,7 +6546,7 @@
         <v>8.99499988555908</v>
       </c>
       <c r="G213" t="n">
-        <v>7.3288722038269</v>
+        <v>7.32887125015259</v>
       </c>
       <c r="H213" t="n">
         <v>47666</v>
@@ -6575,7 +6575,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G214" t="n">
-        <v>7.19443368911743</v>
+        <v>7.19443464279175</v>
       </c>
       <c r="H214" t="n">
         <v>7414</v>
@@ -6604,7 +6604,7 @@
         <v>8.77499961853027</v>
       </c>
       <c r="G215" t="n">
-        <v>7.14962244033813</v>
+        <v>7.14962148666382</v>
       </c>
       <c r="H215" t="n">
         <v>2727</v>
@@ -6633,7 +6633,7 @@
         <v>8.67500019073486</v>
       </c>
       <c r="G216" t="n">
-        <v>7.06814479827881</v>
+        <v>7.06814527511597</v>
       </c>
       <c r="H216" t="n">
         <v>20010</v>
@@ -6749,7 +6749,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G220" t="n">
-        <v>6.8400092124939</v>
+        <v>6.84000873565674</v>
       </c>
       <c r="H220" t="n">
         <v>11363</v>
@@ -6778,7 +6778,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G221" t="n">
-        <v>6.83593559265137</v>
+        <v>6.83593511581421</v>
       </c>
       <c r="H221" t="n">
         <v>11021</v>
@@ -6865,7 +6865,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G224" t="n">
-        <v>7.17813873291016</v>
+        <v>7.17814016342163</v>
       </c>
       <c r="H224" t="n">
         <v>15664</v>
@@ -6952,7 +6952,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G227" t="n">
-        <v>7.23517274856567</v>
+        <v>7.23517322540283</v>
       </c>
       <c r="H227" t="n">
         <v>26085</v>
@@ -6981,7 +6981,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G228" t="n">
-        <v>7.10481023788452</v>
+        <v>7.10480976104736</v>
       </c>
       <c r="H228" t="n">
         <v>8424</v>
@@ -7010,7 +7010,7 @@
         <v>8.63500022888184</v>
       </c>
       <c r="G229" t="n">
-        <v>7.03555536270142</v>
+        <v>7.03555393218994</v>
       </c>
       <c r="H229" t="n">
         <v>2732</v>
@@ -7039,7 +7039,7 @@
         <v>8.74499988555908</v>
       </c>
       <c r="G230" t="n">
-        <v>7.12517833709717</v>
+        <v>7.12517786026001</v>
       </c>
       <c r="H230" t="n">
         <v>4890</v>
@@ -7068,7 +7068,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G231" t="n">
-        <v>7.10481023788452</v>
+        <v>7.10480976104736</v>
       </c>
       <c r="H231" t="n">
         <v>1189</v>
@@ -7097,7 +7097,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G232" t="n">
-        <v>7.0722188949585</v>
+        <v>7.07221841812134</v>
       </c>
       <c r="H232" t="n">
         <v>2113</v>
@@ -7126,7 +7126,7 @@
         <v>8.77499961853027</v>
       </c>
       <c r="G233" t="n">
-        <v>7.14962244033813</v>
+        <v>7.14962148666382</v>
       </c>
       <c r="H233" t="n">
         <v>1494</v>
@@ -7155,7 +7155,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G234" t="n">
-        <v>6.99888944625854</v>
+        <v>6.9988899230957</v>
       </c>
       <c r="H234" t="n">
         <v>4106</v>
@@ -7184,7 +7184,7 @@
         <v>8.52499961853027</v>
       </c>
       <c r="G235" t="n">
-        <v>6.94592905044556</v>
+        <v>6.94592809677124</v>
       </c>
       <c r="H235" t="n">
         <v>5717</v>
@@ -7213,7 +7213,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G236" t="n">
-        <v>7.00703763961792</v>
+        <v>7.00703716278076</v>
       </c>
       <c r="H236" t="n">
         <v>5066</v>
@@ -7242,7 +7242,7 @@
         <v>8.67500019073486</v>
       </c>
       <c r="G237" t="n">
-        <v>7.06814479827881</v>
+        <v>7.06814527511597</v>
       </c>
       <c r="H237" t="n">
         <v>902</v>
@@ -7271,7 +7271,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G238" t="n">
-        <v>7.0722188949585</v>
+        <v>7.07221841812134</v>
       </c>
       <c r="H238" t="n">
         <v>19073</v>
@@ -7329,7 +7329,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G240" t="n">
-        <v>7.22702550888062</v>
+        <v>7.22702503204346</v>
       </c>
       <c r="H240" t="n">
         <v>4198</v>
@@ -7387,7 +7387,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G242" t="n">
-        <v>7.65885448455811</v>
+        <v>7.65885353088379</v>
       </c>
       <c r="H242" t="n">
         <v>14906</v>
@@ -7416,7 +7416,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G243" t="n">
-        <v>7.71181488037109</v>
+        <v>7.71181392669678</v>
       </c>
       <c r="H243" t="n">
         <v>30935</v>
@@ -7445,7 +7445,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G244" t="n">
-        <v>7.72403621673584</v>
+        <v>7.72403573989868</v>
       </c>
       <c r="H244" t="n">
         <v>19310</v>
@@ -7474,7 +7474,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G245" t="n">
-        <v>7.76477432250977</v>
+        <v>7.76477384567261</v>
       </c>
       <c r="H245" t="n">
         <v>17242</v>
@@ -7503,7 +7503,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G246" t="n">
-        <v>7.90328550338745</v>
+        <v>7.90328598022461</v>
       </c>
       <c r="H246" t="n">
         <v>20713</v>
@@ -7532,7 +7532,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G247" t="n">
-        <v>7.96031951904297</v>
+        <v>7.96032047271729</v>
       </c>
       <c r="H247" t="n">
         <v>10737</v>
@@ -7619,7 +7619,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G250" t="n">
-        <v>8.09068393707275</v>
+        <v>8.09068298339844</v>
       </c>
       <c r="H250" t="n">
         <v>10923</v>
@@ -7648,7 +7648,7 @@
         <v>9.76500034332275</v>
       </c>
       <c r="G251" t="n">
-        <v>7.95624685287476</v>
+        <v>7.95624589920044</v>
       </c>
       <c r="H251" t="n">
         <v>6054</v>
@@ -7677,7 +7677,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G252" t="n">
-        <v>7.90328550338745</v>
+        <v>7.90328598022461</v>
       </c>
       <c r="H252" t="n">
         <v>7899</v>
@@ -7706,7 +7706,7 @@
         <v>9.72500038146973</v>
       </c>
       <c r="G253" t="n">
-        <v>7.92365550994873</v>
+        <v>7.92365646362305</v>
       </c>
       <c r="H253" t="n">
         <v>7258</v>
@@ -7735,7 +7735,7 @@
         <v>9.8149995803833</v>
       </c>
       <c r="G254" t="n">
-        <v>7.99698400497437</v>
+        <v>7.99698543548584</v>
       </c>
       <c r="H254" t="n">
         <v>8073</v>
@@ -7851,7 +7851,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G258" t="n">
-        <v>8.38400173187256</v>
+        <v>8.38400077819824</v>
       </c>
       <c r="H258" t="n">
         <v>18321</v>
@@ -7880,7 +7880,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G259" t="n">
-        <v>8.54695510864258</v>
+        <v>8.54695415496826</v>
       </c>
       <c r="H259" t="n">
         <v>13981</v>
@@ -7909,7 +7909,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G260" t="n">
-        <v>8.77509117126465</v>
+        <v>8.77509212493896</v>
       </c>
       <c r="H260" t="n">
         <v>16781</v>
@@ -7938,7 +7938,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G261" t="n">
-        <v>8.67731857299805</v>
+        <v>8.67731761932373</v>
       </c>
       <c r="H261" t="n">
         <v>11679</v>
@@ -7996,7 +7996,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G263" t="n">
-        <v>8.70176124572754</v>
+        <v>8.70176219940186</v>
       </c>
       <c r="H263" t="n">
         <v>17771</v>
@@ -8025,7 +8025,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G264" t="n">
-        <v>8.68546485900879</v>
+        <v>8.68546676635742</v>
       </c>
       <c r="H264" t="n">
         <v>11212</v>
@@ -8054,7 +8054,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G265" t="n">
-        <v>8.84842109680176</v>
+        <v>8.84842014312744</v>
       </c>
       <c r="H265" t="n">
         <v>12525</v>
@@ -8112,7 +8112,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G267" t="n">
-        <v>8.94619464874268</v>
+        <v>8.94619274139404</v>
       </c>
       <c r="H267" t="n">
         <v>16735</v>
@@ -8141,7 +8141,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G268" t="n">
-        <v>9.2069206237793</v>
+        <v>9.20692157745361</v>
       </c>
       <c r="H268" t="n">
         <v>37835</v>
@@ -8170,7 +8170,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G269" t="n">
-        <v>9.61430740356445</v>
+        <v>9.61430549621582</v>
       </c>
       <c r="H269" t="n">
         <v>41124</v>
@@ -8199,7 +8199,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G270" t="n">
-        <v>10.0624303817749</v>
+        <v>10.0624313354492</v>
       </c>
       <c r="H270" t="n">
         <v>158289</v>
@@ -8315,7 +8315,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>10.1031694412231</v>
+        <v>10.1031703948975</v>
       </c>
       <c r="H274" t="n">
         <v>37983</v>
@@ -8402,7 +8402,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G277" t="n">
-        <v>10.5512933731079</v>
+        <v>10.5512924194336</v>
       </c>
       <c r="H277" t="n">
         <v>50593</v>
@@ -8518,7 +8518,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G281" t="n">
-        <v>11.2845878601074</v>
+        <v>11.2845897674561</v>
       </c>
       <c r="H281" t="n">
         <v>75384</v>
@@ -8547,7 +8547,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G282" t="n">
-        <v>11.3253259658813</v>
+        <v>11.3253269195557</v>
       </c>
       <c r="H282" t="n">
         <v>37053</v>
@@ -8576,7 +8576,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G283" t="n">
-        <v>11.4882822036743</v>
+        <v>11.48828125</v>
       </c>
       <c r="H283" t="n">
         <v>40824</v>
@@ -8605,7 +8605,7 @@
         <v>14.5</v>
       </c>
       <c r="G284" t="n">
-        <v>11.8141899108887</v>
+        <v>11.814190864563</v>
       </c>
       <c r="H284" t="n">
         <v>44470</v>
@@ -8721,7 +8721,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G288" t="n">
-        <v>13.7289028167725</v>
+        <v>13.7289037704468</v>
       </c>
       <c r="H288" t="n">
         <v>143297</v>
@@ -8750,7 +8750,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G289" t="n">
-        <v>15.4154815673828</v>
+        <v>15.4154806137085</v>
       </c>
       <c r="H289" t="n">
         <v>192923</v>
@@ -8779,7 +8779,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G290" t="n">
-        <v>13.5252103805542</v>
+        <v>13.5252113342285</v>
       </c>
       <c r="H290" t="n">
         <v>372464</v>
@@ -8808,7 +8808,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G291" t="n">
-        <v>12.0423269271851</v>
+        <v>12.0423259735107</v>
       </c>
       <c r="H291" t="n">
         <v>499257</v>
@@ -8866,7 +8866,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G293" t="n">
-        <v>14.0955495834351</v>
+        <v>14.0955505371094</v>
       </c>
       <c r="H293" t="n">
         <v>249868</v>
@@ -8924,7 +8924,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G295" t="n">
-        <v>13.973334312439</v>
+        <v>13.9733362197876</v>
       </c>
       <c r="H295" t="n">
         <v>102080</v>
@@ -8953,7 +8953,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G296" t="n">
-        <v>13.4763250350952</v>
+        <v>13.4763259887695</v>
       </c>
       <c r="H296" t="n">
         <v>86610</v>
@@ -9011,7 +9011,7 @@
         <v>15.5</v>
       </c>
       <c r="G298" t="n">
-        <v>12.6289625167847</v>
+        <v>12.6289615631104</v>
       </c>
       <c r="H298" t="n">
         <v>63861</v>
@@ -9069,7 +9069,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G300" t="n">
-        <v>12.9141321182251</v>
+        <v>12.9141330718994</v>
       </c>
       <c r="H300" t="n">
         <v>113230</v>
@@ -9098,7 +9098,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G301" t="n">
-        <v>12.9711666107178</v>
+        <v>12.9711647033691</v>
       </c>
       <c r="H301" t="n">
         <v>57512</v>
@@ -9127,7 +9127,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G302" t="n">
-        <v>12.9304275512695</v>
+        <v>12.9304285049438</v>
       </c>
       <c r="H302" t="n">
         <v>30022</v>
@@ -9214,7 +9214,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G305" t="n">
-        <v>13.0119047164917</v>
+        <v>13.011905670166</v>
       </c>
       <c r="H305" t="n">
         <v>32421</v>
@@ -9243,7 +9243,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G306" t="n">
-        <v>12.9874610900879</v>
+        <v>12.9874620437622</v>
       </c>
       <c r="H306" t="n">
         <v>16171</v>
@@ -9272,7 +9272,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G307" t="n">
-        <v>13.0119047164917</v>
+        <v>13.011905670166</v>
       </c>
       <c r="H307" t="n">
         <v>30877</v>
@@ -9301,7 +9301,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G308" t="n">
-        <v>13.2481889724731</v>
+        <v>13.2481880187988</v>
       </c>
       <c r="H308" t="n">
         <v>27779</v>
@@ -9359,7 +9359,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G310" t="n">
-        <v>13.5252103805542</v>
+        <v>13.5252113342285</v>
       </c>
       <c r="H310" t="n">
         <v>28868</v>
@@ -9446,7 +9446,7 @@
         <v>17.25</v>
       </c>
       <c r="G313" t="n">
-        <v>14.0548133850098</v>
+        <v>14.0548124313354</v>
       </c>
       <c r="H313" t="n">
         <v>107618</v>
@@ -9475,7 +9475,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G314" t="n">
-        <v>14.0059251785278</v>
+        <v>14.0059261322021</v>
       </c>
       <c r="H314" t="n">
         <v>61864</v>
@@ -9504,7 +9504,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G315" t="n">
-        <v>14.0140752792358</v>
+        <v>14.0140743255615</v>
       </c>
       <c r="H315" t="n">
         <v>63826</v>
@@ -9533,7 +9533,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G316" t="n">
-        <v>13.9651880264282</v>
+        <v>13.9651861190796</v>
       </c>
       <c r="H316" t="n">
         <v>41577</v>
@@ -9591,7 +9591,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G318" t="n">
-        <v>13.8674154281616</v>
+        <v>13.8674144744873</v>
       </c>
       <c r="H318" t="n">
         <v>22927</v>
@@ -9620,7 +9620,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G319" t="n">
-        <v>13.8755645751953</v>
+        <v>13.875563621521</v>
       </c>
       <c r="H319" t="n">
         <v>25048</v>
@@ -9649,7 +9649,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G320" t="n">
-        <v>13.7940864562988</v>
+        <v>13.7940845489502</v>
       </c>
       <c r="H320" t="n">
         <v>32330</v>
@@ -9678,7 +9678,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G321" t="n">
-        <v>13.7940864562988</v>
+        <v>13.7940845489502</v>
       </c>
       <c r="H321" t="n">
         <v>11251</v>
@@ -9736,7 +9736,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G323" t="n">
-        <v>13.3459615707397</v>
+        <v>13.3459606170654</v>
       </c>
       <c r="H323" t="n">
         <v>50087</v>
@@ -9794,7 +9794,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G325" t="n">
-        <v>13.4600286483765</v>
+        <v>13.4600296020508</v>
       </c>
       <c r="H325" t="n">
         <v>24981</v>
@@ -9823,7 +9823,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G326" t="n">
-        <v>13.3785524368286</v>
+        <v>13.3785514831543</v>
       </c>
       <c r="H326" t="n">
         <v>13988</v>
@@ -9881,7 +9881,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G328" t="n">
-        <v>13.3785524368286</v>
+        <v>13.3785514831543</v>
       </c>
       <c r="H328" t="n">
         <v>19232</v>
@@ -9939,7 +9939,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G330" t="n">
-        <v>13.0933799743652</v>
+        <v>13.0933818817139</v>
       </c>
       <c r="H330" t="n">
         <v>21273</v>
@@ -10142,7 +10142,7 @@
         <v>15.5</v>
       </c>
       <c r="G337" t="n">
-        <v>12.6289625167847</v>
+        <v>12.6289615631104</v>
       </c>
       <c r="H337" t="n">
         <v>20705</v>
@@ -10171,7 +10171,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G338" t="n">
-        <v>13.0200519561768</v>
+        <v>13.0200529098511</v>
       </c>
       <c r="H338" t="n">
         <v>72522</v>
@@ -10200,7 +10200,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G339" t="n">
-        <v>13.0444955825806</v>
+        <v>13.0444965362549</v>
       </c>
       <c r="H339" t="n">
         <v>29767</v>
@@ -10229,7 +10229,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G340" t="n">
-        <v>12.9385747909546</v>
+        <v>12.9385757446289</v>
       </c>
       <c r="H340" t="n">
         <v>28319</v>
@@ -10374,7 +10374,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G345" t="n">
-        <v>12.4551315307617</v>
+        <v>12.4551305770874</v>
       </c>
       <c r="H345" t="n">
         <v>24964</v>
@@ -10432,7 +10432,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G347" t="n">
-        <v>12.6790227890015</v>
+        <v>12.6790237426758</v>
       </c>
       <c r="H347" t="n">
         <v>28075</v>
@@ -10490,7 +10490,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G349" t="n">
-        <v>12.8034076690674</v>
+        <v>12.8034086227417</v>
       </c>
       <c r="H349" t="n">
         <v>47915</v>
@@ -10606,7 +10606,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G353" t="n">
-        <v>12.2146520614624</v>
+        <v>12.2146511077881</v>
       </c>
       <c r="H353" t="n">
         <v>42518</v>
@@ -10635,7 +10635,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G354" t="n">
-        <v>12.728777885437</v>
+        <v>12.7287788391113</v>
       </c>
       <c r="H354" t="n">
         <v>23785</v>
@@ -10664,7 +10664,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G355" t="n">
-        <v>12.728777885437</v>
+        <v>12.7287788391113</v>
       </c>
       <c r="H355" t="n">
         <v>14153</v>
@@ -10693,7 +10693,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G356" t="n">
-        <v>12.6873149871826</v>
+        <v>12.6873159408569</v>
       </c>
       <c r="H356" t="n">
         <v>17586</v>
@@ -10751,7 +10751,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>12.728777885437</v>
+        <v>12.7287788391113</v>
       </c>
       <c r="H358" t="n">
         <v>13306</v>
@@ -10809,7 +10809,7 @@
         <v>14.6899995803833</v>
       </c>
       <c r="G360" t="n">
-        <v>12.1814823150635</v>
+        <v>12.1814813613892</v>
       </c>
       <c r="H360" t="n">
         <v>33585</v>
@@ -10838,7 +10838,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G361" t="n">
-        <v>12.6209774017334</v>
+        <v>12.6209764480591</v>
       </c>
       <c r="H361" t="n">
         <v>41002</v>
@@ -10896,7 +10896,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G363" t="n">
-        <v>12.8282861709595</v>
+        <v>12.8282871246338</v>
       </c>
       <c r="H363" t="n">
         <v>16235</v>
@@ -10925,7 +10925,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G364" t="n">
-        <v>12.7785310745239</v>
+        <v>12.7785329818726</v>
       </c>
       <c r="H364" t="n">
         <v>6011</v>
@@ -10954,7 +10954,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G365" t="n">
-        <v>12.7536544799805</v>
+        <v>12.7536554336548</v>
       </c>
       <c r="H365" t="n">
         <v>4595</v>
@@ -10983,7 +10983,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G366" t="n">
-        <v>12.8034076690674</v>
+        <v>12.8034086227417</v>
       </c>
       <c r="H366" t="n">
         <v>13374</v>
@@ -11012,7 +11012,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G367" t="n">
-        <v>12.7785310745239</v>
+        <v>12.7785329818726</v>
       </c>
       <c r="H367" t="n">
         <v>18865</v>
@@ -11099,7 +11099,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G370" t="n">
-        <v>12.3390378952026</v>
+        <v>12.3390369415283</v>
       </c>
       <c r="H370" t="n">
         <v>10317</v>
@@ -11186,7 +11186,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G373" t="n">
-        <v>11.8746643066406</v>
+        <v>11.8746652603149</v>
       </c>
       <c r="H373" t="n">
         <v>16874</v>
@@ -11244,7 +11244,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G375" t="n">
-        <v>11.451753616333</v>
+        <v>11.4517545700073</v>
       </c>
       <c r="H375" t="n">
         <v>14501</v>
@@ -11331,7 +11331,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G378" t="n">
-        <v>11.8912487030029</v>
+        <v>11.8912496566772</v>
       </c>
       <c r="H378" t="n">
         <v>12393</v>
@@ -11447,7 +11447,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G382" t="n">
-        <v>11.67564868927</v>
+        <v>11.6756477355957</v>
       </c>
       <c r="H382" t="n">
         <v>6885</v>
@@ -11505,7 +11505,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G384" t="n">
-        <v>11.5346765518188</v>
+        <v>11.5346775054932</v>
       </c>
       <c r="H384" t="n">
         <v>6657</v>
@@ -11534,7 +11534,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G385" t="n">
-        <v>11.451753616333</v>
+        <v>11.4517545700073</v>
       </c>
       <c r="H385" t="n">
         <v>19187</v>
@@ -11563,7 +11563,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G386" t="n">
-        <v>11.3937072753906</v>
+        <v>11.3937082290649</v>
       </c>
       <c r="H386" t="n">
         <v>13930</v>
@@ -11621,7 +11621,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G388" t="n">
-        <v>11.2776145935059</v>
+        <v>11.2776136398315</v>
       </c>
       <c r="H388" t="n">
         <v>12024</v>
@@ -11650,7 +11650,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G389" t="n">
-        <v>11.3688297271729</v>
+        <v>11.3688306808472</v>
       </c>
       <c r="H389" t="n">
         <v>9873</v>
@@ -11737,7 +11737,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G392" t="n">
-        <v>11.3771228790283</v>
+        <v>11.377121925354</v>
       </c>
       <c r="H392" t="n">
         <v>6969</v>
@@ -11766,7 +11766,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G393" t="n">
-        <v>11.3356618881226</v>
+        <v>11.3356609344482</v>
       </c>
       <c r="H393" t="n">
         <v>9178</v>
@@ -11824,7 +11824,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>11.2941999435425</v>
+        <v>11.2941989898682</v>
       </c>
       <c r="H395" t="n">
         <v>3799</v>
@@ -11853,7 +11853,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G396" t="n">
-        <v>11.1698141098022</v>
+        <v>11.1698150634766</v>
       </c>
       <c r="H396" t="n">
         <v>7936</v>
@@ -11882,7 +11882,7 @@
         <v>13.5</v>
       </c>
       <c r="G397" t="n">
-        <v>11.19469165802</v>
+        <v>11.1946907043457</v>
       </c>
       <c r="H397" t="n">
         <v>8673</v>
@@ -11911,7 +11911,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G398" t="n">
-        <v>11.5678462982178</v>
+        <v>11.5678472518921</v>
       </c>
       <c r="H398" t="n">
         <v>12101</v>
@@ -12027,7 +12027,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G402" t="n">
-        <v>11.6839408874512</v>
+        <v>11.6839418411255</v>
       </c>
       <c r="H402" t="n">
         <v>6860</v>
@@ -12085,7 +12085,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>11.5678462982178</v>
+        <v>11.5678472518921</v>
       </c>
       <c r="H404" t="n">
         <v>6513</v>
@@ -12114,7 +12114,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G405" t="n">
-        <v>11.6839408874512</v>
+        <v>11.6839418411255</v>
       </c>
       <c r="H405" t="n">
         <v>7252</v>
@@ -12172,7 +12172,7 @@
         <v>14.0299997329712</v>
       </c>
       <c r="G407" t="n">
-        <v>11.6341857910156</v>
+        <v>11.6341867446899</v>
       </c>
       <c r="H407" t="n">
         <v>3908</v>
@@ -12201,7 +12201,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G408" t="n">
-        <v>12.7785310745239</v>
+        <v>12.7785329818726</v>
       </c>
       <c r="H408" t="n">
         <v>149181</v>
@@ -12230,7 +12230,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G409" t="n">
-        <v>12.7204856872559</v>
+        <v>12.7204866409302</v>
       </c>
       <c r="H409" t="n">
         <v>47280</v>
@@ -12259,7 +12259,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G410" t="n">
-        <v>12.6790227890015</v>
+        <v>12.6790237426758</v>
       </c>
       <c r="H410" t="n">
         <v>13482</v>
@@ -12462,7 +12462,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G417" t="n">
-        <v>12.2395296096802</v>
+        <v>12.2395286560059</v>
       </c>
       <c r="H417" t="n">
         <v>7412</v>
@@ -12491,7 +12491,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G418" t="n">
-        <v>11.9575891494751</v>
+        <v>11.9575881958008</v>
       </c>
       <c r="H418" t="n">
         <v>15347</v>
@@ -12636,7 +12636,7 @@
         <v>14.6899995803833</v>
       </c>
       <c r="G423" t="n">
-        <v>12.1814823150635</v>
+        <v>12.1814813613892</v>
       </c>
       <c r="H423" t="n">
         <v>8693</v>
@@ -12665,7 +12665,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G424" t="n">
-        <v>12.1566047668457</v>
+        <v>12.1566038131714</v>
       </c>
       <c r="H424" t="n">
         <v>15306</v>
@@ -12752,7 +12752,7 @@
         <v>14.6899995803833</v>
       </c>
       <c r="G427" t="n">
-        <v>12.1814823150635</v>
+        <v>12.1814813613892</v>
       </c>
       <c r="H427" t="n">
         <v>4013</v>
@@ -12810,7 +12810,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G429" t="n">
-        <v>12.4302530288696</v>
+        <v>12.430251121521</v>
       </c>
       <c r="H429" t="n">
         <v>18527</v>
@@ -12868,7 +12868,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G431" t="n">
-        <v>12.3556222915649</v>
+        <v>12.3556213378906</v>
       </c>
       <c r="H431" t="n">
         <v>20472</v>
@@ -12897,7 +12897,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G432" t="n">
-        <v>12.4302530288696</v>
+        <v>12.430251121521</v>
       </c>
       <c r="H432" t="n">
         <v>28371</v>
@@ -13013,7 +13013,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G436" t="n">
-        <v>12.1731901168823</v>
+        <v>12.173189163208</v>
       </c>
       <c r="H436" t="n">
         <v>38036</v>
@@ -13042,7 +13042,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G437" t="n">
-        <v>12.1566047668457</v>
+        <v>12.1566038131714</v>
       </c>
       <c r="H437" t="n">
         <v>23483</v>
@@ -13129,7 +13129,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G440" t="n">
-        <v>12.2146520614624</v>
+        <v>12.2146511077881</v>
       </c>
       <c r="H440" t="n">
         <v>10898</v>
@@ -13158,7 +13158,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G441" t="n">
-        <v>12.1897745132446</v>
+        <v>12.1897735595703</v>
       </c>
       <c r="H441" t="n">
         <v>3927</v>
@@ -13187,7 +13187,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G442" t="n">
-        <v>12.1566047668457</v>
+        <v>12.1566038131714</v>
       </c>
       <c r="H442" t="n">
         <v>5869</v>
@@ -13216,7 +13216,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G443" t="n">
-        <v>12.2726993560791</v>
+        <v>12.2726984024048</v>
       </c>
       <c r="H443" t="n">
         <v>14042</v>
@@ -13274,7 +13274,7 @@
         <v>14.75</v>
       </c>
       <c r="G445" t="n">
-        <v>12.231237411499</v>
+        <v>12.2312355041504</v>
       </c>
       <c r="H445" t="n">
         <v>13439</v>
@@ -13332,7 +13332,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G447" t="n">
-        <v>12.2726993560791</v>
+        <v>12.2726984024048</v>
       </c>
       <c r="H447" t="n">
         <v>7518</v>
@@ -13506,7 +13506,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G453" t="n">
-        <v>12.3473300933838</v>
+        <v>12.3473310470581</v>
       </c>
       <c r="H453" t="n">
         <v>6380</v>
@@ -13535,7 +13535,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G454" t="n">
-        <v>12.2644062042236</v>
+        <v>12.2644052505493</v>
       </c>
       <c r="H454" t="n">
         <v>6141</v>
@@ -13564,7 +13564,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G455" t="n">
-        <v>12.3887901306152</v>
+        <v>12.3887910842896</v>
       </c>
       <c r="H455" t="n">
         <v>21009</v>
@@ -13651,7 +13651,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G458" t="n">
-        <v>12.5214691162109</v>
+        <v>12.5214681625366</v>
       </c>
       <c r="H458" t="n">
         <v>7823</v>
@@ -13767,7 +13767,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G462" t="n">
-        <v>12.3887901306152</v>
+        <v>12.3887910842896</v>
       </c>
       <c r="H462" t="n">
         <v>10957</v>
@@ -13796,7 +13796,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G463" t="n">
-        <v>12.4717149734497</v>
+        <v>12.4717140197754</v>
       </c>
       <c r="H463" t="n">
         <v>3508</v>
@@ -13825,7 +13825,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G464" t="n">
-        <v>12.3556222915649</v>
+        <v>12.3556213378906</v>
       </c>
       <c r="H464" t="n">
         <v>10716</v>
@@ -13883,7 +13883,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G466" t="n">
-        <v>12.5214691162109</v>
+        <v>12.5214681625366</v>
       </c>
       <c r="H466" t="n">
         <v>8349</v>
@@ -13970,7 +13970,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G469" t="n">
-        <v>12.5878076553345</v>
+        <v>12.5878086090088</v>
       </c>
       <c r="H469" t="n">
         <v>8180</v>
@@ -14086,7 +14086,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G473" t="n">
-        <v>12.6790227890015</v>
+        <v>12.6790237426758</v>
       </c>
       <c r="H473" t="n">
         <v>10931</v>
@@ -14173,7 +14173,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G476" t="n">
-        <v>12.6790227890015</v>
+        <v>12.6790237426758</v>
       </c>
       <c r="H476" t="n">
         <v>7899</v>
@@ -14260,7 +14260,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G479" t="n">
-        <v>12.4302530288696</v>
+        <v>12.430251121521</v>
       </c>
       <c r="H479" t="n">
         <v>12669</v>
@@ -14289,7 +14289,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G480" t="n">
-        <v>12.7039003372192</v>
+        <v>12.7039012908936</v>
       </c>
       <c r="H480" t="n">
         <v>79987</v>
@@ -14347,7 +14347,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G482" t="n">
-        <v>12.7702388763428</v>
+        <v>12.7702398300171</v>
       </c>
       <c r="H482" t="n">
         <v>10713</v>
@@ -14376,7 +14376,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G483" t="n">
-        <v>12.9858417510986</v>
+        <v>12.9858407974243</v>
       </c>
       <c r="H483" t="n">
         <v>27339</v>
@@ -14463,7 +14463,7 @@
         <v>16</v>
       </c>
       <c r="G486" t="n">
-        <v>13.2677822113037</v>
+        <v>13.2677812576294</v>
       </c>
       <c r="H486" t="n">
         <v>48007</v>
@@ -14492,7 +14492,7 @@
         <v>16</v>
       </c>
       <c r="G487" t="n">
-        <v>13.2677822113037</v>
+        <v>13.2677812576294</v>
       </c>
       <c r="H487" t="n">
         <v>21644</v>
@@ -14579,7 +14579,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G490" t="n">
-        <v>13.9477558135986</v>
+        <v>13.9477548599243</v>
       </c>
       <c r="H490" t="n">
         <v>117106</v>
@@ -14637,7 +14637,7 @@
         <v>16.5</v>
       </c>
       <c r="G492" t="n">
-        <v>13.6823987960815</v>
+        <v>13.6824007034302</v>
       </c>
       <c r="H492" t="n">
         <v>235031</v>
@@ -14695,7 +14695,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G494" t="n">
-        <v>13.375581741333</v>
+        <v>13.3755807876587</v>
       </c>
       <c r="H494" t="n">
         <v>20695</v>
@@ -14724,7 +14724,7 @@
         <v>16.0900001525879</v>
       </c>
       <c r="G495" t="n">
-        <v>13.3424129486084</v>
+        <v>13.3424139022827</v>
       </c>
       <c r="H495" t="n">
         <v>11108</v>
@@ -14753,7 +14753,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G496" t="n">
-        <v>13.375581741333</v>
+        <v>13.3755807876587</v>
       </c>
       <c r="H496" t="n">
         <v>27098</v>
@@ -14840,7 +14840,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G499" t="n">
-        <v>13.6243534088135</v>
+        <v>13.6243543624878</v>
       </c>
       <c r="H499" t="n">
         <v>78324</v>
@@ -14898,7 +14898,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G501" t="n">
-        <v>13.4999685287476</v>
+        <v>13.4999675750732</v>
       </c>
       <c r="H501" t="n">
         <v>15452</v>
@@ -14927,7 +14927,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G502" t="n">
-        <v>13.4170436859131</v>
+        <v>13.4170446395874</v>
       </c>
       <c r="H502" t="n">
         <v>10237</v>
@@ -15072,7 +15072,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G507" t="n">
-        <v>13.2760744094849</v>
+        <v>13.2760734558105</v>
       </c>
       <c r="H507" t="n">
         <v>12943</v>
@@ -15101,7 +15101,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G508" t="n">
-        <v>13.1102285385132</v>
+        <v>13.1102275848389</v>
       </c>
       <c r="H508" t="n">
         <v>9747</v>
@@ -15130,7 +15130,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G509" t="n">
-        <v>13.0438871383667</v>
+        <v>13.0438861846924</v>
       </c>
       <c r="H509" t="n">
         <v>12169</v>
@@ -15188,7 +15188,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G511" t="n">
-        <v>13.3009519577026</v>
+        <v>13.3009510040283</v>
       </c>
       <c r="H511" t="n">
         <v>9571</v>
@@ -15217,7 +15217,7 @@
         <v>16</v>
       </c>
       <c r="G512" t="n">
-        <v>13.2677822113037</v>
+        <v>13.2677812576294</v>
       </c>
       <c r="H512" t="n">
         <v>8800</v>
@@ -15246,7 +15246,7 @@
         <v>16</v>
       </c>
       <c r="G513" t="n">
-        <v>13.2677822113037</v>
+        <v>13.2677812576294</v>
       </c>
       <c r="H513" t="n">
         <v>4453</v>
@@ -15275,7 +15275,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G514" t="n">
-        <v>13.3672904968262</v>
+        <v>13.3672914505005</v>
       </c>
       <c r="H514" t="n">
         <v>18072</v>
@@ -15362,7 +15362,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G517" t="n">
-        <v>13.3672904968262</v>
+        <v>13.3672914505005</v>
       </c>
       <c r="H517" t="n">
         <v>16407</v>
@@ -15391,7 +15391,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G518" t="n">
-        <v>13.284366607666</v>
+        <v>13.2843656539917</v>
       </c>
       <c r="H518" t="n">
         <v>13632</v>
@@ -15420,7 +15420,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G519" t="n">
-        <v>13.2180271148682</v>
+        <v>13.2180280685425</v>
       </c>
       <c r="H519" t="n">
         <v>15125</v>
@@ -15449,7 +15449,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G520" t="n">
-        <v>13.2014427185059</v>
+        <v>13.2014436721802</v>
       </c>
       <c r="H520" t="n">
         <v>23672</v>
@@ -15507,7 +15507,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G522" t="n">
-        <v>13.284366607666</v>
+        <v>13.2843656539917</v>
       </c>
       <c r="H522" t="n">
         <v>12088</v>
@@ -15536,7 +15536,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G523" t="n">
-        <v>13.3009519577026</v>
+        <v>13.3009510040283</v>
       </c>
       <c r="H523" t="n">
         <v>5777</v>
@@ -15594,7 +15594,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G525" t="n">
-        <v>13.1682739257812</v>
+        <v>13.1682729721069</v>
       </c>
       <c r="H525" t="n">
         <v>7586</v>
@@ -15623,7 +15623,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G526" t="n">
-        <v>13.3009519577026</v>
+        <v>13.3009510040283</v>
       </c>
       <c r="H526" t="n">
         <v>22442</v>
@@ -15681,7 +15681,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G528" t="n">
-        <v>13.3009519577026</v>
+        <v>13.3009510040283</v>
       </c>
       <c r="H528" t="n">
         <v>25522</v>
@@ -15710,7 +15710,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G529" t="n">
-        <v>13.2180271148682</v>
+        <v>13.2180280685425</v>
       </c>
       <c r="H529" t="n">
         <v>10486</v>
@@ -15884,7 +15884,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G535" t="n">
-        <v>12.7702388763428</v>
+        <v>12.7702398300171</v>
       </c>
       <c r="H535" t="n">
         <v>22072</v>
@@ -16029,7 +16029,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G540" t="n">
-        <v>12.9858417510986</v>
+        <v>12.9858407974243</v>
       </c>
       <c r="H540" t="n">
         <v>16452</v>
@@ -16174,7 +16174,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G545" t="n">
-        <v>13.1682739257812</v>
+        <v>13.1682729721069</v>
       </c>
       <c r="H545" t="n">
         <v>28801</v>
@@ -16232,7 +16232,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G547" t="n">
-        <v>13.11851978302</v>
+        <v>13.1185188293457</v>
       </c>
       <c r="H547" t="n">
         <v>11521</v>
@@ -16406,7 +16406,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G553" t="n">
-        <v>12.7868232727051</v>
+        <v>12.7868251800537</v>
       </c>
       <c r="H553" t="n">
         <v>12202</v>
@@ -16580,7 +16580,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G559" t="n">
-        <v>12.7204856872559</v>
+        <v>12.7204866409302</v>
       </c>
       <c r="H559" t="n">
         <v>8914</v>
@@ -16754,7 +16754,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G565" t="n">
-        <v>12.8365793228149</v>
+        <v>12.8365783691406</v>
       </c>
       <c r="H565" t="n">
         <v>10281</v>
@@ -16783,7 +16783,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G566" t="n">
-        <v>13.0687656402588</v>
+        <v>13.0687646865845</v>
       </c>
       <c r="H566" t="n">
         <v>4417</v>
@@ -16841,7 +16841,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G568" t="n">
-        <v>12.9858417510986</v>
+        <v>12.9858407974243</v>
       </c>
       <c r="H568" t="n">
         <v>5954</v>
@@ -16928,7 +16928,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G571" t="n">
-        <v>12.9858417510986</v>
+        <v>12.9858407974243</v>
       </c>
       <c r="H571" t="n">
         <v>8034</v>
@@ -16957,7 +16957,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G572" t="n">
-        <v>12.7204856872559</v>
+        <v>12.7204866409302</v>
       </c>
       <c r="H572" t="n">
         <v>9033</v>
@@ -17189,7 +17189,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G580" t="n">
-        <v>13.1682739257812</v>
+        <v>13.1682729721069</v>
       </c>
       <c r="H580" t="n">
         <v>5630</v>
@@ -17218,7 +17218,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G581" t="n">
-        <v>13.0024271011353</v>
+        <v>13.0024261474609</v>
       </c>
       <c r="H581" t="n">
         <v>2866</v>
@@ -17334,7 +17334,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G585" t="n">
-        <v>13.0024271011353</v>
+        <v>13.0024261474609</v>
       </c>
       <c r="H585" t="n">
         <v>3549</v>
@@ -17363,7 +17363,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G586" t="n">
-        <v>13.2014427185059</v>
+        <v>13.2014436721802</v>
       </c>
       <c r="H586" t="n">
         <v>11401</v>
@@ -17392,7 +17392,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G587" t="n">
-        <v>13.0687656402588</v>
+        <v>13.0687646865845</v>
       </c>
       <c r="H587" t="n">
         <v>4259</v>
@@ -17479,7 +17479,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G590" t="n">
-        <v>13.2014427185059</v>
+        <v>13.2014436721802</v>
       </c>
       <c r="H590" t="n">
         <v>7153</v>
@@ -17537,7 +17537,7 @@
         <v>16</v>
       </c>
       <c r="G592" t="n">
-        <v>13.2677822113037</v>
+        <v>13.2677812576294</v>
       </c>
       <c r="H592" t="n">
         <v>9379</v>
@@ -17566,7 +17566,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G593" t="n">
-        <v>13.284366607666</v>
+        <v>13.2843656539917</v>
       </c>
       <c r="H593" t="n">
         <v>8278</v>
@@ -17653,7 +17653,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G596" t="n">
-        <v>13.284366607666</v>
+        <v>13.2843656539917</v>
       </c>
       <c r="H596" t="n">
         <v>15741</v>
@@ -17798,7 +17798,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G601" t="n">
-        <v>13.4458980560303</v>
+        <v>13.445897102356</v>
       </c>
       <c r="H601" t="n">
         <v>9348</v>
@@ -17856,7 +17856,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G603" t="n">
-        <v>13.5818862915039</v>
+        <v>13.5818872451782</v>
       </c>
       <c r="H603" t="n">
         <v>11082</v>
@@ -17914,7 +17914,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G605" t="n">
-        <v>13.3949022293091</v>
+        <v>13.3949012756348</v>
       </c>
       <c r="H605" t="n">
         <v>17030</v>
@@ -17972,7 +17972,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G607" t="n">
-        <v>13.1059246063232</v>
+        <v>13.1059255599976</v>
       </c>
       <c r="H607" t="n">
         <v>29495</v>
@@ -18059,7 +18059,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G610" t="n">
-        <v>12.5959663391113</v>
+        <v>12.5959672927856</v>
       </c>
       <c r="H610" t="n">
         <v>11692</v>
@@ -18088,7 +18088,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G611" t="n">
-        <v>12.7999505996704</v>
+        <v>12.7999515533447</v>
       </c>
       <c r="H611" t="n">
         <v>5742</v>
@@ -18175,7 +18175,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G614" t="n">
-        <v>12.5789699554443</v>
+        <v>12.57896900177</v>
       </c>
       <c r="H614" t="n">
         <v>27324</v>
@@ -18262,7 +18262,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G617" t="n">
-        <v>13.7518720626831</v>
+        <v>13.7518730163574</v>
       </c>
       <c r="H617" t="n">
         <v>42337</v>
@@ -18291,7 +18291,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G618" t="n">
-        <v>13.5818862915039</v>
+        <v>13.5818872451782</v>
       </c>
       <c r="H618" t="n">
         <v>4207</v>
@@ -18407,7 +18407,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G622" t="n">
-        <v>13.2249164581299</v>
+        <v>13.2249155044556</v>
       </c>
       <c r="H622" t="n">
         <v>3110</v>
@@ -18523,7 +18523,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G626" t="n">
-        <v>13.5478887557983</v>
+        <v>13.5478897094727</v>
       </c>
       <c r="H626" t="n">
         <v>6944</v>
@@ -18639,7 +18639,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G630" t="n">
-        <v>13.3949022293091</v>
+        <v>13.3949012756348</v>
       </c>
       <c r="H630" t="n">
         <v>3935</v>
@@ -18784,7 +18784,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G635" t="n">
-        <v>13.0889263153076</v>
+        <v>13.0889272689819</v>
       </c>
       <c r="H635" t="n">
         <v>6319</v>
@@ -18842,7 +18842,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G637" t="n">
-        <v>12.9359397888184</v>
+        <v>12.935938835144</v>
       </c>
       <c r="H637" t="n">
         <v>2897</v>
@@ -18958,7 +18958,7 @@
         <v>15.5</v>
       </c>
       <c r="G641" t="n">
-        <v>13.1739206314087</v>
+        <v>13.1739196777344</v>
       </c>
       <c r="H641" t="n">
         <v>6584</v>
@@ -19016,7 +19016,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G643" t="n">
-        <v>13.1229228973389</v>
+        <v>13.1229238510132</v>
       </c>
       <c r="H643" t="n">
         <v>4708</v>
@@ -19045,7 +19045,7 @@
         <v>15.5</v>
       </c>
       <c r="G644" t="n">
-        <v>13.1739206314087</v>
+        <v>13.1739196777344</v>
       </c>
       <c r="H644" t="n">
         <v>6247</v>
@@ -19161,7 +19161,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G648" t="n">
-        <v>13.1569223403931</v>
+        <v>13.1569213867188</v>
       </c>
       <c r="H648" t="n">
         <v>3677</v>
@@ -19190,7 +19190,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G649" t="n">
-        <v>13.2249164581299</v>
+        <v>13.2249155044556</v>
       </c>
       <c r="H649" t="n">
         <v>1782</v>
@@ -19219,7 +19219,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G650" t="n">
-        <v>12.9359397888184</v>
+        <v>12.935938835144</v>
       </c>
       <c r="H650" t="n">
         <v>6653</v>
@@ -19248,7 +19248,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G651" t="n">
-        <v>13.0039329528809</v>
+        <v>13.0039339065552</v>
       </c>
       <c r="H651" t="n">
         <v>3947</v>
@@ -19277,7 +19277,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G652" t="n">
-        <v>13.0379314422607</v>
+        <v>13.0379323959351</v>
       </c>
       <c r="H652" t="n">
         <v>1531</v>
@@ -19422,7 +19422,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G657" t="n">
-        <v>13.1059246063232</v>
+        <v>13.1059255599976</v>
       </c>
       <c r="H657" t="n">
         <v>1798</v>
@@ -19509,7 +19509,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G660" t="n">
-        <v>13.0889263153076</v>
+        <v>13.0889272689819</v>
       </c>
       <c r="H660" t="n">
         <v>3774</v>
@@ -19625,7 +19625,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G664" t="n">
-        <v>12.7319555282593</v>
+        <v>12.731954574585</v>
       </c>
       <c r="H664" t="n">
         <v>5567</v>
@@ -19712,7 +19712,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G667" t="n">
-        <v>12.7319555282593</v>
+        <v>12.731954574585</v>
       </c>
       <c r="H667" t="n">
         <v>5237</v>
@@ -19741,7 +19741,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G668" t="n">
-        <v>12.6809606552124</v>
+        <v>12.6809597015381</v>
       </c>
       <c r="H668" t="n">
         <v>2882</v>
@@ -19770,7 +19770,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G669" t="n">
-        <v>12.7659549713135</v>
+        <v>12.7659540176392</v>
       </c>
       <c r="H669" t="n">
         <v>2986</v>
@@ -19915,7 +19915,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G674" t="n">
-        <v>12.5959663391113</v>
+        <v>12.5959672927856</v>
       </c>
       <c r="H674" t="n">
         <v>1792</v>
@@ -19973,7 +19973,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G676" t="n">
-        <v>12.5959663391113</v>
+        <v>12.5959672927856</v>
       </c>
       <c r="H676" t="n">
         <v>927</v>
@@ -20118,7 +20118,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G681" t="n">
-        <v>12.5789699554443</v>
+        <v>12.57896900177</v>
       </c>
       <c r="H681" t="n">
         <v>9741</v>
@@ -20176,7 +20176,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G683" t="n">
-        <v>12.6809606552124</v>
+        <v>12.6809597015381</v>
       </c>
       <c r="H683" t="n">
         <v>4306</v>
@@ -20205,7 +20205,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G684" t="n">
-        <v>12.4259805679321</v>
+        <v>12.4259815216064</v>
       </c>
       <c r="H684" t="n">
         <v>6540</v>
@@ -20234,7 +20234,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G685" t="n">
-        <v>12.4259805679321</v>
+        <v>12.4259815216064</v>
       </c>
       <c r="H685" t="n">
         <v>6091</v>
@@ -20292,7 +20292,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G687" t="n">
-        <v>12.5449724197388</v>
+        <v>12.5449714660645</v>
       </c>
       <c r="H687" t="n">
         <v>6669</v>
@@ -20321,7 +20321,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G688" t="n">
-        <v>12.5449724197388</v>
+        <v>12.5449714660645</v>
       </c>
       <c r="H688" t="n">
         <v>8177</v>
@@ -20437,7 +20437,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G692" t="n">
-        <v>12.4259805679321</v>
+        <v>12.4259815216064</v>
       </c>
       <c r="H692" t="n">
         <v>5376</v>
@@ -20466,7 +20466,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G693" t="n">
-        <v>12.4089822769165</v>
+        <v>12.4089841842651</v>
       </c>
       <c r="H693" t="n">
         <v>2666</v>
@@ -20495,7 +20495,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G694" t="n">
-        <v>12.6469640731812</v>
+        <v>12.6469631195068</v>
       </c>
       <c r="H694" t="n">
         <v>3256</v>
@@ -20553,7 +20553,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G696" t="n">
-        <v>12.6809606552124</v>
+        <v>12.6809597015381</v>
       </c>
       <c r="H696" t="n">
         <v>3412</v>
@@ -20611,7 +20611,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G698" t="n">
-        <v>12.5789699554443</v>
+        <v>12.57896900177</v>
       </c>
       <c r="H698" t="n">
         <v>544</v>
@@ -20640,7 +20640,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G699" t="n">
-        <v>12.5789699554443</v>
+        <v>12.57896900177</v>
       </c>
       <c r="H699" t="n">
         <v>1193</v>
@@ -20669,7 +20669,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G700" t="n">
-        <v>12.4259805679321</v>
+        <v>12.4259815216064</v>
       </c>
       <c r="H700" t="n">
         <v>4373</v>
@@ -20756,7 +20756,7 @@
         <v>14.5</v>
       </c>
       <c r="G703" t="n">
-        <v>12.3239889144897</v>
+        <v>12.3239898681641</v>
       </c>
       <c r="H703" t="n">
         <v>1364</v>
@@ -20814,7 +20814,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G705" t="n">
-        <v>12.4089822769165</v>
+        <v>12.4089841842651</v>
       </c>
       <c r="H705" t="n">
         <v>8953</v>
@@ -20901,7 +20901,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G708" t="n">
-        <v>10.8451118469238</v>
+        <v>10.8451108932495</v>
       </c>
       <c r="H708" t="n">
         <v>33808</v>
@@ -20959,7 +20959,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G710" t="n">
-        <v>10.7431201934814</v>
+        <v>10.7431192398071</v>
       </c>
       <c r="H710" t="n">
         <v>17273</v>
@@ -21017,7 +21017,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G712" t="n">
-        <v>10.7601184844971</v>
+        <v>10.7601175308228</v>
       </c>
       <c r="H712" t="n">
         <v>3711</v>
@@ -21046,7 +21046,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G713" t="n">
-        <v>10.9980974197388</v>
+        <v>10.9980983734131</v>
       </c>
       <c r="H713" t="n">
         <v>5456</v>
@@ -21075,7 +21075,7 @@
         <v>12.5</v>
       </c>
       <c r="G714" t="n">
-        <v>10.6241292953491</v>
+        <v>10.6241283416748</v>
       </c>
       <c r="H714" t="n">
         <v>4353</v>
@@ -21162,7 +21162,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G717" t="n">
-        <v>10.9301042556763</v>
+        <v>10.930103302002</v>
       </c>
       <c r="H717" t="n">
         <v>2673</v>
@@ -21220,7 +21220,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G719" t="n">
-        <v>10.4711408615112</v>
+        <v>10.4711418151855</v>
       </c>
       <c r="H719" t="n">
         <v>11515</v>
@@ -21249,7 +21249,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G720" t="n">
-        <v>10.5221366882324</v>
+        <v>10.5221376419067</v>
       </c>
       <c r="H720" t="n">
         <v>14593</v>
@@ -21278,7 +21278,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G721" t="n">
-        <v>10.658127784729</v>
+        <v>10.6581268310547</v>
       </c>
       <c r="H721" t="n">
         <v>2544</v>
@@ -21307,7 +21307,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G722" t="n">
-        <v>10.5221366882324</v>
+        <v>10.5221376419067</v>
       </c>
       <c r="H722" t="n">
         <v>4192</v>
@@ -21336,7 +21336,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G723" t="n">
-        <v>10.7601184844971</v>
+        <v>10.7601175308228</v>
       </c>
       <c r="H723" t="n">
         <v>3418</v>
@@ -21365,7 +21365,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G724" t="n">
-        <v>10.7431201934814</v>
+        <v>10.7431192398071</v>
       </c>
       <c r="H724" t="n">
         <v>9535</v>
@@ -21394,7 +21394,7 @@
         <v>12.5</v>
       </c>
       <c r="G725" t="n">
-        <v>10.6241292953491</v>
+        <v>10.6241283416748</v>
       </c>
       <c r="H725" t="n">
         <v>618</v>
@@ -21423,7 +21423,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G726" t="n">
-        <v>10.7431201934814</v>
+        <v>10.7431192398071</v>
       </c>
       <c r="H726" t="n">
         <v>2281</v>
@@ -21481,7 +21481,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G728" t="n">
-        <v>10.9301042556763</v>
+        <v>10.930103302002</v>
       </c>
       <c r="H728" t="n">
         <v>973</v>
@@ -21597,7 +21597,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G732" t="n">
-        <v>11.3210725784302</v>
+        <v>11.3210716247559</v>
       </c>
       <c r="H732" t="n">
         <v>2650</v>
@@ -21655,7 +21655,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G734" t="n">
-        <v>11.2870740890503</v>
+        <v>11.2870750427246</v>
       </c>
       <c r="H734" t="n">
         <v>1704</v>
@@ -21684,7 +21684,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G735" t="n">
-        <v>11.2020816802979</v>
+        <v>11.2020826339722</v>
       </c>
       <c r="H735" t="n">
         <v>2307</v>
@@ -21742,7 +21742,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G737" t="n">
-        <v>10.7431201934814</v>
+        <v>10.7431192398071</v>
       </c>
       <c r="H737" t="n">
         <v>3270</v>
@@ -21829,7 +21829,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G740" t="n">
-        <v>10.3691492080688</v>
+        <v>10.3691501617432</v>
       </c>
       <c r="H740" t="n">
         <v>11056</v>
@@ -21887,7 +21887,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G742" t="n">
-        <v>9.9951810836792</v>
+        <v>9.99518013000488</v>
       </c>
       <c r="H742" t="n">
         <v>3653</v>
@@ -22119,7 +22119,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G750" t="n">
-        <v>10.6071300506592</v>
+        <v>10.6071310043335</v>
       </c>
       <c r="H750" t="n">
         <v>955</v>
@@ -22148,7 +22148,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G751" t="n">
-        <v>10.7601184844971</v>
+        <v>10.7601175308228</v>
       </c>
       <c r="H751" t="n">
         <v>1943</v>
@@ -22177,7 +22177,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G752" t="n">
-        <v>10.6071300506592</v>
+        <v>10.6071310043335</v>
       </c>
       <c r="H752" t="n">
         <v>1850</v>
@@ -22206,7 +22206,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G753" t="n">
-        <v>10.4711408615112</v>
+        <v>10.4711418151855</v>
       </c>
       <c r="H753" t="n">
         <v>1160</v>
@@ -22351,7 +22351,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G758" t="n">
-        <v>9.0602560043335</v>
+        <v>9.06025695800781</v>
       </c>
       <c r="H758" t="n">
         <v>20313</v>
@@ -22409,7 +22409,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G760" t="n">
-        <v>9.26423931121826</v>
+        <v>9.26424026489258</v>
       </c>
       <c r="H760" t="n">
         <v>4915</v>
@@ -22438,7 +22438,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G761" t="n">
-        <v>9.26423931121826</v>
+        <v>9.26424026489258</v>
       </c>
       <c r="H761" t="n">
         <v>6625</v>
@@ -22467,7 +22467,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G762" t="n">
-        <v>9.17924690246582</v>
+        <v>9.17924785614014</v>
       </c>
       <c r="H762" t="n">
         <v>11417</v>
@@ -22525,7 +22525,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G764" t="n">
-        <v>10.318154335022</v>
+        <v>10.3181552886963</v>
       </c>
       <c r="H764" t="n">
         <v>2548</v>
@@ -22612,7 +22612,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G767" t="n">
-        <v>10.7771158218384</v>
+        <v>10.7771167755127</v>
       </c>
       <c r="H767" t="n">
         <v>4276</v>
@@ -22641,7 +22641,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G768" t="n">
-        <v>10.658127784729</v>
+        <v>10.6581268310547</v>
       </c>
       <c r="H768" t="n">
         <v>5651</v>
@@ -22670,7 +22670,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G769" t="n">
-        <v>10.8451118469238</v>
+        <v>10.8451108932495</v>
       </c>
       <c r="H769" t="n">
         <v>4577</v>
@@ -22902,7 +22902,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G777" t="n">
-        <v>9.89318943023682</v>
+        <v>9.89319038391113</v>
       </c>
       <c r="H777" t="n">
         <v>8808</v>
@@ -23047,7 +23047,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G782" t="n">
-        <v>10.3691492080688</v>
+        <v>10.3691501617432</v>
       </c>
       <c r="H782" t="n">
         <v>3355</v>
@@ -23192,7 +23192,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G787" t="n">
-        <v>10.318154335022</v>
+        <v>10.3181552886963</v>
       </c>
       <c r="H787" t="n">
         <v>1444</v>
@@ -23250,7 +23250,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G789" t="n">
-        <v>10.2161626815796</v>
+        <v>10.2161617279053</v>
       </c>
       <c r="H789" t="n">
         <v>2973</v>
@@ -23279,7 +23279,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G790" t="n">
-        <v>10.1651668548584</v>
+        <v>10.1651659011841</v>
       </c>
       <c r="H790" t="n">
         <v>2393</v>
@@ -23366,7 +23366,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G793" t="n">
-        <v>9.9951810836792</v>
+        <v>9.99518013000488</v>
       </c>
       <c r="H793" t="n">
         <v>5567</v>
@@ -23395,7 +23395,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G794" t="n">
-        <v>10.1651668548584</v>
+        <v>10.1651659011841</v>
       </c>
       <c r="H794" t="n">
         <v>1552</v>
@@ -23453,7 +23453,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G796" t="n">
-        <v>10.1651668548584</v>
+        <v>10.1651659011841</v>
       </c>
       <c r="H796" t="n">
         <v>2509</v>
@@ -23540,7 +23540,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G799" t="n">
-        <v>9.94418525695801</v>
+        <v>9.94418430328369</v>
       </c>
       <c r="H799" t="n">
         <v>3445</v>
@@ -23569,7 +23569,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G800" t="n">
-        <v>9.89318943023682</v>
+        <v>9.89319038391113</v>
       </c>
       <c r="H800" t="n">
         <v>3975</v>
@@ -23627,7 +23627,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G802" t="n">
-        <v>9.89318943023682</v>
+        <v>9.89319038391113</v>
       </c>
       <c r="H802" t="n">
         <v>1415</v>
@@ -23685,7 +23685,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G804" t="n">
-        <v>9.9951810836792</v>
+        <v>9.99518013000488</v>
       </c>
       <c r="H804" t="n">
         <v>2769</v>
@@ -23859,7 +23859,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G810" t="n">
-        <v>9.94418525695801</v>
+        <v>9.94418430328369</v>
       </c>
       <c r="H810" t="n">
         <v>5595</v>
@@ -23888,7 +23888,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G811" t="n">
-        <v>10.0461769104004</v>
+        <v>10.0461759567261</v>
       </c>
       <c r="H811" t="n">
         <v>1756</v>
@@ -23975,7 +23975,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G814" t="n">
-        <v>9.9951810836792</v>
+        <v>9.99518013000488</v>
       </c>
       <c r="H814" t="n">
         <v>2540</v>
@@ -24091,7 +24091,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G818" t="n">
-        <v>10.8451118469238</v>
+        <v>10.8451108932495</v>
       </c>
       <c r="H818" t="n">
         <v>13478</v>
@@ -24149,7 +24149,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G820" t="n">
-        <v>10.7771158218384</v>
+        <v>10.7771167755127</v>
       </c>
       <c r="H820" t="n">
         <v>2139</v>
@@ -24207,7 +24207,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G822" t="n">
-        <v>10.4881391525269</v>
+        <v>10.4881401062012</v>
       </c>
       <c r="H822" t="n">
         <v>3340</v>
@@ -24265,7 +24265,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G824" t="n">
-        <v>10.6071300506592</v>
+        <v>10.6071310043335</v>
       </c>
       <c r="H824" t="n">
         <v>5188</v>
@@ -24352,7 +24352,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G827" t="n">
-        <v>10.658127784729</v>
+        <v>10.6581268310547</v>
       </c>
       <c r="H827" t="n">
         <v>6703</v>
@@ -24410,7 +24410,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G829" t="n">
-        <v>10.6411285400391</v>
+        <v>10.6411275863647</v>
       </c>
       <c r="H829" t="n">
         <v>1596</v>
@@ -24439,7 +24439,7 @@
         <v>12.5</v>
       </c>
       <c r="G830" t="n">
-        <v>10.6241292953491</v>
+        <v>10.6241283416748</v>
       </c>
       <c r="H830" t="n">
         <v>2256</v>
@@ -24468,7 +24468,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G831" t="n">
-        <v>10.6411285400391</v>
+        <v>10.6411275863647</v>
       </c>
       <c r="H831" t="n">
         <v>13500</v>
@@ -24555,7 +24555,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G834" t="n">
-        <v>10.8451118469238</v>
+        <v>10.8451108932495</v>
       </c>
       <c r="H834" t="n">
         <v>4394</v>
@@ -24584,7 +24584,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G835" t="n">
-        <v>10.5731325149536</v>
+        <v>10.5731334686279</v>
       </c>
       <c r="H835" t="n">
         <v>9046</v>
@@ -24642,7 +24642,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G837" t="n">
-        <v>10.6411285400391</v>
+        <v>10.6411275863647</v>
       </c>
       <c r="H837" t="n">
         <v>2527</v>
@@ -24729,7 +24729,7 @@
         <v>12.5</v>
       </c>
       <c r="G840" t="n">
-        <v>10.6241292953491</v>
+        <v>10.6241283416748</v>
       </c>
       <c r="H840" t="n">
         <v>5241</v>
@@ -24758,7 +24758,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G841" t="n">
-        <v>10.658127784729</v>
+        <v>10.6581268310547</v>
       </c>
       <c r="H841" t="n">
         <v>2748</v>
@@ -24787,7 +24787,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G842" t="n">
-        <v>10.658127784729</v>
+        <v>10.6581268310547</v>
       </c>
       <c r="H842" t="n">
         <v>5980</v>
@@ -24816,7 +24816,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G843" t="n">
-        <v>10.5731325149536</v>
+        <v>10.5731334686279</v>
       </c>
       <c r="H843" t="n">
         <v>6585</v>
@@ -24845,7 +24845,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G844" t="n">
-        <v>10.7431201934814</v>
+        <v>10.7431192398071</v>
       </c>
       <c r="H844" t="n">
         <v>11580</v>
@@ -24903,7 +24903,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G846" t="n">
-        <v>10.8961057662964</v>
+        <v>10.8961067199707</v>
       </c>
       <c r="H846" t="n">
         <v>10666</v>
@@ -24990,7 +24990,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G849" t="n">
-        <v>11.0279684066772</v>
+        <v>11.0279674530029</v>
       </c>
       <c r="H849" t="n">
         <v>7821</v>
@@ -25048,7 +25048,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G851" t="n">
-        <v>10.8341865539551</v>
+        <v>10.8341856002808</v>
       </c>
       <c r="H851" t="n">
         <v>4536</v>
@@ -25164,7 +25164,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G855" t="n">
-        <v>9.97097396850586</v>
+        <v>9.97097492218018</v>
       </c>
       <c r="H855" t="n">
         <v>20612</v>
@@ -25193,7 +25193,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G856" t="n">
-        <v>10.2176065444946</v>
+        <v>10.2176055908203</v>
       </c>
       <c r="H856" t="n">
         <v>27220</v>
@@ -25280,7 +25280,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G859" t="n">
-        <v>9.51294326782227</v>
+        <v>9.51294422149658</v>
       </c>
       <c r="H859" t="n">
         <v>20225</v>
@@ -25396,7 +25396,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G863" t="n">
-        <v>9.60102558135986</v>
+        <v>9.60102653503418</v>
       </c>
       <c r="H863" t="n">
         <v>38239</v>
@@ -25454,7 +25454,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G865" t="n">
-        <v>9.70672607421875</v>
+        <v>9.70672702789307</v>
       </c>
       <c r="H865" t="n">
         <v>127666</v>
@@ -25483,7 +25483,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G866" t="n">
-        <v>9.70672607421875</v>
+        <v>9.70672702789307</v>
       </c>
       <c r="H866" t="n">
         <v>12913</v>
@@ -25512,7 +25512,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G867" t="n">
-        <v>9.60102558135986</v>
+        <v>9.60102653503418</v>
       </c>
       <c r="H867" t="n">
         <v>8697</v>
@@ -25541,7 +25541,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G868" t="n">
-        <v>9.56579399108887</v>
+        <v>9.56579303741455</v>
       </c>
       <c r="H868" t="n">
         <v>5063</v>
@@ -25628,7 +25628,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G871" t="n">
-        <v>9.51294326782227</v>
+        <v>9.51294422149658</v>
       </c>
       <c r="H871" t="n">
         <v>4375</v>
@@ -25657,7 +25657,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G872" t="n">
-        <v>9.65387630462646</v>
+        <v>9.65387535095215</v>
       </c>
       <c r="H872" t="n">
         <v>8133</v>
@@ -25744,7 +25744,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G875" t="n">
-        <v>9.75957584381104</v>
+        <v>9.75957489013672</v>
       </c>
       <c r="H875" t="n">
         <v>4354</v>
@@ -25773,7 +25773,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>9.60102558135986</v>
+        <v>9.60102653503418</v>
       </c>
       <c r="H876" t="n">
         <v>13773</v>
@@ -25802,7 +25802,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G877" t="n">
-        <v>9.77719211578369</v>
+        <v>9.77719306945801</v>
       </c>
       <c r="H877" t="n">
         <v>11030</v>
@@ -25918,7 +25918,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G881" t="n">
-        <v>10.1119070053101</v>
+        <v>10.1119060516357</v>
       </c>
       <c r="H881" t="n">
         <v>9542</v>
@@ -25976,7 +25976,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G883" t="n">
-        <v>9.86527538299561</v>
+        <v>9.86527442932129</v>
       </c>
       <c r="H883" t="n">
         <v>8697</v>
@@ -26005,7 +26005,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G884" t="n">
-        <v>9.97097396850586</v>
+        <v>9.97097492218018</v>
       </c>
       <c r="H884" t="n">
         <v>8436</v>
@@ -26034,7 +26034,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G885" t="n">
-        <v>9.97097396850586</v>
+        <v>9.97097492218018</v>
       </c>
       <c r="H885" t="n">
         <v>12493</v>
@@ -26063,7 +26063,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G886" t="n">
-        <v>9.75957584381104</v>
+        <v>9.75957489013672</v>
       </c>
       <c r="H886" t="n">
         <v>23233</v>
@@ -26092,7 +26092,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G887" t="n">
-        <v>9.75957584381104</v>
+        <v>9.75957489013672</v>
       </c>
       <c r="H887" t="n">
         <v>2857</v>
@@ -26121,7 +26121,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G888" t="n">
-        <v>9.70672607421875</v>
+        <v>9.70672702789307</v>
       </c>
       <c r="H888" t="n">
         <v>4450</v>
@@ -26440,7 +26440,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G899" t="n">
-        <v>10.1119070053101</v>
+        <v>10.1119060516357</v>
       </c>
       <c r="H899" t="n">
         <v>14293</v>
@@ -26672,7 +26672,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G907" t="n">
-        <v>10.2176065444946</v>
+        <v>10.2176055908203</v>
       </c>
       <c r="H907" t="n">
         <v>12470</v>
@@ -26759,7 +26759,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G910" t="n">
-        <v>10.2176065444946</v>
+        <v>10.2176055908203</v>
       </c>
       <c r="H910" t="n">
         <v>1236</v>
@@ -26846,7 +26846,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G913" t="n">
-        <v>10.2704553604126</v>
+        <v>10.2704563140869</v>
       </c>
       <c r="H913" t="n">
         <v>12358</v>
@@ -27078,7 +27078,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G921" t="n">
-        <v>10.1119070053101</v>
+        <v>10.1119060516357</v>
       </c>
       <c r="H921" t="n">
         <v>5139</v>
@@ -27194,7 +27194,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G925" t="n">
-        <v>10.2704553604126</v>
+        <v>10.2704563140869</v>
       </c>
       <c r="H925" t="n">
         <v>771</v>
@@ -27397,7 +27397,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G932" t="n">
-        <v>10.2176065444946</v>
+        <v>10.2176055908203</v>
       </c>
       <c r="H932" t="n">
         <v>9423</v>
@@ -27542,7 +27542,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G937" t="n">
-        <v>10.8341865539551</v>
+        <v>10.8341856002808</v>
       </c>
       <c r="H937" t="n">
         <v>5961</v>
@@ -27600,7 +27600,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G939" t="n">
-        <v>10.8341865539551</v>
+        <v>10.8341856002808</v>
       </c>
       <c r="H939" t="n">
         <v>7964</v>
@@ -27687,7 +27687,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G942" t="n">
-        <v>10.8341865539551</v>
+        <v>10.8341856002808</v>
       </c>
       <c r="H942" t="n">
         <v>4320</v>
@@ -27716,7 +27716,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G943" t="n">
-        <v>10.8870344161987</v>
+        <v>10.887035369873</v>
       </c>
       <c r="H943" t="n">
         <v>4035</v>
@@ -27948,7 +27948,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G951" t="n">
-        <v>10.8341865539551</v>
+        <v>10.8341856002808</v>
       </c>
       <c r="H951" t="n">
         <v>2693</v>
@@ -27977,7 +27977,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G952" t="n">
-        <v>10.8341865539551</v>
+        <v>10.8341856002808</v>
       </c>
       <c r="H952" t="n">
         <v>9421</v>
@@ -28006,7 +28006,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G953" t="n">
-        <v>10.8341865539551</v>
+        <v>10.8341856002808</v>
       </c>
       <c r="H953" t="n">
         <v>3209</v>
@@ -28412,7 +28412,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G967" t="n">
-        <v>10.3233060836792</v>
+        <v>10.3233051300049</v>
       </c>
       <c r="H967" t="n">
         <v>4355</v>
@@ -29079,7 +29079,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G990" t="n">
-        <v>10.4290046691895</v>
+        <v>10.4290056228638</v>
       </c>
       <c r="H990" t="n">
         <v>4850</v>
@@ -30355,7 +30355,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1034" t="n">
-        <v>10.2176065444946</v>
+        <v>10.2176055908203</v>
       </c>
       <c r="H1034" t="n">
         <v>10936</v>
@@ -30384,7 +30384,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1035" t="n">
-        <v>10.2176065444946</v>
+        <v>10.2176055908203</v>
       </c>
       <c r="H1035" t="n">
         <v>6291</v>
@@ -30442,7 +30442,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1037" t="n">
-        <v>10.2176065444946</v>
+        <v>10.2176055908203</v>
       </c>
       <c r="H1037" t="n">
         <v>4578</v>
@@ -30587,7 +30587,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G1042" t="n">
-        <v>10.2704553604126</v>
+        <v>10.2704563140869</v>
       </c>
       <c r="H1042" t="n">
         <v>741</v>
@@ -30645,7 +30645,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>10.2176065444946</v>
+        <v>10.2176055908203</v>
       </c>
       <c r="H1044" t="n">
         <v>5642</v>
@@ -30819,7 +30819,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1050" t="n">
-        <v>10.1119070053101</v>
+        <v>10.1119060516357</v>
       </c>
       <c r="H1050" t="n">
         <v>8520</v>
@@ -30964,7 +30964,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G1055" t="n">
-        <v>9.65387630462646</v>
+        <v>9.65387535095215</v>
       </c>
       <c r="H1055" t="n">
         <v>8894</v>
@@ -31022,7 +31022,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1057" t="n">
-        <v>8.98444557189941</v>
+        <v>8.98444652557373</v>
       </c>
       <c r="H1057" t="n">
         <v>14648</v>
@@ -31109,7 +31109,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G1060" t="n">
-        <v>7.90983629226685</v>
+        <v>7.90983533859253</v>
       </c>
       <c r="H1060" t="n">
         <v>9851</v>
@@ -31138,7 +31138,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G1061" t="n">
-        <v>7.86579465866089</v>
+        <v>7.86579561233521</v>
       </c>
       <c r="H1061" t="n">
         <v>13588</v>
@@ -31254,7 +31254,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1065" t="n">
-        <v>6.44766187667847</v>
+        <v>6.44766139984131</v>
       </c>
       <c r="H1065" t="n">
         <v>10830</v>
@@ -31341,7 +31341,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G1068" t="n">
-        <v>6.15698862075806</v>
+        <v>6.1569881439209</v>
       </c>
       <c r="H1068" t="n">
         <v>18715</v>
@@ -31370,7 +31370,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1069" t="n">
-        <v>6.13056325912476</v>
+        <v>6.13056373596191</v>
       </c>
       <c r="H1069" t="n">
         <v>12340</v>
@@ -31399,7 +31399,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G1070" t="n">
-        <v>6.15698862075806</v>
+        <v>6.1569881439209</v>
       </c>
       <c r="H1070" t="n">
         <v>3767</v>
@@ -31602,7 +31602,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1077" t="n">
-        <v>7.03781652450562</v>
+        <v>7.03781604766846</v>
       </c>
       <c r="H1077" t="n">
         <v>9341</v>
@@ -31863,7 +31863,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1086" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H1086" t="n">
         <v>9697</v>
@@ -32008,7 +32008,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1091" t="n">
-        <v>7.41657257080078</v>
+        <v>7.41657304763794</v>
       </c>
       <c r="H1091" t="n">
         <v>11099</v>
@@ -32240,7 +32240,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1099" t="n">
-        <v>7.20517444610596</v>
+        <v>7.2051739692688</v>
       </c>
       <c r="H1099" t="n">
         <v>4563</v>
@@ -32385,7 +32385,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1104" t="n">
-        <v>6.99377536773682</v>
+        <v>6.99377489089966</v>
       </c>
       <c r="H1104" t="n">
         <v>693</v>
@@ -32443,7 +32443,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1106" t="n">
-        <v>6.94092559814453</v>
+        <v>6.94092512130737</v>
       </c>
       <c r="H1106" t="n">
         <v>5627</v>
@@ -32501,7 +32501,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1108" t="n">
-        <v>6.43004512786865</v>
+        <v>6.43004560470581</v>
       </c>
       <c r="H1108" t="n">
         <v>13424</v>
@@ -32675,7 +32675,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1114" t="n">
-        <v>6.94092559814453</v>
+        <v>6.94092512130737</v>
       </c>
       <c r="H1114" t="n">
         <v>2363</v>
@@ -32820,7 +32820,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1119" t="n">
-        <v>7.25802373886108</v>
+        <v>7.25802326202393</v>
       </c>
       <c r="H1119" t="n">
         <v>8876</v>
@@ -32849,7 +32849,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1120" t="n">
-        <v>7.25802373886108</v>
+        <v>7.25802326202393</v>
       </c>
       <c r="H1120" t="n">
         <v>6025</v>
@@ -33081,7 +33081,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1128" t="n">
-        <v>7.69843816757202</v>
+        <v>7.69843769073486</v>
       </c>
       <c r="H1128" t="n">
         <v>17568</v>
@@ -33110,7 +33110,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1129" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1129" t="n">
         <v>9422</v>
@@ -33168,7 +33168,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1131" t="n">
-        <v>8.01553630828857</v>
+        <v>8.01553535461426</v>
       </c>
       <c r="H1131" t="n">
         <v>7086</v>
@@ -33197,7 +33197,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1132" t="n">
-        <v>8.01553630828857</v>
+        <v>8.01553535461426</v>
       </c>
       <c r="H1132" t="n">
         <v>11575</v>
@@ -33226,7 +33226,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1133" t="n">
-        <v>8.2269344329834</v>
+        <v>8.22693538665771</v>
       </c>
       <c r="H1133" t="n">
         <v>6508</v>
@@ -33284,7 +33284,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G1135" t="n">
-        <v>7.89222002029419</v>
+        <v>7.89221954345703</v>
       </c>
       <c r="H1135" t="n">
         <v>5303</v>
@@ -33342,7 +33342,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1137" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1137" t="n">
         <v>3370</v>
@@ -33371,7 +33371,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1138" t="n">
-        <v>7.76890325546265</v>
+        <v>7.7689037322998</v>
       </c>
       <c r="H1138" t="n">
         <v>4454</v>
@@ -33632,7 +33632,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1147" t="n">
-        <v>7.45180606842041</v>
+        <v>7.45180559158325</v>
       </c>
       <c r="H1147" t="n">
         <v>1581</v>
@@ -33719,7 +33719,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1150" t="n">
-        <v>7.45180606842041</v>
+        <v>7.45180559158325</v>
       </c>
       <c r="H1150" t="n">
         <v>4736</v>
@@ -33835,7 +33835,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1154" t="n">
-        <v>7.52227210998535</v>
+        <v>7.52227258682251</v>
       </c>
       <c r="H1154" t="n">
         <v>1265</v>
@@ -33864,7 +33864,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1155" t="n">
-        <v>7.69843816757202</v>
+        <v>7.69843769073486</v>
       </c>
       <c r="H1155" t="n">
         <v>2048</v>
@@ -34038,7 +34038,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1161" t="n">
-        <v>7.39895629882812</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1161" t="n">
         <v>3501</v>
@@ -34067,7 +34067,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1162" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1162" t="n">
         <v>4618</v>
@@ -34096,7 +34096,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1163" t="n">
-        <v>7.39895629882812</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1163" t="n">
         <v>2963</v>
@@ -34154,7 +34154,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1165" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1165" t="n">
         <v>4353</v>
@@ -34212,7 +34212,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1167" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1167" t="n">
         <v>2028</v>
@@ -34357,7 +34357,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1172" t="n">
-        <v>7.39895629882812</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1172" t="n">
         <v>3445</v>
@@ -34386,7 +34386,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1173" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1173" t="n">
         <v>3379</v>
@@ -34415,7 +34415,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1174" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1174" t="n">
         <v>2346</v>
@@ -34444,7 +34444,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1175" t="n">
-        <v>7.25802373886108</v>
+        <v>7.25802326202393</v>
       </c>
       <c r="H1175" t="n">
         <v>1902</v>
@@ -34531,7 +34531,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1178" t="n">
-        <v>6.94092559814453</v>
+        <v>6.94092512130737</v>
       </c>
       <c r="H1178" t="n">
         <v>2874</v>
@@ -34821,7 +34821,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1188" t="n">
-        <v>6.76476001739502</v>
+        <v>6.76475954055786</v>
       </c>
       <c r="H1188" t="n">
         <v>10234</v>
@@ -34879,7 +34879,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1190" t="n">
-        <v>6.51812839508057</v>
+        <v>6.51812791824341</v>
       </c>
       <c r="H1190" t="n">
         <v>5405</v>
@@ -34937,7 +34937,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1192" t="n">
-        <v>6.43004512786865</v>
+        <v>6.43004560470581</v>
       </c>
       <c r="H1192" t="n">
         <v>12522</v>
@@ -35024,7 +35024,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1195" t="n">
-        <v>6.21864652633667</v>
+        <v>6.21864604949951</v>
       </c>
       <c r="H1195" t="n">
         <v>17403</v>
@@ -35053,7 +35053,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1196" t="n">
-        <v>6.21864652633667</v>
+        <v>6.21864604949951</v>
       </c>
       <c r="H1196" t="n">
         <v>14235</v>
@@ -35488,7 +35488,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1211" t="n">
-        <v>5.90154790878296</v>
+        <v>5.90154838562012</v>
       </c>
       <c r="H1211" t="n">
         <v>6159</v>
@@ -35546,7 +35546,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1213" t="n">
-        <v>5.90154790878296</v>
+        <v>5.90154838562012</v>
       </c>
       <c r="H1213" t="n">
         <v>4505</v>
@@ -35575,7 +35575,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1214" t="n">
-        <v>5.90154790878296</v>
+        <v>5.90154838562012</v>
       </c>
       <c r="H1214" t="n">
         <v>5958</v>
@@ -35836,7 +35836,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1223" t="n">
-        <v>5.44351720809937</v>
+        <v>5.44351768493652</v>
       </c>
       <c r="H1223" t="n">
         <v>35895</v>
@@ -35981,7 +35981,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1228" t="n">
-        <v>5.05595350265503</v>
+        <v>5.05595302581787</v>
       </c>
       <c r="H1228" t="n">
         <v>10666</v>
@@ -36039,7 +36039,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1230" t="n">
-        <v>5.1616530418396</v>
+        <v>5.16165256500244</v>
       </c>
       <c r="H1230" t="n">
         <v>32693</v>
@@ -36271,7 +36271,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1238" t="n">
-        <v>5.9543981552124</v>
+        <v>5.95439863204956</v>
       </c>
       <c r="H1238" t="n">
         <v>11624</v>
@@ -36474,7 +36474,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1245" t="n">
-        <v>7.25802373886108</v>
+        <v>7.25802326202393</v>
       </c>
       <c r="H1245" t="n">
         <v>54942</v>
@@ -36503,7 +36503,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1246" t="n">
-        <v>7.69843816757202</v>
+        <v>7.69843769073486</v>
       </c>
       <c r="H1246" t="n">
         <v>71944</v>
@@ -36532,7 +36532,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1247" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1247" t="n">
         <v>73842</v>
@@ -36590,7 +36590,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G1249" t="n">
-        <v>7.90983629226685</v>
+        <v>7.90983533859253</v>
       </c>
       <c r="H1249" t="n">
         <v>25778</v>
@@ -36677,7 +36677,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1252" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1252" t="n">
         <v>14997</v>
@@ -36735,7 +36735,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1254" t="n">
-        <v>7.45180606842041</v>
+        <v>7.45180559158325</v>
       </c>
       <c r="H1254" t="n">
         <v>10064</v>
@@ -36793,7 +36793,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1256" t="n">
-        <v>7.68082189559937</v>
+        <v>7.68082141876221</v>
       </c>
       <c r="H1256" t="n">
         <v>10229</v>
@@ -36822,7 +36822,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1257" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1257" t="n">
         <v>15592</v>
@@ -36880,7 +36880,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1259" t="n">
-        <v>7.76890325546265</v>
+        <v>7.7689037322998</v>
       </c>
       <c r="H1259" t="n">
         <v>12283</v>
@@ -36909,7 +36909,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1260" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1260" t="n">
         <v>7809</v>
@@ -36938,7 +36938,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1261" t="n">
-        <v>7.68082189559937</v>
+        <v>7.68082141876221</v>
       </c>
       <c r="H1261" t="n">
         <v>3003</v>
@@ -36967,7 +36967,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1262" t="n">
-        <v>7.68082189559937</v>
+        <v>7.68082141876221</v>
       </c>
       <c r="H1262" t="n">
         <v>13527</v>
@@ -36996,7 +36996,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1263" t="n">
-        <v>7.80413770675659</v>
+        <v>7.80413722991943</v>
       </c>
       <c r="H1263" t="n">
         <v>4368</v>
@@ -37083,7 +37083,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1266" t="n">
-        <v>7.39895629882812</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1266" t="n">
         <v>8274</v>
@@ -37112,7 +37112,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1267" t="n">
-        <v>7.45180606842041</v>
+        <v>7.45180559158325</v>
       </c>
       <c r="H1267" t="n">
         <v>3762</v>
@@ -37315,7 +37315,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1274" t="n">
-        <v>7.45180606842041</v>
+        <v>7.45180559158325</v>
       </c>
       <c r="H1274" t="n">
         <v>5725</v>
@@ -37431,7 +37431,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1278" t="n">
-        <v>7.25802373886108</v>
+        <v>7.25802326202393</v>
       </c>
       <c r="H1278" t="n">
         <v>5220</v>
@@ -37489,7 +37489,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1280" t="n">
-        <v>7.25802373886108</v>
+        <v>7.25802326202393</v>
       </c>
       <c r="H1280" t="n">
         <v>14138</v>
@@ -37518,7 +37518,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1281" t="n">
-        <v>7.20517444610596</v>
+        <v>7.2051739692688</v>
       </c>
       <c r="H1281" t="n">
         <v>10404</v>
@@ -37605,7 +37605,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1284" t="n">
-        <v>6.99377536773682</v>
+        <v>6.99377489089966</v>
       </c>
       <c r="H1284" t="n">
         <v>8566</v>
@@ -37837,7 +37837,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1292" t="n">
-        <v>6.76476001739502</v>
+        <v>6.76475954055786</v>
       </c>
       <c r="H1292" t="n">
         <v>15182</v>
@@ -37866,7 +37866,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1293" t="n">
-        <v>6.94092559814453</v>
+        <v>6.94092512130737</v>
       </c>
       <c r="H1293" t="n">
         <v>43991</v>
@@ -37924,7 +37924,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1295" t="n">
-        <v>7.25802373886108</v>
+        <v>7.25802326202393</v>
       </c>
       <c r="H1295" t="n">
         <v>7392</v>
@@ -38098,7 +38098,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1301" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H1301" t="n">
         <v>19981</v>
@@ -38156,7 +38156,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1303" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H1303" t="n">
         <v>3772</v>
@@ -38330,7 +38330,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1309" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1309" t="n">
         <v>32224</v>
@@ -38359,7 +38359,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1310" t="n">
-        <v>7.15232467651367</v>
+        <v>7.15232419967651</v>
       </c>
       <c r="H1310" t="n">
         <v>6810</v>
@@ -38446,7 +38446,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1313" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1313" t="n">
         <v>11299</v>
@@ -38475,7 +38475,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1314" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H1314" t="n">
         <v>24116</v>
@@ -38562,7 +38562,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1317" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1317" t="n">
         <v>18426</v>
@@ -38620,7 +38620,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1319" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1319" t="n">
         <v>10950</v>
@@ -38823,7 +38823,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G1326" t="n">
-        <v>7.90983629226685</v>
+        <v>7.90983533859253</v>
       </c>
       <c r="H1326" t="n">
         <v>39015</v>
@@ -38852,7 +38852,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1327" t="n">
-        <v>8.03315162658691</v>
+        <v>8.03315258026123</v>
       </c>
       <c r="H1327" t="n">
         <v>40745</v>
@@ -39200,7 +39200,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G1339" t="n">
-        <v>8.40310001373291</v>
+        <v>8.40310096740723</v>
       </c>
       <c r="H1339" t="n">
         <v>50615</v>
@@ -39403,7 +39403,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1346" t="n">
-        <v>8.85232257843018</v>
+        <v>8.85232162475586</v>
       </c>
       <c r="H1346" t="n">
         <v>24844</v>
@@ -39432,7 +39432,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1347" t="n">
-        <v>8.98444557189941</v>
+        <v>8.98444652557373</v>
       </c>
       <c r="H1347" t="n">
         <v>11082</v>
@@ -39693,7 +39693,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1356" t="n">
-        <v>8.73781490325928</v>
+        <v>8.73781394958496</v>
       </c>
       <c r="H1356" t="n">
         <v>10126</v>
@@ -39722,7 +39722,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1357" t="n">
-        <v>8.85232257843018</v>
+        <v>8.85232162475586</v>
       </c>
       <c r="H1357" t="n">
         <v>8377</v>
@@ -39780,7 +39780,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1359" t="n">
-        <v>8.79066371917725</v>
+        <v>8.79066467285156</v>
       </c>
       <c r="H1359" t="n">
         <v>13792</v>
@@ -39896,7 +39896,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1363" t="n">
-        <v>8.73781490325928</v>
+        <v>8.73781394958496</v>
       </c>
       <c r="H1363" t="n">
         <v>9891</v>
@@ -39954,7 +39954,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1365" t="n">
-        <v>8.85232257843018</v>
+        <v>8.85232162475586</v>
       </c>
       <c r="H1365" t="n">
         <v>27953</v>
@@ -40070,7 +40070,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1369" t="n">
-        <v>8.68496417999268</v>
+        <v>8.68496513366699</v>
       </c>
       <c r="H1369" t="n">
         <v>6982</v>
@@ -40128,7 +40128,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1371" t="n">
-        <v>8.85232257843018</v>
+        <v>8.85232162475586</v>
       </c>
       <c r="H1371" t="n">
         <v>3090</v>
@@ -40186,7 +40186,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1373" t="n">
-        <v>8.79066371917725</v>
+        <v>8.79066467285156</v>
       </c>
       <c r="H1373" t="n">
         <v>19472</v>
@@ -40244,7 +40244,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1375" t="n">
-        <v>8.98444557189941</v>
+        <v>8.98444652557373</v>
       </c>
       <c r="H1375" t="n">
         <v>16576</v>
@@ -40273,7 +40273,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1376" t="n">
-        <v>9.16061305999756</v>
+        <v>9.16061210632324</v>
       </c>
       <c r="H1376" t="n">
         <v>16246</v>
@@ -40592,7 +40592,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1387" t="n">
-        <v>9.77719211578369</v>
+        <v>9.77719306945801</v>
       </c>
       <c r="H1387" t="n">
         <v>15068</v>
@@ -40621,7 +40621,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1388" t="n">
-        <v>9.60102558135986</v>
+        <v>9.60102653503418</v>
       </c>
       <c r="H1388" t="n">
         <v>35392</v>
@@ -40650,7 +40650,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1389" t="n">
-        <v>9.60102558135986</v>
+        <v>9.60102653503418</v>
       </c>
       <c r="H1389" t="n">
         <v>10155</v>
@@ -40679,7 +40679,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1390" t="n">
-        <v>9.51294326782227</v>
+        <v>9.51294422149658</v>
       </c>
       <c r="H1390" t="n">
         <v>9382</v>
@@ -40853,7 +40853,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1396" t="n">
-        <v>9.16061305999756</v>
+        <v>9.16061210632324</v>
       </c>
       <c r="H1396" t="n">
         <v>12825</v>
@@ -40998,7 +40998,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1401" t="n">
-        <v>9.16061305999756</v>
+        <v>9.16061210632324</v>
       </c>
       <c r="H1401" t="n">
         <v>2102</v>
@@ -41085,7 +41085,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1404" t="n">
-        <v>9.16061305999756</v>
+        <v>9.16061210632324</v>
       </c>
       <c r="H1404" t="n">
         <v>1674</v>
@@ -41172,7 +41172,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G1407" t="n">
-        <v>9.1165714263916</v>
+        <v>9.11657047271729</v>
       </c>
       <c r="H1407" t="n">
         <v>6331</v>
@@ -41201,7 +41201,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1408" t="n">
-        <v>8.98444557189941</v>
+        <v>8.98444652557373</v>
       </c>
       <c r="H1408" t="n">
         <v>13556</v>
@@ -41259,7 +41259,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1410" t="n">
-        <v>8.68496417999268</v>
+        <v>8.68496513366699</v>
       </c>
       <c r="H1410" t="n">
         <v>24712</v>
@@ -41317,7 +41317,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1412" t="n">
-        <v>8.85232257843018</v>
+        <v>8.85232162475586</v>
       </c>
       <c r="H1412" t="n">
         <v>8211</v>
@@ -41404,7 +41404,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1415" t="n">
-        <v>8.85232257843018</v>
+        <v>8.85232162475586</v>
       </c>
       <c r="H1415" t="n">
         <v>3022</v>
@@ -41520,7 +41520,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1419" t="n">
-        <v>8.85232257843018</v>
+        <v>8.85232162475586</v>
       </c>
       <c r="H1419" t="n">
         <v>7864</v>
@@ -41607,7 +41607,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1422" t="n">
-        <v>8.85232257843018</v>
+        <v>8.85232162475586</v>
       </c>
       <c r="H1422" t="n">
         <v>2481</v>
@@ -41636,7 +41636,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1423" t="n">
-        <v>8.79066371917725</v>
+        <v>8.79066467285156</v>
       </c>
       <c r="H1423" t="n">
         <v>3057</v>
@@ -41665,7 +41665,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1424" t="n">
-        <v>8.98444557189941</v>
+        <v>8.98444652557373</v>
       </c>
       <c r="H1424" t="n">
         <v>6956</v>
@@ -41723,7 +41723,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1426" t="n">
-        <v>8.85232257843018</v>
+        <v>8.85232162475586</v>
       </c>
       <c r="H1426" t="n">
         <v>8098</v>
@@ -41839,7 +41839,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1430" t="n">
-        <v>8.98444557189941</v>
+        <v>8.98444652557373</v>
       </c>
       <c r="H1430" t="n">
         <v>3148</v>
@@ -41868,7 +41868,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1431" t="n">
-        <v>8.98444557189941</v>
+        <v>8.98444652557373</v>
       </c>
       <c r="H1431" t="n">
         <v>3710</v>
@@ -41984,7 +41984,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1435" t="n">
-        <v>8.85232257843018</v>
+        <v>8.85232162475586</v>
       </c>
       <c r="H1435" t="n">
         <v>5120</v>
@@ -42042,7 +42042,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1437" t="n">
-        <v>8.85232257843018</v>
+        <v>8.85232162475586</v>
       </c>
       <c r="H1437" t="n">
         <v>10401</v>
@@ -42071,7 +42071,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1438" t="n">
-        <v>8.79066371917725</v>
+        <v>8.79066467285156</v>
       </c>
       <c r="H1438" t="n">
         <v>7874</v>
@@ -42129,7 +42129,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1440" t="n">
-        <v>8.79066371917725</v>
+        <v>8.79066467285156</v>
       </c>
       <c r="H1440" t="n">
         <v>4460</v>
@@ -42187,7 +42187,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1442" t="n">
-        <v>8.73781490325928</v>
+        <v>8.73781394958496</v>
       </c>
       <c r="H1442" t="n">
         <v>13104</v>
@@ -42216,7 +42216,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1443" t="n">
-        <v>8.73781490325928</v>
+        <v>8.73781394958496</v>
       </c>
       <c r="H1443" t="n">
         <v>3281</v>
@@ -42245,7 +42245,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1444" t="n">
-        <v>8.73781490325928</v>
+        <v>8.73781394958496</v>
       </c>
       <c r="H1444" t="n">
         <v>9205</v>
@@ -42303,7 +42303,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1446" t="n">
-        <v>8.85232257843018</v>
+        <v>8.85232162475586</v>
       </c>
       <c r="H1446" t="n">
         <v>12523</v>
@@ -42390,7 +42390,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1449" t="n">
-        <v>8.73781490325928</v>
+        <v>8.73781394958496</v>
       </c>
       <c r="H1449" t="n">
         <v>2158</v>
@@ -42506,7 +42506,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1453" t="n">
-        <v>8.85232257843018</v>
+        <v>8.85232162475586</v>
       </c>
       <c r="H1453" t="n">
         <v>11045</v>
@@ -42564,7 +42564,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1455" t="n">
-        <v>8.85232257843018</v>
+        <v>8.85232162475586</v>
       </c>
       <c r="H1455" t="n">
         <v>9671</v>
@@ -42622,7 +42622,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1457" t="n">
-        <v>8.85232257843018</v>
+        <v>8.85232162475586</v>
       </c>
       <c r="H1457" t="n">
         <v>7546</v>
@@ -42680,7 +42680,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1459" t="n">
-        <v>8.85232257843018</v>
+        <v>8.85232162475586</v>
       </c>
       <c r="H1459" t="n">
         <v>21062</v>
@@ -42825,7 +42825,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1464" t="n">
-        <v>8.73781490325928</v>
+        <v>8.73781394958496</v>
       </c>
       <c r="H1464" t="n">
         <v>8906</v>
@@ -42854,7 +42854,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1465" t="n">
-        <v>8.66734886169434</v>
+        <v>8.66734790802002</v>
       </c>
       <c r="H1465" t="n">
         <v>1401</v>
@@ -42883,7 +42883,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1466" t="n">
-        <v>8.68496417999268</v>
+        <v>8.68496513366699</v>
       </c>
       <c r="H1466" t="n">
         <v>7884</v>
@@ -42912,7 +42912,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1467" t="n">
-        <v>8.68496417999268</v>
+        <v>8.68496513366699</v>
       </c>
       <c r="H1467" t="n">
         <v>7736</v>
@@ -42999,7 +42999,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1470" t="n">
-        <v>8.59688186645508</v>
+        <v>8.59688282012939</v>
       </c>
       <c r="H1470" t="n">
         <v>2135</v>
@@ -43173,7 +43173,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1476" t="n">
-        <v>8.59688186645508</v>
+        <v>8.59688282012939</v>
       </c>
       <c r="H1476" t="n">
         <v>3103</v>
@@ -43231,7 +43231,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1478" t="n">
-        <v>8.79066371917725</v>
+        <v>8.79066467285156</v>
       </c>
       <c r="H1478" t="n">
         <v>9036</v>
@@ -43318,7 +43318,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1481" t="n">
-        <v>8.59688186645508</v>
+        <v>8.59688282012939</v>
       </c>
       <c r="H1481" t="n">
         <v>2217</v>
@@ -43347,7 +43347,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1482" t="n">
-        <v>8.59688186645508</v>
+        <v>8.59688282012939</v>
       </c>
       <c r="H1482" t="n">
         <v>1011</v>
@@ -43492,7 +43492,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1487" t="n">
-        <v>8.59688186645508</v>
+        <v>8.59688282012939</v>
       </c>
       <c r="H1487" t="n">
         <v>8551</v>
@@ -43753,7 +43753,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G1496" t="n">
-        <v>8.40310001373291</v>
+        <v>8.40310096740723</v>
       </c>
       <c r="H1496" t="n">
         <v>10254</v>
@@ -43782,7 +43782,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1497" t="n">
-        <v>8.13885116577148</v>
+        <v>8.1388521194458</v>
       </c>
       <c r="H1497" t="n">
         <v>24009</v>
@@ -43869,7 +43869,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G1500" t="n">
-        <v>7.99791955947876</v>
+        <v>7.9979190826416</v>
       </c>
       <c r="H1500" t="n">
         <v>12139</v>
@@ -43927,7 +43927,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1502" t="n">
-        <v>8.12123584747314</v>
+        <v>8.12123489379883</v>
       </c>
       <c r="H1502" t="n">
         <v>6699</v>
@@ -43956,7 +43956,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G1503" t="n">
-        <v>7.89222002029419</v>
+        <v>7.89221954345703</v>
       </c>
       <c r="H1503" t="n">
         <v>10787</v>
@@ -44014,7 +44014,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1505" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1505" t="n">
         <v>994</v>
@@ -44043,7 +44043,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G1506" t="n">
-        <v>7.89222002029419</v>
+        <v>7.89221954345703</v>
       </c>
       <c r="H1506" t="n">
         <v>1890</v>
@@ -44072,7 +44072,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1507" t="n">
-        <v>7.80413770675659</v>
+        <v>7.80413722991943</v>
       </c>
       <c r="H1507" t="n">
         <v>7357</v>
@@ -44101,7 +44101,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G1508" t="n">
-        <v>7.89222002029419</v>
+        <v>7.89221954345703</v>
       </c>
       <c r="H1508" t="n">
         <v>4107</v>
@@ -44130,7 +44130,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1509" t="n">
-        <v>7.76890325546265</v>
+        <v>7.7689037322998</v>
       </c>
       <c r="H1509" t="n">
         <v>3569</v>
@@ -44159,7 +44159,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G1510" t="n">
-        <v>7.96268606185913</v>
+        <v>7.96268653869629</v>
       </c>
       <c r="H1510" t="n">
         <v>968</v>
@@ -44188,7 +44188,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G1511" t="n">
-        <v>7.99791955947876</v>
+        <v>7.9979190826416</v>
       </c>
       <c r="H1511" t="n">
         <v>1850</v>
@@ -44217,7 +44217,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1512" t="n">
-        <v>8.01553630828857</v>
+        <v>8.01553535461426</v>
       </c>
       <c r="H1512" t="n">
         <v>4365</v>
@@ -44275,7 +44275,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G1514" t="n">
-        <v>7.96268606185913</v>
+        <v>7.96268653869629</v>
       </c>
       <c r="H1514" t="n">
         <v>1607</v>
@@ -44304,7 +44304,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1515" t="n">
-        <v>7.94507026672363</v>
+        <v>7.94507074356079</v>
       </c>
       <c r="H1515" t="n">
         <v>2402</v>
@@ -44333,7 +44333,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G1516" t="n">
-        <v>7.89222002029419</v>
+        <v>7.89221954345703</v>
       </c>
       <c r="H1516" t="n">
         <v>355</v>
@@ -44391,7 +44391,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G1518" t="n">
-        <v>7.90983629226685</v>
+        <v>7.90983533859253</v>
       </c>
       <c r="H1518" t="n">
         <v>3002</v>
@@ -44420,7 +44420,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1519" t="n">
-        <v>7.82175350189209</v>
+        <v>7.82175397872925</v>
       </c>
       <c r="H1519" t="n">
         <v>3936</v>
@@ -44449,7 +44449,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G1520" t="n">
-        <v>7.89222002029419</v>
+        <v>7.89221954345703</v>
       </c>
       <c r="H1520" t="n">
         <v>37</v>
@@ -44478,7 +44478,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1521" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1521" t="n">
         <v>5013</v>
@@ -44507,7 +44507,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G1522" t="n">
-        <v>7.73367023468018</v>
+        <v>7.73367071151733</v>
       </c>
       <c r="H1522" t="n">
         <v>4506</v>
@@ -44536,7 +44536,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1523" t="n">
-        <v>7.76890325546265</v>
+        <v>7.7689037322998</v>
       </c>
       <c r="H1523" t="n">
         <v>9607</v>
@@ -44565,7 +44565,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1524" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1524" t="n">
         <v>1717</v>
@@ -44594,7 +44594,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1525" t="n">
-        <v>7.59273862838745</v>
+        <v>7.59273815155029</v>
       </c>
       <c r="H1525" t="n">
         <v>3711</v>
@@ -44623,7 +44623,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1526" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1526" t="n">
         <v>4486</v>
@@ -44652,7 +44652,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G1527" t="n">
-        <v>7.99791955947876</v>
+        <v>7.9979190826416</v>
       </c>
       <c r="H1527" t="n">
         <v>12183</v>
@@ -44797,7 +44797,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1532" t="n">
-        <v>8.2269344329834</v>
+        <v>8.22693538665771</v>
       </c>
       <c r="H1532" t="n">
         <v>1605</v>
@@ -45000,7 +45000,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1539" t="n">
-        <v>8.03315162658691</v>
+        <v>8.03315258026123</v>
       </c>
       <c r="H1539" t="n">
         <v>7822</v>
@@ -45029,7 +45029,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1540" t="n">
-        <v>8.01553630828857</v>
+        <v>8.01553535461426</v>
       </c>
       <c r="H1540" t="n">
         <v>1522</v>
@@ -45058,7 +45058,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1541" t="n">
-        <v>8.01553630828857</v>
+        <v>8.01553535461426</v>
       </c>
       <c r="H1541" t="n">
         <v>907</v>
@@ -45145,7 +45145,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1544" t="n">
-        <v>8.12123584747314</v>
+        <v>8.12123489379883</v>
       </c>
       <c r="H1544" t="n">
         <v>9044</v>
@@ -45203,7 +45203,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1546" t="n">
-        <v>7.94507026672363</v>
+        <v>7.94507074356079</v>
       </c>
       <c r="H1546" t="n">
         <v>1129</v>
@@ -45290,7 +45290,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1549" t="n">
-        <v>8.03315162658691</v>
+        <v>8.03315258026123</v>
       </c>
       <c r="H1549" t="n">
         <v>4077</v>
@@ -45319,7 +45319,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1550" t="n">
-        <v>8.03315162658691</v>
+        <v>8.03315258026123</v>
       </c>
       <c r="H1550" t="n">
         <v>1067</v>
@@ -45348,7 +45348,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1551" t="n">
-        <v>8.03315162658691</v>
+        <v>8.03315258026123</v>
       </c>
       <c r="H1551" t="n">
         <v>6495</v>
@@ -45377,7 +45377,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G1552" t="n">
-        <v>7.96268606185913</v>
+        <v>7.96268653869629</v>
       </c>
       <c r="H1552" t="n">
         <v>3314</v>
@@ -45406,7 +45406,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G1553" t="n">
-        <v>7.96268606185913</v>
+        <v>7.96268653869629</v>
       </c>
       <c r="H1553" t="n">
         <v>535</v>
@@ -45522,7 +45522,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1557" t="n">
-        <v>7.94507026672363</v>
+        <v>7.94507074356079</v>
       </c>
       <c r="H1557" t="n">
         <v>6957</v>
@@ -45580,7 +45580,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1559" t="n">
-        <v>8.12123584747314</v>
+        <v>8.12123489379883</v>
       </c>
       <c r="H1559" t="n">
         <v>4102</v>
@@ -45638,7 +45638,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1561" t="n">
-        <v>8.01553630828857</v>
+        <v>8.01553535461426</v>
       </c>
       <c r="H1561" t="n">
         <v>1525</v>
@@ -45667,7 +45667,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1562" t="n">
-        <v>8.13885116577148</v>
+        <v>8.1388521194458</v>
       </c>
       <c r="H1562" t="n">
         <v>1737</v>
@@ -45725,7 +45725,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G1564" t="n">
-        <v>7.96268606185913</v>
+        <v>7.96268653869629</v>
       </c>
       <c r="H1564" t="n">
         <v>874</v>
@@ -45754,7 +45754,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G1565" t="n">
-        <v>7.90983629226685</v>
+        <v>7.90983533859253</v>
       </c>
       <c r="H1565" t="n">
         <v>12559</v>
@@ -45841,7 +45841,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1568" t="n">
-        <v>7.68082189559937</v>
+        <v>7.68082141876221</v>
       </c>
       <c r="H1568" t="n">
         <v>3247</v>
@@ -45870,7 +45870,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G1569" t="n">
-        <v>7.90983629226685</v>
+        <v>7.90983533859253</v>
       </c>
       <c r="H1569" t="n">
         <v>4572</v>
@@ -45899,7 +45899,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G1570" t="n">
-        <v>7.73367023468018</v>
+        <v>7.73367071151733</v>
       </c>
       <c r="H1570" t="n">
         <v>8763</v>
@@ -46015,7 +46015,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1574" t="n">
-        <v>7.39895629882812</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1574" t="n">
         <v>15307</v>
@@ -46160,7 +46160,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G1579" t="n">
-        <v>7.90983629226685</v>
+        <v>7.90983533859253</v>
       </c>
       <c r="H1579" t="n">
         <v>6526</v>
@@ -46189,7 +46189,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1580" t="n">
-        <v>7.68082189559937</v>
+        <v>7.68082141876221</v>
       </c>
       <c r="H1580" t="n">
         <v>2630</v>
@@ -46305,7 +46305,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1584" t="n">
-        <v>7.52227210998535</v>
+        <v>7.52227258682251</v>
       </c>
       <c r="H1584" t="n">
         <v>2763</v>
@@ -46392,7 +46392,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1587" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1587" t="n">
         <v>1280</v>
@@ -46421,7 +46421,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1588" t="n">
-        <v>7.80413770675659</v>
+        <v>7.80413722991943</v>
       </c>
       <c r="H1588" t="n">
         <v>6390</v>
@@ -46450,7 +46450,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1589" t="n">
-        <v>7.80413770675659</v>
+        <v>7.80413722991943</v>
       </c>
       <c r="H1589" t="n">
         <v>4014</v>
@@ -46537,7 +46537,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1592" t="n">
-        <v>7.69843816757202</v>
+        <v>7.69843769073486</v>
       </c>
       <c r="H1592" t="n">
         <v>934</v>
@@ -46566,7 +46566,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1593" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1593" t="n">
         <v>4106</v>
@@ -46595,7 +46595,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1594" t="n">
-        <v>7.76890325546265</v>
+        <v>7.7689037322998</v>
       </c>
       <c r="H1594" t="n">
         <v>3534</v>
@@ -46624,7 +46624,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G1595" t="n">
-        <v>7.71605396270752</v>
+        <v>7.71605443954468</v>
       </c>
       <c r="H1595" t="n">
         <v>2706</v>
@@ -46653,7 +46653,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1596" t="n">
-        <v>7.82175350189209</v>
+        <v>7.82175397872925</v>
       </c>
       <c r="H1596" t="n">
         <v>1806</v>
@@ -46682,7 +46682,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1597" t="n">
-        <v>7.69843816757202</v>
+        <v>7.69843769073486</v>
       </c>
       <c r="H1597" t="n">
         <v>2468</v>
@@ -46711,7 +46711,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1598" t="n">
-        <v>7.68082189559937</v>
+        <v>7.68082141876221</v>
       </c>
       <c r="H1598" t="n">
         <v>2937</v>
@@ -46769,7 +46769,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G1600" t="n">
-        <v>7.73367023468018</v>
+        <v>7.73367071151733</v>
       </c>
       <c r="H1600" t="n">
         <v>1669</v>
@@ -46856,7 +46856,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1603" t="n">
-        <v>7.59273862838745</v>
+        <v>7.59273815155029</v>
       </c>
       <c r="H1603" t="n">
         <v>6068</v>
@@ -46885,7 +46885,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1604" t="n">
-        <v>7.59273862838745</v>
+        <v>7.59273815155029</v>
       </c>
       <c r="H1604" t="n">
         <v>2080</v>
@@ -47001,7 +47001,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1608" t="n">
-        <v>7.20517444610596</v>
+        <v>7.2051739692688</v>
       </c>
       <c r="H1608" t="n">
         <v>4057</v>
@@ -47146,7 +47146,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1613" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1613" t="n">
         <v>2999</v>
@@ -47233,7 +47233,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1616" t="n">
-        <v>7.59273862838745</v>
+        <v>7.59273815155029</v>
       </c>
       <c r="H1616" t="n">
         <v>5720</v>
@@ -47262,7 +47262,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1617" t="n">
-        <v>7.69843816757202</v>
+        <v>7.69843769073486</v>
       </c>
       <c r="H1617" t="n">
         <v>7365</v>
@@ -47291,7 +47291,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1618" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1618" t="n">
         <v>1502</v>
@@ -47320,7 +47320,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G1619" t="n">
-        <v>7.71605396270752</v>
+        <v>7.71605443954468</v>
       </c>
       <c r="H1619" t="n">
         <v>8303</v>
@@ -47349,7 +47349,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1620" t="n">
-        <v>7.80413770675659</v>
+        <v>7.80413722991943</v>
       </c>
       <c r="H1620" t="n">
         <v>2491</v>
@@ -47378,7 +47378,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G1621" t="n">
-        <v>7.71605396270752</v>
+        <v>7.71605443954468</v>
       </c>
       <c r="H1621" t="n">
         <v>2602</v>
@@ -47407,7 +47407,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G1622" t="n">
-        <v>7.73367023468018</v>
+        <v>7.73367071151733</v>
       </c>
       <c r="H1622" t="n">
         <v>1231</v>
@@ -47436,7 +47436,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1623" t="n">
-        <v>7.68082189559937</v>
+        <v>7.68082141876221</v>
       </c>
       <c r="H1623" t="n">
         <v>496</v>
@@ -47465,7 +47465,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1624" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1624" t="n">
         <v>10762</v>
@@ -47494,7 +47494,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G1625" t="n">
-        <v>7.71605396270752</v>
+        <v>7.71605443954468</v>
       </c>
       <c r="H1625" t="n">
         <v>1157</v>
@@ -47552,7 +47552,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1627" t="n">
-        <v>7.52227210998535</v>
+        <v>7.52227258682251</v>
       </c>
       <c r="H1627" t="n">
         <v>2834</v>
@@ -47581,7 +47581,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G1628" t="n">
-        <v>7.73367023468018</v>
+        <v>7.73367071151733</v>
       </c>
       <c r="H1628" t="n">
         <v>2925</v>
@@ -47610,7 +47610,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G1629" t="n">
-        <v>7.73367023468018</v>
+        <v>7.73367071151733</v>
       </c>
       <c r="H1629" t="n">
         <v>25778</v>
@@ -47639,7 +47639,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1630" t="n">
-        <v>7.75128746032715</v>
+        <v>7.75128698348999</v>
       </c>
       <c r="H1630" t="n">
         <v>8071</v>
@@ -47668,7 +47668,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1631" t="n">
-        <v>7.80413770675659</v>
+        <v>7.80413722991943</v>
       </c>
       <c r="H1631" t="n">
         <v>16809</v>
@@ -47697,7 +47697,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G1632" t="n">
-        <v>7.73367023468018</v>
+        <v>7.73367071151733</v>
       </c>
       <c r="H1632" t="n">
         <v>4398</v>
@@ -47726,7 +47726,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1633" t="n">
-        <v>7.94507026672363</v>
+        <v>7.94507074356079</v>
       </c>
       <c r="H1633" t="n">
         <v>9840</v>
@@ -47871,7 +47871,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1638" t="n">
-        <v>8.03315162658691</v>
+        <v>8.03315258026123</v>
       </c>
       <c r="H1638" t="n">
         <v>4240</v>
@@ -47958,7 +47958,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1641" t="n">
-        <v>7.52227210998535</v>
+        <v>7.52227258682251</v>
       </c>
       <c r="H1641" t="n">
         <v>4161</v>
@@ -48074,7 +48074,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1645" t="n">
-        <v>7.45180606842041</v>
+        <v>7.45180559158325</v>
       </c>
       <c r="H1645" t="n">
         <v>6814</v>
@@ -48277,7 +48277,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1652" t="n">
-        <v>7.45180606842041</v>
+        <v>7.45180559158325</v>
       </c>
       <c r="H1652" t="n">
         <v>2682</v>
@@ -48306,7 +48306,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1653" t="n">
-        <v>7.39895629882812</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1653" t="n">
         <v>1693</v>
@@ -48335,7 +48335,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1654" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1654" t="n">
         <v>834</v>
@@ -48509,7 +48509,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1660" t="n">
-        <v>7.41657257080078</v>
+        <v>7.41657304763794</v>
       </c>
       <c r="H1660" t="n">
         <v>1125</v>
@@ -48799,7 +48799,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1670" t="n">
-        <v>7.25802373886108</v>
+        <v>7.25802326202393</v>
       </c>
       <c r="H1670" t="n">
         <v>1018</v>
@@ -48828,7 +48828,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1671" t="n">
-        <v>7.39895629882812</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1671" t="n">
         <v>1430</v>
@@ -48857,7 +48857,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1672" t="n">
-        <v>7.15232467651367</v>
+        <v>7.15232419967651</v>
       </c>
       <c r="H1672" t="n">
         <v>3310</v>
@@ -48886,7 +48886,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1673" t="n">
-        <v>7.39895629882812</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1673" t="n">
         <v>1487</v>
@@ -49002,7 +49002,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1677" t="n">
-        <v>7.45180606842041</v>
+        <v>7.45180559158325</v>
       </c>
       <c r="H1677" t="n">
         <v>487</v>
@@ -49060,7 +49060,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1679" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1679" t="n">
         <v>693</v>
@@ -49089,7 +49089,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1680" t="n">
-        <v>7.39895629882812</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1680" t="n">
         <v>867</v>
@@ -49118,7 +49118,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1681" t="n">
-        <v>7.39895629882812</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1681" t="n">
         <v>529</v>
@@ -49176,7 +49176,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1683" t="n">
-        <v>7.41657257080078</v>
+        <v>7.41657304763794</v>
       </c>
       <c r="H1683" t="n">
         <v>1400</v>
@@ -49292,7 +49292,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1687" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1687" t="n">
         <v>1869</v>
@@ -49350,7 +49350,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1689" t="n">
-        <v>7.20517444610596</v>
+        <v>7.2051739692688</v>
       </c>
       <c r="H1689" t="n">
         <v>1707</v>
@@ -49379,7 +49379,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1690" t="n">
-        <v>7.15232467651367</v>
+        <v>7.15232419967651</v>
       </c>
       <c r="H1690" t="n">
         <v>888</v>
@@ -49466,7 +49466,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1693" t="n">
-        <v>6.87045907974243</v>
+        <v>6.87045955657959</v>
       </c>
       <c r="H1693" t="n">
         <v>5014</v>
@@ -49495,7 +49495,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1694" t="n">
-        <v>6.87045907974243</v>
+        <v>6.87045955657959</v>
       </c>
       <c r="H1694" t="n">
         <v>1378</v>
@@ -49553,7 +49553,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1696" t="n">
-        <v>6.76476001739502</v>
+        <v>6.76475954055786</v>
       </c>
       <c r="H1696" t="n">
         <v>4199</v>
@@ -49582,7 +49582,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1697" t="n">
-        <v>6.87045907974243</v>
+        <v>6.87045955657959</v>
       </c>
       <c r="H1697" t="n">
         <v>2020</v>
@@ -49640,7 +49640,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1699" t="n">
-        <v>6.87045907974243</v>
+        <v>6.87045955657959</v>
       </c>
       <c r="H1699" t="n">
         <v>7208</v>
@@ -49669,7 +49669,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1700" t="n">
-        <v>6.87045907974243</v>
+        <v>6.87045955657959</v>
       </c>
       <c r="H1700" t="n">
         <v>165</v>
@@ -49698,7 +49698,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1701" t="n">
-        <v>6.76476001739502</v>
+        <v>6.76475954055786</v>
       </c>
       <c r="H1701" t="n">
         <v>3563</v>
@@ -49756,7 +49756,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1703" t="n">
-        <v>6.76476001739502</v>
+        <v>6.76475954055786</v>
       </c>
       <c r="H1703" t="n">
         <v>1660</v>
@@ -49785,7 +49785,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1704" t="n">
-        <v>6.87045907974243</v>
+        <v>6.87045955657959</v>
       </c>
       <c r="H1704" t="n">
         <v>801</v>
@@ -50046,7 +50046,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1713" t="n">
-        <v>6.18341302871704</v>
+        <v>6.1834135055542</v>
       </c>
       <c r="H1713" t="n">
         <v>1448</v>
@@ -50191,7 +50191,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1718" t="n">
-        <v>6.25387954711914</v>
+        <v>6.25387907028198</v>
       </c>
       <c r="H1718" t="n">
         <v>1986</v>
@@ -50220,7 +50220,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1719" t="n">
-        <v>6.25387954711914</v>
+        <v>6.25387907028198</v>
       </c>
       <c r="H1719" t="n">
         <v>3572</v>
@@ -50278,7 +50278,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G1721" t="n">
-        <v>6.37719488143921</v>
+        <v>6.37719535827637</v>
       </c>
       <c r="H1721" t="n">
         <v>2554</v>
@@ -50307,7 +50307,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1722" t="n">
-        <v>6.51812839508057</v>
+        <v>6.51812791824341</v>
       </c>
       <c r="H1722" t="n">
         <v>1314</v>
@@ -50365,7 +50365,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1724" t="n">
-        <v>6.44766187667847</v>
+        <v>6.44766139984131</v>
       </c>
       <c r="H1724" t="n">
         <v>2605</v>
@@ -50394,7 +50394,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1725" t="n">
-        <v>6.46527862548828</v>
+        <v>6.46527814865112</v>
       </c>
       <c r="H1725" t="n">
         <v>2803</v>
@@ -50568,7 +50568,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1731" t="n">
-        <v>6.51812839508057</v>
+        <v>6.51812791824341</v>
       </c>
       <c r="H1731" t="n">
         <v>1076</v>
@@ -50597,7 +50597,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1732" t="n">
-        <v>6.46527862548828</v>
+        <v>6.46527814865112</v>
       </c>
       <c r="H1732" t="n">
         <v>3630</v>
@@ -50626,7 +50626,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1733" t="n">
-        <v>6.43004512786865</v>
+        <v>6.43004560470581</v>
       </c>
       <c r="H1733" t="n">
         <v>1793</v>
@@ -50655,7 +50655,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1734" t="n">
-        <v>6.43004512786865</v>
+        <v>6.43004560470581</v>
       </c>
       <c r="H1734" t="n">
         <v>2928</v>
@@ -50829,7 +50829,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1740" t="n">
-        <v>6.43004512786865</v>
+        <v>6.43004560470581</v>
       </c>
       <c r="H1740" t="n">
         <v>897</v>
@@ -51206,7 +51206,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1753" t="n">
-        <v>6.43004512786865</v>
+        <v>6.43004560470581</v>
       </c>
       <c r="H1753" t="n">
         <v>2663</v>
@@ -51235,7 +51235,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1754" t="n">
-        <v>6.44766187667847</v>
+        <v>6.44766139984131</v>
       </c>
       <c r="H1754" t="n">
         <v>3522</v>
@@ -51380,7 +51380,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1759" t="n">
-        <v>6.87045907974243</v>
+        <v>6.87045955657959</v>
       </c>
       <c r="H1759" t="n">
         <v>6414</v>
@@ -51496,7 +51496,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1763" t="n">
-        <v>6.99377536773682</v>
+        <v>6.99377489089966</v>
       </c>
       <c r="H1763" t="n">
         <v>2237</v>
@@ -51525,7 +51525,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1764" t="n">
-        <v>6.99377536773682</v>
+        <v>6.99377489089966</v>
       </c>
       <c r="H1764" t="n">
         <v>604</v>
@@ -51583,7 +51583,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1766" t="n">
-        <v>6.99377536773682</v>
+        <v>6.99377489089966</v>
       </c>
       <c r="H1766" t="n">
         <v>2287</v>
@@ -51641,7 +51641,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1768" t="n">
-        <v>6.99377536773682</v>
+        <v>6.99377489089966</v>
       </c>
       <c r="H1768" t="n">
         <v>1229</v>
@@ -51670,7 +51670,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1769" t="n">
-        <v>6.99377536773682</v>
+        <v>6.99377489089966</v>
       </c>
       <c r="H1769" t="n">
         <v>1989</v>
@@ -51728,7 +51728,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1771" t="n">
-        <v>6.94092559814453</v>
+        <v>6.94092512130737</v>
       </c>
       <c r="H1771" t="n">
         <v>1776</v>
@@ -51757,7 +51757,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1772" t="n">
-        <v>6.94092559814453</v>
+        <v>6.94092512130737</v>
       </c>
       <c r="H1772" t="n">
         <v>1175</v>
@@ -51844,7 +51844,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1775" t="n">
-        <v>6.67667722702026</v>
+        <v>6.67667675018311</v>
       </c>
       <c r="H1775" t="n">
         <v>1012</v>
@@ -52018,7 +52018,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1781" t="n">
-        <v>6.87045907974243</v>
+        <v>6.87045955657959</v>
       </c>
       <c r="H1781" t="n">
         <v>11023</v>
@@ -52047,7 +52047,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1782" t="n">
-        <v>6.87045907974243</v>
+        <v>6.87045955657959</v>
       </c>
       <c r="H1782" t="n">
         <v>482</v>
@@ -52105,7 +52105,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1784" t="n">
-        <v>6.76476001739502</v>
+        <v>6.76475954055786</v>
       </c>
       <c r="H1784" t="n">
         <v>2602</v>
@@ -52192,7 +52192,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1787" t="n">
-        <v>6.87045907974243</v>
+        <v>6.87045955657959</v>
       </c>
       <c r="H1787" t="n">
         <v>6362</v>
@@ -52221,7 +52221,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1788" t="n">
-        <v>6.94092559814453</v>
+        <v>6.94092512130737</v>
       </c>
       <c r="H1788" t="n">
         <v>6295</v>
@@ -52337,7 +52337,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1792" t="n">
-        <v>6.94092559814453</v>
+        <v>6.94092512130737</v>
       </c>
       <c r="H1792" t="n">
         <v>8408</v>
@@ -52743,7 +52743,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1806" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H1806" t="n">
         <v>9481</v>
@@ -52801,7 +52801,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1808" t="n">
-        <v>7.20517444610596</v>
+        <v>7.2051739692688</v>
       </c>
       <c r="H1808" t="n">
         <v>14143</v>
@@ -53033,7 +53033,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1816" t="n">
-        <v>7.20517444610596</v>
+        <v>7.2051739692688</v>
       </c>
       <c r="H1816" t="n">
         <v>217</v>
@@ -53062,7 +53062,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1817" t="n">
-        <v>7.20517444610596</v>
+        <v>7.2051739692688</v>
       </c>
       <c r="H1817" t="n">
         <v>2479</v>
@@ -53091,7 +53091,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1818" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H1818" t="n">
         <v>2903</v>
@@ -53120,7 +53120,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1819" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H1819" t="n">
         <v>3901</v>
@@ -53178,7 +53178,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1821" t="n">
-        <v>7.15232467651367</v>
+        <v>7.15232419967651</v>
       </c>
       <c r="H1821" t="n">
         <v>1231</v>
@@ -53410,7 +53410,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1829" t="n">
-        <v>6.99377536773682</v>
+        <v>6.99377489089966</v>
       </c>
       <c r="H1829" t="n">
         <v>4498</v>
@@ -53671,7 +53671,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1838" t="n">
-        <v>6.87045907974243</v>
+        <v>6.87045955657959</v>
       </c>
       <c r="H1838" t="n">
         <v>3360</v>
@@ -53758,7 +53758,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1841" t="n">
-        <v>6.94092559814453</v>
+        <v>6.94092512130737</v>
       </c>
       <c r="H1841" t="n">
         <v>272</v>
@@ -53845,7 +53845,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1844" t="n">
-        <v>6.87045907974243</v>
+        <v>6.87045955657959</v>
       </c>
       <c r="H1844" t="n">
         <v>872</v>
@@ -54019,7 +54019,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1850" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H1850" t="n">
         <v>3841</v>
@@ -54048,7 +54048,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1851" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H1851" t="n">
         <v>1930</v>
@@ -54193,7 +54193,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1856" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H1856" t="n">
         <v>2405</v>
@@ -54222,7 +54222,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1857" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H1857" t="n">
         <v>3455</v>
@@ -54570,7 +54570,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1869" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1869" t="n">
         <v>2737</v>
@@ -54599,7 +54599,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1870" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1870" t="n">
         <v>9023</v>
@@ -54773,7 +54773,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1876" t="n">
-        <v>7.52227210998535</v>
+        <v>7.52227258682251</v>
       </c>
       <c r="H1876" t="n">
         <v>9698</v>
@@ -54802,7 +54802,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1877" t="n">
-        <v>7.39895629882812</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1877" t="n">
         <v>490</v>
@@ -54976,7 +54976,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1883" t="n">
-        <v>7.41657257080078</v>
+        <v>7.41657304763794</v>
       </c>
       <c r="H1883" t="n">
         <v>3071</v>
@@ -55121,7 +55121,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1888" t="n">
-        <v>7.39895629882812</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1888" t="n">
         <v>3535</v>
@@ -55150,7 +55150,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1889" t="n">
-        <v>7.52227210998535</v>
+        <v>7.52227258682251</v>
       </c>
       <c r="H1889" t="n">
         <v>1611</v>
@@ -55179,7 +55179,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1890" t="n">
-        <v>7.39895629882812</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1890" t="n">
         <v>5179</v>
@@ -55208,7 +55208,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1891" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1891" t="n">
         <v>2003</v>
@@ -55237,7 +55237,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1892" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1892" t="n">
         <v>620</v>
@@ -55295,7 +55295,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1894" t="n">
-        <v>7.39895629882812</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1894" t="n">
         <v>571</v>
@@ -55353,7 +55353,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1896" t="n">
-        <v>7.39895629882812</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1896" t="n">
         <v>4159</v>
@@ -55382,7 +55382,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1897" t="n">
-        <v>7.41657257080078</v>
+        <v>7.41657304763794</v>
       </c>
       <c r="H1897" t="n">
         <v>2058</v>
@@ -55411,7 +55411,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1898" t="n">
-        <v>7.39895629882812</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1898" t="n">
         <v>1408</v>
@@ -55440,7 +55440,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1899" t="n">
-        <v>7.39895629882812</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1899" t="n">
         <v>4504</v>
@@ -55556,7 +55556,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1903" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1903" t="n">
         <v>1015</v>
@@ -55585,7 +55585,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1904" t="n">
-        <v>7.39895629882812</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1904" t="n">
         <v>984</v>
@@ -55672,7 +55672,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1907" t="n">
-        <v>7.41657257080078</v>
+        <v>7.41657304763794</v>
       </c>
       <c r="H1907" t="n">
         <v>478</v>
@@ -55701,7 +55701,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1908" t="n">
-        <v>7.41657257080078</v>
+        <v>7.41657304763794</v>
       </c>
       <c r="H1908" t="n">
         <v>0</v>
@@ -55788,7 +55788,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1911" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1911" t="n">
         <v>401</v>
@@ -55904,7 +55904,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1915" t="n">
-        <v>7.45180606842041</v>
+        <v>7.45180559158325</v>
       </c>
       <c r="H1915" t="n">
         <v>2656</v>
@@ -55991,7 +55991,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1918" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H1918" t="n">
         <v>13617</v>
@@ -56049,7 +56049,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1920" t="n">
-        <v>7.20517444610596</v>
+        <v>7.2051739692688</v>
       </c>
       <c r="H1920" t="n">
         <v>2167</v>
@@ -56223,7 +56223,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1926" t="n">
-        <v>7.39895629882812</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1926" t="n">
         <v>3304</v>
@@ -56281,7 +56281,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1928" t="n">
-        <v>7.39895629882812</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1928" t="n">
         <v>4222</v>
@@ -56368,7 +56368,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1931" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H1931" t="n">
         <v>20231</v>
@@ -56397,7 +56397,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1932" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1932" t="n">
         <v>7637</v>
@@ -56426,7 +56426,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1933" t="n">
-        <v>7.25802373886108</v>
+        <v>7.25802326202393</v>
       </c>
       <c r="H1933" t="n">
         <v>896</v>
@@ -56455,7 +56455,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1934" t="n">
-        <v>7.25802373886108</v>
+        <v>7.25802326202393</v>
       </c>
       <c r="H1934" t="n">
         <v>2970</v>
@@ -56513,7 +56513,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1936" t="n">
-        <v>7.25802373886108</v>
+        <v>7.25802326202393</v>
       </c>
       <c r="H1936" t="n">
         <v>2078</v>
@@ -56658,7 +56658,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1941" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H1941" t="n">
         <v>1400</v>
@@ -56687,7 +56687,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1942" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1942" t="n">
         <v>1760</v>
@@ -56803,7 +56803,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1946" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H1946" t="n">
         <v>2069</v>
@@ -56861,7 +56861,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1948" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H1948" t="n">
         <v>981</v>
@@ -56890,7 +56890,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1949" t="n">
-        <v>7.41657257080078</v>
+        <v>7.41657304763794</v>
       </c>
       <c r="H1949" t="n">
         <v>19988</v>
@@ -57064,7 +57064,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1955" t="n">
-        <v>7.39895629882812</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1955" t="n">
         <v>1768</v>
@@ -57209,7 +57209,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1960" t="n">
-        <v>7.39895629882812</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1960" t="n">
         <v>11829</v>
@@ -57267,7 +57267,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1962" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H1962" t="n">
         <v>1313</v>
@@ -57383,7 +57383,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1966" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H1966" t="n">
         <v>3431</v>
@@ -57412,7 +57412,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1967" t="n">
-        <v>7.25802373886108</v>
+        <v>7.25802326202393</v>
       </c>
       <c r="H1967" t="n">
         <v>7322</v>
@@ -57499,7 +57499,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1970" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1970" t="n">
         <v>7587</v>
@@ -57673,7 +57673,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1976" t="n">
-        <v>6.94092559814453</v>
+        <v>6.94092512130737</v>
       </c>
       <c r="H1976" t="n">
         <v>20691</v>
@@ -57702,7 +57702,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1977" t="n">
-        <v>7.25802373886108</v>
+        <v>7.25802326202393</v>
       </c>
       <c r="H1977" t="n">
         <v>7572</v>
@@ -57760,7 +57760,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1979" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H1979" t="n">
         <v>2912</v>
@@ -57818,7 +57818,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1981" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H1981" t="n">
         <v>17411</v>
@@ -57847,7 +57847,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1982" t="n">
-        <v>7.39895629882812</v>
+        <v>7.39895582199097</v>
       </c>
       <c r="H1982" t="n">
         <v>21863</v>
@@ -57876,7 +57876,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1983" t="n">
-        <v>7.41657257080078</v>
+        <v>7.41657304763794</v>
       </c>
       <c r="H1983" t="n">
         <v>2985</v>
@@ -57934,7 +57934,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1985" t="n">
-        <v>7.15232467651367</v>
+        <v>7.15232419967651</v>
       </c>
       <c r="H1985" t="n">
         <v>9382</v>
@@ -57992,7 +57992,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1987" t="n">
-        <v>7.25802373886108</v>
+        <v>7.25802326202393</v>
       </c>
       <c r="H1987" t="n">
         <v>510</v>
@@ -58050,7 +58050,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1989" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H1989" t="n">
         <v>468</v>
@@ -58079,7 +58079,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1990" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H1990" t="n">
         <v>879</v>
@@ -58108,7 +58108,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1991" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H1991" t="n">
         <v>40</v>
@@ -58195,7 +58195,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1994" t="n">
-        <v>7.15232467651367</v>
+        <v>7.15232419967651</v>
       </c>
       <c r="H1994" t="n">
         <v>6220</v>
@@ -58282,7 +58282,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1997" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H1997" t="n">
         <v>5082</v>
@@ -58514,7 +58514,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2005" t="n">
-        <v>7.15232467651367</v>
+        <v>7.15232419967651</v>
       </c>
       <c r="H2005" t="n">
         <v>9015</v>
@@ -58543,7 +58543,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2006" t="n">
-        <v>7.15232467651367</v>
+        <v>7.15232419967651</v>
       </c>
       <c r="H2006" t="n">
         <v>7011</v>
@@ -58572,7 +58572,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2007" t="n">
-        <v>7.15232467651367</v>
+        <v>7.15232419967651</v>
       </c>
       <c r="H2007" t="n">
         <v>6378</v>
@@ -58601,7 +58601,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2008" t="n">
-        <v>7.15232467651367</v>
+        <v>7.15232419967651</v>
       </c>
       <c r="H2008" t="n">
         <v>280</v>
@@ -58659,7 +58659,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G2010" t="n">
-        <v>7.25802373886108</v>
+        <v>7.25802326202393</v>
       </c>
       <c r="H2010" t="n">
         <v>22885</v>
@@ -58688,7 +58688,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2011" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H2011" t="n">
         <v>3465</v>
@@ -58775,7 +58775,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G2014" t="n">
-        <v>7.25802373886108</v>
+        <v>7.25802326202393</v>
       </c>
       <c r="H2014" t="n">
         <v>6721</v>
@@ -58804,7 +58804,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G2015" t="n">
-        <v>7.25802373886108</v>
+        <v>7.25802326202393</v>
       </c>
       <c r="H2015" t="n">
         <v>3205</v>
@@ -58862,7 +58862,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2017" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H2017" t="n">
         <v>7858</v>
@@ -58920,7 +58920,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G2019" t="n">
-        <v>7.25802373886108</v>
+        <v>7.25802326202393</v>
       </c>
       <c r="H2019" t="n">
         <v>7634</v>
@@ -58949,7 +58949,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2020" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H2020" t="n">
         <v>7520</v>
@@ -59123,7 +59123,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G2026" t="n">
-        <v>7.25802373886108</v>
+        <v>7.25802326202393</v>
       </c>
       <c r="H2026" t="n">
         <v>2120</v>
@@ -59152,7 +59152,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G2027" t="n">
-        <v>7.25802373886108</v>
+        <v>7.25802326202393</v>
       </c>
       <c r="H2027" t="n">
         <v>3093</v>
@@ -59210,7 +59210,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G2029" t="n">
-        <v>7.20517444610596</v>
+        <v>7.2051739692688</v>
       </c>
       <c r="H2029" t="n">
         <v>4378</v>
@@ -59268,7 +59268,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G2031" t="n">
-        <v>7.25802373886108</v>
+        <v>7.25802326202393</v>
       </c>
       <c r="H2031" t="n">
         <v>255</v>
@@ -59384,7 +59384,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G2035" t="n">
-        <v>7.25802373886108</v>
+        <v>7.25802326202393</v>
       </c>
       <c r="H2035" t="n">
         <v>4513</v>
@@ -59442,7 +59442,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2037" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H2037" t="n">
         <v>910</v>
@@ -59500,7 +59500,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2039" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H2039" t="n">
         <v>2378</v>
@@ -59558,7 +59558,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G2041" t="n">
-        <v>7.25802373886108</v>
+        <v>7.25802326202393</v>
       </c>
       <c r="H2041" t="n">
         <v>2109</v>
@@ -59616,7 +59616,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G2043" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H2043" t="n">
         <v>1523</v>
@@ -59703,7 +59703,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G2046" t="n">
-        <v>7.25802373886108</v>
+        <v>7.25802326202393</v>
       </c>
       <c r="H2046" t="n">
         <v>3781</v>
@@ -59761,7 +59761,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2048" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H2048" t="n">
         <v>315</v>
@@ -59848,7 +59848,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2051" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H2051" t="n">
         <v>865</v>
@@ -59906,7 +59906,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G2053" t="n">
-        <v>7.32848930358887</v>
+        <v>7.32848978042603</v>
       </c>
       <c r="H2053" t="n">
         <v>4512</v>
@@ -59993,7 +59993,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2056" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H2056" t="n">
         <v>353</v>
@@ -60022,7 +60022,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2057" t="n">
-        <v>7.27564001083374</v>
+        <v>7.2756404876709</v>
       </c>
       <c r="H2057" t="n">
         <v>2950</v>
@@ -60167,7 +60167,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G2062" t="n">
-        <v>7.20517444610596</v>
+        <v>7.2051739692688</v>
       </c>
       <c r="H2062" t="n">
         <v>4899</v>
@@ -60225,7 +60225,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G2064" t="n">
-        <v>7.20517444610596</v>
+        <v>7.2051739692688</v>
       </c>
       <c r="H2064" t="n">
         <v>2958</v>
@@ -60254,7 +60254,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G2065" t="n">
-        <v>7.20517444610596</v>
+        <v>7.2051739692688</v>
       </c>
       <c r="H2065" t="n">
         <v>3192</v>
@@ -60573,7 +60573,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2076" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H2076" t="n">
         <v>3411</v>
@@ -60776,7 +60776,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G2083" t="n">
-        <v>6.94092559814453</v>
+        <v>6.94092512130737</v>
       </c>
       <c r="H2083" t="n">
         <v>5102</v>
@@ -61037,7 +61037,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G2092" t="n">
-        <v>6.94092559814453</v>
+        <v>6.94092512130737</v>
       </c>
       <c r="H2092" t="n">
         <v>4647</v>
@@ -61269,7 +61269,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G2100" t="n">
-        <v>6.94092559814453</v>
+        <v>6.94092512130737</v>
       </c>
       <c r="H2100" t="n">
         <v>1993</v>
@@ -61646,7 +61646,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G2113" t="n">
-        <v>6.94092559814453</v>
+        <v>6.94092512130737</v>
       </c>
       <c r="H2113" t="n">
         <v>1136</v>
@@ -61907,7 +61907,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2122" t="n">
-        <v>7.09947490692139</v>
+        <v>7.09947538375854</v>
       </c>
       <c r="H2122" t="n">
         <v>5064</v>
@@ -80067,6 +80067,35 @@
         <v>285</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>9.02000045776367</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>9.0600004196167</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>8.84000015258789</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>8.84000015258789</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>8.84000015258789</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>2351</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>
